--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -53870,6 +53870,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2327" t="n">
+        <v>801482</v>
+      </c>
+      <c r="C2327" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>1.70799994468689</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>1.74399995803833</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -53893,6 +53893,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2328">
+      <c r="A2328" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2328" t="n">
+        <v>642988</v>
+      </c>
+      <c r="C2328" t="n">
+        <v>1.75499999523163</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>1.69900000095367</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>1.72099995613098</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>1.75300002098083</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -53916,6 +53916,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2329" t="n">
+        <v>835624</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>1.72300004959106</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>1.83800005912781</v>
+      </c>
+      <c r="G2329" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -53924,7 +53924,7 @@
         <v>835624</v>
       </c>
       <c r="C2329" t="n">
-        <v>1.83000004291534</v>
+        <v>1.83800005912781</v>
       </c>
       <c r="D2329" t="n">
         <v>1.72300004959106</v>
@@ -53936,6 +53936,29 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G2329" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2330" t="n">
+        <v>1139328</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>1.84899997711182</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>1.77799999713898</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G2330" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -53780,22 +53780,22 @@
     </row>
     <row r="2323">
       <c r="A2323" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2323" t="n">
-        <v>575876</v>
+        <v>551451</v>
       </c>
       <c r="C2323" t="n">
-        <v>1.63399994373322</v>
+        <v>1.62600004673004</v>
       </c>
       <c r="D2323" t="n">
-        <v>1.60199999809265</v>
+        <v>1.59700000286102</v>
       </c>
       <c r="E2323" t="n">
-        <v>1.62800002098083</v>
+        <v>1.60599994659424</v>
       </c>
       <c r="F2323" t="n">
-        <v>1.60199999809265</v>
+        <v>1.61800003051758</v>
       </c>
       <c r="G2323" t="s">
         <v>7</v>
@@ -53803,22 +53803,22 @@
     </row>
     <row r="2324">
       <c r="A2324" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2324" t="n">
-        <v>1458355</v>
+        <v>575876</v>
       </c>
       <c r="C2324" t="n">
-        <v>1.71000003814697</v>
+        <v>1.63399994373322</v>
       </c>
       <c r="D2324" t="n">
-        <v>1.59099996089935</v>
+        <v>1.60199999809265</v>
       </c>
       <c r="E2324" t="n">
-        <v>1.62300002574921</v>
+        <v>1.62800002098083</v>
       </c>
       <c r="F2324" t="n">
-        <v>1.71000003814697</v>
+        <v>1.60199999809265</v>
       </c>
       <c r="G2324" t="s">
         <v>7</v>
@@ -53826,22 +53826,22 @@
     </row>
     <row r="2325">
       <c r="A2325" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2325" t="n">
-        <v>1039615</v>
+        <v>1458355</v>
       </c>
       <c r="C2325" t="n">
-        <v>1.76199996471405</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="D2325" t="n">
-        <v>1.69200003147125</v>
+        <v>1.59099996089935</v>
       </c>
       <c r="E2325" t="n">
-        <v>1.74000000953674</v>
+        <v>1.62300002574921</v>
       </c>
       <c r="F2325" t="n">
-        <v>1.74300003051758</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="G2325" t="s">
         <v>7</v>
@@ -53849,22 +53849,22 @@
     </row>
     <row r="2326">
       <c r="A2326" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2326" t="n">
-        <v>567289</v>
+        <v>1039615</v>
       </c>
       <c r="C2326" t="n">
-        <v>1.78999996185303</v>
+        <v>1.76199996471405</v>
       </c>
       <c r="D2326" t="n">
-        <v>1.71599996089935</v>
+        <v>1.69200003147125</v>
       </c>
       <c r="E2326" t="n">
-        <v>1.75999999046326</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="F2326" t="n">
-        <v>1.78999996185303</v>
+        <v>1.74300003051758</v>
       </c>
       <c r="G2326" t="s">
         <v>7</v>
@@ -53872,22 +53872,22 @@
     </row>
     <row r="2327">
       <c r="A2327" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2327" t="n">
-        <v>801482</v>
+        <v>567289</v>
       </c>
       <c r="C2327" t="n">
-        <v>1.79999995231628</v>
+        <v>1.78999996185303</v>
       </c>
       <c r="D2327" t="n">
-        <v>1.70799994468689</v>
+        <v>1.71599996089935</v>
       </c>
       <c r="E2327" t="n">
-        <v>1.79999995231628</v>
+        <v>1.75999999046326</v>
       </c>
       <c r="F2327" t="n">
-        <v>1.74399995803833</v>
+        <v>1.78999996185303</v>
       </c>
       <c r="G2327" t="s">
         <v>7</v>
@@ -53895,22 +53895,22 @@
     </row>
     <row r="2328">
       <c r="A2328" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2328" t="n">
-        <v>642988</v>
+        <v>801482</v>
       </c>
       <c r="C2328" t="n">
-        <v>1.75499999523163</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="D2328" t="n">
-        <v>1.69900000095367</v>
+        <v>1.70799994468689</v>
       </c>
       <c r="E2328" t="n">
-        <v>1.72099995613098</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="F2328" t="n">
-        <v>1.75300002098083</v>
+        <v>1.74399995803833</v>
       </c>
       <c r="G2328" t="s">
         <v>7</v>
@@ -53918,22 +53918,22 @@
     </row>
     <row r="2329">
       <c r="A2329" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2329" t="n">
-        <v>835624</v>
+        <v>642988</v>
       </c>
       <c r="C2329" t="n">
-        <v>1.83800005912781</v>
+        <v>1.75499999523163</v>
       </c>
       <c r="D2329" t="n">
-        <v>1.72300004959106</v>
+        <v>1.69900000095367</v>
       </c>
       <c r="E2329" t="n">
-        <v>1.75</v>
+        <v>1.72099995613098</v>
       </c>
       <c r="F2329" t="n">
-        <v>1.83800005912781</v>
+        <v>1.75300002098083</v>
       </c>
       <c r="G2329" t="s">
         <v>7</v>
@@ -53941,24 +53941,47 @@
     </row>
     <row r="2330">
       <c r="A2330" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2330" t="n">
-        <v>1139328</v>
+        <v>835624</v>
       </c>
       <c r="C2330" t="n">
-        <v>1.84899997711182</v>
+        <v>1.83800005912781</v>
       </c>
       <c r="D2330" t="n">
-        <v>1.77799999713898</v>
+        <v>1.72300004959106</v>
       </c>
       <c r="E2330" t="n">
-        <v>1.8400000333786</v>
+        <v>1.75</v>
       </c>
       <c r="F2330" t="n">
-        <v>1.78999996185303</v>
+        <v>1.83800005912781</v>
       </c>
       <c r="G2330" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2331" t="n">
+        <v>1307809</v>
+      </c>
+      <c r="C2331" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>1.7059999704361</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G2331" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503227233887</v>
+        <v>44.8503189086914</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569198608398</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318496704102</v>
+        <v>46.7318534851074</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507301330566</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632209777832</v>
+        <v>47.5632171630859</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319496154785</v>
+        <v>47.4319534301758</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506340026855</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.4693069458008</v>
+        <v>46.469310760498</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131652832031</v>
+        <v>47.2131729125977</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880912780762</v>
+        <v>46.6880836486816</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256484985352</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756004333496</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443328857422</v>
+        <v>46.6443367004395</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>53</v>
       </c>
       <c r="G32" t="n">
-        <v>46.3817977905273</v>
+        <v>46.3817939758301</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816902160645</v>
+        <v>45.6816940307617</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567237854004</v>
+        <v>45.8567161560059</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256484985352</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069831848145</v>
+        <v>47.6069793701172</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.906867980957</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881950378418</v>
+        <v>47.3881874084473</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756004333496</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.994384765625</v>
+        <v>46.9943885803223</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569198608398</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882987976074</v>
+        <v>48.0882949829102</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.906867980957</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507301330566</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194625854492</v>
+        <v>47.519458770752</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445404052734</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135841369629</v>
+        <v>50.0135803222656</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953071594238</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579536437988</v>
+        <v>54.2579498291016</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336906433105</v>
+        <v>59.3336944580078</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589836120605</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965446472168</v>
+        <v>61.6965370178223</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965446472168</v>
+        <v>61.6965370178223</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.134105682373</v>
+        <v>62.1341094970703</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902549743652</v>
+        <v>61.3902397155762</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339904785156</v>
+        <v>61.4339942932129</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964408874512</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462890625</v>
+        <v>59.9462852478027</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399917602539</v>
+        <v>59.6399879455566</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275009155273</v>
+        <v>59.7275047302246</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838424682617</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026306152344</v>
+        <v>60.6026229858398</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771415710449</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204849243164</v>
+        <v>54.5204887390137</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273010253906</v>
+        <v>58.3272972106934</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772415161133</v>
+        <v>57.9772491455078</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273971557617</v>
+        <v>59.0273933410645</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834426879883</v>
+        <v>57.583438873291</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583534240723</v>
+        <v>57.0583610534668</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646659851074</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708480834961</v>
+        <v>56.9708442687988</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712631225586</v>
+        <v>59.7712669372559</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.252571105957</v>
+        <v>60.2525825500488</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646659851074</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.7456703186035</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709518432617</v>
+        <v>57.6709480285645</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648620605469</v>
+        <v>58.7648582458496</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899398803711</v>
+        <v>59.2899475097656</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334907531738</v>
+        <v>57.9334869384766</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962295532227</v>
+        <v>59.5962257385254</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.9900436401367</v>
+        <v>59.9900398254395</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770416259766</v>
+        <v>56.5770454406738</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.2707443237305</v>
+        <v>56.2707481384277</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145065307617</v>
+        <v>56.3144989013672</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146102905273</v>
+        <v>57.0146026611328</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520637512207</v>
+        <v>56.7520599365234</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892211914062</v>
+        <v>54.389217376709</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518600463867</v>
+        <v>55.3518562316895</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138877868652</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449440002441</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196701049805</v>
+        <v>48.9196662902832</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.3572273254395</v>
+        <v>49.357234954834</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883987426758</v>
+        <v>48.7883949279785</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764228820801</v>
+        <v>52.3764266967773</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201850891113</v>
+        <v>52.4201812744141</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265747070312</v>
+        <v>53.4265785217285</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G171" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8950996398926</v>
+        <v>51.8951072692871</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889137268066</v>
+        <v>52.2889099121094</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.751033782959</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449440002441</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.989013671875</v>
+        <v>52.9890098571777</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.95166015625</v>
+        <v>53.9516525268555</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015007019043</v>
+        <v>52.9015045166016</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G198" t="n">
-        <v>56.4020156860352</v>
+        <v>56.4020118713379</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518600463867</v>
+        <v>55.3518562316895</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391693115234</v>
+        <v>54.0391731262207</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830238342285</v>
+        <v>54.7830276489258</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390731811523</v>
+        <v>53.3390693664551</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.2205924987793</v>
+        <v>55.220588684082</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623001098633</v>
+        <v>44.662296295166</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179847717285</v>
+        <v>44.6179885864258</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>45.8143043518066</v>
+        <v>45.8143005371094</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358428955078</v>
+        <v>46.0358390808105</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.386589050293</v>
+        <v>40.3865928649902</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.928150177002</v>
+        <v>44.9281463623047</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509117126465</v>
+        <v>44.7509155273438</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019821166992</v>
+        <v>42.6019897460938</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536933898926</v>
+        <v>47.4536895751953</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475402832031</v>
+        <v>49.4475440979004</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361557006836</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.226001739502</v>
+        <v>49.2260055541992</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.181697845459</v>
+        <v>49.1817016601562</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410781860352</v>
+        <v>47.9410743713379</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373863220215</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158515930176</v>
+        <v>48.915843963623</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373863220215</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844757080078</v>
+        <v>51.8844718933105</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.3970947265625</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715400695801</v>
+        <v>48.8715438842773</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056938171387</v>
+        <v>48.6056976318359</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.33984375</v>
+        <v>48.3398475646973</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.852466583252</v>
+        <v>47.8524627685547</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192192077637</v>
+        <v>44.2192230224609</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>50</v>
       </c>
       <c r="G265" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>50</v>
       </c>
       <c r="G266" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927696228027</v>
+        <v>45.5927581787109</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346160888672</v>
+        <v>46.4346122741699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586044311523</v>
+        <v>45.8586120605469</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>50</v>
       </c>
       <c r="G275" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570571899414</v>
+        <v>42.7570610046387</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918281555176</v>
+        <v>42.2918243408203</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324478149414</v>
+        <v>43.5324440002441</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.310905456543</v>
+        <v>43.3109130859375</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222900390625</v>
+        <v>43.2222938537598</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.2001419067383</v>
+        <v>43.200138092041</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450592041016</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>48.8250007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>43.2666015625</v>
+        <v>43.2665977478027</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102882385254</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170585632324</v>
+        <v>41.3170547485352</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465827941895</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>45.9249992370605</v>
       </c>
       <c r="G328" t="n">
-        <v>40.6967468261719</v>
+        <v>40.6967506408691</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>48.7249984741211</v>
       </c>
       <c r="G332" t="n">
-        <v>43.1779861450195</v>
+        <v>43.1779823303223</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696762084961</v>
+        <v>42.2696723937988</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.984748840332</v>
+        <v>40.9847450256348</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555137634277</v>
+        <v>39.6555099487305</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.9908981323242</v>
+        <v>38.990894317627</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684494018555</v>
+        <v>42.6684455871582</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096786499023</v>
+        <v>43.7096824645996</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764625549316</v>
+        <v>47.2764549255371</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878433227539</v>
+        <v>47.1878471374512</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>45.9915313720703</v>
+        <v>45.9915351867676</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419845581055</v>
+        <v>44.0419883728027</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992080688477</v>
+        <v>39.8992042541504</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321311950684</v>
+        <v>40.0321273803711</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625854492188</v>
+        <v>40.9625968933105</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>50</v>
       </c>
       <c r="G372" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780059814453</v>
+        <v>50.3780097961426</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893943786621</v>
+        <v>50.2893905639648</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.3970947265625</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121635437012</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589324951172</v>
+        <v>49.3589286804199</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.7577018737793</v>
+        <v>49.757698059082</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463096618652</v>
+        <v>49.8463134765625</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032325744629</v>
+        <v>49.4032363891602</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263221740723</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263221740723</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>52.1060104370117</v>
+        <v>52.106014251709</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250991821289</v>
+        <v>53.1250953674316</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.7774124145508</v>
+        <v>57.777416229248</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001853942871</v>
+        <v>57.6001815795898</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.7835655212402</v>
+        <v>55.783561706543</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.954647064209</v>
+        <v>57.9546508789062</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.0875778198242</v>
+        <v>58.087574005127</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>52.9921646118164</v>
+        <v>52.9921722412109</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478607177734</v>
+        <v>52.9478645324707</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.2457237243652</v>
+        <v>57.245719909668</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026428222656</v>
+        <v>56.8026466369629</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798736572266</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798736572266</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798736572266</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254196166992</v>
+        <v>56.6254119873047</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734039306641</v>
+        <v>55.4734077453613</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1694030761719</v>
+        <v>53.1693954467773</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149375915527</v>
+        <v>52.81494140625</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>50.7767791748047</v>
+        <v>50.7767753601074</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743217468262</v>
+        <v>51.5743255615234</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441566467285</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9555969238281</v>
+        <v>50.9555931091309</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075630187988</v>
+        <v>49.6075592041016</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>58</v>
       </c>
       <c r="G497" t="n">
-        <v>52.1238861083984</v>
+        <v>52.1238899230957</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441566467285</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>60</v>
       </c>
       <c r="G502" t="n">
-        <v>53.9212646484375</v>
+        <v>53.9212608337402</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653663635254</v>
+        <v>57.9653587341309</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477210998535</v>
+        <v>56.3477249145508</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745491027832</v>
+        <v>51.6745452880859</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353378295898</v>
+        <v>51.1353340148926</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644157409668</v>
+        <v>51.7644081115723</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502426147461</v>
+        <v>44.3502388000488</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>44.8445205688477</v>
+        <v>44.8445243835449</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>49.75</v>
       </c>
       <c r="G542" t="n">
-        <v>44.7097206115723</v>
+        <v>44.709716796875</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>45.2039985656738</v>
+        <v>45.2039947509766</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732307434082</v>
+        <v>52.5732345581055</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203178405762</v>
+        <v>47.7203216552734</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.9768104553223</v>
+        <v>56.976806640625</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781173706055</v>
+        <v>56.0781135559082</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.4719200134277</v>
+        <v>53.471923828125</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617866516113</v>
+        <v>53.5617904663086</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.101001739502</v>
+        <v>54.1010055541992</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516609191895</v>
+        <v>53.6516571044922</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>58</v>
       </c>
       <c r="G650" t="n">
-        <v>52.1238861083984</v>
+        <v>52.1238899230957</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>52.7529678344727</v>
+        <v>52.7529716491699</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>60</v>
       </c>
       <c r="G655" t="n">
-        <v>53.9212646484375</v>
+        <v>53.9212608337402</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071990966797</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071990966797</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441566467285</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441566467285</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948081970215</v>
+        <v>51.4948043823242</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>48</v>
       </c>
       <c r="G671" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.1166458129883</v>
+        <v>33.1166381835938</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>33.3413162231445</v>
+        <v>33.3413124084473</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>27.6795806884766</v>
+        <v>27.6795825958252</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.163257598877</v>
+        <v>25.1632556915283</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7368011474609</v>
+        <v>22.7367992401123</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861419677734</v>
+        <v>23.1861438751221</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>29</v>
       </c>
       <c r="G688" t="n">
-        <v>26.0619430541992</v>
+        <v>26.0619449615479</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258304595947</v>
+        <v>26.8258285522461</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130756378174</v>
+        <v>28.7130737304688</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.050500869751</v>
+        <v>27.0505027770996</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>27.7694530487061</v>
+        <v>27.7694511413574</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359600067139</v>
+        <v>26.7359619140625</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>29</v>
       </c>
       <c r="G716" t="n">
-        <v>26.0619430541992</v>
+        <v>26.0619449615479</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959056854248</v>
+        <v>30.1959075927734</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743339538574</v>
+        <v>31.2743358612061</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642063140869</v>
+        <v>31.3642024993896</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990062713623</v>
+        <v>31.4990081787109</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>36.5</v>
       </c>
       <c r="G732" t="n">
-        <v>32.8021087646484</v>
+        <v>32.8021049499512</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620468139648</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717124938965</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.442626953125</v>
+        <v>32.4426307678223</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373764038086</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.5430946350098</v>
+        <v>35.543098449707</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298721313477</v>
+        <v>34.3298759460449</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>38.1043663024902</v>
+        <v>38.104362487793</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643043518066</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>41.2947006225586</v>
+        <v>41.2947044372559</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.2832565307617</v>
+        <v>42.283260345459</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224716186523</v>
+        <v>42.8224754333496</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>42.8674087524414</v>
+        <v>42.8674049377441</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>46.7999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>42.0585861206055</v>
+        <v>42.0585899353027</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0250968933105</v>
+        <v>41.0251007080078</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>42.6427345275879</v>
+        <v>42.6427307128906</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991157531738</v>
+        <v>41.6991119384766</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440452575684</v>
+        <v>41.7440490722656</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>48</v>
       </c>
       <c r="G791" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>48</v>
       </c>
       <c r="G801" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>48</v>
       </c>
       <c r="G805" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G806" t="n">
-        <v>42.3731307983398</v>
+        <v>42.3731269836426</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>45.5</v>
       </c>
       <c r="G807" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347549438477</v>
+        <v>37.8347511291504</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651512145996</v>
+        <v>37.5651435852051</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986442565918</v>
+        <v>38.5986404418945</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.4523963928223</v>
+        <v>39.452392578125</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656227111816</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>39.7220001220703</v>
+        <v>39.721996307373</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G834" t="n">
-        <v>36.9360656738281</v>
+        <v>36.9360618591309</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620468139648</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.182788848877</v>
+        <v>39.1827850341797</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643043518066</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453598022461</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017372131348</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1598968505859</v>
+        <v>41.1599006652832</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.800422668457</v>
+        <v>40.8004264831543</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>45.5</v>
       </c>
       <c r="G860" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960151672363</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>45.5</v>
       </c>
       <c r="G864" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>42.3731307983398</v>
+        <v>42.3731269836426</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.361686706543</v>
+        <v>43.3616828918457</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G883" t="n">
-        <v>42.1035232543945</v>
+        <v>42.1035194396973</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281898498535</v>
+        <v>42.3281936645508</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G925" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608436584473</v>
+        <v>47.3608474731445</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608436584473</v>
+        <v>47.3608474731445</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G942" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>49.75</v>
       </c>
       <c r="G989" t="n">
-        <v>44.7097206115723</v>
+        <v>44.709716796875</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519195556641</v>
+        <v>42.9519233703613</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551773071289</v>
+        <v>41.4551811218262</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316627502441</v>
+        <v>39.7316589355469</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.051326751709</v>
+        <v>39.0513229370117</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797828674316</v>
+        <v>42.6797866821289</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306854248047</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306854248047</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328521728516</v>
+        <v>47.5328559875488</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443130493164</v>
+        <v>46.4443168640137</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164497375488</v>
+        <v>46.7164535522461</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>46.3536071777344</v>
+        <v>46.3536033630371</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>46.081470489502</v>
+        <v>46.0814666748047</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093376159668</v>
+        <v>45.8093338012695</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125953674316</v>
+        <v>44.3125915527344</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>44.0404624938965</v>
+        <v>44.0404586791992</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>46.081470489502</v>
+        <v>46.0814666748047</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>40.6387748718262</v>
+        <v>40.6387786865234</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.459529876709</v>
+        <v>39.4595260620117</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895637512207</v>
+        <v>38.1895599365234</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>34.7878761291504</v>
+        <v>34.7878799438477</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>39.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>33.8807678222656</v>
+        <v>33.8807640075684</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463813781738</v>
+        <v>37.1463851928711</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884841918945</v>
+        <v>38.6884803771973</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299751281738</v>
+        <v>36.3299789428711</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>39.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611000061035</v>
+        <v>34.5611038208008</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092239379883</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742523193359</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.882942199707</v>
+        <v>32.8829383850098</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861961364746</v>
+        <v>31.386194229126</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>29.2998313903809</v>
+        <v>29.2998294830322</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561622619629</v>
+        <v>32.6561584472656</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272079467773</v>
+        <v>33.4272041320801</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600166320801</v>
+        <v>35.0600204467773</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>33.8807678222656</v>
+        <v>33.8807640075684</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053695678711</v>
+        <v>35.1053733825684</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742523193359</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092239379883</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -61030,6 +61030,32 @@
         <v>1.72500002384186</v>
       </c>
       <c r="H2333" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2334" t="n">
+        <v>965885</v>
+      </c>
+      <c r="C2334" t="n">
+        <v>1.72599995136261</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>1.70299994945526</v>
+      </c>
+      <c r="F2334" t="n">
+        <v>1.66400003433228</v>
+      </c>
+      <c r="G2334" t="n">
+        <v>1.66400003433228</v>
+      </c>
+      <c r="H2334" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503189086914</v>
+        <v>44.8503265380859</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569198608398</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382469177246</v>
+        <v>47.7382431030273</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318534851074</v>
+        <v>46.7318496704102</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507301330566</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632171630859</v>
+        <v>47.5632209777832</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319534301758</v>
+        <v>47.4319496154785</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382469177246</v>
+        <v>47.7382431030273</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.081901550293</v>
+        <v>47.0818977355957</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506301879883</v>
+        <v>46.9506340026855</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131729125977</v>
+        <v>47.2131690979004</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880836486816</v>
+        <v>46.6880912780762</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256484985352</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.119255065918</v>
+        <v>46.1192588806152</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254486083984</v>
+        <v>45.7254524230957</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.513069152832</v>
+        <v>46.5130653381348</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>53</v>
       </c>
       <c r="G32" t="n">
-        <v>46.3817939758301</v>
+        <v>46.3817977905273</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567161560059</v>
+        <v>45.8567199707031</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256484985352</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069793701172</v>
+        <v>47.6069755554199</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881874084473</v>
+        <v>47.3882026672363</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.9943885803223</v>
+        <v>46.994384765625</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569198608398</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507301330566</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.519458770752</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445442199707</v>
+        <v>48.0445404052734</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135841369629</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.1950035095215</v>
+        <v>51.1949996948242</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.820384979248</v>
+        <v>53.8203811645508</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953147888184</v>
+        <v>53.2953109741211</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579498291016</v>
+        <v>54.2579536437988</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769378662109</v>
+        <v>55.8769416809082</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336944580078</v>
+        <v>59.3337020874023</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.258975982666</v>
+        <v>61.2589797973633</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403991699219</v>
+        <v>62.4403953552246</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965484619141</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965484619141</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.1341094970703</v>
+        <v>62.134105682373</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902397155762</v>
+        <v>61.3902435302734</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339942932129</v>
+        <v>61.4339981079102</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964332580566</v>
+        <v>60.9964256286621</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462852478027</v>
+        <v>59.9462890625</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275047302246</v>
+        <v>59.7275009155273</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838500976562</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775566101074</v>
+        <v>60.0775489807129</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026229858398</v>
+        <v>60.6026306152344</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771415710449</v>
+        <v>57.2771377563477</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204887390137</v>
+        <v>54.5204925537109</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3272972106934</v>
+        <v>58.3273010253906</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772491455078</v>
+        <v>57.9772453308105</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711555480957</v>
+        <v>59.0711517333984</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273933410645</v>
+        <v>59.0273971557617</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583610534668</v>
+        <v>57.0583572387695</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646659851074</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395767211914</v>
+        <v>56.8395729064941</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708442687988</v>
+        <v>56.9708480834961</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646659851074</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456703186035</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897323608398</v>
+        <v>57.8897361755371</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648582458496</v>
+        <v>58.7648658752441</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899475097656</v>
+        <v>59.2899436950684</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962333679199</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770454406738</v>
+        <v>56.5770416259766</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3144989013672</v>
+        <v>56.3145027160645</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146026611328</v>
+        <v>57.0146064758301</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896286010742</v>
+        <v>57.1896324157715</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520599365234</v>
+        <v>56.752067565918</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582611083984</v>
+        <v>56.3582572937012</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.389217376709</v>
+        <v>54.3892211914062</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703330993652</v>
+        <v>53.4703369140625</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518562316895</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078979492188</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264823913574</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078979492188</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.113883972168</v>
+        <v>52.1138877868652</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196662902832</v>
+        <v>48.9196701049805</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.357234954834</v>
+        <v>49.3572311401367</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883949279785</v>
+        <v>48.788402557373</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265785217285</v>
+        <v>53.4265747070312</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889099121094</v>
+        <v>52.2889137268066</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511413574219</v>
+        <v>50.4511451721191</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.7510414123535</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137840270996</v>
+        <v>51.4137878417969</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264823913574</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890098571777</v>
+        <v>52.989013671875</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017082214355</v>
+        <v>54.301700592041</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516525268555</v>
+        <v>53.95166015625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015045166016</v>
+        <v>52.901496887207</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017082214355</v>
+        <v>54.301700592041</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519638061523</v>
+        <v>56.0519676208496</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518562316895</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142951965332</v>
+        <v>54.9142990112305</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891136169434</v>
+        <v>53.6891174316406</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078979492188</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.220588684082</v>
+        <v>55.2205848693848</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>52.463939666748</v>
+        <v>52.4639358520508</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358390808105</v>
+        <v>46.0358428955078</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.424747467041</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.3865928649902</v>
+        <v>40.386589050293</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.9755249023438</v>
+        <v>43.975528717041</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509155273438</v>
+        <v>44.7509117126465</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019897460938</v>
+        <v>42.6019859313965</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.9663047790527</v>
+        <v>46.9663009643555</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536895751953</v>
+        <v>47.4536933898926</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361557006836</v>
+        <v>49.5361595153809</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.1817016601562</v>
+        <v>49.181697845459</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410781860352</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.1373863220215</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.915843963623</v>
+        <v>48.9158477783203</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.1373863220215</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844718933105</v>
+        <v>51.8844757080078</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715438842773</v>
+        <v>48.8715400695801</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056976318359</v>
+        <v>48.6056938171387</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.8524627685547</v>
+        <v>47.852466583252</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927581787109</v>
+        <v>45.5927619934082</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.371223449707</v>
+        <v>45.3712196350098</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699966430664</v>
+        <v>45.7699928283691</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586120605469</v>
+        <v>45.8586044311523</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121360778809</v>
+        <v>42.9121398925781</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570610046387</v>
+        <v>42.7570571899414</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918243408203</v>
+        <v>42.2918281555176</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761421203613</v>
+        <v>43.7761459350586</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324440002441</v>
+        <v>43.5324516296387</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.3109130859375</v>
+        <v>43.3109092712402</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222938537598</v>
+        <v>43.2222900390625</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>48.3250007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>42.8235244750977</v>
+        <v>42.8235282897949</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450592041016</v>
+        <v>43.0450630187988</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444534301758</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444534301758</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>48.8250007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>43.2665977478027</v>
+        <v>43.2666015625</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102958679199</v>
+        <v>43.5102920532227</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349052429199</v>
+        <v>42.7349014282227</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493682861328</v>
+        <v>41.6493606567383</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.804443359375</v>
+        <v>41.8044395446777</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>40.6081314086914</v>
+        <v>40.6081352233887</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.9465827941895</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112060546875</v>
+        <v>39.6112098693848</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>45.6749992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>40.475212097168</v>
+        <v>40.4752082824707</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4308967590332</v>
+        <v>40.4309005737305</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>45.9249992370605</v>
       </c>
       <c r="G328" t="n">
-        <v>40.6967506408691</v>
+        <v>40.6967468261719</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>40.6081314086914</v>
+        <v>40.6081352233887</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099754333496</v>
+        <v>40.0099792480469</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>48.7249984741211</v>
       </c>
       <c r="G332" t="n">
-        <v>43.1779823303223</v>
+        <v>43.177978515625</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.424747467041</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>48.2999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>42.8013687133789</v>
+        <v>42.8013725280762</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.9847450256348</v>
+        <v>40.984748840332</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096824645996</v>
+        <v>43.7096786499023</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610694885254</v>
+        <v>45.0610656738281</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764549255371</v>
+        <v>47.2764587402344</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992317199707</v>
+        <v>47.0992279052734</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878471374512</v>
+        <v>47.1878433227539</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>45.9915351867676</v>
+        <v>45.9915313720703</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973602294922</v>
+        <v>40.4973640441895</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321273803711</v>
+        <v>40.0321311950684</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625968933105</v>
+        <v>40.962589263916</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724540710449</v>
+        <v>44.9724502563477</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.0801467895508</v>
+        <v>46.080150604248</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780097961426</v>
+        <v>50.3780059814453</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893905639648</v>
+        <v>50.2893943786621</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958602905273</v>
+        <v>51.7958564758301</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.6881637573242</v>
+        <v>50.688159942627</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121635437012</v>
+        <v>50.1121597290039</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463134765625</v>
+        <v>49.8463172912598</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250953674316</v>
+        <v>53.1250915527344</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.3909378051758</v>
+        <v>53.390941619873</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657150268555</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164810180664</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998649597168</v>
+        <v>54.0998611450195</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380233764648</v>
+        <v>56.1380271911621</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001815795898</v>
+        <v>57.6001853942871</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.783561706543</v>
+        <v>55.7835655212402</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863395690918</v>
+        <v>58.4863433837891</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038734436035</v>
+        <v>56.4038696289062</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.3595657348633</v>
+        <v>56.359561920166</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6888008117676</v>
+        <v>57.6887969970703</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>57.11279296875</v>
+        <v>57.1127967834473</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>53.4795570373535</v>
+        <v>53.4795532226562</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>52.9921722412109</v>
+        <v>52.9921684265137</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.245719909668</v>
+        <v>57.2457237243652</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823387145996</v>
+        <v>56.1823348999023</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709541320801</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026466369629</v>
+        <v>56.8026428222656</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254119873047</v>
+        <v>56.625415802002</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709541320801</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164810180664</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506385803223</v>
+        <v>55.6506423950195</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.701099395752</v>
+        <v>53.7010955810547</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1693954467773</v>
+        <v>53.1694030761719</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.81494140625</v>
+        <v>52.8149375915527</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>50.7767753601074</v>
+        <v>50.7767791748047</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743255615234</v>
+        <v>51.5743179321289</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450828552246</v>
+        <v>50.2450866699219</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792404174805</v>
+        <v>49.9792366027832</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>54.5</v>
       </c>
       <c r="G473" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886108398438</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>54.5</v>
       </c>
       <c r="G484" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265113830566</v>
+        <v>50.3265190124512</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9555931091309</v>
+        <v>50.9555969238281</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075592041016</v>
+        <v>49.6075630187988</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886108398438</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>54.5</v>
       </c>
       <c r="G494" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653587341309</v>
+        <v>57.9653625488281</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186431884766</v>
+        <v>55.7186393737793</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.7415313720703</v>
+        <v>53.7415237426758</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8313941955566</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111351013184</v>
+        <v>54.0111312866211</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745452880859</v>
+        <v>51.6745491027832</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265113830566</v>
+        <v>50.3265190124512</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644081115723</v>
+        <v>51.7644157409668</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603721618652</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.0356979370117</v>
+        <v>44.0357055664062</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>44.8445243835449</v>
+        <v>44.8445205688477</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>53</v>
       </c>
       <c r="G546" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696662902832</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>53</v>
       </c>
       <c r="G551" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.0356979370117</v>
+        <v>44.0357055664062</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379554748535</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886108398438</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>53</v>
       </c>
       <c r="G584" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124496459961</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.236644744873</v>
+        <v>50.2366485595703</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.596118927002</v>
+        <v>50.5961227416992</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938613891602</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.540584564209</v>
+        <v>47.5405807495117</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>46.012809753418</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203216552734</v>
+        <v>47.7203178405762</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781135559082</v>
+        <v>56.0781173706055</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617904663086</v>
+        <v>53.5617866516113</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098205566406</v>
+        <v>54.9098243713379</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.1010055541992</v>
+        <v>54.101001739502</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111351013184</v>
+        <v>54.0111312866211</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8313941955566</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124496459961</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225791931152</v>
+        <v>53.0225830078125</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225791931152</v>
+        <v>53.0225830078125</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>52.8428382873535</v>
+        <v>52.8428421020508</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225791931152</v>
+        <v>53.0225830078125</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124496459961</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225791931152</v>
+        <v>53.0225830078125</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578544616699</v>
+        <v>56.2578506469727</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.7415313720703</v>
+        <v>53.7415237426758</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379554748535</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>48</v>
       </c>
       <c r="G671" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916038513184</v>
+        <v>39.9916000366211</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>39.2726554870605</v>
+        <v>39.2726593017578</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.1166381835938</v>
+        <v>33.116641998291</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>33.3413124084473</v>
+        <v>33.3413162231445</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.1632556915283</v>
+        <v>25.1632595062256</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7367992401123</v>
+        <v>22.7368011474609</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139148712158</v>
+        <v>24.7139129638672</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024707794189</v>
+        <v>25.7024688720703</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31</v>
       </c>
       <c r="G697" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>31</v>
       </c>
       <c r="G699" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201065063477</v>
+        <v>27.3201084136963</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161743164062</v>
+        <v>30.016170501709</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857799530029</v>
+        <v>30.2857780456543</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130737304688</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.308666229248</v>
+        <v>28.3086643218994</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.0505027770996</v>
+        <v>27.050500869751</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.5562210083008</v>
+        <v>26.556224822998</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>31</v>
       </c>
       <c r="G718" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5562210083008</v>
+        <v>26.556224822998</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998455047607</v>
+        <v>27.4998474121094</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566963195801</v>
+        <v>29.6566982269287</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699264526367</v>
+        <v>30.8699245452881</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959075927734</v>
+        <v>30.1959056854248</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743358612061</v>
+        <v>31.2743320465088</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990081787109</v>
+        <v>31.4990043640137</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241500854492</v>
+        <v>34.8241539001465</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161743164062</v>
+        <v>30.016170501709</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699264526367</v>
+        <v>30.8699245452881</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.4426307678223</v>
+        <v>32.442626953125</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373802185059</v>
+        <v>36.0373764038086</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823173522949</v>
+        <v>36.0823135375977</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>38.104362487793</v>
+        <v>38.1043586730957</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202140808105</v>
+        <v>37.5202102661133</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643081665039</v>
+        <v>41.5643119812012</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.283260345459</v>
+        <v>42.2832565307617</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224754333496</v>
+        <v>42.8224716186523</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>46.7999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>42.0585899353027</v>
+        <v>42.0585861206055</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.507926940918</v>
+        <v>42.5079307556152</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>42.6427307128906</v>
+        <v>42.6427345275879</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991119384766</v>
+        <v>41.6991157531738</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>48</v>
       </c>
       <c r="G791" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>48</v>
       </c>
       <c r="G801" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.586353302002</v>
+        <v>43.5863571166992</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>48</v>
       </c>
       <c r="G805" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>45.5</v>
       </c>
       <c r="G807" t="n">
-        <v>40.8902969360352</v>
+        <v>40.8902931213379</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479850769043</v>
+        <v>39.047981262207</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854103088379</v>
+        <v>37.3854064941406</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100845336914</v>
+        <v>37.6100769042969</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069877624512</v>
+        <v>36.3069915771484</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347549438477</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651435852051</v>
+        <v>37.5651473999023</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986404418945</v>
+        <v>38.5986442565918</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118667602539</v>
+        <v>39.8118629455566</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.452392578125</v>
+        <v>39.4523963928223</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656227111816</v>
+        <v>40.6656188964844</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638366699219</v>
+        <v>38.4638328552246</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.430347442627</v>
+        <v>37.4303436279297</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G834" t="n">
-        <v>36.9360618591309</v>
+        <v>36.9360656738281</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.1827850341797</v>
+        <v>39.182788848877</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105522155762</v>
+        <v>40.7105560302734</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>44.75</v>
       </c>
       <c r="G845" t="n">
-        <v>40.2162742614746</v>
+        <v>40.2162780761719</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>46</v>
       </c>
       <c r="G849" t="n">
-        <v>41.3396377563477</v>
+        <v>41.3396339416504</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643081665039</v>
+        <v>41.5643119812012</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453559875488</v>
+        <v>40.8453598022461</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.901741027832</v>
+        <v>39.9017333984375</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744415283203</v>
+        <v>41.4744453430176</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1599006652832</v>
+        <v>41.1598968505859</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.5308151245117</v>
+        <v>40.530818939209</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>45.5</v>
       </c>
       <c r="G860" t="n">
-        <v>40.8902969360352</v>
+        <v>40.8902931213379</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960189819336</v>
+        <v>40.3960113525391</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>45.5</v>
       </c>
       <c r="G864" t="n">
-        <v>40.8902969360352</v>
+        <v>40.8902931213379</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801597595215</v>
+        <v>40.9801635742188</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.3616828918457</v>
+        <v>43.361686706543</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281936645508</v>
+        <v>42.3281898498535</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938613891602</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938613891602</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.0356979370117</v>
+        <v>44.0357055664062</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696662902832</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>46.012809753418</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>46.012809753418</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>44.305305480957</v>
+        <v>44.3053016662598</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603721618652</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.540584564209</v>
+        <v>47.5405807495117</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>53</v>
       </c>
       <c r="G944" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886108398438</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>46.012809753418</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938613891602</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938613891602</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519233703613</v>
+        <v>42.9519195556641</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087371826172</v>
+        <v>41.9087409973145</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>42.0448036193848</v>
+        <v>42.044807434082</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551811218262</v>
+        <v>41.4551849365234</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1008" t="n">
-        <v>40.5027084350586</v>
+        <v>40.5027122497559</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>39.6409492492676</v>
+        <v>39.6409530639648</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G1011" t="n">
-        <v>40.2759323120117</v>
+        <v>40.2759284973145</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316589355469</v>
+        <v>39.7316627502441</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.0513229370117</v>
+        <v>39.051326751709</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797866821289</v>
+        <v>42.6797828674316</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043922424316</v>
+        <v>43.9043960571289</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>43.2694129943848</v>
+        <v>43.2694091796875</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>44.7207946777344</v>
+        <v>44.7207908630371</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>53</v>
       </c>
       <c r="G1043" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306854248047</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>53</v>
       </c>
       <c r="G1047" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>53</v>
       </c>
       <c r="G1048" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306854248047</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071594238281</v>
+        <v>46.8071632385254</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>46.0814666748047</v>
+        <v>46.081470489502</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093338012695</v>
+        <v>45.8093376159668</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.4486618041992</v>
+        <v>44.4486656188965</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125915527344</v>
+        <v>44.3125953674316</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836448669434</v>
+        <v>45.0836410522461</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>46.0814666748047</v>
+        <v>46.081470489502</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>40.6387786865234</v>
+        <v>40.6387748718262</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595260620117</v>
+        <v>39.459529876709</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895599365234</v>
+        <v>38.1895637512207</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452941894531</v>
+        <v>37.6452980041504</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010246276855</v>
+        <v>37.1010284423828</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.1485557556152</v>
+        <v>36.148551940918</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1125" t="n">
-        <v>36.6474685668945</v>
+        <v>36.6474723815918</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1126" t="n">
-        <v>36.6474685668945</v>
+        <v>36.6474723815918</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>40.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>42.25</v>
       </c>
       <c r="G1132" t="n">
-        <v>38.3256340026855</v>
+        <v>38.3256301879883</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299789428711</v>
+        <v>36.3299751281738</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>40.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146560668945</v>
+        <v>35.0146598815918</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250335693359</v>
+        <v>34.4250373840332</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611038208008</v>
+        <v>34.5611000061035</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>40.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092239379883</v>
+        <v>37.5092315673828</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742523193359</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556678771973</v>
+        <v>37.0556716918945</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.1031951904297</v>
+        <v>36.103199005127</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.8829383850098</v>
+        <v>32.882942199707</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.386194229126</v>
+        <v>31.3861980438232</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>29.2998294830322</v>
+        <v>29.2998313903809</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691951751709</v>
+        <v>26.6691970825195</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577362060547</v>
+        <v>27.7577381134033</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.6500015258789</v>
       </c>
       <c r="G1184" t="n">
-        <v>29.6173248291016</v>
+        <v>29.6173229217529</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419303894043</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561584472656</v>
+        <v>32.6561622619629</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600204467773</v>
+        <v>35.0600166320801</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053733825684</v>
+        <v>35.1053771972656</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742523193359</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1212" t="n">
-        <v>36.919605255127</v>
+        <v>36.9196014404297</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092239379883</v>
+        <v>37.5092315673828</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>40.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>35.5589294433594</v>
+        <v>35.5589256286621</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475547790527</v>
+        <v>34.2475509643555</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377815246582</v>
+        <v>33.7377777099609</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280044555664</v>
+        <v>33.2280006408691</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719566345215</v>
+        <v>34.5719528198242</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792045593262</v>
+        <v>32.5792007446289</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546661376953</v>
+        <v>28.4546642303467</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692928314209</v>
+        <v>28.2692909240723</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911655426025</v>
+        <v>26.0911674499512</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131084442139</v>
+        <v>25.8131065368652</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887710571289</v>
+        <v>27.3887729644775</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473499298096</v>
+        <v>28.5473518371582</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107139587402</v>
+        <v>27.1107158660889</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545295715332</v>
+        <v>24.6545314788818</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984115600586</v>
+        <v>24.0984134674072</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033332824707</v>
+        <v>25.3033313751221</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.720422744751</v>
+        <v>25.7204208374023</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350494384766</v>
+        <v>25.5350475311279</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301959991455</v>
+        <v>26.2301940917969</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.5741443634033</v>
+        <v>27.574146270752</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352523803711</v>
+        <v>31.2352504730225</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377113342285</v>
+        <v>31.8377075195312</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571914672852</v>
+        <v>30.9571933746338</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.9303970336914</v>
+        <v>31.93039894104</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596504211426</v>
+        <v>31.5596523284912</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986808776855</v>
+        <v>31.6986827850342</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182312011719</v>
+        <v>32.7182273864746</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914367675781</v>
+        <v>33.6914329528809</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.3597869873047</v>
+        <v>35.359790802002</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988136291504</v>
+        <v>35.4988174438477</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744117736816</v>
+        <v>35.1744155883789</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012138366699</v>
+        <v>34.2012100219727</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.5183639526367</v>
+        <v>36.518367767334</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085868835449</v>
+        <v>36.0085906982422</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059288024902</v>
+        <v>29.7059268951416</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2033996582031</v>
+        <v>27.2034015655518</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156337738037</v>
+        <v>28.3156356811523</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -61056,6 +61056,32 @@
         <v>1.66400003433228</v>
       </c>
       <c r="H2334" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2335" t="n">
+        <v>745699</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>1.65699994564056</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>1.67799997329712</v>
+      </c>
+      <c r="G2335" t="n">
+        <v>1.67799997329712</v>
+      </c>
+      <c r="H2335" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503265380859</v>
+        <v>44.8503189086914</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569236755371</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632209777832</v>
+        <v>47.5632171630859</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319496154785</v>
+        <v>47.431957244873</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0818977355957</v>
+        <v>47.0818939208984</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506340026855</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.469310760498</v>
+        <v>46.4693069458008</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256561279297</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443367004395</v>
+        <v>46.6443328857422</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.1192588806152</v>
+        <v>46.119255065918</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254524230957</v>
+        <v>45.7254447937012</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692070007324</v>
+        <v>45.7692108154297</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.5130653381348</v>
+        <v>46.513069152832</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567199707031</v>
+        <v>45.8567161560059</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256561279297</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3882026672363</v>
+        <v>47.3881912231445</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569236755371</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445404052734</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135841369629</v>
+        <v>50.0135803222656</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.1949996948242</v>
+        <v>51.1950035095215</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577461242676</v>
+        <v>52.8577499389648</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.8203811645508</v>
+        <v>53.820384979248</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769416809082</v>
+        <v>55.8769378662109</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3337020874023</v>
+        <v>59.3336868286133</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403953552246</v>
+        <v>62.4403991699219</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965484619141</v>
+        <v>61.6965446472168</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965484619141</v>
+        <v>61.6965446472168</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.134105682373</v>
+        <v>62.1341094970703</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902435302734</v>
+        <v>61.3902473449707</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339981079102</v>
+        <v>61.4340019226074</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964256286621</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399879455566</v>
+        <v>59.6399955749512</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838500976562</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775489807129</v>
+        <v>60.0775604248047</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276123046875</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214149475098</v>
+        <v>60.821418762207</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771415710449</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204925537109</v>
+        <v>54.5204887390137</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273010253906</v>
+        <v>58.3272972106934</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772453308105</v>
+        <v>57.9772415161133</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711517333984</v>
+        <v>59.071159362793</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273971557617</v>
+        <v>59.027400970459</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834426879883</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583572387695</v>
+        <v>57.0583610534668</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395729064941</v>
+        <v>56.8395805358887</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708480834961</v>
+        <v>56.9708442687988</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396842956543</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712669372559</v>
+        <v>59.7712593078613</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276123046875</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525825500488</v>
+        <v>60.252571105957</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.7456703186035</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709480285645</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648658752441</v>
+        <v>58.7648620605469</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899436950684</v>
+        <v>59.2899360656738</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334869384766</v>
+        <v>57.9334945678711</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962333679199</v>
+        <v>59.5962257385254</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.9900398254395</v>
+        <v>59.990047454834</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770416259766</v>
+        <v>56.5770454406738</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145027160645</v>
+        <v>56.3144989013672</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896324157715</v>
+        <v>57.189624786377</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396842956543</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.752067565918</v>
+        <v>56.7520599365234</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831314086914</v>
+        <v>55.4831275939941</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582572937012</v>
+        <v>56.3582611083984</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892211914062</v>
+        <v>54.389217376709</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703369140625</v>
+        <v>53.4703330993652</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.139476776123</v>
+        <v>56.1394805908203</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264823913574</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765342712402</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138877868652</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.788402557373</v>
+        <v>48.7883987426758</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265747070312</v>
+        <v>53.4265785217285</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8951072692871</v>
+        <v>51.8951034545898</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889137268066</v>
+        <v>52.2889099121094</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571273803711</v>
+        <v>48.6571311950684</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264823913574</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765342712402</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.301700592041</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.95166015625</v>
+        <v>53.9516563415527</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140914916992</v>
+        <v>53.5140953063965</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.901496887207</v>
+        <v>52.9015007019043</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.301700592041</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519676208496</v>
+        <v>56.0519638061523</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891174316406</v>
+        <v>53.6891136169434</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391731262207</v>
+        <v>54.0391693115234</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830276489258</v>
+        <v>54.7830238342285</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.2205848693848</v>
+        <v>55.2205924987793</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>52.4639358520508</v>
+        <v>52.463939666748</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.662296295166</v>
+        <v>44.6623039245605</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179885864258</v>
+        <v>44.617992401123</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358428955078</v>
+        <v>46.0358390808105</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.386589050293</v>
+        <v>40.3865928649902</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281463623047</v>
+        <v>44.9281425476074</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982940673828</v>
+        <v>43.7982902526855</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.9663009643555</v>
+        <v>46.9663047790527</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475402832031</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361633300781</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410781860352</v>
+        <v>47.9410743713379</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983177185059</v>
+        <v>50.9983139038086</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715400695801</v>
+        <v>48.8715438842773</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056938171387</v>
+        <v>48.6056976318359</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G254" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626091003418</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G256" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626091003418</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192230224609</v>
+        <v>44.2192192077637</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.301685333252</v>
+        <v>46.3016891479492</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346122741699</v>
+        <v>46.4346084594727</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232238769531</v>
+        <v>46.5232276916504</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699928283691</v>
+        <v>45.7699966430664</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586044311523</v>
+        <v>45.8586120605469</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570571899414</v>
+        <v>42.7570610046387</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918281555176</v>
+        <v>42.2918243408203</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761459350586</v>
+        <v>43.7761421203613</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324516296387</v>
+        <v>43.5324478149414</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222900390625</v>
+        <v>43.2222938537598</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G291" t="n">
-        <v>42.2253684997559</v>
+        <v>42.2253723144531</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>48.3250007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>42.8235282897949</v>
+        <v>42.8235244750977</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450592041016</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444534301758</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444534301758</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539863586426</v>
+        <v>43.7539825439453</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102920532227</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349014282227</v>
+        <v>42.7349090576172</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493606567383</v>
+        <v>41.6493682861328</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.8044395446777</v>
+        <v>41.804443359375</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170547485352</v>
+        <v>41.3170509338379</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853622436523</v>
+        <v>40.7853584289551</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062835693359</v>
+        <v>41.2062873840332</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638236999512</v>
+        <v>40.5638198852539</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573539733887</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465827941895</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112098693848</v>
+        <v>39.6112022399902</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782791137695</v>
+        <v>39.4782829284668</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213562011719</v>
+        <v>39.9213600158691</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099792480469</v>
+        <v>40.0099754333496</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.275821685791</v>
+        <v>40.2758255004883</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>48.7249984741211</v>
       </c>
       <c r="G332" t="n">
-        <v>43.177978515625</v>
+        <v>43.1779823303223</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062835693359</v>
+        <v>41.2062873840332</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361396789551</v>
+        <v>42.3361434936523</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696723937988</v>
+        <v>42.2696800231934</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>48.2999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>42.8013725280762</v>
+        <v>42.8013687133789</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555099487305</v>
+        <v>39.6555137634277</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573539733887</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.990894317627</v>
+        <v>38.9908981323242</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684455871582</v>
+        <v>42.6684494018555</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610656738281</v>
+        <v>45.0610694885254</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.833381652832</v>
+        <v>46.8333778381348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>45.9915313720703</v>
+        <v>45.9915351867676</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973640441895</v>
+        <v>40.4973602294922</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992042541504</v>
+        <v>39.8992080688477</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321311950684</v>
+        <v>40.0321273803711</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.962589263916</v>
+        <v>40.9625930786133</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.080150604248</v>
+        <v>46.0801467895508</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118431091309</v>
+        <v>46.6118392944336</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.5109329223633</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780059814453</v>
+        <v>50.3780097961426</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.688159942627</v>
+        <v>50.6881637573242</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121635437012</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463172912598</v>
+        <v>49.8463134765625</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032363891602</v>
+        <v>49.4032325744629</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250915527344</v>
+        <v>53.1250991821289</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.390941619873</v>
+        <v>53.3909378051758</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657150268555</v>
+        <v>54.3657112121582</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961769104004</v>
+        <v>55.2961807250977</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164810180664</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998611450195</v>
+        <v>54.0998649597168</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.777416229248</v>
+        <v>57.7774124145508</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001853942871</v>
+        <v>57.6001892089844</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.157112121582</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.7835655212402</v>
+        <v>55.783561706543</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038696289062</v>
+        <v>56.4038734436035</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.359561920166</v>
+        <v>56.3595657348633</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>57.4672622680664</v>
+        <v>57.4672584533691</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.087574005127</v>
+        <v>58.0875778198242</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6887969970703</v>
+        <v>57.6888008117676</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.5238647460938</v>
+        <v>53.523868560791</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709541320801</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709541320801</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164810180664</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506423950195</v>
+        <v>55.6506385803223</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743179321289</v>
+        <v>51.5743217468262</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450866699219</v>
+        <v>50.2450828552246</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703094482422</v>
+        <v>49.2703132629395</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.5109329223633</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569076538086</v>
+        <v>50.0569114685059</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>54.5</v>
       </c>
       <c r="G473" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.8886108398438</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>54.5</v>
       </c>
       <c r="G484" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265190124512</v>
+        <v>50.3265151977539</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.8886108398438</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>54.5</v>
       </c>
       <c r="G494" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>60</v>
       </c>
       <c r="G502" t="n">
-        <v>53.9212608337402</v>
+        <v>53.9212646484375</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653625488281</v>
+        <v>57.9653587341309</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186393737793</v>
+        <v>55.7186431884766</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.7415237426758</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111389160156</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745491027832</v>
+        <v>51.6745452880859</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265190124512</v>
+        <v>50.3265151977539</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644157409668</v>
+        <v>51.7644119262695</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502388000488</v>
+        <v>44.3502349853516</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.0357055664062</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>53</v>
       </c>
       <c r="G546" t="n">
-        <v>47.6304473876953</v>
+        <v>47.6304512023926</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>53</v>
       </c>
       <c r="G551" t="n">
-        <v>47.6304473876953</v>
+        <v>47.6304512023926</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.0357055664062</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190071105957</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.8886108398438</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>53</v>
       </c>
       <c r="G584" t="n">
-        <v>47.6304473876953</v>
+        <v>47.6304512023926</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732345581055</v>
+        <v>52.5732307434082</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.5961227416992</v>
+        <v>50.596118927002</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595367431641</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837356567383</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837356567383</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203178405762</v>
+        <v>47.7203216552734</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.976806640625</v>
+        <v>56.9768028259277</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781173706055</v>
+        <v>56.0781211853027</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.101001739502</v>
+        <v>54.1010055541992</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516571044922</v>
+        <v>53.6516609191895</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111389160156</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>52.8428421020508</v>
+        <v>52.8428382873535</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>60</v>
       </c>
       <c r="G655" t="n">
-        <v>53.9212608337402</v>
+        <v>53.9212646484375</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578506469727</v>
+        <v>56.2578544616699</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300872802734</v>
+        <v>54.7300834655762</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.7415237426758</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948043823242</v>
+        <v>51.4948081970215</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.1632595062256</v>
+        <v>25.163257598877</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7368011474609</v>
+        <v>22.7367992401123</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139129638672</v>
+        <v>24.7139148712158</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024688720703</v>
+        <v>25.7024707794189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31</v>
       </c>
       <c r="G697" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>31</v>
       </c>
       <c r="G699" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258285522461</v>
+        <v>26.8258304595947</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967468261719</v>
+        <v>26.1967487335205</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>31.7236785888672</v>
+        <v>31.7236747741699</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857780456543</v>
+        <v>30.2857799530029</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.050500869751</v>
+        <v>27.0505027770996</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.556224822998</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>31</v>
       </c>
       <c r="G718" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.556224822998</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998474121094</v>
+        <v>27.4998435974121</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566982269287</v>
+        <v>29.6566963195801</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959056854248</v>
+        <v>30.1959075927734</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743320465088</v>
+        <v>31.2743358612061</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642024993896</v>
+        <v>31.3642063140869</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241539001465</v>
+        <v>34.8241500854492</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717086791992</v>
+        <v>33.0717124938965</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060390472412</v>
+        <v>30.1060371398926</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.442626953125</v>
+        <v>32.4426307678223</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373764038086</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298759460449</v>
+        <v>34.3298721313477</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.8690872192383</v>
+        <v>34.869083404541</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.6444129943848</v>
+        <v>34.644416809082</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G748" t="n">
-        <v>35.3633613586426</v>
+        <v>35.3633575439453</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>42.5</v>
       </c>
       <c r="G751" t="n">
-        <v>38.1942291259766</v>
+        <v>38.1942329406738</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>42.5</v>
       </c>
       <c r="G752" t="n">
-        <v>38.1942291259766</v>
+        <v>38.1942329406738</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>38.1043586730957</v>
+        <v>38.104362487793</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.2832565307617</v>
+        <v>42.283260345459</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224716186523</v>
+        <v>42.8224754333496</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>42.8674049377441</v>
+        <v>42.8674087524414</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0251007080078</v>
+        <v>41.0250968933105</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409484863281</v>
+        <v>40.4409523010254</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.5079307556152</v>
+        <v>42.507926940918</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991157531738</v>
+        <v>41.6991119384766</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.957275390625</v>
+        <v>42.9572715759277</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.5863571166992</v>
+        <v>43.586353302002</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.047981262207</v>
+        <v>39.0479850769043</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854064941406</v>
+        <v>37.3854103088379</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100769042969</v>
+        <v>37.6100845336914</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069915771484</v>
+        <v>36.3069877624512</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594215393066</v>
+        <v>38.0594253540039</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651473999023</v>
+        <v>37.5651435852051</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118629455566</v>
+        <v>39.8118705749512</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.4523963928223</v>
+        <v>39.452392578125</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656227111816</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638328552246</v>
+        <v>38.4638366699219</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.4303436279297</v>
+        <v>37.430347442627</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.8690872192383</v>
+        <v>34.869083404541</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.182788848877</v>
+        <v>39.1827850341797</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448883056641</v>
+        <v>37.7448844909668</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612113952637</v>
+        <v>40.2612075805664</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017333984375</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744453430176</v>
+        <v>41.4744415283203</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.530818939209</v>
+        <v>40.5308151245117</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960113525391</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801635742188</v>
+        <v>40.9801597595215</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471458435059</v>
+        <v>43.0471420288086</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281898498535</v>
+        <v>42.3281936645508</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.0357055664062</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837356567383</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190071105957</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837356567383</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>44.3053016662598</v>
+        <v>44.305305480957</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>53</v>
       </c>
       <c r="G944" t="n">
-        <v>47.6304473876953</v>
+        <v>47.6304512023926</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595367431641</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.8886108398438</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G969" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G972" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837356567383</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087409973145</v>
+        <v>41.9087371826172</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>42.044807434082</v>
+        <v>42.0448036193848</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.0901641845703</v>
+        <v>42.090160369873</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551849365234</v>
+        <v>41.4551811218262</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>39.6409530639648</v>
+        <v>39.6409492492676</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G1011" t="n">
-        <v>40.2759284973145</v>
+        <v>40.2759323120117</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316627502441</v>
+        <v>39.7316589355469</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.051326751709</v>
+        <v>39.0513229370117</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.636604309082</v>
+        <v>41.6366081237793</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797828674316</v>
+        <v>42.6797866821289</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043960571289</v>
+        <v>43.9043922424316</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>43.2694091796875</v>
+        <v>43.2694129943848</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218818664551</v>
+        <v>44.2218856811523</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>44.7207908630371</v>
+        <v>44.7207946777344</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>53</v>
       </c>
       <c r="G1043" t="n">
-        <v>48.0771217346191</v>
+        <v>48.0771255493164</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678352355957</v>
+        <v>48.1678314208984</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>53</v>
       </c>
       <c r="G1047" t="n">
-        <v>48.0771217346191</v>
+        <v>48.0771255493164</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>53</v>
       </c>
       <c r="G1048" t="n">
-        <v>48.0771217346191</v>
+        <v>48.0771255493164</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328559875488</v>
+        <v>47.5328598022461</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443168640137</v>
+        <v>46.4443206787109</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164535522461</v>
+        <v>46.7164497375488</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071632385254</v>
+        <v>46.8071594238281</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093376159668</v>
+        <v>45.8093338012695</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.4486656188965</v>
+        <v>44.448657989502</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125953674316</v>
+        <v>44.3125915527344</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836410522461</v>
+        <v>45.0836448669434</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563743591309</v>
+        <v>49.2563705444336</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.459529876709</v>
+        <v>39.4595222473145</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9174270629883</v>
+        <v>37.9174308776855</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452980041504</v>
+        <v>37.6452941894531</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010284423828</v>
+        <v>37.1010246276855</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.148551940918</v>
+        <v>36.1485557556152</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578422546387</v>
+        <v>36.0578460693359</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228630065918</v>
+        <v>35.4228591918945</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1125" t="n">
-        <v>36.6474723815918</v>
+        <v>36.6474685668945</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1126" t="n">
-        <v>36.6474723815918</v>
+        <v>36.6474685668945</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>37.9174270629883</v>
+        <v>37.9174308776855</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299751281738</v>
+        <v>36.3299789428711</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146598815918</v>
+        <v>35.0146560668945</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250373840332</v>
+        <v>34.4250335693359</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092315673828</v>
+        <v>37.5092277526855</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556716918945</v>
+        <v>37.0556678771973</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.103199005127</v>
+        <v>36.1031951904297</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.882942199707</v>
+        <v>32.8829383850098</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605033874512</v>
+        <v>30.6605072021484</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861980438232</v>
+        <v>31.3861961364746</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691970825195</v>
+        <v>26.6691951751709</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577381134033</v>
+        <v>27.7577362060547</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.6500015258789</v>
       </c>
       <c r="G1184" t="n">
-        <v>29.6173229217529</v>
+        <v>29.6173248291016</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419303894043</v>
+        <v>30.8419322967529</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561622619629</v>
+        <v>32.6561584472656</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272041320801</v>
+        <v>33.4272079467773</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600166320801</v>
+        <v>35.0600204467773</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053771972656</v>
+        <v>35.1053733825684</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1212" t="n">
-        <v>36.9196014404297</v>
+        <v>36.919605255127</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092315673828</v>
+        <v>37.5092277526855</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>35.5589256286621</v>
+        <v>35.5589294433594</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475509643555</v>
+        <v>34.2475547790527</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377777099609</v>
+        <v>33.7377815246582</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280006408691</v>
+        <v>33.2280044555664</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719528198242</v>
+        <v>34.5719566345215</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792007446289</v>
+        <v>32.5792045593262</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546642303467</v>
+        <v>28.4546661376953</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692909240723</v>
+        <v>28.2692928314209</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911674499512</v>
+        <v>26.0911655426025</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131065368652</v>
+        <v>25.8131084442139</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887729644775</v>
+        <v>27.3887710571289</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473518371582</v>
+        <v>28.5473499298096</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107158660889</v>
+        <v>27.1107139587402</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545314788818</v>
+        <v>24.6545295715332</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984134674072</v>
+        <v>24.0984115600586</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033313751221</v>
+        <v>25.3033332824707</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.7204208374023</v>
+        <v>25.720422744751</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350475311279</v>
+        <v>25.5350494384766</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301940917969</v>
+        <v>26.2301959991455</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.574146270752</v>
+        <v>27.5741443634033</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352504730225</v>
+        <v>31.2352523803711</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377075195312</v>
+        <v>31.8377113342285</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571933746338</v>
+        <v>30.9571914672852</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.93039894104</v>
+        <v>31.9303970336914</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596523284912</v>
+        <v>31.5596504211426</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986827850342</v>
+        <v>31.6986808776855</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182273864746</v>
+        <v>32.7182312011719</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914329528809</v>
+        <v>33.6914367675781</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.359790802002</v>
+        <v>35.3597869873047</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988174438477</v>
+        <v>35.4988136291504</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744155883789</v>
+        <v>35.1744117736816</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012100219727</v>
+        <v>34.2012138366699</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.518367767334</v>
+        <v>36.5183639526367</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085906982422</v>
+        <v>36.0085868835449</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059268951416</v>
+        <v>29.7059288024902</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2034015655518</v>
+        <v>27.2033996582031</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156356811523</v>
+        <v>28.3156337738037</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -61082,6 +61082,32 @@
         <v>1.67799997329712</v>
       </c>
       <c r="H2335" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2336" t="n">
+        <v>352398</v>
+      </c>
+      <c r="C2336" t="n">
+        <v>1.70099997520447</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>1.65600001811981</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>1.692999958992</v>
+      </c>
+      <c r="F2336" t="n">
+        <v>1.66600000858307</v>
+      </c>
+      <c r="G2336" t="n">
+        <v>1.66600000858307</v>
+      </c>
+      <c r="H2336" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503189086914</v>
+        <v>44.8503227233887</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>54.25</v>
       </c>
       <c r="G7" t="n">
-        <v>47.4757118225098</v>
+        <v>47.4757080078125</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.431957244873</v>
+        <v>47.4319496154785</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>54.25</v>
       </c>
       <c r="G18" t="n">
-        <v>47.4757118225098</v>
+        <v>47.4757080078125</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0818939208984</v>
+        <v>47.081901550293</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.4693069458008</v>
+        <v>46.469310760498</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131690979004</v>
+        <v>47.2131729125977</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880912780762</v>
+        <v>46.6880874633789</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254447937012</v>
+        <v>45.7254524230957</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.513069152832</v>
+        <v>46.5130653381348</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567161560059</v>
+        <v>45.8567199707031</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069755554199</v>
+        <v>47.6069793701172</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068756103516</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881912231445</v>
+        <v>47.3881950378418</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.994384765625</v>
+        <v>46.9943885803223</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0883026123047</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068756103516</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445442199707</v>
+        <v>48.0445365905762</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135765075684</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.1950035095215</v>
+        <v>51.194995880127</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.820384979248</v>
+        <v>53.8203887939453</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336868286133</v>
+        <v>59.3337020874023</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589797973633</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403991699219</v>
+        <v>62.4403953552246</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.1341094970703</v>
+        <v>62.1341018676758</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399955749512</v>
+        <v>59.6399879455566</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275009155273</v>
+        <v>59.7275047302246</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838577270508</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775604248047</v>
+        <v>60.0775527954102</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026306152344</v>
+        <v>60.6026344299316</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.821418762207</v>
+        <v>60.8214073181152</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771415710449</v>
+        <v>57.2771377563477</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3272972106934</v>
+        <v>58.3272933959961</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772415161133</v>
+        <v>57.9772529602051</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.027400970459</v>
+        <v>59.0273971557617</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834426879883</v>
+        <v>57.5834465026855</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583610534668</v>
+        <v>57.0583534240723</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395805358887</v>
+        <v>56.8395767211914</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708442687988</v>
+        <v>56.9708518981934</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396842956543</v>
+        <v>57.5396766662598</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.252571105957</v>
+        <v>60.2525749206543</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456703186035</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.670955657959</v>
+        <v>57.6709518432617</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897361755371</v>
+        <v>57.8897285461426</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648620605469</v>
+        <v>58.7648658752441</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899398803711</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334945678711</v>
+        <v>57.933479309082</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962371826172</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770454406738</v>
+        <v>56.5770378112793</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3144989013672</v>
+        <v>56.3145065307617</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146064758301</v>
+        <v>57.0146026611328</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.189624786377</v>
+        <v>57.1896362304688</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396842956543</v>
+        <v>57.5396766662598</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520599365234</v>
+        <v>56.7520637512207</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831275939941</v>
+        <v>55.4831314086914</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643508911133</v>
+        <v>55.2643547058105</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.389217376709</v>
+        <v>54.3892250061035</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264709472656</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765342712402</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578498840332</v>
+        <v>53.5578460693359</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.113883972168</v>
+        <v>52.1138877868652</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764266967773</v>
+        <v>52.3764228820801</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201850891113</v>
+        <v>52.4201889038086</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265785217285</v>
+        <v>53.4265823364258</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510414123535</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571311950684</v>
+        <v>48.6571273803711</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137840270996</v>
+        <v>51.4137802124023</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264709472656</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765342712402</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516563415527</v>
+        <v>53.95166015625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015007019043</v>
+        <v>52.9015083312988</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077980041504</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077980041504</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519638061523</v>
+        <v>56.0519676208496</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893173217773</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891136169434</v>
+        <v>53.6891174316406</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830238342285</v>
+        <v>54.7830276489258</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390693664551</v>
+        <v>53.3390655517578</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.3454627990723</v>
+        <v>54.345458984375</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893173217773</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.2205924987793</v>
+        <v>55.2205848693848</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623039245605</v>
+        <v>44.6623001098633</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.617992401123</v>
+        <v>44.6179885864258</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041465759277</v>
+        <v>45.5041427612305</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>45.8143005371094</v>
+        <v>45.8143043518066</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.9755249023438</v>
+        <v>43.975528717041</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281425476074</v>
+        <v>44.9281463623047</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982902526855</v>
+        <v>43.7982940673828</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536933898926</v>
+        <v>47.4536895751953</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272323608398</v>
+        <v>48.8272361755371</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.295539855957</v>
+        <v>48.2955360412598</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755485534668</v>
+        <v>51.1755523681641</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410820007324</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983139038086</v>
+        <v>50.9983177185059</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715438842773</v>
+        <v>48.8715400695801</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056976318359</v>
+        <v>48.6056938171387</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G254" t="n">
-        <v>48.1626091003418</v>
+        <v>48.1626129150391</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G256" t="n">
-        <v>48.1626091003418</v>
+        <v>48.1626129150391</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.852466583252</v>
+        <v>47.8524627685547</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>47.8967704772949</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>47.8967704772949</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370658874512</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370658874512</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496849060059</v>
+        <v>45.1496810913086</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927619934082</v>
+        <v>45.5927658081055</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.3712196350098</v>
+        <v>45.371223449707</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939926147461</v>
+        <v>45.1939964294434</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346084594727</v>
+        <v>46.4346122741699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586120605469</v>
+        <v>45.8586082458496</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989074707031</v>
+        <v>43.5989151000977</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324478149414</v>
+        <v>43.5324440002441</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G291" t="n">
-        <v>42.2253723144531</v>
+        <v>42.2253684997559</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.200138092041</v>
+        <v>43.2001419067383</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450592041016</v>
+        <v>43.0450630187988</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102958679199</v>
+        <v>43.5102882385254</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493682861328</v>
+        <v>41.6493644714355</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.804443359375</v>
+        <v>41.8044471740723</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170509338379</v>
+        <v>41.3170585632324</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853584289551</v>
+        <v>40.7853622436523</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062911987305</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>40.6081352233887</v>
+        <v>40.6081314086914</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638198852539</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573539733887</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782829284668</v>
+        <v>39.4782791137695</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213600158691</v>
+        <v>39.9213562011719</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>45.6749992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>40.4752082824707</v>
+        <v>40.4752044677734</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693519592285</v>
+        <v>38.7693557739258</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>40.6081352233887</v>
+        <v>40.6081314086914</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099754333496</v>
+        <v>40.0099716186523</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758255004883</v>
+        <v>40.2758178710938</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>48.7249984741211</v>
       </c>
       <c r="G332" t="n">
-        <v>43.1779823303223</v>
+        <v>43.1779861450195</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062911987305</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361434936523</v>
+        <v>42.3361396789551</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696800231934</v>
+        <v>42.2696762084961</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912109375</v>
+        <v>42.4912147521973</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.984748840332</v>
+        <v>40.9847450256348</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573539733887</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807441711426</v>
+        <v>38.6807403564453</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684494018555</v>
+        <v>42.6684455871582</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370658874512</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764587402344</v>
+        <v>47.2764549255371</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992317199707</v>
+        <v>47.0992279052734</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878433227539</v>
+        <v>47.1878471374512</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.8333778381348</v>
+        <v>46.833381652832</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419845581055</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>46.375</v>
       </c>
       <c r="G365" t="n">
-        <v>41.0955200195312</v>
+        <v>41.095516204834</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992080688477</v>
+        <v>39.8992042541504</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724502563477</v>
+        <v>44.9724540710449</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.0801467895508</v>
+        <v>46.080150604248</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118392944336</v>
+        <v>46.6118431091309</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>55.25</v>
       </c>
       <c r="G376" t="n">
-        <v>48.9601593017578</v>
+        <v>48.9601631164551</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780097961426</v>
+        <v>50.3780059814453</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.6881637573242</v>
+        <v>50.6881675720215</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589286804199</v>
+        <v>49.3589324951172</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>52.106014251709</v>
+        <v>52.1060104370117</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250991821289</v>
+        <v>53.1250953674316</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657150268555</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164810180664</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998649597168</v>
+        <v>54.0998687744141</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>52.7706298828125</v>
+        <v>52.7706336975098</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.157112121582</v>
+        <v>57.1571044921875</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115661621094</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546508789062</v>
+        <v>57.9546546936035</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038734436035</v>
+        <v>56.4038696289062</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.0875778198242</v>
+        <v>58.087574005127</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>53.4795532226562</v>
+        <v>53.4795570373535</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.523868560791</v>
+        <v>53.5238647460938</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115661621094</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164810180664</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734077453613</v>
+        <v>55.4734115600586</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>61.5</v>
       </c>
       <c r="G459" t="n">
-        <v>54.4986343383789</v>
+        <v>54.4986381530762</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1694030761719</v>
+        <v>53.1693992614746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>50.7767791748047</v>
+        <v>50.7767753601074</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515487670898</v>
+        <v>51.7515525817871</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743217468262</v>
+        <v>51.5743179321289</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792404174805</v>
+        <v>49.9792366027832</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703132629395</v>
+        <v>49.2703094482422</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>54.5</v>
       </c>
       <c r="G473" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>54.5</v>
       </c>
       <c r="G484" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9555969238281</v>
+        <v>50.9555931091309</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>54.5</v>
       </c>
       <c r="G494" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111389160156</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745452880859</v>
+        <v>51.6745491027832</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454635620117</v>
+        <v>51.045467376709</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644119262695</v>
+        <v>51.7644081115723</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502349853516</v>
+        <v>44.3502388000488</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603759765625</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621620178223</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G565" t="n">
-        <v>44.2154388427734</v>
+        <v>44.2154426574707</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G583" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454635620117</v>
+        <v>51.045467376709</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>53.3820533752441</v>
+        <v>53.3820495605469</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G591" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621620178223</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781211853027</v>
+        <v>56.0781173706055</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617866516113</v>
+        <v>53.5617904663086</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098243713379</v>
+        <v>54.9098205566406</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111389160156</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G641" t="n">
-        <v>53.3820533752441</v>
+        <v>53.3820495605469</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300834655762</v>
+        <v>54.7300872802734</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948081970215</v>
+        <v>51.4948043823242</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621620178223</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916038513184</v>
+        <v>39.9916076660156</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.116641998291</v>
+        <v>33.1166381835938</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>33.3413162231445</v>
+        <v>33.3413124084473</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>22.1077194213867</v>
+        <v>22.1077213287354</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024707794189</v>
+        <v>25.7024726867676</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910247802734</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967487335205</v>
+        <v>26.1967468261719</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910247802734</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910247802734</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857799530029</v>
+        <v>30.2857780456543</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.5562229156494</v>
+        <v>26.5562210083008</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5562229156494</v>
+        <v>26.5562210083008</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998435974121</v>
+        <v>27.4998455047607</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959075927734</v>
+        <v>30.1959114074707</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642063140869</v>
+        <v>31.3642024993896</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717124938965</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060371398926</v>
+        <v>30.1060390472412</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.4426307678223</v>
+        <v>32.442626953125</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501350402832</v>
+        <v>34.1501312255859</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373802185059</v>
+        <v>36.0373764038086</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298721313477</v>
+        <v>34.3298759460449</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.644416809082</v>
+        <v>34.6444129943848</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823135375977</v>
+        <v>36.0823173522949</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202102661133</v>
+        <v>37.5202140808105</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>40.5757522583008</v>
+        <v>40.5757484436035</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>46.7999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>42.0585861206055</v>
+        <v>42.0585899353027</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0250968933105</v>
+        <v>41.0251007080078</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409523010254</v>
+        <v>40.4409484863281</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889862060547</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>48.75</v>
       </c>
       <c r="G803" t="n">
-        <v>43.8110275268555</v>
+        <v>43.8110313415527</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>45.5</v>
       </c>
       <c r="G807" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069877624512</v>
+        <v>36.3069839477539</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898178100586</v>
+        <v>37.7898216247559</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625183105469</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G834" t="n">
-        <v>36.9360656738281</v>
+        <v>36.9360618591309</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612075805664</v>
+        <v>40.2612113952637</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105560302734</v>
+        <v>40.7105522155762</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625183105469</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149597167969</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453598022461</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.755485534668</v>
+        <v>40.7554893493652</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.901741027832</v>
+        <v>39.9017372131348</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1598968505859</v>
+        <v>41.1599006652832</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149597167969</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G857" t="n">
-        <v>40.5757522583008</v>
+        <v>40.5757484436035</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>45.5</v>
       </c>
       <c r="G860" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.755485534668</v>
+        <v>40.7554893493652</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>45.5</v>
       </c>
       <c r="G864" t="n">
-        <v>40.8902931213379</v>
+        <v>40.8902969360352</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889862060547</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801597595215</v>
+        <v>40.9801559448242</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471420288086</v>
+        <v>43.0471458435059</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.361686706543</v>
+        <v>43.3616828918457</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603759765625</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621620178223</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938652038574</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519195556641</v>
+        <v>42.9519233703613</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.090160369873</v>
+        <v>42.0901641845703</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1008" t="n">
-        <v>40.5027122497559</v>
+        <v>40.5027084350586</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.6366081237793</v>
+        <v>41.636604309082</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218856811523</v>
+        <v>44.2218818664551</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951057434082</v>
+        <v>43.9951019287109</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306854248047</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678314208984</v>
+        <v>48.1678352355957</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306854248047</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328598022461</v>
+        <v>47.5328559875488</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443206787109</v>
+        <v>46.4443168640137</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>45.0382881164551</v>
+        <v>45.0382919311523</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164497375488</v>
+        <v>46.7164535522461</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>46.081470489502</v>
+        <v>46.0814666748047</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>45.0382881164551</v>
+        <v>45.0382919311523</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.448657989502</v>
+        <v>44.4486618041992</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563705444336</v>
+        <v>49.2563743591309</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>46.081470489502</v>
+        <v>46.0814666748047</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>40.6387748718262</v>
+        <v>40.6387786865234</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595222473145</v>
+        <v>39.4595260620117</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895637512207</v>
+        <v>38.1895599365234</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578460693359</v>
+        <v>36.0578422546387</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228591918945</v>
+        <v>35.4228630065918</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>40.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>36.5113983154297</v>
+        <v>36.511402130127</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>42.25</v>
       </c>
       <c r="G1132" t="n">
-        <v>38.3256301879883</v>
+        <v>38.3256340026855</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>40.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>36.7381820678711</v>
+        <v>36.7381782531738</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611000061035</v>
+        <v>34.5611038208008</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>40.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>36.7381820678711</v>
+        <v>36.7381782531738</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092239379883</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742523193359</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605072021484</v>
+        <v>30.6605033874512</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861961364746</v>
+        <v>31.386194229126</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>29.2998313903809</v>
+        <v>29.2998294830322</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419322967529</v>
+        <v>30.8419284820557</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272079467773</v>
+        <v>33.4272041320801</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545883178711</v>
+        <v>37.5545845031738</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742523193359</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092239379883</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>40.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>36.5113983154297</v>
+        <v>36.511402130127</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -61108,6 +61108,32 @@
         <v>1.66600000858307</v>
       </c>
       <c r="H2336" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2337" t="n">
+        <v>816382</v>
+      </c>
+      <c r="C2337" t="n">
+        <v>1.68700003623962</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>1.62300002574921</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F2337" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2337" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="H2337" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -447,7 +447,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382392883301</v>
+        <v>47.7382507324219</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>54.25</v>
       </c>
       <c r="G7" t="n">
-        <v>47.4757118225098</v>
+        <v>47.4757041931152</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632209777832</v>
+        <v>47.5632171630859</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319534301758</v>
+        <v>47.4319496154785</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>54.25</v>
       </c>
       <c r="G18" t="n">
-        <v>47.4757118225098</v>
+        <v>47.4757041931152</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382392883301</v>
+        <v>47.7382507324219</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506340026855</v>
+        <v>46.9506378173828</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880874633789</v>
+        <v>46.6880912780762</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443328857422</v>
+        <v>46.6443367004395</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567199707031</v>
+        <v>45.8567237854004</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068717956543</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0882911682129</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068717956543</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194664001465</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135765075684</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.820384979248</v>
+        <v>53.8203887939453</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579536437988</v>
+        <v>54.2579498291016</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769416809082</v>
+        <v>55.8769378662109</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.258975982666</v>
+        <v>61.2589797973633</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.134105682373</v>
+        <v>62.1341018676758</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902397155762</v>
+        <v>61.390251159668</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339981079102</v>
+        <v>61.4340057373047</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964294433594</v>
+        <v>60.9964408874512</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462852478027</v>
+        <v>59.9462890625</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275047302246</v>
+        <v>59.7275009155273</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775527954102</v>
+        <v>60.0775566101074</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771415710449</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772453308105</v>
+        <v>57.9772491455078</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273933410645</v>
+        <v>59.0273971557617</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834465026855</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712669372559</v>
+        <v>59.7712593078613</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525825500488</v>
+        <v>60.2525787353516</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709518432617</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897323608398</v>
+        <v>57.8897361755371</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648582458496</v>
+        <v>58.7648620605469</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899436950684</v>
+        <v>59.2899322509766</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334831237793</v>
+        <v>57.9334869384766</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962371826172</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397918701172</v>
+        <v>58.2397804260254</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833427429199</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770454406738</v>
+        <v>56.5770416259766</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.2707443237305</v>
+        <v>56.2707481384277</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833427429199</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833427429199</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.189624786377</v>
+        <v>57.1896286010742</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520637512207</v>
+        <v>56.7520599365234</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643508911133</v>
+        <v>55.264347076416</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518524169922</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766304016113</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138916015625</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326721191406</v>
+        <v>52.3326683044434</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>59.5</v>
       </c>
       <c r="G159" t="n">
-        <v>52.070125579834</v>
+        <v>52.0701293945312</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883949279785</v>
+        <v>48.7883987426758</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265747070312</v>
+        <v>53.4265823364258</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G171" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>49.8385543823242</v>
+        <v>49.838550567627</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571273803711</v>
+        <v>48.6571311950684</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890098571777</v>
+        <v>52.989013671875</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766304016113</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017120361328</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017120361328</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G198" t="n">
-        <v>56.4020156860352</v>
+        <v>56.4020118713379</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519599914551</v>
+        <v>56.0519638061523</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518524169922</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391731262207</v>
+        <v>54.0391693115234</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141914367676</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390693664551</v>
+        <v>53.3390655517578</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.220588684082</v>
+        <v>55.2205924987793</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.662296295166</v>
+        <v>44.6623001098633</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041465759277</v>
+        <v>45.5041427612305</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>45.8143005371094</v>
+        <v>45.8143043518066</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.3865928649902</v>
+        <v>40.386589050293</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.9663047790527</v>
+        <v>46.96630859375</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536933898926</v>
+        <v>47.4536895751953</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.295539855957</v>
+        <v>48.2955360412598</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755447387695</v>
+        <v>51.1755485534668</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475364685059</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361633300781</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.1817016601562</v>
+        <v>49.181697845459</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410781860352</v>
+        <v>47.9410820007324</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158477783203</v>
+        <v>48.9158554077148</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844718933105</v>
+        <v>51.8844795227051</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.3398399353027</v>
+        <v>48.3398513793945</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.8524627685547</v>
+        <v>47.8524589538574</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>47.8967742919922</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>47.8967742919922</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004623413086</v>
+        <v>46.7004585266113</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>50</v>
       </c>
       <c r="G265" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>50</v>
       </c>
       <c r="G266" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.301685333252</v>
+        <v>46.3016891479492</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927619934082</v>
+        <v>45.5927658081055</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.3712196350098</v>
+        <v>45.371223449707</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346084594727</v>
+        <v>46.4346122741699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699966430664</v>
+        <v>45.7699928283691</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586120605469</v>
+        <v>45.8586082458496</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>50</v>
       </c>
       <c r="G275" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761421203613</v>
+        <v>43.7761459350586</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324478149414</v>
+        <v>43.5324440002441</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.3109092712402</v>
+        <v>43.310905456543</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222938537598</v>
+        <v>43.222297668457</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G291" t="n">
-        <v>42.2253684997559</v>
+        <v>42.2253646850586</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450592041016</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539863586426</v>
+        <v>43.7539825439453</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102920532227</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349014282227</v>
+        <v>42.7349052429199</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.8044471740723</v>
+        <v>41.804443359375</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170547485352</v>
+        <v>41.3170585632324</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853584289551</v>
+        <v>40.7853622436523</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638198852539</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.946590423584</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112098693848</v>
+        <v>39.6112060546875</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>45.6749992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>40.4752082824707</v>
+        <v>40.4752044677734</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4309005737305</v>
+        <v>40.4309043884277</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099716186523</v>
+        <v>40.0099754333496</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758255004883</v>
+        <v>40.275821685791</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361396789551</v>
+        <v>42.3361358642578</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555099487305</v>
+        <v>39.6555137634277</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.9908981323242</v>
+        <v>38.990894317627</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096786499023</v>
+        <v>43.7096824645996</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610694885254</v>
+        <v>45.0610656738281</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878433227539</v>
+        <v>47.1878471374512</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419921875</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>46.375</v>
       </c>
       <c r="G365" t="n">
-        <v>41.0955200195312</v>
+        <v>41.095516204834</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973640441895</v>
+        <v>40.4973602294922</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992118835449</v>
+        <v>39.8992080688477</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>45.25</v>
       </c>
       <c r="G368" t="n">
-        <v>40.0985870361328</v>
+        <v>40.0985908508301</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321273803711</v>
+        <v>40.0321311950684</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625930786133</v>
+        <v>40.962589263916</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>50</v>
       </c>
       <c r="G372" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.080150604248</v>
+        <v>46.0801467895508</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>55.25</v>
       </c>
       <c r="G376" t="n">
-        <v>48.9601631164551</v>
+        <v>48.9601593017578</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109367370605</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958602905273</v>
+        <v>51.7958564758301</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.6881637573242</v>
+        <v>50.6881675720215</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121673583984</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589286804199</v>
+        <v>49.3589324951172</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>52.1060104370117</v>
+        <v>52.106014251709</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.390941619873</v>
+        <v>53.3909378051758</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657073974609</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961769104004</v>
+        <v>55.2961807250977</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.777416229248</v>
+        <v>57.7774124145508</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001815795898</v>
+        <v>57.6001853942871</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.1571044921875</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.7835655212402</v>
+        <v>55.783561706543</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115737915039</v>
+        <v>57.5115776062012</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546508789062</v>
+        <v>57.9546546936035</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863433837891</v>
+        <v>58.4863471984863</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.0875778198242</v>
+        <v>58.087574005127</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6887969970703</v>
+        <v>57.6888008117676</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>55.2075576782227</v>
+        <v>55.2075614929199</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>57.11279296875</v>
+        <v>57.1128005981445</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>52.9921684265137</v>
+        <v>52.9921646118164</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0173988342285</v>
+        <v>52.0173950195312</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.5238647460938</v>
+        <v>53.523868560791</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.245719909668</v>
+        <v>57.2457237243652</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709541320801</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026466369629</v>
+        <v>56.8026428222656</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>55.2075576782227</v>
+        <v>55.2075614929199</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115737915039</v>
+        <v>57.5115776062012</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709541320801</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506385803223</v>
+        <v>55.6506423950195</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>61.5</v>
       </c>
       <c r="G459" t="n">
-        <v>54.4986343383789</v>
+        <v>54.4986381530762</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1694030761719</v>
+        <v>53.1693992614746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>50.776782989502</v>
+        <v>50.7767791748047</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540061950684</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743217468262</v>
+        <v>51.5743179321289</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540061950684</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450866699219</v>
+        <v>50.2450828552246</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109367370605</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569076538086</v>
+        <v>50.0569114685059</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>54.5</v>
       </c>
       <c r="G473" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>53.5</v>
       </c>
       <c r="G482" t="n">
-        <v>48.0797996520996</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>54.5</v>
       </c>
       <c r="G484" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075630187988</v>
+        <v>49.6075668334961</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>54.5</v>
       </c>
       <c r="G494" t="n">
-        <v>48.9784812927246</v>
+        <v>48.9784774780273</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653663635254</v>
+        <v>57.9653587341309</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477210998535</v>
+        <v>56.3477249145508</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>61</v>
       </c>
       <c r="G507" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199577331543</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G508" t="n">
-        <v>55.628776550293</v>
+        <v>55.6287727355957</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186393737793</v>
+        <v>55.7186431884766</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>61</v>
       </c>
       <c r="G513" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199577331543</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415237426758</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>53.5</v>
       </c>
       <c r="G526" t="n">
-        <v>48.0797996520996</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330726623535</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>53.5</v>
       </c>
       <c r="G531" t="n">
-        <v>48.0797996520996</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502426147461</v>
+        <v>44.3502388000488</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>50</v>
       </c>
       <c r="G540" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>49.75</v>
       </c>
       <c r="G542" t="n">
-        <v>44.709716796875</v>
+        <v>44.7097129821777</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>50</v>
       </c>
       <c r="G543" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>53.5</v>
       </c>
       <c r="G550" t="n">
-        <v>48.0797996520996</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330726623535</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>45.2039985656738</v>
+        <v>45.2039947509766</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>53.5</v>
       </c>
       <c r="G571" t="n">
-        <v>48.0797996520996</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190071105957</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>53.3820533752441</v>
+        <v>53.3820571899414</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.2366409301758</v>
+        <v>50.2366485595703</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.540584564209</v>
+        <v>47.5405807495117</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330726623535</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203178405762</v>
+        <v>47.7203216552734</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.976806640625</v>
+        <v>56.9768028259277</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>61</v>
       </c>
       <c r="G625" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199577331543</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>60.5</v>
       </c>
       <c r="G627" t="n">
-        <v>54.3706130981445</v>
+        <v>54.3706092834473</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617904663086</v>
+        <v>53.5617866516113</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516571044922</v>
+        <v>53.6516647338867</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>61</v>
       </c>
       <c r="G635" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199577331543</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>61</v>
       </c>
       <c r="G638" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199577331543</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G641" t="n">
-        <v>53.3820533752441</v>
+        <v>53.3820571899414</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G642" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225830078125</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578506469727</v>
+        <v>56.2578544616699</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415237426758</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>28.2637310028076</v>
+        <v>28.263729095459</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>27.6795825958252</v>
+        <v>27.6795806884766</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>26.75</v>
       </c>
       <c r="G679" t="n">
-        <v>24.0398998260498</v>
+        <v>24.0398960113525</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7368011474609</v>
+        <v>22.7367992401123</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139148712158</v>
+        <v>24.7139129638672</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32</v>
       </c>
       <c r="G684" t="n">
-        <v>28.7580070495605</v>
+        <v>28.7580089569092</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024688720703</v>
+        <v>25.7024707794189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.5905532836914</v>
+        <v>23.5905513763428</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.4557514190674</v>
+        <v>23.4557495117188</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>30.5</v>
       </c>
       <c r="G694" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099788665771</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910285949707</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993721008301</v>
+        <v>24.3993740081787</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31</v>
       </c>
       <c r="G697" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928108215332</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>31</v>
       </c>
       <c r="G699" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258285522461</v>
+        <v>26.8258323669434</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201084136963</v>
+        <v>27.3201065063477</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910285949707</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>26.6910266876221</v>
+        <v>26.6910285949707</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857818603516</v>
+        <v>30.2857780456543</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130737304688</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.5562210083008</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>30.5</v>
       </c>
       <c r="G712" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099788665771</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>27.7694530487061</v>
+        <v>27.7694511413574</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>26.6011581420898</v>
+        <v>26.6011562347412</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>31</v>
       </c>
       <c r="G718" t="n">
-        <v>27.8593196868896</v>
+        <v>27.8593215942383</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30.5</v>
       </c>
       <c r="G720" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099788665771</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5562210083008</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928108215332</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699207305908</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959056854248</v>
+        <v>30.1959075927734</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642063140869</v>
+        <v>31.3642044067383</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990043640137</v>
+        <v>31.499002456665</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>36.5</v>
       </c>
       <c r="G732" t="n">
-        <v>32.8021087646484</v>
+        <v>32.8021049499512</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620468139648</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.016170501709</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699207305908</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501350402832</v>
+        <v>34.1501312255859</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>40.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>36.4417877197266</v>
+        <v>36.4417915344238</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373764038086</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298721313477</v>
+        <v>34.3298683166504</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G748" t="n">
-        <v>35.3633613586426</v>
+        <v>35.3633575439453</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643043518066</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>41.2947006225586</v>
+        <v>41.2947044372559</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224754333496</v>
+        <v>42.8224716186523</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.833911895752</v>
+        <v>41.8339195251465</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>46.7999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>42.0585899353027</v>
+        <v>42.0585861206055</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409484863281</v>
+        <v>40.4409523010254</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.507926940918</v>
+        <v>42.5079307556152</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991157531738</v>
+        <v>41.6991119384766</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>43.2718162536621</v>
+        <v>43.2718200683594</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G790" t="n">
-        <v>43.2718162536621</v>
+        <v>43.2718200683594</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.957275390625</v>
+        <v>42.9572715759277</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479850769043</v>
+        <v>39.047981262207</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>43</v>
       </c>
       <c r="G809" t="n">
-        <v>38.6435699462891</v>
+        <v>38.6435737609863</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246253967285</v>
+        <v>37.9246215820312</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854103088379</v>
+        <v>37.3854141235352</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594215393066</v>
+        <v>38.0594253540039</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347587585449</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651473999023</v>
+        <v>37.5651435852051</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898178100586</v>
+        <v>37.7898216247559</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986442565918</v>
+        <v>38.5986404418945</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422630310059</v>
+        <v>39.5422592163086</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656227111816</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>43</v>
       </c>
       <c r="G829" t="n">
-        <v>38.6435699462891</v>
+        <v>38.6435737609863</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144958496094</v>
+        <v>38.0144920349121</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638366699219</v>
+        <v>38.4638328552246</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.430347442627</v>
+        <v>37.4303436279297</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620468139648</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448883056641</v>
+        <v>37.7448844909668</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612152099609</v>
+        <v>40.2612075805664</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643043518066</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.7554931640625</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017372131348</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744453430176</v>
+        <v>41.4744415283203</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.530818939209</v>
+        <v>40.5308151245117</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.8004264831543</v>
+        <v>40.8004302978516</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.7554931640625</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960151672363</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801597595215</v>
+        <v>40.9801559448242</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471458435059</v>
+        <v>43.0471420288086</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>42.7775382995605</v>
+        <v>42.7775344848633</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G883" t="n">
-        <v>42.1035194396973</v>
+        <v>42.1035232543945</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>50</v>
       </c>
       <c r="G897" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190071105957</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>50</v>
       </c>
       <c r="G912" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>46.5520286560059</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>50</v>
       </c>
       <c r="G921" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.540584564209</v>
+        <v>47.5405807495117</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>46.5520286560059</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G969" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>46.5520286560059</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G972" t="n">
-        <v>46.5520286560059</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>49.75</v>
       </c>
       <c r="G989" t="n">
-        <v>44.709716796875</v>
+        <v>44.7097129821777</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>50</v>
       </c>
       <c r="G994" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519233703613</v>
+        <v>42.9519157409668</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087371826172</v>
+        <v>41.9087409973145</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1008" t="n">
-        <v>40.5027084350586</v>
+        <v>40.5027122497559</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316589355469</v>
+        <v>39.7316627502441</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.636604309082</v>
+        <v>41.6366081237793</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1022" t="n">
-        <v>42.9972801208496</v>
+        <v>42.9972763061523</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1023" t="n">
-        <v>41.8180236816406</v>
+        <v>41.8180274963379</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>43.8590354919434</v>
+        <v>43.8590393066406</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1031" t="n">
-        <v>43.6322555541992</v>
+        <v>43.6322593688965</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218818664551</v>
+        <v>44.2218856811523</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1040" t="n">
-        <v>45.7186241149902</v>
+        <v>45.7186279296875</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306854248047</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306854248047</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443168640137</v>
+        <v>46.4443206787109</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>50</v>
       </c>
       <c r="G1057" t="n">
-        <v>45.3557777404785</v>
+        <v>45.3557739257812</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071594238281</v>
+        <v>46.8071632385254</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>46.0814666748047</v>
+        <v>46.081470489502</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1068" t="n">
-        <v>44.6300849914551</v>
+        <v>44.6300811767578</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125915527344</v>
+        <v>44.3125953674316</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836448669434</v>
+        <v>45.0836410522461</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>44.0404586791992</v>
+        <v>44.0404624938965</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>44.6300849914551</v>
+        <v>44.6300811767578</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563743591309</v>
+        <v>49.2563705444336</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>46.0814666748047</v>
+        <v>46.081470489502</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>40.6387786865234</v>
+        <v>40.6387748718262</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9174270629883</v>
+        <v>37.9174308776855</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452941894531</v>
+        <v>37.6452980041504</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010246276855</v>
+        <v>37.1010284423828</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.1485557556152</v>
+        <v>36.148551940918</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>40</v>
       </c>
       <c r="G1110" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.2867965698242</v>
+        <v>35.2868003845215</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>39.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>35.6042861938477</v>
+        <v>35.6042823791504</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>37.9174270629883</v>
+        <v>37.9174308776855</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884803771973</v>
+        <v>38.6884765625</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>42.25</v>
       </c>
       <c r="G1132" t="n">
-        <v>38.3256340026855</v>
+        <v>38.3256301879883</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>37.4638710021973</v>
+        <v>37.4638748168945</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299789428711</v>
+        <v>36.3299751281738</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>40.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>39.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>35.6042861938477</v>
+        <v>35.6042823791504</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146560668945</v>
+        <v>35.0146598815918</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>40.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092239379883</v>
+        <v>37.5092277526855</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742523193359</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.8829383850098</v>
+        <v>32.882942199707</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605033874512</v>
+        <v>30.6605052947998</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.386194229126</v>
+        <v>31.3861980438232</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>29.2998294830322</v>
+        <v>29.2998313903809</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691951751709</v>
+        <v>26.6691970825195</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577362060547</v>
+        <v>27.7577381134033</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233516693115</v>
+        <v>31.0233554840088</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419303894043</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561584472656</v>
+        <v>32.6561622619629</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742523193359</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092239379883</v>
+        <v>37.5092277526855</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>40</v>
       </c>
       <c r="G1216" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475547790527</v>
+        <v>34.2475509643555</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377815246582</v>
+        <v>33.7377777099609</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280044555664</v>
+        <v>33.2280006408691</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719566345215</v>
+        <v>34.5719528198242</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792045593262</v>
+        <v>32.5792007446289</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546661376953</v>
+        <v>28.4546642303467</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692928314209</v>
+        <v>28.2692909240723</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911655426025</v>
+        <v>26.0911674499512</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131084442139</v>
+        <v>25.8131065368652</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887710571289</v>
+        <v>27.3887729644775</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473499298096</v>
+        <v>28.5473518371582</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107139587402</v>
+        <v>27.1107158660889</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545295715332</v>
+        <v>24.6545314788818</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984115600586</v>
+        <v>24.0984134674072</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033332824707</v>
+        <v>25.3033313751221</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.720422744751</v>
+        <v>25.7204208374023</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350494384766</v>
+        <v>25.5350475311279</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301959991455</v>
+        <v>26.2301940917969</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.5741443634033</v>
+        <v>27.574146270752</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352523803711</v>
+        <v>31.2352504730225</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377113342285</v>
+        <v>31.8377075195312</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571914672852</v>
+        <v>30.9571933746338</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.9303970336914</v>
+        <v>31.93039894104</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596504211426</v>
+        <v>31.5596523284912</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986808776855</v>
+        <v>31.6986827850342</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182312011719</v>
+        <v>32.7182273864746</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914367675781</v>
+        <v>33.6914329528809</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.3597869873047</v>
+        <v>35.359790802002</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988136291504</v>
+        <v>35.4988174438477</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744117736816</v>
+        <v>35.1744155883789</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012138366699</v>
+        <v>34.2012100219727</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.5183639526367</v>
+        <v>36.518367767334</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085868835449</v>
+        <v>36.0085906982422</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059288024902</v>
+        <v>29.7059268951416</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2033996582031</v>
+        <v>27.2034015655518</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156337738037</v>
+        <v>28.3156356811523</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -61186,6 +61186,32 @@
         <v>1.67999994754791</v>
       </c>
       <c r="H2339" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2340" t="n">
+        <v>680451</v>
+      </c>
+      <c r="C2340" t="n">
+        <v>1.74399995803833</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>1.67900002002716</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>1.68799996376038</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="G2340" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="H2340" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -54246,7 +54246,7 @@
         <v>1650741</v>
       </c>
       <c r="C2343" t="n">
-        <v>1.82099997997284</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="D2343" t="n">
         <v>1.66199994087219</v>
@@ -54254,8 +54254,31 @@
       <c r="E2343" t="n">
         <v>1.67200005054474</v>
       </c>
-      <c r="F2343"/>
+      <c r="F2343" t="n">
+        <v>1.83000004291534</v>
+      </c>
       <c r="G2343" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2344" t="n">
+        <v>1515337</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>1.77199995517731</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="F2344"/>
+      <c r="G2344" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -54277,8 +54277,31 @@
       <c r="E2344" t="n">
         <v>1.83000004291534</v>
       </c>
-      <c r="F2344"/>
+      <c r="F2344" t="n">
+        <v>1.82000005245209</v>
+      </c>
       <c r="G2344" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2345" t="n">
+        <v>895468</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>1.84700000286102</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>1.77300000190735</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>1.82400000095367</v>
+      </c>
+      <c r="F2345"/>
+      <c r="G2345" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -54300,8 +54300,31 @@
       <c r="E2345" t="n">
         <v>1.82400000095367</v>
       </c>
-      <c r="F2345"/>
+      <c r="F2345" t="n">
+        <v>1.82000005245209</v>
+      </c>
       <c r="G2345" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2346" t="n">
+        <v>1749550</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>1.89499998092651</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2346"/>
+      <c r="G2346" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -54323,8 +54323,31 @@
       <c r="E2346" t="n">
         <v>1.79999995231628</v>
       </c>
-      <c r="F2346"/>
+      <c r="F2346" t="n">
+        <v>1.83000004291534</v>
+      </c>
       <c r="G2346" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2347" t="n">
+        <v>2158004</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>1.86600005626678</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>1.82599997520447</v>
+      </c>
+      <c r="F2347"/>
+      <c r="G2347" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -54353,6 +54353,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2348">
+      <c r="A2348" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2348" t="n">
+        <v>859723</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G2348" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503227233887</v>
+        <v>44.8503189086914</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631210327148</v>
+        <v>46.8631172180176</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319496154785</v>
+        <v>47.431957244873</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506378173828</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.469310760498</v>
+        <v>46.4693069458008</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880874633789</v>
+        <v>46.6880912780762</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692031860352</v>
+        <v>45.7692108154297</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816902160645</v>
+        <v>45.6816940307617</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567276000977</v>
+        <v>45.8567161560059</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0882987976074</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194625854492</v>
+        <v>47.5194664001465</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445365905762</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.8203811645508</v>
+        <v>53.820384979248</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769416809082</v>
+        <v>55.8769340515137</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336944580078</v>
+        <v>59.3336906433105</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589797973633</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403991699219</v>
+        <v>62.4403953552246</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.390251159668</v>
+        <v>61.3902473449707</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964408874512</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462776184082</v>
+        <v>59.9462890625</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399917602539</v>
+        <v>59.6399879455566</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275123596191</v>
+        <v>59.7275009155273</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276084899902</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026344299316</v>
+        <v>60.6026268005371</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214111328125</v>
+        <v>60.8214149475098</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273010253906</v>
+        <v>58.3272933959961</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711555480957</v>
+        <v>59.071159362793</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834426879883</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646545410156</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276084899902</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646545410156</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.7456703186035</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709480285645</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897361755371</v>
+        <v>57.8897323608398</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899398803711</v>
+        <v>59.2899360656738</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334869384766</v>
+        <v>57.9334945678711</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962295532227</v>
+        <v>59.5962257385254</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.9900436401367</v>
+        <v>59.990047454834</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397918701172</v>
+        <v>58.2397842407227</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770454406738</v>
+        <v>56.5770416259766</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146064758301</v>
+        <v>57.0146102905273</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.6207962036133</v>
+        <v>56.620792388916</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.189624786377</v>
+        <v>57.1896286010742</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.752067565918</v>
+        <v>56.7520637512207</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831314086914</v>
+        <v>55.4831275939941</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643508911133</v>
+        <v>55.264347076416</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394729614258</v>
+        <v>56.139476776123</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078979492188</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078979492188</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326683044434</v>
+        <v>52.3326644897461</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.3572311401367</v>
+        <v>49.357234954834</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883987426758</v>
+        <v>48.788402557373</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265747070312</v>
+        <v>53.4265785217285</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889137268066</v>
+        <v>52.2889099121094</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571273803711</v>
+        <v>48.6571311950684</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015007019043</v>
+        <v>52.901496887207</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077980041504</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077980041504</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519676208496</v>
+        <v>56.0519638061523</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391693115234</v>
+        <v>54.0391654968262</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078979492188</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.220588684082</v>
+        <v>55.2205963134766</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823127746582</v>
+        <v>49.8823089599609</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.662296295166</v>
+        <v>44.6623039245605</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041465759277</v>
+        <v>45.5041427612305</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358467102051</v>
+        <v>46.0358390808105</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.386589050293</v>
+        <v>40.3865928649902</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G224" t="n">
-        <v>44.839527130127</v>
+        <v>44.8395309448242</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281463623047</v>
+        <v>44.9281425476074</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272361755371</v>
+        <v>48.8272323608398</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475402832031</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410781860352</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158477783203</v>
+        <v>48.915843963623</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983177185059</v>
+        <v>50.9983139038086</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844757080078</v>
+        <v>51.8844718933105</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715400695801</v>
+        <v>48.8715438842773</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.852466583252</v>
+        <v>47.8524627685547</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004585266113</v>
+        <v>46.7004547119141</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192192077637</v>
+        <v>44.2192230224609</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939926147461</v>
+        <v>45.1939888000488</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346160888672</v>
+        <v>46.4346122741699</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232238769531</v>
+        <v>46.5232276916504</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699928283691</v>
+        <v>45.7700004577637</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989074707031</v>
+        <v>43.5989112854004</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570610046387</v>
+        <v>42.7570571899414</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918281555176</v>
+        <v>42.2918243408203</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324516296387</v>
+        <v>43.5324478149414</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.310905456543</v>
+        <v>43.3109092712402</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.2001419067383</v>
+        <v>43.200138092041</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>48.3250007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>42.8235282897949</v>
+        <v>42.8235244750977</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552093505859</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552093505859</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349052429199</v>
+        <v>42.7349090576172</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638275146484</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573539733887</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.946590423584</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782791137695</v>
+        <v>39.4782829284668</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213638305664</v>
+        <v>39.9213562011719</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4309005737305</v>
+        <v>40.4308967590332</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758255004883</v>
+        <v>40.275821685791</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069007873535</v>
+        <v>41.006908416748</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462898254395</v>
+        <v>42.6462860107422</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696723937988</v>
+        <v>42.2696800231934</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912109375</v>
+        <v>42.4912147521973</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069007873535</v>
+        <v>41.006908416748</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.984748840332</v>
+        <v>40.9847450256348</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555137634277</v>
+        <v>39.6555099487305</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573539733887</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.9908981323242</v>
+        <v>38.990894317627</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684494018555</v>
+        <v>42.6684455871582</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610656738281</v>
+        <v>45.0610694885254</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764587402344</v>
+        <v>47.2764625549316</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459930419922</v>
+        <v>46.3459968566895</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.8333854675293</v>
+        <v>46.833381652832</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>45.9915313720703</v>
+        <v>45.9915351867676</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419921875</v>
+        <v>44.0419883728027</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552093505859</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992080688477</v>
+        <v>39.8992118835449</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321311950684</v>
+        <v>40.0321273803711</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.080150604248</v>
+        <v>46.0801467895508</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118431091309</v>
+        <v>46.6118392944336</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.5109329223633</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780059814453</v>
+        <v>50.3780097961426</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893905639648</v>
+        <v>50.2893943786621</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.3527870178223</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958564758301</v>
+        <v>51.7958602905273</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.3527870178223</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.688159942627</v>
+        <v>50.6881637573242</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121635437012</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463172912598</v>
+        <v>49.8463134765625</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>59</v>
       </c>
       <c r="G392" t="n">
-        <v>52.2832412719727</v>
+        <v>52.2832450866699</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>52.1060104370117</v>
+        <v>52.106014251709</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466377258301</v>
+        <v>53.3466300964355</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961769104004</v>
+        <v>55.2961807250977</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164924621582</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998611450195</v>
+        <v>54.0998649597168</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.777416229248</v>
+        <v>57.7774124145508</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001853942871</v>
+        <v>57.6001892089844</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546508789062</v>
+        <v>57.954647064209</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.0875701904297</v>
+        <v>58.0875778198242</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6887969970703</v>
+        <v>57.6888008117676</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>57.11279296875</v>
+        <v>57.1127967834473</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>53.4795532226562</v>
+        <v>53.4795570373535</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0173988342285</v>
+        <v>52.0174026489258</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G443" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392616271973</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164924621582</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392616271973</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734115600586</v>
+        <v>55.4734077453613</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506423950195</v>
+        <v>55.6506385803223</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.7010955810547</v>
+        <v>53.701099395752</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149375915527</v>
+        <v>52.8149337768555</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515487670898</v>
+        <v>51.7515525817871</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540138244629</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540138244629</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450904846191</v>
+        <v>50.2450828552246</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703094482422</v>
+        <v>49.2703132629395</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.5109329223633</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>54.5</v>
       </c>
       <c r="G473" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987403869629</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>54.5</v>
       </c>
       <c r="G484" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G489" t="n">
-        <v>49.9670372009277</v>
+        <v>49.967041015625</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075630187988</v>
+        <v>49.6075668334961</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>54.5</v>
       </c>
       <c r="G494" t="n">
-        <v>48.9784774780273</v>
+        <v>48.9784812927246</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.6974334716797</v>
+        <v>49.6974296569824</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666732788086</v>
+        <v>57.0666770935059</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186431884766</v>
+        <v>55.7186393737793</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745491027832</v>
+        <v>51.6745452880859</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.6974334716797</v>
+        <v>49.6974296569824</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>50</v>
       </c>
       <c r="G540" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>50</v>
       </c>
       <c r="G543" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G565" t="n">
-        <v>44.2154350280762</v>
+        <v>44.2154426574707</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987403869629</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379592895508</v>
+        <v>49.337963104248</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G583" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>53.3820495605469</v>
+        <v>53.3820533752441</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G591" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.5961227416992</v>
+        <v>50.596118927002</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987403869629</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.976806640625</v>
+        <v>56.9768028259277</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>60.5</v>
       </c>
       <c r="G627" t="n">
-        <v>54.3706092834473</v>
+        <v>54.37060546875</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.101001739502</v>
+        <v>54.1010055541992</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516571044922</v>
+        <v>53.6516609191895</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G641" t="n">
-        <v>53.3820495605469</v>
+        <v>53.3820533752441</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>52.8428421020508</v>
+        <v>52.8428382873535</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124496459961</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578506469727</v>
+        <v>56.2578544616699</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379592895508</v>
+        <v>49.337963104248</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948043823242</v>
+        <v>51.4948081970215</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.116641998291</v>
+        <v>33.1166381835938</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>28.263729095459</v>
+        <v>28.2637310028076</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7368011474609</v>
+        <v>22.7367992401123</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>22.1077175140381</v>
+        <v>22.1077213287354</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861438751221</v>
+        <v>23.1861419677734</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139129638672</v>
+        <v>24.7139148712158</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024688720703</v>
+        <v>25.7024707794189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>24.9835186004639</v>
+        <v>24.9835205078125</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879318237305</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328632354736</v>
+        <v>25.4328651428223</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879318237305</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>26.6910247802734</v>
+        <v>26.6910266876221</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993701934814</v>
+        <v>24.3993740081787</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31</v>
       </c>
       <c r="G697" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>31</v>
       </c>
       <c r="G699" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258285522461</v>
+        <v>26.8258304595947</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967487335205</v>
+        <v>26.1967449188232</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201084136963</v>
+        <v>27.3201103210449</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>26.6910247802734</v>
+        <v>26.6910266876221</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>26.6910247802734</v>
+        <v>26.6910266876221</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130737304688</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.050500869751</v>
+        <v>27.0505027770996</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.556224822998</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663562774658</v>
+        <v>26.4663543701172</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>31</v>
       </c>
       <c r="G718" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.556224822998</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998474121094</v>
+        <v>27.4998435974121</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G725" t="n">
-        <v>29.0725479125977</v>
+        <v>29.072546005249</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566982269287</v>
+        <v>29.6566963195801</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959075927734</v>
+        <v>30.1959095001221</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642024993896</v>
+        <v>31.3642082214355</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717086791992</v>
+        <v>33.071704864502</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699245452881</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501350402832</v>
+        <v>34.1501312255859</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373764038086</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>41</v>
       </c>
       <c r="G744" t="n">
-        <v>36.8461990356445</v>
+        <v>36.8461952209473</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G750" t="n">
-        <v>36.4867210388184</v>
+        <v>36.4867248535156</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2840995788574</v>
+        <v>38.2840957641602</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202140808105</v>
+        <v>37.5202102661133</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>41.2947044372559</v>
+        <v>41.2947006225586</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.833911895752</v>
+        <v>41.8339157104492</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409484863281</v>
+        <v>40.4409523010254</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991157531738</v>
+        <v>41.6991119384766</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.047981262207</v>
+        <v>39.0479850769043</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246253967285</v>
+        <v>37.9246215820312</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854064941406</v>
+        <v>37.3854103088379</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100769042969</v>
+        <v>37.6100807189941</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069877624512</v>
+        <v>36.3069839477539</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347549438477</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651512145996</v>
+        <v>37.5651473999023</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898178100586</v>
+        <v>37.7898254394531</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118629455566</v>
+        <v>39.8118705749512</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.4523963928223</v>
+        <v>39.452392578125</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422630310059</v>
+        <v>39.5422554016113</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656227111816</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>39.721996307373</v>
+        <v>39.7220001220703</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144920349121</v>
+        <v>38.0144958496094</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.4303436279297</v>
+        <v>37.430347442627</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329689025879</v>
+        <v>35.6329727172852</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448883056641</v>
+        <v>37.7448844909668</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105522155762</v>
+        <v>40.7105560302734</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453636169434</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960151672363</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528602600098</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.361686706543</v>
+        <v>43.3616828918457</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528602600098</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281898498535</v>
+        <v>42.3281936645508</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>50</v>
       </c>
       <c r="G897" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987403869629</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>50</v>
       </c>
       <c r="G912" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>50</v>
       </c>
       <c r="G921" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G939" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987403869629</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.192554473877</v>
+        <v>46.1925506591797</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>50</v>
       </c>
       <c r="G994" t="n">
-        <v>44.934383392334</v>
+        <v>44.9343872070312</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519157409668</v>
+        <v>42.9519195556641</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765289306641</v>
+        <v>44.1765251159668</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863059997559</v>
+        <v>39.6863021850586</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.6366081237793</v>
+        <v>41.636604309082</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797866821289</v>
+        <v>42.6797828674316</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1022" t="n">
-        <v>42.9972763061523</v>
+        <v>42.9972801208496</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1023" t="n">
-        <v>41.8180274963379</v>
+        <v>41.8180236816406</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043922424316</v>
+        <v>43.9043960571289</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>43.8590393066406</v>
+        <v>43.8590354919434</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1031" t="n">
-        <v>43.6322593688965</v>
+        <v>43.6322555541992</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218856811523</v>
+        <v>44.2218818664551</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951057434082</v>
+        <v>43.9951019287109</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1040" t="n">
-        <v>45.7186279296875</v>
+        <v>45.7186241149902</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328559875488</v>
+        <v>47.5328521728516</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443206787109</v>
+        <v>46.4443168640137</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>50</v>
       </c>
       <c r="G1057" t="n">
-        <v>45.3557739257812</v>
+        <v>45.3557777404785</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1068" t="n">
-        <v>44.6300811767578</v>
+        <v>44.6300849914551</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093338012695</v>
+        <v>45.8093376159668</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836410522461</v>
+        <v>45.0836448669434</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>44.0404624938965</v>
+        <v>44.0404586791992</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>44.6300811767578</v>
+        <v>44.6300849914551</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.8978729248047</v>
+        <v>46.897876739502</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563705444336</v>
+        <v>49.2563743591309</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595260620117</v>
+        <v>39.459529876709</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895599365234</v>
+        <v>38.1895637512207</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452980041504</v>
+        <v>37.6452941894531</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.148551940918</v>
+        <v>36.1485557556152</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578422546387</v>
+        <v>36.0578460693359</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>40</v>
       </c>
       <c r="G1110" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.2868003845215</v>
+        <v>35.2867965698242</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>39.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>40.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463851928711</v>
+        <v>37.1463813781738</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884765625</v>
+        <v>38.6884803771973</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>37.4638748168945</v>
+        <v>37.4638710021973</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753318786621</v>
+        <v>36.3753280639648</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688163757324</v>
+        <v>39.3688125610352</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>39.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146598815918</v>
+        <v>35.0146560668945</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250335693359</v>
+        <v>34.4250373840332</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611038208008</v>
+        <v>34.5611000061035</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556678771973</v>
+        <v>37.0556716918945</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.1031951904297</v>
+        <v>36.103199005127</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.882942199707</v>
+        <v>32.8829383850098</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605052947998</v>
+        <v>30.6605033874512</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861980438232</v>
+        <v>31.3861961364746</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691970825195</v>
+        <v>26.6691951751709</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577381134033</v>
+        <v>27.7577362060547</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233554840088</v>
+        <v>31.0233535766602</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419303894043</v>
+        <v>30.8419284820557</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272041320801</v>
+        <v>33.4272079467773</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600204467773</v>
+        <v>35.0600166320801</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545883178711</v>
+        <v>37.5545845031738</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>40.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>40</v>
       </c>
       <c r="G1216" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -61472,6 +61472,32 @@
         <v>1.53999996185303</v>
       </c>
       <c r="H2350" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2351" t="n">
+        <v>809066</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>1.57799994945526</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>1.52799999713898</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2351" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503189086914</v>
+        <v>44.8503227233887</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318496704102</v>
+        <v>46.7318458557129</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631172180176</v>
+        <v>46.8631210327148</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132766723633</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632171630859</v>
+        <v>47.5632209777832</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.431957244873</v>
+        <v>47.4319534301758</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0818977355957</v>
+        <v>47.081901550293</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.4693069458008</v>
+        <v>46.469310760498</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131652832031</v>
+        <v>47.2131729125977</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880912780762</v>
+        <v>46.6880874633789</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443328857422</v>
+        <v>46.6443367004395</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.119255065918</v>
+        <v>46.1192626953125</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254486083984</v>
+        <v>45.7254524230957</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692108154297</v>
+        <v>45.7692070007324</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.5130653381348</v>
+        <v>46.513069152832</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816940307617</v>
+        <v>45.681697845459</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567161560059</v>
+        <v>45.8567199707031</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.994384765625</v>
+        <v>46.9943885803223</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882987976074</v>
+        <v>48.0882949829102</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132766723633</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194664001465</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445442199707</v>
+        <v>48.0445365905762</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135841369629</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577499389648</v>
+        <v>52.8577461242676</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.820384979248</v>
+        <v>53.8203887939453</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336906433105</v>
+        <v>59.3336982727051</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403953552246</v>
+        <v>62.4404029846191</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.134105682373</v>
+        <v>62.1341018676758</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339942932129</v>
+        <v>61.4340019226074</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399879455566</v>
+        <v>59.6399917602539</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275009155273</v>
+        <v>59.7275047302246</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838539123535</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775604248047</v>
+        <v>60.0775566101074</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204887390137</v>
+        <v>54.5204849243164</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3272933959961</v>
+        <v>58.3273010253906</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772415161133</v>
+        <v>57.9772453308105</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273971557617</v>
+        <v>59.027400970459</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583572387695</v>
+        <v>57.0583610534668</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395767211914</v>
+        <v>56.8395805358887</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708442687988</v>
+        <v>56.9708480834961</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712593078613</v>
+        <v>59.7712554931641</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525749206543</v>
+        <v>60.252571105957</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335945129395</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456703186035</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.670955657959</v>
+        <v>57.6709518432617</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899322509766</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334945678711</v>
+        <v>57.9334907531738</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.990047454834</v>
+        <v>59.9900436401367</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145027160645</v>
+        <v>56.3145065307617</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146102905273</v>
+        <v>57.0146064758301</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896286010742</v>
+        <v>57.189624786377</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831275939941</v>
+        <v>55.4831314086914</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.264347076416</v>
+        <v>55.2643508911133</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892211914062</v>
+        <v>54.3892250061035</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703330993652</v>
+        <v>53.4703369140625</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518676757812</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.139476776123</v>
+        <v>56.1394805908203</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264785766602</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578536987305</v>
+        <v>53.5578460693359</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138877868652</v>
+        <v>52.1138916015625</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326644897461</v>
+        <v>52.3326683044434</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449478149414</v>
+        <v>50.8449440002441</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196739196777</v>
+        <v>48.9196701049805</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.788402557373</v>
+        <v>48.7883987426758</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201850891113</v>
+        <v>52.4201812744141</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8951034545898</v>
+        <v>51.8951072692871</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511413574219</v>
+        <v>50.4511451721191</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.7510414123535</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>49.838550567627</v>
+        <v>49.8385543823242</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449478149414</v>
+        <v>50.8449440002441</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264785766602</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890174865723</v>
+        <v>52.9890098571777</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.901496887207</v>
+        <v>52.9015045166016</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519638061523</v>
+        <v>56.0519676208496</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518676757812</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142951965332</v>
+        <v>54.9143028259277</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391654968262</v>
+        <v>54.0391693115234</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390655517578</v>
+        <v>53.3390693664551</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.3454627990723</v>
+        <v>54.3454666137695</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.2205963134766</v>
+        <v>55.2205848693848</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623039245605</v>
+        <v>44.662296295166</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041427612305</v>
+        <v>45.5041465759277</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.3865928649902</v>
+        <v>40.386589050293</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G224" t="n">
-        <v>44.8395309448242</v>
+        <v>44.839527130127</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509117126465</v>
+        <v>44.750919342041</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982940673828</v>
+        <v>43.7982978820801</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019821166992</v>
+        <v>42.6019859313965</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536933898926</v>
+        <v>47.4536895751953</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.2955360412598</v>
+        <v>48.295539855957</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361633300781</v>
+        <v>49.5361595153809</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.915843963623</v>
+        <v>48.9158515930176</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983139038086</v>
+        <v>50.9983177185059</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844718933105</v>
+        <v>51.8844757080078</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G254" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626167297363</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.33984375</v>
+        <v>48.3398475646973</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G256" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626167297363</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.8524627685547</v>
+        <v>47.8524589538574</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004547119141</v>
+        <v>46.7004585266113</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496849060059</v>
+        <v>45.1496887207031</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.301685333252</v>
+        <v>46.3016891479492</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939888000488</v>
+        <v>45.1939926147461</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7700004577637</v>
+        <v>45.7699966430664</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121360778809</v>
+        <v>42.9121398925781</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918243408203</v>
+        <v>42.2918281555176</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761421203613</v>
+        <v>43.7761459350586</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450668334961</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444458007812</v>
+        <v>43.2444496154785</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444458007812</v>
+        <v>43.2444496154785</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539825439453</v>
+        <v>43.7539863586426</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102920532227</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349090576172</v>
+        <v>42.7349014282227</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493644714355</v>
+        <v>41.6493606567383</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.804443359375</v>
+        <v>41.8044395446777</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170547485352</v>
+        <v>41.3170509338379</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.946590423584</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782829284668</v>
+        <v>39.4782791137695</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213562011719</v>
+        <v>39.9213600158691</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4308967590332</v>
+        <v>40.4309005737305</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693519592285</v>
+        <v>38.7693557739258</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099754333496</v>
+        <v>40.0099792480469</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.006908416748</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462860107422</v>
+        <v>42.6462936401367</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361396789551</v>
+        <v>42.3361358642578</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696800231934</v>
+        <v>42.2696723937988</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.006908416748</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.9847450256348</v>
+        <v>40.984748840332</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807441711426</v>
+        <v>38.6807403564453</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096786499023</v>
+        <v>43.7096748352051</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610694885254</v>
+        <v>45.0610618591309</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764625549316</v>
+        <v>47.2764587402344</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459968566895</v>
+        <v>46.3459930419922</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.833381652832</v>
+        <v>46.8333778381348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419845581055</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992118835449</v>
+        <v>39.8992042541504</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.962589263916</v>
+        <v>40.9625930786133</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>59</v>
       </c>
       <c r="G392" t="n">
-        <v>52.2832450866699</v>
+        <v>52.2832489013672</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466300964355</v>
+        <v>53.3466339111328</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250953674316</v>
+        <v>53.1250915527344</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.3909378051758</v>
+        <v>53.390941619873</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657150268555</v>
+        <v>54.3657112121582</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164924621582</v>
+        <v>55.9164848327637</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998649597168</v>
+        <v>54.0998611450195</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001892089844</v>
+        <v>57.6001853942871</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.1571044921875</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.783561706543</v>
+        <v>55.7835655212402</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115661621094</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.954647064209</v>
+        <v>57.9546508789062</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038734436035</v>
+        <v>56.4038696289062</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.3595657348633</v>
+        <v>56.359561920166</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229507446289</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>62</v>
       </c>
       <c r="G431" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478645324707</v>
+        <v>52.9478607177734</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0174026489258</v>
+        <v>52.0173988342285</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115661621094</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164924621582</v>
+        <v>55.9164848327637</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506385803223</v>
+        <v>55.6506423950195</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>62</v>
       </c>
       <c r="G455" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>62</v>
       </c>
       <c r="G456" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1694030761719</v>
+        <v>53.1693992614746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149337768555</v>
+        <v>52.8149375915527</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515525817871</v>
+        <v>51.7515487670898</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450828552246</v>
+        <v>50.2450866699219</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569114685059</v>
+        <v>50.0569076538086</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>49.0683479309082</v>
+        <v>49.0683517456055</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075668334961</v>
+        <v>49.6075630187988</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.6974296569824</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>58</v>
       </c>
       <c r="G497" t="n">
-        <v>52.1238899230957</v>
+        <v>52.123893737793</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477210998535</v>
+        <v>56.347728729248</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666770935059</v>
+        <v>57.0666732788086</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8314018249512</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454635620117</v>
+        <v>51.045467376709</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353340148926</v>
+        <v>51.1353378295898</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644119262695</v>
+        <v>51.7644157409668</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.6974296569824</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229393005371</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502388000488</v>
+        <v>44.3502426147461</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603759765625</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>44.5749092102051</v>
+        <v>44.5749130249023</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>50</v>
       </c>
       <c r="G540" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>44.8445205688477</v>
+        <v>44.8445243835449</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>50</v>
       </c>
       <c r="G543" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>53</v>
       </c>
       <c r="G546" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>53</v>
       </c>
       <c r="G551" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229393005371</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G565" t="n">
-        <v>44.2154426574707</v>
+        <v>44.2154388427734</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>45.2039947509766</v>
+        <v>45.2039909362793</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190032958984</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.337963104248</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>53</v>
       </c>
       <c r="G584" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454635620117</v>
+        <v>51.045467376709</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595367431641</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837280273438</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837280273438</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203178405762</v>
+        <v>47.7203216552734</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.9768028259277</v>
+        <v>56.976806640625</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.4719200134277</v>
+        <v>53.471923828125</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617904663086</v>
+        <v>53.5617866516113</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>53.2023162841797</v>
+        <v>53.202320098877</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8314018249512</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G642" t="n">
-        <v>53.2023162841797</v>
+        <v>53.202320098877</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>53.2023162841797</v>
+        <v>53.202320098877</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>58</v>
       </c>
       <c r="G650" t="n">
-        <v>52.1238899230957</v>
+        <v>52.123893737793</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578544616699</v>
+        <v>56.2578506469727</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441528320312</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.337963104248</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948081970215</v>
+        <v>51.4948043823242</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.1166381835938</v>
+        <v>33.116641998291</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>28.2637310028076</v>
+        <v>28.263729095459</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>27.6795825958252</v>
+        <v>27.6795845031738</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.163257598877</v>
+        <v>25.1632556915283</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>22.1077213287354</v>
+        <v>22.1077194213867</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861419677734</v>
+        <v>23.1861438751221</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139148712158</v>
+        <v>24.7139129638672</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024707794189</v>
+        <v>25.7024688720703</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>29</v>
       </c>
       <c r="G688" t="n">
-        <v>26.0619449615479</v>
+        <v>26.0619468688965</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328651428223</v>
+        <v>25.4328632354736</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.5905532836914</v>
+        <v>23.5905513763428</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967449188232</v>
+        <v>26.1967468261719</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201103210449</v>
+        <v>27.3201065063477</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857780456543</v>
+        <v>30.2857761383057</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.308666229248</v>
+        <v>28.3086643218994</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>26.6011581420898</v>
+        <v>26.6011600494385</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359600067139</v>
+        <v>26.7359619140625</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>29</v>
       </c>
       <c r="G716" t="n">
-        <v>26.0619449615479</v>
+        <v>26.0619468688965</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663543701172</v>
+        <v>26.4663562774658</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998435974121</v>
+        <v>27.4998474121094</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>27.5447788238525</v>
+        <v>27.5447807312012</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566963195801</v>
+        <v>29.6566982269287</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699207305908</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959095001221</v>
+        <v>30.1959075927734</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743320465088</v>
+        <v>31.2743339538574</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642082214355</v>
+        <v>31.3642044067383</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990043640137</v>
+        <v>31.4990100860596</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>36.5</v>
       </c>
       <c r="G732" t="n">
-        <v>32.8021049499512</v>
+        <v>32.8021011352539</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.071704864502</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060390472412</v>
+        <v>30.1060409545898</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699207305908</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.4426231384277</v>
+        <v>32.4426307678223</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373802185059</v>
+        <v>36.0373764038086</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.543098449707</v>
+        <v>35.5431022644043</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298721313477</v>
+        <v>34.3298759460449</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823173522949</v>
+        <v>36.0823135375977</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G753" t="n">
-        <v>38.778377532959</v>
+        <v>38.7783813476562</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2840957641602</v>
+        <v>38.2840995788574</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202102661133</v>
+        <v>37.5202140808105</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>40.5757522583008</v>
+        <v>40.575756072998</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224716186523</v>
+        <v>42.8224754333496</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>41.9687156677246</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0251007080078</v>
+        <v>41.0250968933105</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>41.9687156677246</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409523010254</v>
+        <v>40.4409484863281</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440452575684</v>
+        <v>41.7440490722656</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484527587891</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>41.9687156677246</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889862060547</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>48.75</v>
       </c>
       <c r="G803" t="n">
-        <v>43.8110313415527</v>
+        <v>43.8110275268555</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479850769043</v>
+        <v>39.047981262207</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>43</v>
       </c>
       <c r="G809" t="n">
-        <v>38.6435737609863</v>
+        <v>38.6435775756836</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069839477539</v>
+        <v>36.3069877624512</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594253540039</v>
+        <v>38.0594215393066</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898254394531</v>
+        <v>37.7898178100586</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118705749512</v>
+        <v>39.8118667602539</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.452392578125</v>
+        <v>39.4523963928223</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422554016113</v>
+        <v>39.5422592163086</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G827" t="n">
-        <v>38.778377532959</v>
+        <v>38.7783813476562</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>39.7220001220703</v>
+        <v>39.7220039367676</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>43</v>
       </c>
       <c r="G829" t="n">
-        <v>38.6435737609863</v>
+        <v>38.6435775756836</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144958496094</v>
+        <v>38.0144882202148</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638366699219</v>
+        <v>38.4638328552246</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G836" t="n">
-        <v>34.2400054931641</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329727172852</v>
+        <v>35.6329689025879</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.182788848877</v>
+        <v>39.1827850341797</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448844909668</v>
+        <v>37.7448883056641</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>44.75</v>
       </c>
       <c r="G845" t="n">
-        <v>40.2162742614746</v>
+        <v>40.2162780761719</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453559875488</v>
+        <v>40.8453598022461</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.755485534668</v>
+        <v>40.7554893493652</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744415283203</v>
+        <v>41.4744453430176</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G857" t="n">
-        <v>40.5757522583008</v>
+        <v>40.575756072998</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.5308151245117</v>
+        <v>40.530818939209</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.8004264831543</v>
+        <v>40.8004302978516</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.755485534668</v>
+        <v>40.7554893493652</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960189819336</v>
+        <v>40.3960151672363</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889862060547</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484527587891</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471458435059</v>
+        <v>43.0471420288086</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484527587891</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484527587891</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>41.9687156677246</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484527587891</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281936645508</v>
+        <v>42.3281898498535</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>50</v>
       </c>
       <c r="G897" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837280273438</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>49.0683479309082</v>
+        <v>49.0683517456055</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190032958984</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>50</v>
       </c>
       <c r="G912" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837280273438</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>50</v>
       </c>
       <c r="G921" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603759765625</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G939" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>53</v>
       </c>
       <c r="G944" t="n">
-        <v>47.6304512023926</v>
+        <v>47.6304473876953</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811027526855</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229393005371</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595367431641</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229393005371</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>45.5634727478027</v>
+        <v>45.5634689331055</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837280273438</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>50</v>
       </c>
       <c r="G994" t="n">
-        <v>44.9343872070312</v>
+        <v>44.9343910217285</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765251159668</v>
+        <v>44.1765289306641</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>42.0448036193848</v>
+        <v>42.044807434082</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551811218262</v>
+        <v>41.4551849365234</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>39.6409492492676</v>
+        <v>39.6409530639648</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G1011" t="n">
-        <v>40.2759323120117</v>
+        <v>40.2759284973145</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863021850586</v>
+        <v>39.6863059997559</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.0513229370117</v>
+        <v>39.051326751709</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>43.2694129943848</v>
+        <v>43.2694091796875</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>44.7207946777344</v>
+        <v>44.7207908630371</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>53</v>
       </c>
       <c r="G1043" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>53</v>
       </c>
       <c r="G1047" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>53</v>
       </c>
       <c r="G1048" t="n">
-        <v>48.0771255493164</v>
+        <v>48.0771217346191</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328521728516</v>
+        <v>47.5328559875488</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.4486618041992</v>
+        <v>44.4486656188965</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836448669434</v>
+        <v>45.0836410522461</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.897876739502</v>
+        <v>46.8978729248047</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452941894531</v>
+        <v>37.6452980041504</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.1485557556152</v>
+        <v>36.148551940918</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578460693359</v>
+        <v>36.0578422546387</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1125" t="n">
-        <v>36.6474685668945</v>
+        <v>36.6474723815918</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1126" t="n">
-        <v>36.6474685668945</v>
+        <v>36.6474723815918</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463813781738</v>
+        <v>37.1463851928711</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>37.9174308776855</v>
+        <v>37.9174270629883</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753280639648</v>
+        <v>36.3753318786621</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688125610352</v>
+        <v>39.3688163757324</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146560668945</v>
+        <v>35.0146598815918</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092315673828</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.8829383850098</v>
+        <v>32.882942199707</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861961364746</v>
+        <v>31.3861980438232</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691951751709</v>
+        <v>26.6691970825195</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577362060547</v>
+        <v>27.7577381134033</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.6500015258789</v>
       </c>
       <c r="G1184" t="n">
-        <v>29.6173248291016</v>
+        <v>29.6173229217529</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233535766602</v>
+        <v>31.0233516693115</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419303894043</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272079467773</v>
+        <v>33.4272041320801</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053733825684</v>
+        <v>35.1053771972656</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1212" t="n">
-        <v>36.919605255127</v>
+        <v>36.9196014404297</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1213" t="n">
-        <v>37.5092277526855</v>
+        <v>37.5092315673828</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>35.5589294433594</v>
+        <v>35.5589256286621</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -61486,7 +61486,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="D2351" t="n">
-        <v>1.5</v>
+        <v>1.49000000953674</v>
       </c>
       <c r="E2351" t="n">
         <v>1.52799999713898</v>
@@ -61498,6 +61498,32 @@
         <v>1.5</v>
       </c>
       <c r="H2351" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2352" t="n">
+        <v>1224732</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>1.47399997711182</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>1.51900005340576</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>1.47399997711182</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>1.47399997711182</v>
+      </c>
+      <c r="H2352" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503227233887</v>
+        <v>44.8503189086914</v>
       </c>
       <c r="H2" t="n">
         <v>2040000</v>
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569313049316</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -630,7 +630,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631210327148</v>
+        <v>46.8631134033203</v>
       </c>
       <c r="H9" t="n">
         <v>27464</v>
@@ -659,7 +659,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H10" t="n">
         <v>24546</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -746,7 +746,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007781982422</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H13" t="n">
         <v>28253</v>
@@ -775,7 +775,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007781982422</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H14" t="n">
         <v>82998</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -862,7 +862,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319496154785</v>
+        <v>47.4319458007812</v>
       </c>
       <c r="H17" t="n">
         <v>9145</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.950626373291</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131729125977</v>
+        <v>47.2131690979004</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1065,7 +1065,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880874633789</v>
+        <v>46.6880912780762</v>
       </c>
       <c r="H24" t="n">
         <v>35958</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443367004395</v>
+        <v>46.6443328857422</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1210,7 +1210,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254524230957</v>
+        <v>45.7254447937012</v>
       </c>
       <c r="H29" t="n">
         <v>15825</v>
@@ -1239,7 +1239,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692108154297</v>
+        <v>45.7692031860352</v>
       </c>
       <c r="H30" t="n">
         <v>7291</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.681697845459</v>
+        <v>45.6816940307617</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1355,7 +1355,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567161560059</v>
+        <v>45.8567199707031</v>
       </c>
       <c r="H34" t="n">
         <v>9627</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069793701172</v>
+        <v>47.6069717407227</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1442,7 +1442,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H37" t="n">
         <v>10252</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881950378418</v>
+        <v>47.3881988525391</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1529,7 +1529,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.9943885803223</v>
+        <v>46.994384765625</v>
       </c>
       <c r="H40" t="n">
         <v>9334</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569313049316</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1703,7 +1703,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H46" t="n">
         <v>84037</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1906,7 +1906,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H53" t="n">
         <v>13389</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194625854492</v>
+        <v>47.519458770752</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -1993,7 +1993,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445404052734</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="n">
         <v>39379</v>
@@ -2051,7 +2051,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.194995880127</v>
+        <v>51.1950035095215</v>
       </c>
       <c r="H58" t="n">
         <v>44749</v>
@@ -2109,7 +2109,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.820384979248</v>
+        <v>53.8203887939453</v>
       </c>
       <c r="H60" t="n">
         <v>54877</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953147888184</v>
+        <v>53.2953071594238</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579498291016</v>
+        <v>54.2579536437988</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2312,7 +2312,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3337020874023</v>
+        <v>59.3336982727051</v>
       </c>
       <c r="H67" t="n">
         <v>66049</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589721679688</v>
+        <v>61.2589836120605</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2370,7 +2370,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403953552246</v>
+        <v>62.4403991699219</v>
       </c>
       <c r="H69" t="n">
         <v>51076</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965446472168</v>
+        <v>61.696533203125</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965446472168</v>
+        <v>61.696533203125</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2457,7 +2457,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.1341094970703</v>
+        <v>62.1340980529785</v>
       </c>
       <c r="H72" t="n">
         <v>24358</v>
@@ -2486,7 +2486,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902473449707</v>
+        <v>61.3902397155762</v>
       </c>
       <c r="H73" t="n">
         <v>19520</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4340019226074</v>
+        <v>61.4340057373047</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838500976562</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2689,7 +2689,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775566101074</v>
+        <v>60.077564239502</v>
       </c>
       <c r="H80" t="n">
         <v>17247</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.821418762207</v>
+        <v>60.821403503418</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898284912109</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2863,7 +2863,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H86" t="n">
         <v>30413</v>
@@ -2892,7 +2892,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204849243164</v>
+        <v>54.5204887390137</v>
       </c>
       <c r="H87" t="n">
         <v>43778</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.071159362793</v>
+        <v>59.0711555480957</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3095,7 +3095,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H94" t="n">
         <v>25066</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273971557617</v>
+        <v>59.027400970459</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H97" t="n">
         <v>26035</v>
@@ -3240,7 +3240,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583572387695</v>
+        <v>57.0583610534668</v>
       </c>
       <c r="H99" t="n">
         <v>27245</v>
@@ -3269,7 +3269,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H100" t="n">
         <v>194669</v>
@@ -3298,7 +3298,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395729064941</v>
+        <v>56.8395767211914</v>
       </c>
       <c r="H101" t="n">
         <v>37551</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708518981934</v>
+        <v>56.9708480834961</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3356,7 +3356,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H103" t="n">
         <v>43096</v>
@@ -3414,7 +3414,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712593078613</v>
+        <v>59.7712631225586</v>
       </c>
       <c r="H105" t="n">
         <v>21082</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.252571105957</v>
+        <v>60.2525787353516</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H108" t="n">
         <v>43417</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898284912109</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3588,7 +3588,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H111" t="n">
         <v>384860</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.745662689209</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3646,7 +3646,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H113" t="n">
         <v>116509</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3733,7 +3733,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709518432617</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="n">
         <v>53938</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897285461426</v>
+        <v>57.8897323608398</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899398803711</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -4023,7 +4023,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H126" t="n">
         <v>36944</v>
@@ -4052,7 +4052,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770378112793</v>
+        <v>56.5770454406738</v>
       </c>
       <c r="H127" t="n">
         <v>42192</v>
@@ -4110,7 +4110,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.2707481384277</v>
+        <v>56.270751953125</v>
       </c>
       <c r="H129" t="n">
         <v>14664</v>
@@ -4139,7 +4139,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145027160645</v>
+        <v>56.3144989013672</v>
       </c>
       <c r="H130" t="n">
         <v>10098</v>
@@ -4168,7 +4168,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H131" t="n">
         <v>10634</v>
@@ -4197,7 +4197,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146064758301</v>
+        <v>57.0146026611328</v>
       </c>
       <c r="H132" t="n">
         <v>14544</v>
@@ -4255,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833312988281</v>
       </c>
       <c r="H134" t="n">
         <v>10051</v>
@@ -4313,7 +4313,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396842956543</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H136" t="n">
         <v>78309</v>
@@ -4371,7 +4371,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.752067565918</v>
+        <v>56.7520637512207</v>
       </c>
       <c r="H138" t="n">
         <v>16052</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831314086914</v>
+        <v>55.4831352233887</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582611083984</v>
+        <v>56.3582649230957</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4574,7 +4574,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892211914062</v>
+        <v>54.3892250061035</v>
       </c>
       <c r="H145" t="n">
         <v>31730</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703369140625</v>
+        <v>53.470329284668</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4632,7 +4632,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H147" t="n">
         <v>49677</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394805908203</v>
+        <v>56.1394729614258</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4806,7 +4806,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="n">
         <v>14177</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4864,7 +4864,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578460693359</v>
+        <v>53.5578498840332</v>
       </c>
       <c r="H155" t="n">
         <v>11308</v>
@@ -4893,7 +4893,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766265869141</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H156" t="n">
         <v>10320</v>
@@ -4922,7 +4922,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138916015625</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="n">
         <v>24689</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326644897461</v>
+        <v>52.3326683044434</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -5009,7 +5009,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449440002441</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H160" t="n">
         <v>11068</v>
@@ -5038,7 +5038,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H161" t="n">
         <v>19271</v>
@@ -5067,7 +5067,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196701049805</v>
+        <v>48.9196739196777</v>
       </c>
       <c r="H162" t="n">
         <v>15929</v>
@@ -5183,7 +5183,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H166" t="n">
         <v>9806</v>
@@ -5357,7 +5357,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8951072692871</v>
+        <v>51.8951034545898</v>
       </c>
       <c r="H172" t="n">
         <v>4493</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889099121094</v>
+        <v>52.2889137268066</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5473,7 +5473,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511451721191</v>
+        <v>50.4511413574219</v>
       </c>
       <c r="H176" t="n">
         <v>8990</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510414123535</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5618,7 +5618,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571235656738</v>
+        <v>48.6571273803711</v>
       </c>
       <c r="H181" t="n">
         <v>8552</v>
@@ -5647,7 +5647,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H182" t="n">
         <v>28706</v>
@@ -5676,7 +5676,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449440002441</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H183" t="n">
         <v>12299</v>
@@ -5792,7 +5792,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766265869141</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H187" t="n">
         <v>10680</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.95166015625</v>
+        <v>53.9516525268555</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140953063965</v>
+        <v>53.5140991210938</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -5966,7 +5966,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="n">
         <v>9212</v>
@@ -5995,7 +5995,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015045166016</v>
+        <v>52.9015007019043</v>
       </c>
       <c r="H194" t="n">
         <v>32354</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077980041504</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6169,7 +6169,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H200" t="n">
         <v>18598</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6285,7 +6285,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891212463379</v>
+        <v>53.6891174316406</v>
       </c>
       <c r="H204" t="n">
         <v>7160</v>
@@ -6314,7 +6314,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391693115234</v>
+        <v>54.0391654968262</v>
       </c>
       <c r="H205" t="n">
         <v>7569</v>
@@ -6546,7 +6546,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>52.4639434814453</v>
+        <v>52.463939666748</v>
       </c>
       <c r="H213" t="n">
         <v>17630</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823089599609</v>
+        <v>49.8823051452637</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179885864258</v>
+        <v>44.617992401123</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6691,7 +6691,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041427612305</v>
+        <v>45.5041465759277</v>
       </c>
       <c r="H218" t="n">
         <v>23030</v>
@@ -6749,7 +6749,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358390808105</v>
+        <v>46.0358428955078</v>
       </c>
       <c r="H220" t="n">
         <v>30045</v>
@@ -6807,7 +6807,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.3865928649902</v>
+        <v>40.3865966796875</v>
       </c>
       <c r="H222" t="n">
         <v>50890</v>
@@ -6836,7 +6836,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="n">
         <v>24305</v>
@@ -6894,7 +6894,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281425476074</v>
+        <v>44.9281463623047</v>
       </c>
       <c r="H225" t="n">
         <v>28013</v>
@@ -6923,7 +6923,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509117126465</v>
+        <v>44.7509155273438</v>
       </c>
       <c r="H226" t="n">
         <v>9809</v>
@@ -6952,7 +6952,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982978820801</v>
+        <v>43.7982940673828</v>
       </c>
       <c r="H227" t="n">
         <v>8139</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019821166992</v>
+        <v>42.6019859313965</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7184,7 +7184,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536895751953</v>
+        <v>47.453685760498</v>
       </c>
       <c r="H235" t="n">
         <v>27871</v>
@@ -7213,7 +7213,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272323608398</v>
+        <v>48.8272361755371</v>
       </c>
       <c r="H236" t="n">
         <v>13514</v>
@@ -7242,7 +7242,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.295539855957</v>
+        <v>48.2955360412598</v>
       </c>
       <c r="H237" t="n">
         <v>20676</v>
@@ -7271,7 +7271,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755523681641</v>
+        <v>51.1755485534668</v>
       </c>
       <c r="H238" t="n">
         <v>56868</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475402832031</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7329,7 +7329,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361633300781</v>
       </c>
       <c r="H240" t="n">
         <v>97891</v>
@@ -7358,7 +7358,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.226001739502</v>
+        <v>49.2260055541992</v>
       </c>
       <c r="H241" t="n">
         <v>21035</v>
@@ -7387,7 +7387,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.181697845459</v>
+        <v>49.1816940307617</v>
       </c>
       <c r="H242" t="n">
         <v>12836</v>
@@ -7416,7 +7416,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410781860352</v>
       </c>
       <c r="H243" t="n">
         <v>19274</v>
@@ -7474,7 +7474,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H245" t="n">
         <v>24572</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158477783203</v>
+        <v>48.9158515930176</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7619,7 +7619,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H250" t="n">
         <v>14687</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H251" t="n">
         <v>9250</v>
@@ -7677,7 +7677,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715400695801</v>
+        <v>48.8715438842773</v>
       </c>
       <c r="H252" t="n">
         <v>19047</v>
@@ -7822,7 +7822,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.8524589538574</v>
+        <v>47.852466583252</v>
       </c>
       <c r="H257" t="n">
         <v>5700</v>
@@ -7851,7 +7851,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>47.8967666625977</v>
+        <v>47.8967704772949</v>
       </c>
       <c r="H258" t="n">
         <v>6947</v>
@@ -7880,7 +7880,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>47.8967666625977</v>
+        <v>47.8967704772949</v>
       </c>
       <c r="H259" t="n">
         <v>3097</v>
@@ -7909,7 +7909,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004623413086</v>
+        <v>46.7004585266113</v>
       </c>
       <c r="H260" t="n">
         <v>8510</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -7996,7 +7996,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496887207031</v>
+        <v>45.1496849060059</v>
       </c>
       <c r="H263" t="n">
         <v>17681</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192192077637</v>
+        <v>44.2192230224609</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8112,7 +8112,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.3016929626465</v>
+        <v>46.3016815185547</v>
       </c>
       <c r="H267" t="n">
         <v>13254</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.371223449707</v>
+        <v>45.3712272644043</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8199,7 +8199,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939926147461</v>
+        <v>45.1939964294434</v>
       </c>
       <c r="H270" t="n">
         <v>9794</v>
@@ -8315,7 +8315,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586082458496</v>
+        <v>45.8586120605469</v>
       </c>
       <c r="H274" t="n">
         <v>4374</v>
@@ -8373,7 +8373,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989112854004</v>
+        <v>43.5989074707031</v>
       </c>
       <c r="H276" t="n">
         <v>6787</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8518,7 +8518,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="n">
         <v>13077</v>
@@ -8547,7 +8547,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>42.8456726074219</v>
+        <v>42.8456764221191</v>
       </c>
       <c r="H282" t="n">
         <v>7592</v>
@@ -8605,7 +8605,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918243408203</v>
+        <v>42.2918281555176</v>
       </c>
       <c r="H284" t="n">
         <v>1881</v>
@@ -8663,7 +8663,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216728210449</v>
       </c>
       <c r="H286" t="n">
         <v>13125</v>
@@ -8692,7 +8692,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324478149414</v>
+        <v>43.5324440002441</v>
       </c>
       <c r="H287" t="n">
         <v>11020</v>
@@ -8779,7 +8779,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H290" t="n">
         <v>2864</v>
@@ -8837,7 +8837,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.200138092041</v>
+        <v>43.2001419067383</v>
       </c>
       <c r="H292" t="n">
         <v>25355</v>
@@ -8866,7 +8866,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H293" t="n">
         <v>11169</v>
@@ -8924,7 +8924,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H295" t="n">
         <v>8398</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444496154785</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9011,7 +9011,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H298" t="n">
         <v>11117</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444496154785</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9098,7 +9098,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H301" t="n">
         <v>1288</v>
@@ -9156,7 +9156,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102882385254</v>
+        <v>43.5102920532227</v>
       </c>
       <c r="H303" t="n">
         <v>15525</v>
@@ -9185,7 +9185,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216728210449</v>
       </c>
       <c r="H304" t="n">
         <v>13328</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349052429199</v>
+        <v>42.7349090576172</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9359,7 +9359,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170547485352</v>
+        <v>41.3170509338379</v>
       </c>
       <c r="H310" t="n">
         <v>20434</v>
@@ -9388,7 +9388,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853660583496</v>
+        <v>40.7853622436523</v>
       </c>
       <c r="H311" t="n">
         <v>17137</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638275146484</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9533,7 +9533,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H316" t="n">
         <v>7190</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.946590423584</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9591,7 +9591,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112060546875</v>
+        <v>39.6112022399902</v>
       </c>
       <c r="H318" t="n">
         <v>13054</v>
@@ -9620,7 +9620,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782829284668</v>
+        <v>39.4782791137695</v>
       </c>
       <c r="H319" t="n">
         <v>3338</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213562011719</v>
+        <v>39.9213600158691</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9736,7 +9736,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H323" t="n">
         <v>2457</v>
@@ -9765,7 +9765,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4309005737305</v>
+        <v>40.4308967590332</v>
       </c>
       <c r="H324" t="n">
         <v>19512</v>
@@ -9794,7 +9794,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H325" t="n">
         <v>6799</v>
@@ -9823,7 +9823,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693557739258</v>
+        <v>38.7693519592285</v>
       </c>
       <c r="H326" t="n">
         <v>16647</v>
@@ -9852,7 +9852,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H327" t="n">
         <v>5952</v>
@@ -9939,7 +9939,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099792480469</v>
+        <v>40.0099754333496</v>
       </c>
       <c r="H330" t="n">
         <v>3763</v>
@@ -9968,7 +9968,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.275821685791</v>
+        <v>40.2758255004883</v>
       </c>
       <c r="H331" t="n">
         <v>6546</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10258,7 +10258,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696762084961</v>
+        <v>42.2696800231934</v>
       </c>
       <c r="H341" t="n">
         <v>4403</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912147521973</v>
+        <v>42.4912109375</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10432,7 +10432,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H347" t="n">
         <v>20248</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807403564453</v>
+        <v>38.6807441711426</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10548,7 +10548,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096748352051</v>
+        <v>43.7096786499023</v>
       </c>
       <c r="H351" t="n">
         <v>27897</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10693,7 +10693,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="n">
         <v>3633</v>
@@ -10751,7 +10751,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459968566895</v>
+        <v>46.3459930419922</v>
       </c>
       <c r="H358" t="n">
         <v>34572</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419921875</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10925,7 +10925,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H364" t="n">
         <v>1387</v>
@@ -10954,7 +10954,7 @@
         <v>46.375</v>
       </c>
       <c r="G365" t="n">
-        <v>41.0955200195312</v>
+        <v>41.095516204834</v>
       </c>
       <c r="H365" t="n">
         <v>6971</v>
@@ -11012,7 +11012,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992042541504</v>
+        <v>39.8992080688477</v>
       </c>
       <c r="H367" t="n">
         <v>21291</v>
@@ -11041,7 +11041,7 @@
         <v>45.25</v>
       </c>
       <c r="G368" t="n">
-        <v>40.0985870361328</v>
+        <v>40.0985946655273</v>
       </c>
       <c r="H368" t="n">
         <v>8869</v>
@@ -11070,7 +11070,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H369" t="n">
         <v>22056</v>
@@ -11099,7 +11099,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321350097656</v>
+        <v>40.0321311950684</v>
       </c>
       <c r="H370" t="n">
         <v>10048</v>
@@ -11128,7 +11128,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625930786133</v>
+        <v>40.9625968933105</v>
       </c>
       <c r="H371" t="n">
         <v>7882</v>
@@ -11186,7 +11186,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724502563477</v>
+        <v>44.9724540710449</v>
       </c>
       <c r="H373" t="n">
         <v>15133</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780097961426</v>
+        <v>50.3780059814453</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11418,7 +11418,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H381" t="n">
         <v>8438</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958602905273</v>
+        <v>51.7958564758301</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121635437012</v>
+        <v>50.1121597290039</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11621,7 +11621,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463096618652</v>
+        <v>49.8463172912598</v>
       </c>
       <c r="H388" t="n">
         <v>9469</v>
@@ -11650,7 +11650,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032402038574</v>
+        <v>49.4032363891602</v>
       </c>
       <c r="H389" t="n">
         <v>4963</v>
@@ -11679,7 +11679,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H390" t="n">
         <v>14079</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11911,7 +11911,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466339111328</v>
+        <v>53.3466377258301</v>
       </c>
       <c r="H398" t="n">
         <v>16109</v>
@@ -11940,7 +11940,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250991821289</v>
+        <v>53.1250953674316</v>
       </c>
       <c r="H399" t="n">
         <v>11868</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657150268555</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12056,7 +12056,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H403" t="n">
         <v>55252</v>
@@ -12143,7 +12143,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>52.7706336975098</v>
+        <v>52.7706298828125</v>
       </c>
       <c r="H406" t="n">
         <v>16569</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12230,7 +12230,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="n">
         <v>12835</v>
@@ -12259,7 +12259,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.7774124145508</v>
+        <v>57.777416229248</v>
       </c>
       <c r="H410" t="n">
         <v>15892</v>
@@ -12288,7 +12288,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001892089844</v>
+        <v>57.6001815795898</v>
       </c>
       <c r="H411" t="n">
         <v>34918</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.157112121582</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12375,7 +12375,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.7835655212402</v>
+        <v>55.783561706543</v>
       </c>
       <c r="H414" t="n">
         <v>6786</v>
@@ -12462,7 +12462,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863395690918</v>
+        <v>58.4863433837891</v>
       </c>
       <c r="H417" t="n">
         <v>56533</v>
@@ -12549,7 +12549,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.359561920166</v>
+        <v>56.3595657348633</v>
       </c>
       <c r="H420" t="n">
         <v>35472</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12781,7 +12781,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>57.11279296875</v>
+        <v>57.1127967834473</v>
       </c>
       <c r="H428" t="n">
         <v>7432</v>
@@ -12955,7 +12955,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478607177734</v>
+        <v>52.9478645324707</v>
       </c>
       <c r="H434" t="n">
         <v>15198</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.5238647460938</v>
+        <v>53.523868560791</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13129,7 +13129,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H440" t="n">
         <v>5382</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026428222656</v>
+        <v>56.8026466369629</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13216,7 +13216,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G443" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392539978027</v>
       </c>
       <c r="H443" t="n">
         <v>5854</v>
@@ -13245,7 +13245,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H444" t="n">
         <v>6381</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13303,7 +13303,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H446" t="n">
         <v>7435</v>
@@ -13332,7 +13332,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H447" t="n">
         <v>11987</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.625415802002</v>
+        <v>56.6254119873047</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13419,7 +13419,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H450" t="n">
         <v>5021</v>
@@ -13448,7 +13448,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H451" t="n">
         <v>1739</v>
@@ -13477,7 +13477,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392539978027</v>
       </c>
       <c r="H452" t="n">
         <v>2949</v>
@@ -13506,7 +13506,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734115600586</v>
+        <v>55.4734077453613</v>
       </c>
       <c r="H453" t="n">
         <v>9803</v>
@@ -13535,7 +13535,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506423950195</v>
+        <v>55.6506385803223</v>
       </c>
       <c r="H454" t="n">
         <v>5826</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13651,7 +13651,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.7010917663574</v>
+        <v>53.7010955810547</v>
       </c>
       <c r="H458" t="n">
         <v>31030</v>
@@ -13709,7 +13709,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1693992614746</v>
+        <v>53.1694030761719</v>
       </c>
       <c r="H460" t="n">
         <v>20381</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.81494140625</v>
+        <v>52.8149375915527</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13796,7 +13796,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515525817871</v>
+        <v>51.7515487670898</v>
       </c>
       <c r="H463" t="n">
         <v>3551</v>
@@ -13854,7 +13854,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743179321289</v>
+        <v>51.5743217468262</v>
       </c>
       <c r="H465" t="n">
         <v>7910</v>
@@ -13912,7 +13912,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450866699219</v>
+        <v>50.2450904846191</v>
       </c>
       <c r="H467" t="n">
         <v>8697</v>
@@ -13941,7 +13941,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="n">
         <v>4011</v>
@@ -13970,7 +13970,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H469" t="n">
         <v>4828</v>
@@ -14347,7 +14347,7 @@
         <v>53.5</v>
       </c>
       <c r="G482" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H482" t="n">
         <v>3928</v>
@@ -14376,7 +14376,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H483" t="n">
         <v>12430</v>
@@ -14434,7 +14434,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="n">
         <v>17601</v>
@@ -14579,7 +14579,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H490" t="n">
         <v>8141</v>
@@ -14724,7 +14724,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.6974334716797</v>
+        <v>49.697437286377</v>
       </c>
       <c r="H495" t="n">
         <v>6839</v>
@@ -14753,7 +14753,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H496" t="n">
         <v>19509</v>
@@ -14840,7 +14840,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H499" t="n">
         <v>8348</v>
@@ -14869,7 +14869,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H500" t="n">
         <v>16458</v>
@@ -14898,7 +14898,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H501" t="n">
         <v>10967</v>
@@ -15014,7 +15014,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.347728729248</v>
+        <v>56.3477210998535</v>
       </c>
       <c r="H505" t="n">
         <v>11751</v>
@@ -15043,7 +15043,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666732788086</v>
+        <v>57.0666694641113</v>
       </c>
       <c r="H506" t="n">
         <v>15695</v>
@@ -15072,7 +15072,7 @@
         <v>61</v>
       </c>
       <c r="G507" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H507" t="n">
         <v>21501</v>
@@ -15188,7 +15188,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H511" t="n">
         <v>8102</v>
@@ -15246,7 +15246,7 @@
         <v>61</v>
       </c>
       <c r="G513" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H513" t="n">
         <v>4354</v>
@@ -15275,7 +15275,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H514" t="n">
         <v>1131</v>
@@ -15304,7 +15304,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H515" t="n">
         <v>5949</v>
@@ -15362,7 +15362,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="n">
         <v>1572</v>
@@ -15391,7 +15391,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745452880859</v>
+        <v>51.6745491027832</v>
       </c>
       <c r="H518" t="n">
         <v>5582</v>
@@ -15478,7 +15478,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="n">
         <v>4391</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15536,7 +15536,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353378295898</v>
+        <v>51.1353340148926</v>
       </c>
       <c r="H523" t="n">
         <v>2020</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644157409668</v>
+        <v>51.7644119262695</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15594,7 +15594,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.6974334716797</v>
+        <v>49.697437286377</v>
       </c>
       <c r="H525" t="n">
         <v>128694</v>
@@ -15623,7 +15623,7 @@
         <v>53.5</v>
       </c>
       <c r="G526" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H526" t="n">
         <v>45916</v>
@@ -15710,7 +15710,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H529" t="n">
         <v>9560</v>
@@ -15739,7 +15739,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="n">
         <v>3420</v>
@@ -15768,7 +15768,7 @@
         <v>53.5</v>
       </c>
       <c r="G531" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H531" t="n">
         <v>7140</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.9114990234375</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15884,7 +15884,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H535" t="n">
         <v>48609</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16000,7 +16000,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>44.5749130249023</v>
+        <v>44.5749092102051</v>
       </c>
       <c r="H539" t="n">
         <v>33506</v>
@@ -16319,7 +16319,7 @@
         <v>53.5</v>
       </c>
       <c r="G550" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H550" t="n">
         <v>11825</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.9114990234375</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.9114990234375</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16493,7 +16493,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="n">
         <v>14230</v>
@@ -16522,7 +16522,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824249267578</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H557" t="n">
         <v>5027</v>
@@ -16580,7 +16580,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="n">
         <v>15220</v>
@@ -16609,7 +16609,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="n">
         <v>18625</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16870,7 +16870,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="n">
         <v>7932</v>
@@ -16928,7 +16928,7 @@
         <v>53.5</v>
       </c>
       <c r="G571" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H571" t="n">
         <v>6282</v>
@@ -16957,7 +16957,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H572" t="n">
         <v>12818</v>
@@ -17015,7 +17015,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190032958984</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H574" t="n">
         <v>4749</v>
@@ -17044,7 +17044,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H575" t="n">
         <v>4241</v>
@@ -17073,7 +17073,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H576" t="n">
         <v>5068</v>
@@ -17247,7 +17247,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="n">
         <v>5028</v>
@@ -17276,7 +17276,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G583" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H583" t="n">
         <v>16905</v>
@@ -17363,7 +17363,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732383728027</v>
+        <v>52.5732307434082</v>
       </c>
       <c r="H586" t="n">
         <v>22708</v>
@@ -17450,7 +17450,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H589" t="n">
         <v>11027</v>
@@ -17479,7 +17479,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H590" t="n">
         <v>18775</v>
@@ -17508,7 +17508,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G591" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H591" t="n">
         <v>9843</v>
@@ -17537,7 +17537,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.236644744873</v>
+        <v>50.2366485595703</v>
       </c>
       <c r="H592" t="n">
         <v>13961</v>
@@ -17566,7 +17566,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H593" t="n">
         <v>40288</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17769,7 +17769,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H600" t="n">
         <v>24224</v>
@@ -17856,7 +17856,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H603" t="n">
         <v>36430</v>
@@ -17943,7 +17943,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824249267578</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H606" t="n">
         <v>25059</v>
@@ -17972,7 +17972,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="n">
         <v>15227</v>
@@ -18030,7 +18030,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>46.0128135681152</v>
+        <v>46.0128173828125</v>
       </c>
       <c r="H609" t="n">
         <v>12898</v>
@@ -18088,7 +18088,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H611" t="n">
         <v>7555</v>
@@ -18175,7 +18175,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203216552734</v>
+        <v>47.7203178405762</v>
       </c>
       <c r="H614" t="n">
         <v>9199</v>
@@ -18204,7 +18204,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H615" t="n">
         <v>16713</v>
@@ -18233,7 +18233,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582221984863</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H616" t="n">
         <v>15159</v>
@@ -18262,7 +18262,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H617" t="n">
         <v>22606</v>
@@ -18320,7 +18320,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="n">
         <v>81517</v>
@@ -18436,7 +18436,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H623" t="n">
         <v>17457</v>
@@ -18494,7 +18494,7 @@
         <v>61</v>
       </c>
       <c r="G625" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H625" t="n">
         <v>14322</v>
@@ -18581,7 +18581,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617942810059</v>
+        <v>53.5617904663086</v>
       </c>
       <c r="H628" t="n">
         <v>10371</v>
@@ -18610,7 +18610,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098243713379</v>
+        <v>54.9098205566406</v>
       </c>
       <c r="H629" t="n">
         <v>33501</v>
@@ -18668,7 +18668,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516609191895</v>
+        <v>53.6516571044922</v>
       </c>
       <c r="H631" t="n">
         <v>10031</v>
@@ -18697,7 +18697,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="n">
         <v>15661</v>
@@ -18784,7 +18784,7 @@
         <v>61</v>
       </c>
       <c r="G635" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H635" t="n">
         <v>37857</v>
@@ -18813,7 +18813,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H636" t="n">
         <v>5975</v>
@@ -18871,7 +18871,7 @@
         <v>61</v>
       </c>
       <c r="G638" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H638" t="n">
         <v>10943</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19509,7 +19509,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300872802734</v>
+        <v>54.7300834655762</v>
       </c>
       <c r="H660" t="n">
         <v>38065</v>
@@ -19567,7 +19567,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="n">
         <v>35448</v>
@@ -19596,7 +19596,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H663" t="n">
         <v>43542</v>
@@ -19683,7 +19683,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H666" t="n">
         <v>33866</v>
@@ -19741,7 +19741,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H668" t="n">
         <v>31289</v>
@@ -19828,7 +19828,7 @@
         <v>48</v>
       </c>
       <c r="G671" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H671" t="n">
         <v>34722</v>
@@ -19857,7 +19857,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="n">
         <v>35845</v>
@@ -20002,7 +20002,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>27.6795845031738</v>
+        <v>27.6795825958252</v>
       </c>
       <c r="H677" t="n">
         <v>30874</v>
@@ -20060,7 +20060,7 @@
         <v>26.75</v>
       </c>
       <c r="G679" t="n">
-        <v>24.0398960113525</v>
+        <v>24.0398979187012</v>
       </c>
       <c r="H679" t="n">
         <v>36114</v>
@@ -20205,7 +20205,7 @@
         <v>32</v>
       </c>
       <c r="G684" t="n">
-        <v>28.7580089569092</v>
+        <v>28.7580070495605</v>
       </c>
       <c r="H684" t="n">
         <v>20060</v>
@@ -20234,7 +20234,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024707794189</v>
+        <v>25.7024688720703</v>
       </c>
       <c r="H685" t="n">
         <v>34700</v>
@@ -20292,7 +20292,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879318237305</v>
       </c>
       <c r="H687" t="n">
         <v>17426</v>
@@ -20379,7 +20379,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.5905532836914</v>
+        <v>23.59055519104</v>
       </c>
       <c r="H690" t="n">
         <v>49158</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.4557495117188</v>
+        <v>23.455753326416</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20437,7 +20437,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879318237305</v>
       </c>
       <c r="H692" t="n">
         <v>106161</v>
@@ -20466,7 +20466,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346492767334</v>
+        <v>27.6346473693848</v>
       </c>
       <c r="H693" t="n">
         <v>49337</v>
@@ -20495,7 +20495,7 @@
         <v>30.5</v>
       </c>
       <c r="G694" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H694" t="n">
         <v>37669</v>
@@ -20553,7 +20553,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993740081787</v>
+        <v>24.3993721008301</v>
       </c>
       <c r="H696" t="n">
         <v>24674</v>
@@ -20669,7 +20669,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258304595947</v>
+        <v>26.8258285522461</v>
       </c>
       <c r="H700" t="n">
         <v>41033</v>
@@ -20698,7 +20698,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967468261719</v>
+        <v>26.1967487335205</v>
       </c>
       <c r="H701" t="n">
         <v>24223</v>
@@ -20843,7 +20843,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>31.7236747741699</v>
+        <v>31.7236785888672</v>
       </c>
       <c r="H706" t="n">
         <v>93719</v>
@@ -20872,7 +20872,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857780456543</v>
+        <v>30.2857799530029</v>
       </c>
       <c r="H707" t="n">
         <v>60261</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130756378174</v>
+        <v>28.7130737304688</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -21017,7 +21017,7 @@
         <v>30.5</v>
       </c>
       <c r="G712" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H712" t="n">
         <v>17158</v>
@@ -21046,7 +21046,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>27.7694511413574</v>
+        <v>27.7694530487061</v>
       </c>
       <c r="H713" t="n">
         <v>21183</v>
@@ -21162,7 +21162,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663543701172</v>
+        <v>26.4663562774658</v>
       </c>
       <c r="H717" t="n">
         <v>21538</v>
@@ -21220,7 +21220,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346492767334</v>
+        <v>27.6346473693848</v>
       </c>
       <c r="H719" t="n">
         <v>31154</v>
@@ -21249,7 +21249,7 @@
         <v>30.5</v>
       </c>
       <c r="G720" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H720" t="n">
         <v>38236</v>
@@ -21394,7 +21394,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G725" t="n">
-        <v>29.072546005249</v>
+        <v>29.0725498199463</v>
       </c>
       <c r="H725" t="n">
         <v>48547</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566944122314</v>
+        <v>29.6566982269287</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21481,7 +21481,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959075927734</v>
+        <v>30.1959095001221</v>
       </c>
       <c r="H728" t="n">
         <v>39492</v>
@@ -21510,7 +21510,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743339538574</v>
+        <v>31.2743358612061</v>
       </c>
       <c r="H729" t="n">
         <v>35167</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990081787109</v>
+        <v>31.4990043640137</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.071704864502</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21742,7 +21742,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060409545898</v>
+        <v>30.1060390472412</v>
       </c>
       <c r="H737" t="n">
         <v>76564</v>
@@ -21829,7 +21829,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501312255859</v>
+        <v>34.1501350402832</v>
       </c>
       <c r="H740" t="n">
         <v>64579</v>
@@ -21887,7 +21887,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373764038086</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="n">
         <v>82973</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.543098449707</v>
+        <v>35.5431022644043</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -21974,7 +21974,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298759460449</v>
+        <v>34.3298721313477</v>
       </c>
       <c r="H745" t="n">
         <v>55801</v>
@@ -22003,7 +22003,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H746" t="n">
         <v>44390</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823173522949</v>
+        <v>36.0823135375977</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22206,7 +22206,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G753" t="n">
-        <v>38.7783813476562</v>
+        <v>38.778377532959</v>
       </c>
       <c r="H753" t="n">
         <v>21833</v>
@@ -22264,7 +22264,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2840957641602</v>
+        <v>38.2840995788574</v>
       </c>
       <c r="H755" t="n">
         <v>52989</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202102661133</v>
+        <v>37.5202140808105</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22322,7 +22322,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>40.575756072998</v>
+        <v>40.5757522583008</v>
       </c>
       <c r="H757" t="n">
         <v>62215</v>
@@ -22409,7 +22409,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.2832565307617</v>
+        <v>42.283260345459</v>
       </c>
       <c r="H760" t="n">
         <v>39270</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22728,7 +22728,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0251007080078</v>
+        <v>41.0250968933105</v>
       </c>
       <c r="H771" t="n">
         <v>23411</v>
@@ -22815,7 +22815,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.5079345703125</v>
+        <v>42.5079307556152</v>
       </c>
       <c r="H774" t="n">
         <v>35151</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440452575684</v>
+        <v>41.7440490722656</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -23047,7 +23047,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H782" t="n">
         <v>12518</v>
@@ -23076,7 +23076,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H783" t="n">
         <v>15651</v>
@@ -23308,7 +23308,7 @@
         <v>48</v>
       </c>
       <c r="G791" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H791" t="n">
         <v>5834</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23511,7 +23511,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.957275390625</v>
+        <v>42.9572715759277</v>
       </c>
       <c r="H798" t="n">
         <v>12261</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23598,7 +23598,7 @@
         <v>48</v>
       </c>
       <c r="G801" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H801" t="n">
         <v>20720</v>
@@ -23714,7 +23714,7 @@
         <v>48</v>
       </c>
       <c r="G805" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H805" t="n">
         <v>8676</v>
@@ -23801,7 +23801,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479850769043</v>
+        <v>39.047981262207</v>
       </c>
       <c r="H808" t="n">
         <v>25259</v>
@@ -23859,7 +23859,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246215820312</v>
+        <v>37.9246253967285</v>
       </c>
       <c r="H810" t="n">
         <v>12601</v>
@@ -23917,7 +23917,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854103088379</v>
+        <v>37.3854141235352</v>
       </c>
       <c r="H812" t="n">
         <v>13843</v>
@@ -23946,7 +23946,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100769042969</v>
+        <v>37.6100807189941</v>
       </c>
       <c r="H813" t="n">
         <v>22502</v>
@@ -24033,7 +24033,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347549438477</v>
       </c>
       <c r="H816" t="n">
         <v>19737</v>
@@ -24091,7 +24091,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898216247559</v>
+        <v>37.7898178100586</v>
       </c>
       <c r="H818" t="n">
         <v>15517</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.003044128418</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986404418945</v>
+        <v>38.5986366271973</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24265,7 +24265,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422592163086</v>
+        <v>39.5422630310059</v>
       </c>
       <c r="H824" t="n">
         <v>9758</v>
@@ -24294,7 +24294,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656265258789</v>
       </c>
       <c r="H825" t="n">
         <v>18320</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.003044128418</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24352,7 +24352,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G827" t="n">
-        <v>38.7783813476562</v>
+        <v>38.778377532959</v>
       </c>
       <c r="H827" t="n">
         <v>9351</v>
@@ -24468,7 +24468,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144920349121</v>
+        <v>38.0144882202148</v>
       </c>
       <c r="H831" t="n">
         <v>12021</v>
@@ -24497,7 +24497,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638328552246</v>
+        <v>38.4638366699219</v>
       </c>
       <c r="H832" t="n">
         <v>15760</v>
@@ -24526,7 +24526,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.430347442627</v>
+        <v>37.4303436279297</v>
       </c>
       <c r="H833" t="n">
         <v>8832</v>
@@ -24584,7 +24584,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.869083404541</v>
+        <v>34.8690872192383</v>
       </c>
       <c r="H835" t="n">
         <v>29428</v>
@@ -24613,7 +24613,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G836" t="n">
-        <v>34.2400054931641</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="H836" t="n">
         <v>24293</v>
@@ -24642,7 +24642,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329727172852</v>
+        <v>35.6329689025879</v>
       </c>
       <c r="H837" t="n">
         <v>24505</v>
@@ -24816,7 +24816,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612113952637</v>
+        <v>40.2612075805664</v>
       </c>
       <c r="H843" t="n">
         <v>56674</v>
@@ -24845,7 +24845,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105560302734</v>
+        <v>40.7105522155762</v>
       </c>
       <c r="H844" t="n">
         <v>80049</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24961,7 +24961,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H848" t="n">
         <v>26342</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453598022461</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017372131348</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25135,7 +25135,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744453430176</v>
+        <v>41.4744415283203</v>
       </c>
       <c r="H854" t="n">
         <v>24859</v>
@@ -25164,7 +25164,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1598968505859</v>
+        <v>41.1599006652832</v>
       </c>
       <c r="H855" t="n">
         <v>12496</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25222,7 +25222,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G857" t="n">
-        <v>40.575756072998</v>
+        <v>40.5757522583008</v>
       </c>
       <c r="H857" t="n">
         <v>12350</v>
@@ -25251,7 +25251,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.530818939209</v>
+        <v>40.5308113098145</v>
       </c>
       <c r="H858" t="n">
         <v>18769</v>
@@ -25454,7 +25454,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H865" t="n">
         <v>24079</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25599,7 +25599,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H870" t="n">
         <v>6994</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25715,7 +25715,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H874" t="n">
         <v>8152</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25889,7 +25889,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H880" t="n">
         <v>11127</v>
@@ -25918,7 +25918,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H881" t="n">
         <v>11939</v>
@@ -26005,7 +26005,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H884" t="n">
         <v>7700</v>
@@ -26092,7 +26092,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H887" t="n">
         <v>28055</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26353,7 +26353,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806312561035</v>
+        <v>44.0806350708008</v>
       </c>
       <c r="H896" t="n">
         <v>19639</v>
@@ -26527,7 +26527,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="n">
         <v>15877</v>
@@ -26614,7 +26614,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H905" t="n">
         <v>8945</v>
@@ -26672,7 +26672,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190032958984</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H907" t="n">
         <v>2482</v>
@@ -26701,7 +26701,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582221984863</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H908" t="n">
         <v>10471</v>
@@ -26788,7 +26788,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H911" t="n">
         <v>10719</v>
@@ -26846,7 +26846,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="n">
         <v>12859</v>
@@ -26933,7 +26933,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>46.0128135681152</v>
+        <v>46.0128173828125</v>
       </c>
       <c r="H916" t="n">
         <v>3511</v>
@@ -26991,7 +26991,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>46.0128135681152</v>
+        <v>46.0128173828125</v>
       </c>
       <c r="H918" t="n">
         <v>20374</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.9114990234375</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27368,7 +27368,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>48.7088775634766</v>
+        <v>48.7088737487793</v>
       </c>
       <c r="H931" t="n">
         <v>10286</v>
@@ -27571,7 +27571,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H938" t="n">
         <v>7754</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27832,7 +27832,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H947" t="n">
         <v>9996</v>
@@ -27861,7 +27861,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H948" t="n">
         <v>6269</v>
@@ -27890,7 +27890,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H949" t="n">
         <v>4814</v>
@@ -28006,7 +28006,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H953" t="n">
         <v>23396</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28209,7 +28209,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="n">
         <v>16648</v>
@@ -28267,7 +28267,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824249267578</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H962" t="n">
         <v>10727</v>
@@ -28383,7 +28383,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H966" t="n">
         <v>2872</v>
@@ -28441,7 +28441,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H968" t="n">
         <v>12385</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.1925506591797</v>
+        <v>46.192554473877</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28876,7 +28876,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>45.5634689331055</v>
+        <v>45.5634727478027</v>
       </c>
       <c r="H983" t="n">
         <v>13464</v>
@@ -28905,7 +28905,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>46.0128135681152</v>
+        <v>46.0128173828125</v>
       </c>
       <c r="H984" t="n">
         <v>9617</v>
@@ -29311,7 +29311,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765251159668</v>
+        <v>44.1765289306641</v>
       </c>
       <c r="H998" t="n">
         <v>76506</v>
@@ -29427,7 +29427,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087409973145</v>
+        <v>41.9087371826172</v>
       </c>
       <c r="H1002" t="n">
         <v>14318</v>
@@ -29485,7 +29485,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.0901641845703</v>
+        <v>42.090160369873</v>
       </c>
       <c r="H1004" t="n">
         <v>24860</v>
@@ -29543,7 +29543,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1006" t="n">
         <v>12674</v>
@@ -29572,7 +29572,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1007" t="n">
         <v>7762</v>
@@ -29717,7 +29717,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1012" t="n">
         <v>16272</v>
@@ -29746,7 +29746,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863021850586</v>
+        <v>39.6863059997559</v>
       </c>
       <c r="H1013" t="n">
         <v>19765</v>
@@ -29775,7 +29775,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1014" t="n">
         <v>13467</v>
@@ -29804,7 +29804,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316627502441</v>
+        <v>39.7316589355469</v>
       </c>
       <c r="H1015" t="n">
         <v>12739</v>
@@ -29833,7 +29833,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1016" t="n">
         <v>130810</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.636604309082</v>
+        <v>41.6366081237793</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797828674316</v>
+        <v>42.6797866821289</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30123,7 +30123,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043960571289</v>
+        <v>43.9043922424316</v>
       </c>
       <c r="H1026" t="n">
         <v>28292</v>
@@ -30210,7 +30210,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1029" t="n">
         <v>17463</v>
@@ -30326,7 +30326,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1033" t="n">
         <v>17232</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218818664551</v>
+        <v>44.2218856811523</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30442,7 +30442,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1037" t="n">
         <v>8307</v>
@@ -30500,7 +30500,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1039" t="n">
         <v>43123</v>
@@ -30645,7 +30645,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1044" t="n">
         <v>18875</v>
@@ -30703,7 +30703,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678352355957</v>
+        <v>48.1678314208984</v>
       </c>
       <c r="H1046" t="n">
         <v>11015</v>
@@ -30790,7 +30790,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1049" t="n">
         <v>8692</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328521728516</v>
+        <v>47.5328598022461</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443168640137</v>
+        <v>46.4443206787109</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -30964,7 +30964,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1055" t="n">
         <v>9979</v>
@@ -31051,7 +31051,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164535522461</v>
+        <v>46.7164497375488</v>
       </c>
       <c r="H1058" t="n">
         <v>15938</v>
@@ -31080,7 +31080,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071632385254</v>
+        <v>46.8071594238281</v>
       </c>
       <c r="H1059" t="n">
         <v>10169</v>
@@ -31109,7 +31109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1060" t="n">
         <v>8913</v>
@@ -31283,7 +31283,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1066" t="n">
         <v>12121</v>
@@ -31399,7 +31399,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1070" t="n">
         <v>9883</v>
@@ -31428,7 +31428,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1071" t="n">
         <v>12696</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093376159668</v>
+        <v>45.8093338012695</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31515,7 +31515,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.4486618041992</v>
+        <v>44.448657989502</v>
       </c>
       <c r="H1074" t="n">
         <v>6081</v>
@@ -31544,7 +31544,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125953674316</v>
+        <v>44.3125915527344</v>
       </c>
       <c r="H1075" t="n">
         <v>11302</v>
@@ -31689,7 +31689,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.897876739502</v>
+        <v>46.8978729248047</v>
       </c>
       <c r="H1080" t="n">
         <v>42778</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563743591309</v>
+        <v>49.2563705444336</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31834,7 +31834,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1085" t="n">
         <v>9377</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.459529876709</v>
+        <v>39.4595222473145</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31921,7 +31921,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1088" t="n">
         <v>48832</v>
@@ -32008,7 +32008,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1091" t="n">
         <v>42578</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32182,7 +32182,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1097" t="n">
         <v>51723</v>
@@ -32269,7 +32269,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1100" t="n">
         <v>35064</v>
@@ -32327,7 +32327,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1102" t="n">
         <v>21799</v>
@@ -32356,7 +32356,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010284423828</v>
+        <v>37.1010246276855</v>
       </c>
       <c r="H1103" t="n">
         <v>27248</v>
@@ -32385,7 +32385,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1104" t="n">
         <v>25963</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32704,7 +32704,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228630065918</v>
+        <v>35.4228591918945</v>
       </c>
       <c r="H1115" t="n">
         <v>18782</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463813781738</v>
+        <v>37.1463851928711</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33342,7 +33342,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1137" t="n">
         <v>52206</v>
@@ -33429,7 +33429,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753280639648</v>
+        <v>36.3753318786621</v>
       </c>
       <c r="H1140" t="n">
         <v>22080</v>
@@ -33458,7 +33458,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299751281738</v>
+        <v>36.3299789428711</v>
       </c>
       <c r="H1141" t="n">
         <v>7118</v>
@@ -33516,7 +33516,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688125610352</v>
+        <v>39.3688163757324</v>
       </c>
       <c r="H1143" t="n">
         <v>170822</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33719,7 +33719,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1150" t="n">
         <v>39042</v>
@@ -33806,7 +33806,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1153" t="n">
         <v>41376</v>
@@ -33835,7 +33835,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250373840332</v>
+        <v>34.4250335693359</v>
       </c>
       <c r="H1154" t="n">
         <v>41497</v>
@@ -33893,7 +33893,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1156" t="n">
         <v>64899</v>
@@ -33980,7 +33980,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1159" t="n">
         <v>19943</v>
@@ -34125,7 +34125,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1164" t="n">
         <v>26580</v>
@@ -34154,7 +34154,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1165" t="n">
         <v>37830</v>
@@ -34183,7 +34183,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1166" t="n">
         <v>18336</v>
@@ -34241,7 +34241,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556716918945</v>
+        <v>37.0556678771973</v>
       </c>
       <c r="H1168" t="n">
         <v>36948</v>
@@ -34328,7 +34328,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.103199005127</v>
+        <v>36.1031951904297</v>
       </c>
       <c r="H1171" t="n">
         <v>37325</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605033874512</v>
+        <v>30.6605072021484</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34734,7 +34734,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233535766602</v>
+        <v>31.0233516693115</v>
       </c>
       <c r="H1185" t="n">
         <v>64152</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419322967529</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34792,7 +34792,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561622619629</v>
+        <v>32.6561584472656</v>
       </c>
       <c r="H1187" t="n">
         <v>23709</v>
@@ -34879,7 +34879,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1190" t="n">
         <v>13571</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600166320801</v>
+        <v>35.0600204467773</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34995,7 +34995,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1194" t="n">
         <v>141817</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35401,7 +35401,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1208" t="n">
         <v>18290</v>
@@ -35430,7 +35430,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1209" t="n">
         <v>25845</v>
@@ -35691,7 +35691,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1218" t="n">
         <v>55769</v>
@@ -35720,7 +35720,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475509643555</v>
+        <v>34.2475547790527</v>
       </c>
       <c r="H1219" t="n">
         <v>11676</v>
@@ -35923,7 +35923,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377777099609</v>
+        <v>33.7377815246582</v>
       </c>
       <c r="H1226" t="n">
         <v>7077</v>
@@ -35981,7 +35981,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280006408691</v>
+        <v>33.2280044555664</v>
       </c>
       <c r="H1228" t="n">
         <v>17594</v>
@@ -36271,7 +36271,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1238" t="n">
         <v>26308</v>
@@ -36329,7 +36329,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719528198242</v>
+        <v>34.5719566345215</v>
       </c>
       <c r="H1240" t="n">
         <v>30852</v>
@@ -36503,7 +36503,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792007446289</v>
+        <v>32.5792045593262</v>
       </c>
       <c r="H1246" t="n">
         <v>16319</v>
@@ -36532,7 +36532,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1247" t="n">
         <v>23766</v>
@@ -36590,7 +36590,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546642303467</v>
+        <v>28.4546661376953</v>
       </c>
       <c r="H1249" t="n">
         <v>16778</v>
@@ -36677,7 +36677,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1252" t="n">
         <v>55493</v>
@@ -36706,7 +36706,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692909240723</v>
+        <v>28.2692928314209</v>
       </c>
       <c r="H1253" t="n">
         <v>9517</v>
@@ -36735,7 +36735,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1254" t="n">
         <v>12548</v>
@@ -36880,7 +36880,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1259" t="n">
         <v>38924</v>
@@ -36938,7 +36938,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911674499512</v>
+        <v>26.0911655426025</v>
       </c>
       <c r="H1261" t="n">
         <v>31910</v>
@@ -37083,7 +37083,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131065368652</v>
+        <v>25.8131084442139</v>
       </c>
       <c r="H1266" t="n">
         <v>7598</v>
@@ -37112,7 +37112,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1267" t="n">
         <v>12771</v>
@@ -37170,7 +37170,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1269" t="n">
         <v>18414</v>
@@ -37344,7 +37344,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1275" t="n">
         <v>15913</v>
@@ -37431,7 +37431,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1278" t="n">
         <v>11119</v>
@@ -37489,7 +37489,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1280" t="n">
         <v>11239</v>
@@ -37547,7 +37547,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1282" t="n">
         <v>29030</v>
@@ -37576,7 +37576,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887729644775</v>
+        <v>27.3887710571289</v>
       </c>
       <c r="H1283" t="n">
         <v>13951</v>
@@ -37808,7 +37808,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473518371582</v>
+        <v>28.5473499298096</v>
       </c>
       <c r="H1291" t="n">
         <v>49073</v>
@@ -37837,7 +37837,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1292" t="n">
         <v>22316</v>
@@ -38040,7 +38040,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107158660889</v>
+        <v>27.1107139587402</v>
       </c>
       <c r="H1299" t="n">
         <v>2701</v>
@@ -38156,7 +38156,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1303" t="n">
         <v>11541</v>
@@ -38301,7 +38301,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1308" t="n">
         <v>7747</v>
@@ -38359,7 +38359,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1310" t="n">
         <v>8183</v>
@@ -38533,7 +38533,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1316" t="n">
         <v>8506</v>
@@ -38562,7 +38562,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1317" t="n">
         <v>6463</v>
@@ -38765,7 +38765,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545314788818</v>
+        <v>24.6545295715332</v>
       </c>
       <c r="H1324" t="n">
         <v>11339</v>
@@ -38794,7 +38794,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984134674072</v>
+        <v>24.0984115600586</v>
       </c>
       <c r="H1325" t="n">
         <v>17104</v>
@@ -38852,7 +38852,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033313751221</v>
+        <v>25.3033332824707</v>
       </c>
       <c r="H1327" t="n">
         <v>29720</v>
@@ -38910,7 +38910,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.7204208374023</v>
+        <v>25.720422744751</v>
       </c>
       <c r="H1329" t="n">
         <v>7898</v>
@@ -39229,7 +39229,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350475311279</v>
+        <v>25.5350494384766</v>
       </c>
       <c r="H1340" t="n">
         <v>7940</v>
@@ -39316,7 +39316,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1343" t="n">
         <v>17193</v>
@@ -39345,7 +39345,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1344" t="n">
         <v>16994</v>
@@ -39374,7 +39374,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301940917969</v>
+        <v>26.2301959991455</v>
       </c>
       <c r="H1345" t="n">
         <v>26909</v>
@@ -39432,7 +39432,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1347" t="n">
         <v>13917</v>
@@ -39461,7 +39461,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1348" t="n">
         <v>8737</v>
@@ -39548,7 +39548,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1351" t="n">
         <v>20501</v>
@@ -39577,7 +39577,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.574146270752</v>
+        <v>27.5741443634033</v>
       </c>
       <c r="H1352" t="n">
         <v>16729</v>
@@ -39693,7 +39693,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1356" t="n">
         <v>75277</v>
@@ -39722,7 +39722,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1357" t="n">
         <v>36177</v>
@@ -39751,7 +39751,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1358" t="n">
         <v>16319</v>
@@ -39809,7 +39809,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352504730225</v>
+        <v>31.2352523803711</v>
       </c>
       <c r="H1360" t="n">
         <v>14299</v>
@@ -39867,7 +39867,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1362" t="n">
         <v>13411</v>
@@ -39896,7 +39896,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1363" t="n">
         <v>7826</v>
@@ -39954,7 +39954,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377075195312</v>
+        <v>31.8377113342285</v>
       </c>
       <c r="H1365" t="n">
         <v>22255</v>
@@ -39983,7 +39983,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1366" t="n">
         <v>49622</v>
@@ -40041,7 +40041,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571933746338</v>
+        <v>30.9571914672852</v>
       </c>
       <c r="H1368" t="n">
         <v>11052</v>
@@ -40070,7 +40070,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1369" t="n">
         <v>31735</v>
@@ -40099,7 +40099,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.93039894104</v>
+        <v>31.9303970336914</v>
       </c>
       <c r="H1370" t="n">
         <v>19225</v>
@@ -40244,7 +40244,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596523284912</v>
+        <v>31.5596504211426</v>
       </c>
       <c r="H1375" t="n">
         <v>14100</v>
@@ -40273,7 +40273,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1376" t="n">
         <v>10686</v>
@@ -40302,7 +40302,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1377" t="n">
         <v>13797</v>
@@ -40331,7 +40331,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986827850342</v>
+        <v>31.6986808776855</v>
       </c>
       <c r="H1378" t="n">
         <v>16079</v>
@@ -40476,7 +40476,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182273864746</v>
+        <v>32.7182312011719</v>
       </c>
       <c r="H1383" t="n">
         <v>16458</v>
@@ -40708,7 +40708,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914329528809</v>
+        <v>33.6914367675781</v>
       </c>
       <c r="H1391" t="n">
         <v>5315</v>
@@ -40766,7 +40766,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1393" t="n">
         <v>20537</v>
@@ -40911,7 +40911,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.359790802002</v>
+        <v>35.3597869873047</v>
       </c>
       <c r="H1398" t="n">
         <v>20503</v>
@@ -40969,7 +40969,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1400" t="n">
         <v>25006</v>
@@ -40998,7 +40998,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1401" t="n">
         <v>9472</v>
@@ -41056,7 +41056,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988174438477</v>
+        <v>35.4988136291504</v>
       </c>
       <c r="H1403" t="n">
         <v>23148</v>
@@ -41085,7 +41085,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744155883789</v>
+        <v>35.1744117736816</v>
       </c>
       <c r="H1404" t="n">
         <v>45623</v>
@@ -41114,7 +41114,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1405" t="n">
         <v>28718</v>
@@ -41201,7 +41201,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1408" t="n">
         <v>18517</v>
@@ -41259,7 +41259,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012100219727</v>
+        <v>34.2012138366699</v>
       </c>
       <c r="H1410" t="n">
         <v>15419</v>
@@ -41317,7 +41317,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1412" t="n">
         <v>38690</v>
@@ -41346,7 +41346,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1413" t="n">
         <v>44206</v>
@@ -41404,7 +41404,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1415" t="n">
         <v>21797</v>
@@ -41433,7 +41433,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.518367767334</v>
+        <v>36.5183639526367</v>
       </c>
       <c r="H1416" t="n">
         <v>19385</v>
@@ -41520,7 +41520,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085906982422</v>
+        <v>36.0085868835449</v>
       </c>
       <c r="H1419" t="n">
         <v>19338</v>
@@ -41607,7 +41607,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1422" t="n">
         <v>28131</v>
@@ -41665,7 +41665,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1424" t="n">
         <v>37415</v>
@@ -41926,7 +41926,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059268951416</v>
+        <v>29.7059288024902</v>
       </c>
       <c r="H1433" t="n">
         <v>169855</v>
@@ -41955,7 +41955,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1434" t="n">
         <v>83833</v>
@@ -41984,7 +41984,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1435" t="n">
         <v>50233</v>
@@ -42100,7 +42100,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1439" t="n">
         <v>39783</v>
@@ -42129,7 +42129,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1440" t="n">
         <v>36958</v>
@@ -42187,7 +42187,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1442" t="n">
         <v>39311</v>
@@ -42332,7 +42332,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1447" t="n">
         <v>48734</v>
@@ -42361,7 +42361,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1448" t="n">
         <v>29333</v>
@@ -42419,7 +42419,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1450" t="n">
         <v>74959</v>
@@ -42448,7 +42448,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2034015655518</v>
+        <v>27.2033996582031</v>
       </c>
       <c r="H1451" t="n">
         <v>28955</v>
@@ -42506,7 +42506,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156356811523</v>
+        <v>28.3156337738037</v>
       </c>
       <c r="H1453" t="n">
         <v>45425</v>
@@ -42564,7 +42564,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1455" t="n">
         <v>26258</v>
@@ -42622,7 +42622,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1457" t="n">
         <v>41539</v>
@@ -42767,7 +42767,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1462" t="n">
         <v>27647</v>
@@ -42796,7 +42796,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1463" t="n">
         <v>32514</v>
@@ -42825,7 +42825,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1464" t="n">
         <v>59385</v>
@@ -42912,7 +42912,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1467" t="n">
         <v>22423</v>
@@ -42970,7 +42970,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1469" t="n">
         <v>33838</v>
@@ -42999,7 +42999,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1470" t="n">
         <v>20524</v>
@@ -43028,7 +43028,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1471" t="n">
         <v>38899</v>
@@ -43057,7 +43057,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1472" t="n">
         <v>26587</v>
@@ -43086,7 +43086,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1473" t="n">
         <v>61483</v>
@@ -43202,7 +43202,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1477" t="n">
         <v>81786</v>
@@ -68612,6 +68612,35 @@
         <v>689950</v>
       </c>
       <c r="I2353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2354" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>1.45500004291534</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>1.53799998760223</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>1.45500004291534</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2354" t="n">
+        <v>1551201</v>
+      </c>
+      <c r="I2354" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503189086914</v>
+        <v>44.8503227233887</v>
       </c>
       <c r="H2" t="n">
         <v>2040000</v>
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -543,7 +543,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382469177246</v>
+        <v>47.7382431030273</v>
       </c>
       <c r="H6" t="n">
         <v>100979</v>
@@ -572,7 +572,7 @@
         <v>54.25</v>
       </c>
       <c r="G7" t="n">
-        <v>47.4757080078125</v>
+        <v>47.4757041931152</v>
       </c>
       <c r="H7" t="n">
         <v>58881</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318458557129</v>
+        <v>46.7318496704102</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -630,7 +630,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631134033203</v>
+        <v>46.8631172180176</v>
       </c>
       <c r="H9" t="n">
         <v>27464</v>
@@ -659,7 +659,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H10" t="n">
         <v>24546</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -746,7 +746,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H13" t="n">
         <v>28253</v>
@@ -775,7 +775,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007820129395</v>
+        <v>48.0007858276367</v>
       </c>
       <c r="H14" t="n">
         <v>82998</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695220947266</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -862,7 +862,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319458007812</v>
+        <v>47.4319496154785</v>
       </c>
       <c r="H17" t="n">
         <v>9145</v>
@@ -891,7 +891,7 @@
         <v>54.25</v>
       </c>
       <c r="G18" t="n">
-        <v>47.4757080078125</v>
+        <v>47.4757041931152</v>
       </c>
       <c r="H18" t="n">
         <v>15527</v>
@@ -920,7 +920,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382469177246</v>
+        <v>47.7382431030273</v>
       </c>
       <c r="H19" t="n">
         <v>39604</v>
@@ -949,7 +949,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.081901550293</v>
+        <v>47.0818977355957</v>
       </c>
       <c r="H20" t="n">
         <v>12065</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506301879883</v>
+        <v>46.9506340026855</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1094,7 +1094,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256561279297</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H25" t="n">
         <v>24385</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443328857422</v>
+        <v>46.6443367004395</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1181,7 +1181,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.1192588806152</v>
+        <v>46.119255065918</v>
       </c>
       <c r="H28" t="n">
         <v>23503</v>
@@ -1210,7 +1210,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254447937012</v>
+        <v>45.7254524230957</v>
       </c>
       <c r="H29" t="n">
         <v>15825</v>
@@ -1239,7 +1239,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692031860352</v>
+        <v>45.7692070007324</v>
       </c>
       <c r="H30" t="n">
         <v>7291</v>
@@ -1268,7 +1268,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.513069152832</v>
+        <v>46.5130653381348</v>
       </c>
       <c r="H31" t="n">
         <v>8478</v>
@@ -1355,7 +1355,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567199707031</v>
+        <v>45.8567161560059</v>
       </c>
       <c r="H34" t="n">
         <v>9627</v>
@@ -1384,7 +1384,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256561279297</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H35" t="n">
         <v>35180</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069717407227</v>
+        <v>47.6069755554199</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569236755371</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0882987976074</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695220947266</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1906,7 +1906,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H53" t="n">
         <v>13389</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.519458770752</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944923400879</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -1993,7 +1993,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445442199707</v>
+        <v>48.0445404052734</v>
       </c>
       <c r="H56" t="n">
         <v>39379</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135765075684</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2080,7 +2080,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577499389648</v>
+        <v>52.8577461242676</v>
       </c>
       <c r="H59" t="n">
         <v>33673</v>
@@ -2109,7 +2109,7 @@
         <v>61.5</v>
       </c>
       <c r="G60" t="n">
-        <v>53.8203887939453</v>
+        <v>53.820384979248</v>
       </c>
       <c r="H60" t="n">
         <v>54877</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953071594238</v>
+        <v>53.2953109741211</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589836120605</v>
+        <v>61.2589797973633</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.696533203125</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.696533203125</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2457,7 +2457,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.1340980529785</v>
+        <v>62.134105682373</v>
       </c>
       <c r="H72" t="n">
         <v>24358</v>
@@ -2486,7 +2486,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902397155762</v>
+        <v>61.3902549743652</v>
       </c>
       <c r="H73" t="n">
         <v>19520</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4340057373047</v>
+        <v>61.4339981079102</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964370727539</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2573,7 +2573,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462814331055</v>
+        <v>59.9462852478027</v>
       </c>
       <c r="H76" t="n">
         <v>17560</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838539123535</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2689,7 +2689,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.077564239502</v>
+        <v>60.0775566101074</v>
       </c>
       <c r="H80" t="n">
         <v>17247</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.821403503418</v>
+        <v>60.8214073181152</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2834,7 +2834,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771415710449</v>
       </c>
       <c r="H85" t="n">
         <v>30458</v>
@@ -2863,7 +2863,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H86" t="n">
         <v>30413</v>
@@ -2921,7 +2921,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H88" t="n">
         <v>37736</v>
@@ -2950,7 +2950,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H89" t="n">
         <v>30442</v>
@@ -2979,7 +2979,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273048400879</v>
+        <v>58.3273010253906</v>
       </c>
       <c r="H90" t="n">
         <v>24556</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772415161133</v>
+        <v>57.9772453308105</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711555480957</v>
+        <v>59.0711517333984</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3095,7 +3095,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335983276367</v>
       </c>
       <c r="H94" t="n">
         <v>25066</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.027400970459</v>
+        <v>59.0273933410645</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335983276367</v>
       </c>
       <c r="H97" t="n">
         <v>26035</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834350585938</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3240,7 +3240,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583610534668</v>
+        <v>57.0583572387695</v>
       </c>
       <c r="H99" t="n">
         <v>27245</v>
@@ -3414,7 +3414,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712631225586</v>
+        <v>59.7712593078613</v>
       </c>
       <c r="H105" t="n">
         <v>21082</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525787353516</v>
+        <v>60.2525825500488</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335983276367</v>
       </c>
       <c r="H108" t="n">
         <v>43417</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.745662689209</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3646,7 +3646,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H113" t="n">
         <v>116509</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3791,7 +3791,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648582458496</v>
+        <v>58.7648620605469</v>
       </c>
       <c r="H118" t="n">
         <v>16964</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962333679199</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3936,7 +3936,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.9900436401367</v>
+        <v>59.9900398254395</v>
       </c>
       <c r="H123" t="n">
         <v>14704</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397918701172</v>
+        <v>58.2397842407227</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4023,7 +4023,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H126" t="n">
         <v>36944</v>
@@ -4052,7 +4052,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770454406738</v>
+        <v>56.5770416259766</v>
       </c>
       <c r="H127" t="n">
         <v>42192</v>
@@ -4110,7 +4110,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.270751953125</v>
+        <v>56.2707481384277</v>
       </c>
       <c r="H129" t="n">
         <v>14664</v>
@@ -4139,7 +4139,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3144989013672</v>
+        <v>56.3145027160645</v>
       </c>
       <c r="H130" t="n">
         <v>10098</v>
@@ -4168,7 +4168,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H131" t="n">
         <v>10634</v>
@@ -4197,7 +4197,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146026611328</v>
+        <v>57.0146064758301</v>
       </c>
       <c r="H132" t="n">
         <v>14544</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.620792388916</v>
+        <v>56.6207885742188</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4255,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833312988281</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H134" t="n">
         <v>10051</v>
@@ -4284,7 +4284,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896286010742</v>
+        <v>57.1896362304688</v>
       </c>
       <c r="H135" t="n">
         <v>6298</v>
@@ -4400,7 +4400,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.795825958252</v>
       </c>
       <c r="H139" t="n">
         <v>15720</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582649230957</v>
+        <v>56.3582572937012</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.470329284668</v>
+        <v>53.4703369140625</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4690,7 +4690,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H149" t="n">
         <v>19902</v>
@@ -4719,7 +4719,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264785766602</v>
       </c>
       <c r="H150" t="n">
         <v>21367</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4777,7 +4777,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H152" t="n">
         <v>6908</v>
@@ -4806,7 +4806,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H153" t="n">
         <v>14177</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4922,7 +4922,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.113883972168</v>
+        <v>52.1138877868652</v>
       </c>
       <c r="H157" t="n">
         <v>24689</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326683044434</v>
+        <v>52.3326721191406</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -5038,7 +5038,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H161" t="n">
         <v>19271</v>
@@ -5067,7 +5067,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196739196777</v>
+        <v>48.9196662902832</v>
       </c>
       <c r="H162" t="n">
         <v>15929</v>
@@ -5125,7 +5125,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H164" t="n">
         <v>9928</v>
@@ -5154,7 +5154,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883987426758</v>
+        <v>48.788402557373</v>
       </c>
       <c r="H165" t="n">
         <v>49976</v>
@@ -5183,7 +5183,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H166" t="n">
         <v>9806</v>
@@ -5270,7 +5270,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265785217285</v>
+        <v>53.4265747070312</v>
       </c>
       <c r="H169" t="n">
         <v>13847</v>
@@ -5299,7 +5299,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H170" t="n">
         <v>15151</v>
@@ -5328,7 +5328,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G171" t="n">
-        <v>52.2014007568359</v>
+        <v>52.2013969421387</v>
       </c>
       <c r="H171" t="n">
         <v>6434</v>
@@ -5357,7 +5357,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8951034545898</v>
+        <v>51.8950996398926</v>
       </c>
       <c r="H172" t="n">
         <v>4493</v>
@@ -5415,7 +5415,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>52.2014007568359</v>
+        <v>52.2013969421387</v>
       </c>
       <c r="H174" t="n">
         <v>4529</v>
@@ -5444,7 +5444,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H175" t="n">
         <v>7119</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.7510414123535</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5560,7 +5560,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H179" t="n">
         <v>6559</v>
@@ -5589,7 +5589,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H180" t="n">
         <v>6556</v>
@@ -5647,7 +5647,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H182" t="n">
         <v>28706</v>
@@ -5734,7 +5734,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264785766602</v>
       </c>
       <c r="H185" t="n">
         <v>20301</v>
@@ -5763,7 +5763,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890098571777</v>
+        <v>52.9890174865723</v>
       </c>
       <c r="H186" t="n">
         <v>12495</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516525268555</v>
+        <v>53.95166015625</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140991210938</v>
+        <v>53.5140914916992</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -5966,7 +5966,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H193" t="n">
         <v>9212</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077903747559</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2077903747559</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6111,7 +6111,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G198" t="n">
-        <v>56.4020118713379</v>
+        <v>56.4020156860352</v>
       </c>
       <c r="H198" t="n">
         <v>18097</v>
@@ -6140,7 +6140,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519676208496</v>
+        <v>56.0519638061523</v>
       </c>
       <c r="H199" t="n">
         <v>8382</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6256,7 +6256,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="n">
         <v>6842</v>
@@ -6285,7 +6285,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891174316406</v>
+        <v>53.6891098022461</v>
       </c>
       <c r="H204" t="n">
         <v>7160</v>
@@ -6314,7 +6314,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391654968262</v>
+        <v>54.0391731262207</v>
       </c>
       <c r="H205" t="n">
         <v>7569</v>
@@ -6343,7 +6343,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078979492188</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H206" t="n">
         <v>2508</v>
@@ -6401,7 +6401,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830276489258</v>
+        <v>54.7830238342285</v>
       </c>
       <c r="H208" t="n">
         <v>8498</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390693664551</v>
+        <v>53.3390655517578</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6517,7 +6517,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.2205924987793</v>
+        <v>55.220588684082</v>
       </c>
       <c r="H212" t="n">
         <v>2916</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823051452637</v>
+        <v>49.8823089599609</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695220947266</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6633,7 +6633,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623001098633</v>
+        <v>44.662296295166</v>
       </c>
       <c r="H216" t="n">
         <v>40064</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.617992401123</v>
+        <v>44.6179847717285</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6720,7 +6720,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>45.8143005371094</v>
+        <v>45.8143043518066</v>
       </c>
       <c r="H219" t="n">
         <v>12637</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6807,7 +6807,7 @@
         <v>45.5750007629395</v>
       </c>
       <c r="G222" t="n">
-        <v>40.3865966796875</v>
+        <v>40.3865928649902</v>
       </c>
       <c r="H222" t="n">
         <v>50890</v>
@@ -6836,7 +6836,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.9755249023438</v>
+        <v>43.975528717041</v>
       </c>
       <c r="H223" t="n">
         <v>24305</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019859313965</v>
+        <v>42.601978302002</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025993347168</v>
+        <v>42.4025955200195</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7126,7 +7126,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H233" t="n">
         <v>12552</v>
@@ -7184,7 +7184,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.453685760498</v>
+        <v>47.4536933898926</v>
       </c>
       <c r="H235" t="n">
         <v>27871</v>
@@ -7213,7 +7213,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272361755371</v>
+        <v>48.8272285461426</v>
       </c>
       <c r="H236" t="n">
         <v>13514</v>
@@ -7242,7 +7242,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.2955360412598</v>
+        <v>48.295539855957</v>
       </c>
       <c r="H237" t="n">
         <v>20676</v>
@@ -7271,7 +7271,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755485534668</v>
+        <v>51.1755523681641</v>
       </c>
       <c r="H238" t="n">
         <v>56868</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475402832031</v>
+        <v>49.4475440979004</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7329,7 +7329,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361633300781</v>
+        <v>49.5361595153809</v>
       </c>
       <c r="H240" t="n">
         <v>97891</v>
@@ -7387,7 +7387,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.1816940307617</v>
+        <v>49.181697845459</v>
       </c>
       <c r="H242" t="n">
         <v>12836</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158515930176</v>
+        <v>48.9158477783203</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7619,7 +7619,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H250" t="n">
         <v>14687</v>
@@ -7677,7 +7677,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715438842773</v>
+        <v>48.8715362548828</v>
       </c>
       <c r="H252" t="n">
         <v>19047</v>
@@ -7764,7 +7764,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.3398475646973</v>
+        <v>48.33984375</v>
       </c>
       <c r="H255" t="n">
         <v>7923</v>
@@ -7822,7 +7822,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.852466583252</v>
+        <v>47.8524627685547</v>
       </c>
       <c r="H257" t="n">
         <v>5700</v>
@@ -7851,7 +7851,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>47.8967704772949</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H258" t="n">
         <v>6947</v>
@@ -7880,7 +7880,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>47.8967704772949</v>
+        <v>47.8967666625977</v>
       </c>
       <c r="H259" t="n">
         <v>3097</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -7996,7 +7996,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496849060059</v>
+        <v>45.1496887207031</v>
       </c>
       <c r="H263" t="n">
         <v>17681</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192230224609</v>
+        <v>44.2192192077637</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8054,7 +8054,7 @@
         <v>50</v>
       </c>
       <c r="G265" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H265" t="n">
         <v>13686</v>
@@ -8083,7 +8083,7 @@
         <v>50</v>
       </c>
       <c r="G266" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H266" t="n">
         <v>13575</v>
@@ -8112,7 +8112,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.3016815185547</v>
+        <v>46.3016891479492</v>
       </c>
       <c r="H267" t="n">
         <v>13254</v>
@@ -8141,7 +8141,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927581787109</v>
+        <v>45.5927619934082</v>
       </c>
       <c r="H268" t="n">
         <v>9230</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.3712272644043</v>
+        <v>45.371223449707</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8199,7 +8199,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939964294434</v>
+        <v>45.1939926147461</v>
       </c>
       <c r="H270" t="n">
         <v>9794</v>
@@ -8228,7 +8228,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346122741699</v>
+        <v>46.4346084594727</v>
       </c>
       <c r="H271" t="n">
         <v>6611</v>
@@ -8257,7 +8257,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232276916504</v>
+        <v>46.5232238769531</v>
       </c>
       <c r="H272" t="n">
         <v>8521</v>
@@ -8315,7 +8315,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586120605469</v>
+        <v>45.8586082458496</v>
       </c>
       <c r="H274" t="n">
         <v>4374</v>
@@ -8344,7 +8344,7 @@
         <v>50</v>
       </c>
       <c r="G275" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H275" t="n">
         <v>10055</v>
@@ -8402,7 +8402,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432113647461</v>
       </c>
       <c r="H277" t="n">
         <v>2613</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8518,7 +8518,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121360778809</v>
+        <v>42.9121398925781</v>
       </c>
       <c r="H281" t="n">
         <v>13077</v>
@@ -8634,7 +8634,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761421203613</v>
+        <v>43.7761459350586</v>
       </c>
       <c r="H285" t="n">
         <v>11503</v>
@@ -8663,7 +8663,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216728210449</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H286" t="n">
         <v>13125</v>
@@ -8692,7 +8692,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324440002441</v>
+        <v>43.5324478149414</v>
       </c>
       <c r="H287" t="n">
         <v>11020</v>
@@ -8750,7 +8750,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222938537598</v>
+        <v>43.2222900390625</v>
       </c>
       <c r="H289" t="n">
         <v>13085</v>
@@ -8779,7 +8779,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H290" t="n">
         <v>2864</v>
@@ -8837,7 +8837,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.2001419067383</v>
+        <v>43.200138092041</v>
       </c>
       <c r="H292" t="n">
         <v>25355</v>
@@ -8866,7 +8866,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H293" t="n">
         <v>11169</v>
@@ -8924,7 +8924,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H295" t="n">
         <v>8398</v>
@@ -8953,7 +8953,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450592041016</v>
+        <v>43.0450630187988</v>
       </c>
       <c r="H296" t="n">
         <v>6836</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444496154785</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9011,7 +9011,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H298" t="n">
         <v>11117</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444496154785</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9098,7 +9098,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H301" t="n">
         <v>1288</v>
@@ -9127,7 +9127,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539901733398</v>
+        <v>43.7539863586426</v>
       </c>
       <c r="H302" t="n">
         <v>6369</v>
@@ -9185,7 +9185,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216728210449</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H304" t="n">
         <v>13328</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349090576172</v>
+        <v>42.7349014282227</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9446,7 +9446,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H313" t="n">
         <v>4752</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638236999512</v>
+        <v>40.5638275146484</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.946590423584</v>
+        <v>38.9465827941895</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9591,7 +9591,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112022399902</v>
+        <v>39.6112060546875</v>
       </c>
       <c r="H318" t="n">
         <v>13054</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213600158691</v>
+        <v>39.9213562011719</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9765,7 +9765,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4308967590332</v>
+        <v>40.4309005737305</v>
       </c>
       <c r="H324" t="n">
         <v>19512</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10142,7 +10142,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H337" t="n">
         <v>2833</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10200,7 +10200,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462898254395</v>
+        <v>42.6462936401367</v>
       </c>
       <c r="H339" t="n">
         <v>10608</v>
@@ -10258,7 +10258,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696800231934</v>
+        <v>42.2696762084961</v>
       </c>
       <c r="H341" t="n">
         <v>4403</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912109375</v>
+        <v>42.4912147521973</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764587402344</v>
+        <v>47.2764625549316</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10693,7 +10693,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992317199707</v>
+        <v>47.0992279052734</v>
       </c>
       <c r="H356" t="n">
         <v>3633</v>
@@ -10867,7 +10867,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432113647461</v>
       </c>
       <c r="H362" t="n">
         <v>6139</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419921875</v>
+        <v>44.0419883728027</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10925,7 +10925,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H364" t="n">
         <v>1387</v>
@@ -11041,7 +11041,7 @@
         <v>45.25</v>
       </c>
       <c r="G368" t="n">
-        <v>40.0985946655273</v>
+        <v>40.0985870361328</v>
       </c>
       <c r="H368" t="n">
         <v>8869</v>
@@ -11128,7 +11128,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625968933105</v>
+        <v>40.9625930786133</v>
       </c>
       <c r="H371" t="n">
         <v>7882</v>
@@ -11157,7 +11157,7 @@
         <v>50</v>
       </c>
       <c r="G372" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H372" t="n">
         <v>19533</v>
@@ -11244,7 +11244,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118431091309</v>
+        <v>46.6118469238281</v>
       </c>
       <c r="H375" t="n">
         <v>5727</v>
@@ -11273,7 +11273,7 @@
         <v>55.25</v>
       </c>
       <c r="G376" t="n">
-        <v>48.9601593017578</v>
+        <v>48.9601631164551</v>
       </c>
       <c r="H376" t="n">
         <v>10916</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780059814453</v>
+        <v>50.3780097961426</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11418,7 +11418,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H381" t="n">
         <v>8438</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958564758301</v>
+        <v>51.7958602905273</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121559143066</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11563,7 +11563,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589286804199</v>
+        <v>49.3589248657227</v>
       </c>
       <c r="H386" t="n">
         <v>5737</v>
@@ -11592,7 +11592,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="n">
         <v>12225</v>
@@ -11621,7 +11621,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463172912598</v>
+        <v>49.8463096618652</v>
       </c>
       <c r="H388" t="n">
         <v>9469</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11766,7 +11766,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263221740723</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H393" t="n">
         <v>9144</v>
@@ -11795,7 +11795,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263221740723</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H394" t="n">
         <v>11783</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555534362793</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11911,7 +11911,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466377258301</v>
+        <v>53.3466339111328</v>
       </c>
       <c r="H398" t="n">
         <v>16109</v>
@@ -11969,7 +11969,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.3909378051758</v>
+        <v>53.390941619873</v>
       </c>
       <c r="H400" t="n">
         <v>20005</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657150268555</v>
+        <v>54.3657112121582</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12027,7 +12027,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961807250977</v>
+        <v>55.2961769104004</v>
       </c>
       <c r="H402" t="n">
         <v>18544</v>
@@ -12056,7 +12056,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164848327637</v>
       </c>
       <c r="H403" t="n">
         <v>55252</v>
@@ -12085,7 +12085,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H404" t="n">
         <v>12420</v>
@@ -12172,7 +12172,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.6124801635742</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H407" t="n">
         <v>16902</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555534362793</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12230,7 +12230,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380233764648</v>
+        <v>56.1380271911621</v>
       </c>
       <c r="H409" t="n">
         <v>12835</v>
@@ -12259,7 +12259,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.777416229248</v>
+        <v>57.7774124145508</v>
       </c>
       <c r="H410" t="n">
         <v>15892</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.157112121582</v>
+        <v>57.1571083068848</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12375,7 +12375,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.783561706543</v>
+        <v>55.7835655212402</v>
       </c>
       <c r="H414" t="n">
         <v>6786</v>
@@ -12491,7 +12491,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H418" t="n">
         <v>12366</v>
@@ -12520,7 +12520,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038734436035</v>
+        <v>56.4038772583008</v>
       </c>
       <c r="H419" t="n">
         <v>16100</v>
@@ -12549,7 +12549,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.3595657348633</v>
+        <v>56.359561920166</v>
       </c>
       <c r="H420" t="n">
         <v>35472</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12607,7 +12607,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>57.4672584533691</v>
+        <v>57.4672622680664</v>
       </c>
       <c r="H422" t="n">
         <v>5806</v>
@@ -12665,7 +12665,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H424" t="n">
         <v>12768</v>
@@ -12694,7 +12694,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H425" t="n">
         <v>11750</v>
@@ -12810,7 +12810,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H429" t="n">
         <v>9582</v>
@@ -12839,7 +12839,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H430" t="n">
         <v>4618</v>
@@ -12955,7 +12955,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478645324707</v>
+        <v>52.9478607177734</v>
       </c>
       <c r="H434" t="n">
         <v>15198</v>
@@ -12984,7 +12984,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0173988342285</v>
+        <v>52.0174026489258</v>
       </c>
       <c r="H435" t="n">
         <v>15195</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.523868560791</v>
+        <v>53.5238647460938</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13129,7 +13129,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H440" t="n">
         <v>5382</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026466369629</v>
+        <v>56.8026428222656</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13216,7 +13216,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G443" t="n">
-        <v>55.7392539978027</v>
+        <v>55.7392578125</v>
       </c>
       <c r="H443" t="n">
         <v>5854</v>
@@ -13245,7 +13245,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H444" t="n">
         <v>6381</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13303,7 +13303,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H446" t="n">
         <v>7435</v>
@@ -13332,7 +13332,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H447" t="n">
         <v>11987</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254119873047</v>
+        <v>56.6254196166992</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13419,7 +13419,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H450" t="n">
         <v>5021</v>
@@ -13448,7 +13448,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164848327637</v>
       </c>
       <c r="H451" t="n">
         <v>1739</v>
@@ -13477,7 +13477,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>55.7392539978027</v>
+        <v>55.7392578125</v>
       </c>
       <c r="H452" t="n">
         <v>2949</v>
@@ -13535,7 +13535,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506385803223</v>
+        <v>55.6506423950195</v>
       </c>
       <c r="H454" t="n">
         <v>5826</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555534362793</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13651,7 +13651,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.7010955810547</v>
+        <v>53.701099395752</v>
       </c>
       <c r="H458" t="n">
         <v>31030</v>
@@ -13680,7 +13680,7 @@
         <v>61.5</v>
       </c>
       <c r="G459" t="n">
-        <v>54.4986381530762</v>
+        <v>54.4986343383789</v>
       </c>
       <c r="H459" t="n">
         <v>7761</v>
@@ -13854,7 +13854,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743217468262</v>
+        <v>51.5743179321289</v>
       </c>
       <c r="H465" t="n">
         <v>7910</v>
@@ -13912,7 +13912,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450904846191</v>
+        <v>50.2450866699219</v>
       </c>
       <c r="H467" t="n">
         <v>8697</v>
@@ -14057,7 +14057,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569076538086</v>
+        <v>50.0569038391113</v>
       </c>
       <c r="H472" t="n">
         <v>6766</v>
@@ -14115,7 +14115,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H474" t="n">
         <v>11773</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14231,7 +14231,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>47.0912399291992</v>
+        <v>47.091236114502</v>
       </c>
       <c r="H478" t="n">
         <v>29594</v>
@@ -14260,7 +14260,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H479" t="n">
         <v>117335</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14347,7 +14347,7 @@
         <v>53.5</v>
       </c>
       <c r="G482" t="n">
-        <v>48.0797958374023</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H482" t="n">
         <v>3928</v>
@@ -14434,7 +14434,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H485" t="n">
         <v>17601</v>
@@ -14579,7 +14579,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H490" t="n">
         <v>8141</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14724,7 +14724,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.697437286377</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H495" t="n">
         <v>6839</v>
@@ -14782,7 +14782,7 @@
         <v>58</v>
       </c>
       <c r="G497" t="n">
-        <v>52.123893737793</v>
+        <v>52.1238899230957</v>
       </c>
       <c r="H497" t="n">
         <v>7368</v>
@@ -15014,7 +15014,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477210998535</v>
+        <v>56.3477249145508</v>
       </c>
       <c r="H505" t="n">
         <v>11751</v>
@@ -15043,7 +15043,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666694641113</v>
+        <v>57.0666732788086</v>
       </c>
       <c r="H506" t="n">
         <v>15695</v>
@@ -15072,7 +15072,7 @@
         <v>61</v>
       </c>
       <c r="G507" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199501037598</v>
       </c>
       <c r="H507" t="n">
         <v>21501</v>
@@ -15130,7 +15130,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H509" t="n">
         <v>5019</v>
@@ -15217,7 +15217,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H512" t="n">
         <v>3818</v>
@@ -15246,7 +15246,7 @@
         <v>61</v>
       </c>
       <c r="G513" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199501037598</v>
       </c>
       <c r="H513" t="n">
         <v>4354</v>
@@ -15304,7 +15304,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.7415313720703</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H515" t="n">
         <v>5949</v>
@@ -15333,7 +15333,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8313941955566</v>
       </c>
       <c r="H516" t="n">
         <v>4297</v>
@@ -15362,7 +15362,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111351013184</v>
+        <v>54.0111312866211</v>
       </c>
       <c r="H517" t="n">
         <v>1572</v>
@@ -15478,7 +15478,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H521" t="n">
         <v>4391</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137603759766</v>
+        <v>52.2137565612793</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15536,7 +15536,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353340148926</v>
+        <v>51.1353378295898</v>
       </c>
       <c r="H523" t="n">
         <v>2020</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644119262695</v>
+        <v>51.7644157409668</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15594,7 +15594,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.697437286377</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H525" t="n">
         <v>128694</v>
@@ -15623,7 +15623,7 @@
         <v>53.5</v>
       </c>
       <c r="G526" t="n">
-        <v>48.0797958374023</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H526" t="n">
         <v>45916</v>
@@ -15710,7 +15710,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H529" t="n">
         <v>9560</v>
@@ -15739,7 +15739,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H530" t="n">
         <v>3420</v>
@@ -15768,7 +15768,7 @@
         <v>53.5</v>
       </c>
       <c r="G531" t="n">
-        <v>48.0797958374023</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H531" t="n">
         <v>7140</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15884,7 +15884,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H535" t="n">
         <v>48609</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603721618652</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16261,7 +16261,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696662902832</v>
       </c>
       <c r="H548" t="n">
         <v>5805</v>
@@ -16319,7 +16319,7 @@
         <v>53.5</v>
       </c>
       <c r="G550" t="n">
-        <v>48.0797958374023</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H550" t="n">
         <v>11825</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16493,7 +16493,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H556" t="n">
         <v>14230</v>
@@ -16522,7 +16522,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H557" t="n">
         <v>5027</v>
@@ -16551,7 +16551,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H558" t="n">
         <v>8255</v>
@@ -16580,7 +16580,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H559" t="n">
         <v>15220</v>
@@ -16609,7 +16609,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H560" t="n">
         <v>18625</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16725,7 +16725,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H564" t="n">
         <v>7354</v>
@@ -16812,7 +16812,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H567" t="n">
         <v>24457</v>
@@ -16841,7 +16841,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>45.2039909362793</v>
+        <v>45.2039947509766</v>
       </c>
       <c r="H568" t="n">
         <v>1835</v>
@@ -16870,7 +16870,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H569" t="n">
         <v>7932</v>
@@ -16928,7 +16928,7 @@
         <v>53.5</v>
       </c>
       <c r="G571" t="n">
-        <v>48.0797958374023</v>
+        <v>48.0797920227051</v>
       </c>
       <c r="H571" t="n">
         <v>6282</v>
@@ -17044,7 +17044,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379554748535</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H575" t="n">
         <v>4241</v>
@@ -17073,7 +17073,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H576" t="n">
         <v>5068</v>
@@ -17131,7 +17131,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="n">
         <v>3272</v>
@@ -17160,7 +17160,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="n">
         <v>3967</v>
@@ -17189,7 +17189,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657264709473</v>
+        <v>50.86572265625</v>
       </c>
       <c r="H580" t="n">
         <v>33442</v>
@@ -17218,7 +17218,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657264709473</v>
+        <v>50.86572265625</v>
       </c>
       <c r="H581" t="n">
         <v>21771</v>
@@ -17247,7 +17247,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H582" t="n">
         <v>5028</v>
@@ -17276,7 +17276,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G583" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H583" t="n">
         <v>16905</v>
@@ -17363,7 +17363,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732307434082</v>
+        <v>52.5732345581055</v>
       </c>
       <c r="H586" t="n">
         <v>22708</v>
@@ -17479,7 +17479,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H590" t="n">
         <v>18775</v>
@@ -17508,7 +17508,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G591" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H591" t="n">
         <v>9843</v>
@@ -17537,7 +17537,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.2366485595703</v>
+        <v>50.236644744873</v>
       </c>
       <c r="H592" t="n">
         <v>13961</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17711,7 +17711,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H598" t="n">
         <v>23794</v>
@@ -17769,7 +17769,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H600" t="n">
         <v>24224</v>
@@ -17827,7 +17827,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H602" t="n">
         <v>37767</v>
@@ -17856,7 +17856,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H603" t="n">
         <v>36430</v>
@@ -17943,7 +17943,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H606" t="n">
         <v>25059</v>
@@ -17972,7 +17972,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H607" t="n">
         <v>15227</v>
@@ -18030,7 +18030,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H609" t="n">
         <v>12898</v>
@@ -18088,7 +18088,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H611" t="n">
         <v>7555</v>
@@ -18146,7 +18146,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H613" t="n">
         <v>8437</v>
@@ -18233,7 +18233,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582260131836</v>
       </c>
       <c r="H616" t="n">
         <v>15159</v>
@@ -18262,7 +18262,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H617" t="n">
         <v>22606</v>
@@ -18320,7 +18320,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H619" t="n">
         <v>81517</v>
@@ -18349,7 +18349,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173248291016</v>
       </c>
       <c r="H620" t="n">
         <v>114943</v>
@@ -18465,7 +18465,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173248291016</v>
       </c>
       <c r="H624" t="n">
         <v>9412</v>
@@ -18494,7 +18494,7 @@
         <v>61</v>
       </c>
       <c r="G625" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199501037598</v>
       </c>
       <c r="H625" t="n">
         <v>14322</v>
@@ -18523,7 +18523,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.4719200134277</v>
+        <v>53.471923828125</v>
       </c>
       <c r="H626" t="n">
         <v>14829</v>
@@ -18610,7 +18610,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098205566406</v>
+        <v>54.9098243713379</v>
       </c>
       <c r="H629" t="n">
         <v>33501</v>
@@ -18639,7 +18639,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.1010055541992</v>
+        <v>54.101001739502</v>
       </c>
       <c r="H630" t="n">
         <v>9653</v>
@@ -18668,7 +18668,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516571044922</v>
+        <v>53.6516609191895</v>
       </c>
       <c r="H631" t="n">
         <v>10031</v>
@@ -18697,7 +18697,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111351013184</v>
+        <v>54.0111312866211</v>
       </c>
       <c r="H632" t="n">
         <v>15661</v>
@@ -18755,7 +18755,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8313941955566</v>
       </c>
       <c r="H634" t="n">
         <v>16777</v>
@@ -18784,7 +18784,7 @@
         <v>61</v>
       </c>
       <c r="G635" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199501037598</v>
       </c>
       <c r="H635" t="n">
         <v>37857</v>
@@ -18871,7 +18871,7 @@
         <v>61</v>
       </c>
       <c r="G638" t="n">
-        <v>54.819953918457</v>
+        <v>54.8199501037598</v>
       </c>
       <c r="H638" t="n">
         <v>10943</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19219,7 +19219,7 @@
         <v>58</v>
       </c>
       <c r="G650" t="n">
-        <v>52.123893737793</v>
+        <v>52.1238899230957</v>
       </c>
       <c r="H650" t="n">
         <v>17538</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19393,7 +19393,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173248291016</v>
       </c>
       <c r="H656" t="n">
         <v>87829</v>
@@ -19422,7 +19422,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071990966797</v>
       </c>
       <c r="H657" t="n">
         <v>41152</v>
@@ -19451,7 +19451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071990966797</v>
       </c>
       <c r="H658" t="n">
         <v>26511</v>
@@ -19480,7 +19480,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578544616699</v>
+        <v>56.2578506469727</v>
       </c>
       <c r="H659" t="n">
         <v>14809</v>
@@ -19509,7 +19509,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300834655762</v>
+        <v>54.7300872802734</v>
       </c>
       <c r="H660" t="n">
         <v>38065</v>
@@ -19567,7 +19567,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H662" t="n">
         <v>35448</v>
@@ -19596,7 +19596,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.7415313720703</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H663" t="n">
         <v>43542</v>
@@ -19654,7 +19654,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657264709473</v>
+        <v>50.86572265625</v>
       </c>
       <c r="H665" t="n">
         <v>44030</v>
@@ -19683,7 +19683,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379554748535</v>
+        <v>49.3379592895508</v>
       </c>
       <c r="H666" t="n">
         <v>33866</v>
@@ -19712,7 +19712,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948081970215</v>
+        <v>51.4948043823242</v>
       </c>
       <c r="H667" t="n">
         <v>35732</v>
@@ -19741,7 +19741,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H668" t="n">
         <v>31289</v>
@@ -19770,7 +19770,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H669" t="n">
         <v>36876</v>
@@ -19857,7 +19857,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916038513184</v>
+        <v>39.9916000366211</v>
       </c>
       <c r="H672" t="n">
         <v>35845</v>
@@ -19915,7 +19915,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.116641998291</v>
+        <v>33.1166458129883</v>
       </c>
       <c r="H674" t="n">
         <v>38571</v>
@@ -20060,7 +20060,7 @@
         <v>26.75</v>
       </c>
       <c r="G679" t="n">
-        <v>24.0398979187012</v>
+        <v>24.0398960113525</v>
       </c>
       <c r="H679" t="n">
         <v>36114</v>
@@ -20089,7 +20089,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7367992401123</v>
+        <v>22.7368011474609</v>
       </c>
       <c r="H680" t="n">
         <v>105256</v>
@@ -20205,7 +20205,7 @@
         <v>32</v>
       </c>
       <c r="G684" t="n">
-        <v>28.7580070495605</v>
+        <v>28.7580089569092</v>
       </c>
       <c r="H684" t="n">
         <v>20060</v>
@@ -20234,7 +20234,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024688720703</v>
+        <v>25.7024707794189</v>
       </c>
       <c r="H685" t="n">
         <v>34700</v>
@@ -20292,7 +20292,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879318237305</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H687" t="n">
         <v>17426</v>
@@ -20321,7 +20321,7 @@
         <v>29</v>
       </c>
       <c r="G688" t="n">
-        <v>26.0619468688965</v>
+        <v>26.0619449615479</v>
       </c>
       <c r="H688" t="n">
         <v>24393</v>
@@ -20350,7 +20350,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328632354736</v>
+        <v>25.432861328125</v>
       </c>
       <c r="H689" t="n">
         <v>33327</v>
@@ -20379,7 +20379,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.59055519104</v>
+        <v>23.5905532836914</v>
       </c>
       <c r="H690" t="n">
         <v>49158</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.455753326416</v>
+        <v>23.4557514190674</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20437,7 +20437,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879318237305</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H692" t="n">
         <v>106161</v>
@@ -20495,7 +20495,7 @@
         <v>30.5</v>
       </c>
       <c r="G694" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099750518799</v>
       </c>
       <c r="H694" t="n">
         <v>37669</v>
@@ -20669,7 +20669,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258285522461</v>
+        <v>26.8258304595947</v>
       </c>
       <c r="H700" t="n">
         <v>41033</v>
@@ -20727,7 +20727,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201084136963</v>
+        <v>27.3201065063477</v>
       </c>
       <c r="H702" t="n">
         <v>11386</v>
@@ -20814,7 +20814,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H705" t="n">
         <v>71298</v>
@@ -20843,7 +20843,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>31.7236785888672</v>
+        <v>31.7236747741699</v>
       </c>
       <c r="H706" t="n">
         <v>93719</v>
@@ -20872,7 +20872,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857799530029</v>
+        <v>30.2857780456543</v>
       </c>
       <c r="H707" t="n">
         <v>60261</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130737304688</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -20930,7 +20930,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.3086624145508</v>
       </c>
       <c r="H709" t="n">
         <v>38489</v>
@@ -20959,7 +20959,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.0505027770996</v>
+        <v>27.050500869751</v>
       </c>
       <c r="H710" t="n">
         <v>34512</v>
@@ -21017,7 +21017,7 @@
         <v>30.5</v>
       </c>
       <c r="G712" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099750518799</v>
       </c>
       <c r="H712" t="n">
         <v>17158</v>
@@ -21104,7 +21104,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359600067139</v>
+        <v>26.7359619140625</v>
       </c>
       <c r="H715" t="n">
         <v>47799</v>
@@ -21133,7 +21133,7 @@
         <v>29</v>
       </c>
       <c r="G716" t="n">
-        <v>26.0619468688965</v>
+        <v>26.0619449615479</v>
       </c>
       <c r="H716" t="n">
         <v>39181</v>
@@ -21249,7 +21249,7 @@
         <v>30.5</v>
       </c>
       <c r="G720" t="n">
-        <v>27.4099769592285</v>
+        <v>27.4099750518799</v>
       </c>
       <c r="H720" t="n">
         <v>38236</v>
@@ -21394,7 +21394,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G725" t="n">
-        <v>29.0725498199463</v>
+        <v>29.072546005249</v>
       </c>
       <c r="H725" t="n">
         <v>48547</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566982269287</v>
+        <v>29.6566963195801</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21481,7 +21481,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959095001221</v>
+        <v>30.1959056854248</v>
       </c>
       <c r="H728" t="n">
         <v>39492</v>
@@ -21510,7 +21510,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743358612061</v>
+        <v>31.2743339538574</v>
       </c>
       <c r="H729" t="n">
         <v>35167</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990043640137</v>
+        <v>31.4990062713623</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21597,7 +21597,7 @@
         <v>36.5</v>
       </c>
       <c r="G732" t="n">
-        <v>32.8021011352539</v>
+        <v>32.8021049499512</v>
       </c>
       <c r="H732" t="n">
         <v>87694</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241500854492</v>
+        <v>34.8241539001465</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21713,7 +21713,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H736" t="n">
         <v>76858</v>
@@ -21742,7 +21742,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060390472412</v>
+        <v>30.1060409545898</v>
       </c>
       <c r="H737" t="n">
         <v>76564</v>
@@ -21887,7 +21887,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373802185059</v>
+        <v>36.0373725891113</v>
       </c>
       <c r="H742" t="n">
         <v>82973</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.5431022644043</v>
+        <v>35.5430946350098</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -21945,7 +21945,7 @@
         <v>41</v>
       </c>
       <c r="G744" t="n">
-        <v>36.8461952209473</v>
+        <v>36.8461990356445</v>
       </c>
       <c r="H744" t="n">
         <v>59580</v>
@@ -21974,7 +21974,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298721313477</v>
+        <v>34.3298759460449</v>
       </c>
       <c r="H745" t="n">
         <v>55801</v>
@@ -22003,7 +22003,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>34.8690872192383</v>
+        <v>34.869083404541</v>
       </c>
       <c r="H746" t="n">
         <v>44390</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823135375977</v>
+        <v>36.0823173522949</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22264,7 +22264,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2840995788574</v>
+        <v>38.2840957641602</v>
       </c>
       <c r="H755" t="n">
         <v>52989</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202140808105</v>
+        <v>37.5202102661133</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22351,7 +22351,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H758" t="n">
         <v>54121</v>
@@ -22409,7 +22409,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.283260345459</v>
+        <v>42.2832565307617</v>
       </c>
       <c r="H760" t="n">
         <v>39270</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22496,7 +22496,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224754333496</v>
+        <v>42.8224716186523</v>
       </c>
       <c r="H763" t="n">
         <v>25169</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22728,7 +22728,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0250968933105</v>
+        <v>41.0251007080078</v>
       </c>
       <c r="H771" t="n">
         <v>23411</v>
@@ -22873,7 +22873,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991119384766</v>
+        <v>41.6991157531738</v>
       </c>
       <c r="H776" t="n">
         <v>46090</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -22931,7 +22931,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H778" t="n">
         <v>34460</v>
@@ -23047,7 +23047,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H782" t="n">
         <v>12518</v>
@@ -23076,7 +23076,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H783" t="n">
         <v>15651</v>
@@ -23134,7 +23134,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H785" t="n">
         <v>14310</v>
@@ -23250,7 +23250,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>43.2718162536621</v>
+        <v>43.2718124389648</v>
       </c>
       <c r="H789" t="n">
         <v>32576</v>
@@ -23279,7 +23279,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G790" t="n">
-        <v>43.2718162536621</v>
+        <v>43.2718124389648</v>
       </c>
       <c r="H790" t="n">
         <v>17846</v>
@@ -23395,7 +23395,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H794" t="n">
         <v>19217</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23511,7 +23511,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.9572715759277</v>
+        <v>42.957275390625</v>
       </c>
       <c r="H798" t="n">
         <v>12261</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23569,7 +23569,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889785766602</v>
       </c>
       <c r="H800" t="n">
         <v>29039</v>
@@ -23627,7 +23627,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.5863571166992</v>
+        <v>43.586353302002</v>
       </c>
       <c r="H802" t="n">
         <v>53936</v>
@@ -23685,7 +23685,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H804" t="n">
         <v>10945</v>
@@ -23743,7 +23743,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G806" t="n">
-        <v>42.3731269836426</v>
+        <v>42.3731307983398</v>
       </c>
       <c r="H806" t="n">
         <v>14107</v>
@@ -23917,7 +23917,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G812" t="n">
-        <v>37.3854141235352</v>
+        <v>37.3854103088379</v>
       </c>
       <c r="H812" t="n">
         <v>13843</v>
@@ -24004,7 +24004,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594253540039</v>
+        <v>38.0594215393066</v>
       </c>
       <c r="H815" t="n">
         <v>25044</v>
@@ -24062,7 +24062,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651473999023</v>
+        <v>37.5651512145996</v>
       </c>
       <c r="H817" t="n">
         <v>18022</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986366271973</v>
+        <v>38.5986442565918</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24178,7 +24178,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625259399414</v>
       </c>
       <c r="H821" t="n">
         <v>16005</v>
@@ -24207,7 +24207,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118667602539</v>
+        <v>39.8118629455566</v>
       </c>
       <c r="H822" t="n">
         <v>9284</v>
@@ -24265,7 +24265,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422630310059</v>
+        <v>39.5422592163086</v>
       </c>
       <c r="H824" t="n">
         <v>9758</v>
@@ -24294,7 +24294,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656265258789</v>
+        <v>40.6656188964844</v>
       </c>
       <c r="H825" t="n">
         <v>18320</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24497,7 +24497,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638366699219</v>
+        <v>38.4638328552246</v>
       </c>
       <c r="H832" t="n">
         <v>15760</v>
@@ -24526,7 +24526,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.4303436279297</v>
+        <v>37.430347442627</v>
       </c>
       <c r="H833" t="n">
         <v>8832</v>
@@ -24584,7 +24584,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>34.8690872192383</v>
+        <v>34.869083404541</v>
       </c>
       <c r="H835" t="n">
         <v>29428</v>
@@ -24816,7 +24816,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612075805664</v>
+        <v>40.2612113952637</v>
       </c>
       <c r="H843" t="n">
         <v>56674</v>
@@ -24845,7 +24845,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105522155762</v>
+        <v>40.7105560302734</v>
       </c>
       <c r="H844" t="n">
         <v>80049</v>
@@ -24903,7 +24903,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625259399414</v>
       </c>
       <c r="H846" t="n">
         <v>19364</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24961,7 +24961,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H848" t="n">
         <v>26342</v>
@@ -25019,7 +25019,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643119812012</v>
+        <v>41.5643081665039</v>
       </c>
       <c r="H850" t="n">
         <v>22251</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453559875488</v>
+        <v>40.8453636169434</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.901741027832</v>
+        <v>39.9017372131348</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25164,7 +25164,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1599006652832</v>
+        <v>41.1598968505859</v>
       </c>
       <c r="H855" t="n">
         <v>12496</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25251,7 +25251,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.5308113098145</v>
+        <v>40.530818939209</v>
       </c>
       <c r="H858" t="n">
         <v>18769</v>
@@ -25280,7 +25280,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.8004264831543</v>
+        <v>40.800422668457</v>
       </c>
       <c r="H859" t="n">
         <v>9064</v>
@@ -25396,7 +25396,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G863" t="n">
-        <v>40.3510818481445</v>
+        <v>40.3510856628418</v>
       </c>
       <c r="H863" t="n">
         <v>11672</v>
@@ -25483,7 +25483,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889785766602</v>
       </c>
       <c r="H866" t="n">
         <v>12381</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25570,7 +25570,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>42.3731269836426</v>
+        <v>42.3731307983398</v>
       </c>
       <c r="H869" t="n">
         <v>9988</v>
@@ -25599,7 +25599,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H870" t="n">
         <v>6994</v>
@@ -25657,7 +25657,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H872" t="n">
         <v>17923</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25715,7 +25715,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H874" t="n">
         <v>8152</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25802,7 +25802,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H877" t="n">
         <v>8885</v>
@@ -25831,7 +25831,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.3616828918457</v>
+        <v>43.361686706543</v>
       </c>
       <c r="H878" t="n">
         <v>3445</v>
@@ -25860,7 +25860,7 @@
         <v>47.25</v>
       </c>
       <c r="G879" t="n">
-        <v>42.4629936218262</v>
+        <v>42.4629974365234</v>
       </c>
       <c r="H879" t="n">
         <v>14904</v>
@@ -25889,7 +25889,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H880" t="n">
         <v>11127</v>
@@ -25976,7 +25976,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G883" t="n">
-        <v>42.1035194396973</v>
+        <v>42.1035232543945</v>
       </c>
       <c r="H883" t="n">
         <v>5807</v>
@@ -26005,7 +26005,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484565734863</v>
       </c>
       <c r="H884" t="n">
         <v>7700</v>
@@ -26034,7 +26034,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281936645508</v>
+        <v>42.3281898498535</v>
       </c>
       <c r="H885" t="n">
         <v>8308</v>
@@ -26063,7 +26063,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H886" t="n">
         <v>16328</v>
@@ -26092,7 +26092,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H887" t="n">
         <v>28055</v>
@@ -26179,7 +26179,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H890" t="n">
         <v>20904</v>
@@ -26208,7 +26208,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H891" t="n">
         <v>22960</v>
@@ -26266,7 +26266,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H893" t="n">
         <v>9090</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26353,7 +26353,7 @@
         <v>49.0499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>44.0806350708008</v>
+        <v>44.0806312561035</v>
       </c>
       <c r="H896" t="n">
         <v>19639</v>
@@ -26469,7 +26469,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H900" t="n">
         <v>1802</v>
@@ -26498,7 +26498,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H901" t="n">
         <v>12391</v>
@@ -26527,7 +26527,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H902" t="n">
         <v>15877</v>
@@ -26556,7 +26556,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>47.0912399291992</v>
+        <v>47.091236114502</v>
       </c>
       <c r="H903" t="n">
         <v>40528</v>
@@ -26701,7 +26701,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582260131836</v>
       </c>
       <c r="H908" t="n">
         <v>10471</v>
@@ -26730,7 +26730,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H909" t="n">
         <v>24643</v>
@@ -26759,7 +26759,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696662902832</v>
       </c>
       <c r="H910" t="n">
         <v>7813</v>
@@ -26788,7 +26788,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H911" t="n">
         <v>10719</v>
@@ -26846,7 +26846,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H913" t="n">
         <v>12859</v>
@@ -26933,7 +26933,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H916" t="n">
         <v>3511</v>
@@ -26991,7 +26991,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H918" t="n">
         <v>20374</v>
@@ -27049,7 +27049,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H920" t="n">
         <v>13604</v>
@@ -27136,7 +27136,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603721618652</v>
+        <v>44.260368347168</v>
       </c>
       <c r="H923" t="n">
         <v>10806</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27194,7 +27194,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G925" t="n">
-        <v>47.0912399291992</v>
+        <v>47.091236114502</v>
       </c>
       <c r="H925" t="n">
         <v>24024</v>
@@ -27368,7 +27368,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>48.7088737487793</v>
+        <v>48.7088775634766</v>
       </c>
       <c r="H931" t="n">
         <v>10286</v>
@@ -27397,7 +27397,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H932" t="n">
         <v>10386</v>
@@ -27455,7 +27455,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H934" t="n">
         <v>3732</v>
@@ -27484,7 +27484,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000549316406</v>
+        <v>47.9000587463379</v>
       </c>
       <c r="H935" t="n">
         <v>7592</v>
@@ -27513,7 +27513,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H936" t="n">
         <v>6052</v>
@@ -27571,7 +27571,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H938" t="n">
         <v>7754</v>
@@ -27687,7 +27687,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G942" t="n">
-        <v>47.0912399291992</v>
+        <v>47.091236114502</v>
       </c>
       <c r="H942" t="n">
         <v>9550</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27832,7 +27832,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H947" t="n">
         <v>9996</v>
@@ -27861,7 +27861,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H948" t="n">
         <v>6269</v>
@@ -27890,7 +27890,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H949" t="n">
         <v>4814</v>
@@ -28006,7 +28006,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H953" t="n">
         <v>23396</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28209,7 +28209,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026840209961</v>
+        <v>46.1026802062988</v>
       </c>
       <c r="H960" t="n">
         <v>16648</v>
@@ -28267,7 +28267,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H962" t="n">
         <v>10727</v>
@@ -28441,7 +28441,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H968" t="n">
         <v>12385</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.192554473877</v>
+        <v>46.1925506591797</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28876,7 +28876,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>45.5634727478027</v>
+        <v>45.5634689331055</v>
       </c>
       <c r="H983" t="n">
         <v>13464</v>
@@ -28905,7 +28905,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>46.0128173828125</v>
+        <v>46.0128135681152</v>
       </c>
       <c r="H984" t="n">
         <v>9617</v>
@@ -28934,7 +28934,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4735984802246</v>
+        <v>45.4736022949219</v>
       </c>
       <c r="H985" t="n">
         <v>14166</v>
@@ -28963,7 +28963,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837356567383</v>
       </c>
       <c r="H986" t="n">
         <v>9545</v>
@@ -29079,7 +29079,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H990" t="n">
         <v>18331</v>
@@ -29311,7 +29311,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765289306641</v>
+        <v>44.1765251159668</v>
       </c>
       <c r="H998" t="n">
         <v>76506</v>
@@ -29427,7 +29427,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087371826172</v>
+        <v>41.9087409973145</v>
       </c>
       <c r="H1002" t="n">
         <v>14318</v>
@@ -29485,7 +29485,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.090160369873</v>
+        <v>42.0901641845703</v>
       </c>
       <c r="H1004" t="n">
         <v>24860</v>
@@ -29543,7 +29543,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1006" t="n">
         <v>12674</v>
@@ -29572,7 +29572,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1007" t="n">
         <v>7762</v>
@@ -29717,7 +29717,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1012" t="n">
         <v>16272</v>
@@ -29746,7 +29746,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863059997559</v>
+        <v>39.6863021850586</v>
       </c>
       <c r="H1013" t="n">
         <v>19765</v>
@@ -29775,7 +29775,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1014" t="n">
         <v>13467</v>
@@ -29804,7 +29804,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316589355469</v>
+        <v>39.7316627502441</v>
       </c>
       <c r="H1015" t="n">
         <v>12739</v>
@@ -29833,7 +29833,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1016" t="n">
         <v>130810</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.6366081237793</v>
+        <v>41.636604309082</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797866821289</v>
+        <v>42.6797828674316</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30123,7 +30123,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043922424316</v>
+        <v>43.9043960571289</v>
       </c>
       <c r="H1026" t="n">
         <v>28292</v>
@@ -30210,7 +30210,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1029" t="n">
         <v>17463</v>
@@ -30326,7 +30326,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1033" t="n">
         <v>17232</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218856811523</v>
+        <v>44.2218818664551</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951057434082</v>
+        <v>43.9951019287109</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30442,7 +30442,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1037" t="n">
         <v>8307</v>
@@ -30500,7 +30500,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1039" t="n">
         <v>43123</v>
@@ -30645,7 +30645,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1044" t="n">
         <v>18875</v>
@@ -30703,7 +30703,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678314208984</v>
+        <v>48.1678352355957</v>
       </c>
       <c r="H1046" t="n">
         <v>11015</v>
@@ -30790,7 +30790,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1049" t="n">
         <v>8692</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328598022461</v>
+        <v>47.5328521728516</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443206787109</v>
+        <v>46.4443168640137</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -30964,7 +30964,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1055" t="n">
         <v>9979</v>
@@ -31051,7 +31051,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164497375488</v>
+        <v>46.7164535522461</v>
       </c>
       <c r="H1058" t="n">
         <v>15938</v>
@@ -31080,7 +31080,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071594238281</v>
+        <v>46.8071632385254</v>
       </c>
       <c r="H1059" t="n">
         <v>10169</v>
@@ -31109,7 +31109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1060" t="n">
         <v>8913</v>
@@ -31283,7 +31283,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1066" t="n">
         <v>12121</v>
@@ -31399,7 +31399,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1070" t="n">
         <v>9883</v>
@@ -31428,7 +31428,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1071" t="n">
         <v>12696</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093338012695</v>
+        <v>45.8093376159668</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31515,7 +31515,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.448657989502</v>
+        <v>44.4486618041992</v>
       </c>
       <c r="H1074" t="n">
         <v>6081</v>
@@ -31544,7 +31544,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125915527344</v>
+        <v>44.3125953674316</v>
       </c>
       <c r="H1075" t="n">
         <v>11302</v>
@@ -31689,7 +31689,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.8978729248047</v>
+        <v>46.897876739502</v>
       </c>
       <c r="H1080" t="n">
         <v>42778</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563705444336</v>
+        <v>49.2563743591309</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31834,7 +31834,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1085" t="n">
         <v>9377</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595222473145</v>
+        <v>39.459529876709</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31921,7 +31921,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1088" t="n">
         <v>48832</v>
@@ -32008,7 +32008,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1091" t="n">
         <v>42578</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32182,7 +32182,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1097" t="n">
         <v>51723</v>
@@ -32269,7 +32269,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1100" t="n">
         <v>35064</v>
@@ -32327,7 +32327,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1102" t="n">
         <v>21799</v>
@@ -32356,7 +32356,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010246276855</v>
+        <v>37.1010284423828</v>
       </c>
       <c r="H1103" t="n">
         <v>27248</v>
@@ -32385,7 +32385,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1104" t="n">
         <v>25963</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32704,7 +32704,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228591918945</v>
+        <v>35.4228630065918</v>
       </c>
       <c r="H1115" t="n">
         <v>18782</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463851928711</v>
+        <v>37.1463813781738</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33342,7 +33342,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1137" t="n">
         <v>52206</v>
@@ -33429,7 +33429,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753318786621</v>
+        <v>36.3753280639648</v>
       </c>
       <c r="H1140" t="n">
         <v>22080</v>
@@ -33458,7 +33458,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299789428711</v>
+        <v>36.3299751281738</v>
       </c>
       <c r="H1141" t="n">
         <v>7118</v>
@@ -33516,7 +33516,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688163757324</v>
+        <v>39.3688125610352</v>
       </c>
       <c r="H1143" t="n">
         <v>170822</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33719,7 +33719,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1150" t="n">
         <v>39042</v>
@@ -33806,7 +33806,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1153" t="n">
         <v>41376</v>
@@ -33835,7 +33835,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250335693359</v>
+        <v>34.4250373840332</v>
       </c>
       <c r="H1154" t="n">
         <v>41497</v>
@@ -33893,7 +33893,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1156" t="n">
         <v>64899</v>
@@ -33980,7 +33980,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1159" t="n">
         <v>19943</v>
@@ -34125,7 +34125,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1164" t="n">
         <v>26580</v>
@@ -34154,7 +34154,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1165" t="n">
         <v>37830</v>
@@ -34183,7 +34183,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1166" t="n">
         <v>18336</v>
@@ -34241,7 +34241,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556678771973</v>
+        <v>37.0556716918945</v>
       </c>
       <c r="H1168" t="n">
         <v>36948</v>
@@ -34328,7 +34328,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.1031951904297</v>
+        <v>36.103199005127</v>
       </c>
       <c r="H1171" t="n">
         <v>37325</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605072021484</v>
+        <v>30.6605033874512</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34734,7 +34734,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233516693115</v>
+        <v>31.0233535766602</v>
       </c>
       <c r="H1185" t="n">
         <v>64152</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419322967529</v>
+        <v>30.8419284820557</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34792,7 +34792,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561584472656</v>
+        <v>32.6561622619629</v>
       </c>
       <c r="H1187" t="n">
         <v>23709</v>
@@ -34879,7 +34879,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1190" t="n">
         <v>13571</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600204467773</v>
+        <v>35.0600166320801</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34995,7 +34995,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1194" t="n">
         <v>141817</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545883178711</v>
+        <v>37.5545845031738</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35401,7 +35401,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1208" t="n">
         <v>18290</v>
@@ -35430,7 +35430,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1209" t="n">
         <v>25845</v>
@@ -35691,7 +35691,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1218" t="n">
         <v>55769</v>
@@ -35720,7 +35720,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475547790527</v>
+        <v>34.2475509643555</v>
       </c>
       <c r="H1219" t="n">
         <v>11676</v>
@@ -35923,7 +35923,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377815246582</v>
+        <v>33.7377777099609</v>
       </c>
       <c r="H1226" t="n">
         <v>7077</v>
@@ -35981,7 +35981,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280044555664</v>
+        <v>33.2280006408691</v>
       </c>
       <c r="H1228" t="n">
         <v>17594</v>
@@ -36271,7 +36271,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1238" t="n">
         <v>26308</v>
@@ -36329,7 +36329,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719566345215</v>
+        <v>34.5719528198242</v>
       </c>
       <c r="H1240" t="n">
         <v>30852</v>
@@ -36503,7 +36503,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792045593262</v>
+        <v>32.5792007446289</v>
       </c>
       <c r="H1246" t="n">
         <v>16319</v>
@@ -36532,7 +36532,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1247" t="n">
         <v>23766</v>
@@ -36590,7 +36590,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546661376953</v>
+        <v>28.4546642303467</v>
       </c>
       <c r="H1249" t="n">
         <v>16778</v>
@@ -36677,7 +36677,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1252" t="n">
         <v>55493</v>
@@ -36706,7 +36706,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692928314209</v>
+        <v>28.2692909240723</v>
       </c>
       <c r="H1253" t="n">
         <v>9517</v>
@@ -36735,7 +36735,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1254" t="n">
         <v>12548</v>
@@ -36880,7 +36880,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1259" t="n">
         <v>38924</v>
@@ -36938,7 +36938,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911655426025</v>
+        <v>26.0911674499512</v>
       </c>
       <c r="H1261" t="n">
         <v>31910</v>
@@ -37083,7 +37083,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131084442139</v>
+        <v>25.8131065368652</v>
       </c>
       <c r="H1266" t="n">
         <v>7598</v>
@@ -37112,7 +37112,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1267" t="n">
         <v>12771</v>
@@ -37170,7 +37170,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1269" t="n">
         <v>18414</v>
@@ -37344,7 +37344,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1275" t="n">
         <v>15913</v>
@@ -37431,7 +37431,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1278" t="n">
         <v>11119</v>
@@ -37489,7 +37489,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1280" t="n">
         <v>11239</v>
@@ -37547,7 +37547,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1282" t="n">
         <v>29030</v>
@@ -37576,7 +37576,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887710571289</v>
+        <v>27.3887729644775</v>
       </c>
       <c r="H1283" t="n">
         <v>13951</v>
@@ -37808,7 +37808,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473499298096</v>
+        <v>28.5473518371582</v>
       </c>
       <c r="H1291" t="n">
         <v>49073</v>
@@ -37837,7 +37837,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1292" t="n">
         <v>22316</v>
@@ -38040,7 +38040,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107139587402</v>
+        <v>27.1107158660889</v>
       </c>
       <c r="H1299" t="n">
         <v>2701</v>
@@ -38156,7 +38156,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1303" t="n">
         <v>11541</v>
@@ -38301,7 +38301,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1308" t="n">
         <v>7747</v>
@@ -38359,7 +38359,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1310" t="n">
         <v>8183</v>
@@ -38533,7 +38533,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1316" t="n">
         <v>8506</v>
@@ -38562,7 +38562,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1317" t="n">
         <v>6463</v>
@@ -38765,7 +38765,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545295715332</v>
+        <v>24.6545314788818</v>
       </c>
       <c r="H1324" t="n">
         <v>11339</v>
@@ -38794,7 +38794,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984115600586</v>
+        <v>24.0984134674072</v>
       </c>
       <c r="H1325" t="n">
         <v>17104</v>
@@ -38852,7 +38852,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033332824707</v>
+        <v>25.3033313751221</v>
       </c>
       <c r="H1327" t="n">
         <v>29720</v>
@@ -38910,7 +38910,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.720422744751</v>
+        <v>25.7204208374023</v>
       </c>
       <c r="H1329" t="n">
         <v>7898</v>
@@ -39229,7 +39229,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350494384766</v>
+        <v>25.5350475311279</v>
       </c>
       <c r="H1340" t="n">
         <v>7940</v>
@@ -39316,7 +39316,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1343" t="n">
         <v>17193</v>
@@ -39345,7 +39345,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1344" t="n">
         <v>16994</v>
@@ -39374,7 +39374,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301959991455</v>
+        <v>26.2301940917969</v>
       </c>
       <c r="H1345" t="n">
         <v>26909</v>
@@ -39432,7 +39432,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1347" t="n">
         <v>13917</v>
@@ -39461,7 +39461,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1348" t="n">
         <v>8737</v>
@@ -39548,7 +39548,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1351" t="n">
         <v>20501</v>
@@ -39577,7 +39577,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.5741443634033</v>
+        <v>27.574146270752</v>
       </c>
       <c r="H1352" t="n">
         <v>16729</v>
@@ -39693,7 +39693,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1356" t="n">
         <v>75277</v>
@@ -39722,7 +39722,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1357" t="n">
         <v>36177</v>
@@ -39751,7 +39751,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1358" t="n">
         <v>16319</v>
@@ -39809,7 +39809,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352523803711</v>
+        <v>31.2352504730225</v>
       </c>
       <c r="H1360" t="n">
         <v>14299</v>
@@ -39867,7 +39867,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1362" t="n">
         <v>13411</v>
@@ -39896,7 +39896,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1363" t="n">
         <v>7826</v>
@@ -39954,7 +39954,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377113342285</v>
+        <v>31.8377075195312</v>
       </c>
       <c r="H1365" t="n">
         <v>22255</v>
@@ -39983,7 +39983,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1366" t="n">
         <v>49622</v>
@@ -40041,7 +40041,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571914672852</v>
+        <v>30.9571933746338</v>
       </c>
       <c r="H1368" t="n">
         <v>11052</v>
@@ -40070,7 +40070,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1369" t="n">
         <v>31735</v>
@@ -40099,7 +40099,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.9303970336914</v>
+        <v>31.93039894104</v>
       </c>
       <c r="H1370" t="n">
         <v>19225</v>
@@ -40244,7 +40244,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596504211426</v>
+        <v>31.5596523284912</v>
       </c>
       <c r="H1375" t="n">
         <v>14100</v>
@@ -40273,7 +40273,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1376" t="n">
         <v>10686</v>
@@ -40302,7 +40302,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1377" t="n">
         <v>13797</v>
@@ -40331,7 +40331,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986808776855</v>
+        <v>31.6986827850342</v>
       </c>
       <c r="H1378" t="n">
         <v>16079</v>
@@ -40476,7 +40476,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182312011719</v>
+        <v>32.7182273864746</v>
       </c>
       <c r="H1383" t="n">
         <v>16458</v>
@@ -40708,7 +40708,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914367675781</v>
+        <v>33.6914329528809</v>
       </c>
       <c r="H1391" t="n">
         <v>5315</v>
@@ -40766,7 +40766,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1393" t="n">
         <v>20537</v>
@@ -40911,7 +40911,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.3597869873047</v>
+        <v>35.359790802002</v>
       </c>
       <c r="H1398" t="n">
         <v>20503</v>
@@ -40969,7 +40969,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1400" t="n">
         <v>25006</v>
@@ -40998,7 +40998,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1401" t="n">
         <v>9472</v>
@@ -41056,7 +41056,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988136291504</v>
+        <v>35.4988174438477</v>
       </c>
       <c r="H1403" t="n">
         <v>23148</v>
@@ -41085,7 +41085,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744117736816</v>
+        <v>35.1744155883789</v>
       </c>
       <c r="H1404" t="n">
         <v>45623</v>
@@ -41114,7 +41114,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1405" t="n">
         <v>28718</v>
@@ -41201,7 +41201,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1408" t="n">
         <v>18517</v>
@@ -41259,7 +41259,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012138366699</v>
+        <v>34.2012100219727</v>
       </c>
       <c r="H1410" t="n">
         <v>15419</v>
@@ -41317,7 +41317,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1412" t="n">
         <v>38690</v>
@@ -41346,7 +41346,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1413" t="n">
         <v>44206</v>
@@ -41404,7 +41404,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1415" t="n">
         <v>21797</v>
@@ -41433,7 +41433,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.5183639526367</v>
+        <v>36.518367767334</v>
       </c>
       <c r="H1416" t="n">
         <v>19385</v>
@@ -41520,7 +41520,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085868835449</v>
+        <v>36.0085906982422</v>
       </c>
       <c r="H1419" t="n">
         <v>19338</v>
@@ -41607,7 +41607,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1422" t="n">
         <v>28131</v>
@@ -41665,7 +41665,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1424" t="n">
         <v>37415</v>
@@ -41926,7 +41926,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059288024902</v>
+        <v>29.7059268951416</v>
       </c>
       <c r="H1433" t="n">
         <v>169855</v>
@@ -41955,7 +41955,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1434" t="n">
         <v>83833</v>
@@ -41984,7 +41984,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1435" t="n">
         <v>50233</v>
@@ -42100,7 +42100,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1439" t="n">
         <v>39783</v>
@@ -42129,7 +42129,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1440" t="n">
         <v>36958</v>
@@ -42187,7 +42187,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1442" t="n">
         <v>39311</v>
@@ -42332,7 +42332,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1447" t="n">
         <v>48734</v>
@@ -42361,7 +42361,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1448" t="n">
         <v>29333</v>
@@ -42419,7 +42419,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1450" t="n">
         <v>74959</v>
@@ -42448,7 +42448,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2033996582031</v>
+        <v>27.2034015655518</v>
       </c>
       <c r="H1451" t="n">
         <v>28955</v>
@@ -42506,7 +42506,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156337738037</v>
+        <v>28.3156356811523</v>
       </c>
       <c r="H1453" t="n">
         <v>45425</v>
@@ -42564,7 +42564,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1455" t="n">
         <v>26258</v>
@@ -42622,7 +42622,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1457" t="n">
         <v>41539</v>
@@ -42767,7 +42767,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1462" t="n">
         <v>27647</v>
@@ -42796,7 +42796,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1463" t="n">
         <v>32514</v>
@@ -42825,7 +42825,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1464" t="n">
         <v>59385</v>
@@ -42912,7 +42912,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1467" t="n">
         <v>22423</v>
@@ -42970,7 +42970,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1469" t="n">
         <v>33838</v>
@@ -42999,7 +42999,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1470" t="n">
         <v>20524</v>
@@ -43028,7 +43028,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1471" t="n">
         <v>38899</v>
@@ -43057,7 +43057,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1472" t="n">
         <v>26587</v>
@@ -43086,7 +43086,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1473" t="n">
         <v>61483</v>
@@ -43202,7 +43202,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1477" t="n">
         <v>81786</v>
@@ -68641,6 +68641,35 @@
         <v>1551201</v>
       </c>
       <c r="I2354" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2355" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>1.51400005817413</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H2355" t="n">
+        <v>1625592</v>
+      </c>
+      <c r="I2355" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569236755371</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -572,7 +572,7 @@
         <v>54.25</v>
       </c>
       <c r="G7" t="n">
-        <v>47.4757041931152</v>
+        <v>47.4757080078125</v>
       </c>
       <c r="H7" t="n">
         <v>58881</v>
@@ -717,7 +717,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132652282715</v>
       </c>
       <c r="H12" t="n">
         <v>19418</v>
@@ -746,7 +746,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H13" t="n">
         <v>28253</v>
@@ -775,7 +775,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G14" t="n">
-        <v>48.0007858276367</v>
+        <v>48.0007820129395</v>
       </c>
       <c r="H14" t="n">
         <v>82998</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.8695220947266</v>
+        <v>47.8695106506348</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -891,7 +891,7 @@
         <v>54.25</v>
       </c>
       <c r="G18" t="n">
-        <v>47.4757041931152</v>
+        <v>47.4757080078125</v>
       </c>
       <c r="H18" t="n">
         <v>15527</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506340026855</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1007,7 +1007,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.469310760498</v>
+        <v>46.4693069458008</v>
       </c>
       <c r="H22" t="n">
         <v>15015</v>
@@ -1065,7 +1065,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880912780762</v>
+        <v>46.6880950927734</v>
       </c>
       <c r="H24" t="n">
         <v>35958</v>
@@ -1094,7 +1094,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256523132324</v>
+        <v>47.125659942627</v>
       </c>
       <c r="H25" t="n">
         <v>24385</v>
@@ -1181,7 +1181,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.119255065918</v>
+        <v>46.1192588806152</v>
       </c>
       <c r="H28" t="n">
         <v>23503</v>
@@ -1297,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="G32" t="n">
-        <v>46.3817977905273</v>
+        <v>46.3818016052246</v>
       </c>
       <c r="H32" t="n">
         <v>21384</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816940307617</v>
+        <v>45.681697845459</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1355,7 +1355,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567161560059</v>
+        <v>45.8567199707031</v>
       </c>
       <c r="H34" t="n">
         <v>9627</v>
@@ -1384,7 +1384,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256523132324</v>
+        <v>47.125659942627</v>
       </c>
       <c r="H35" t="n">
         <v>35180</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069755554199</v>
+        <v>47.6069793701172</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881988525391</v>
+        <v>47.3881950378418</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1529,7 +1529,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.994384765625</v>
+        <v>46.9943809509277</v>
       </c>
       <c r="H40" t="n">
         <v>9334</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569236755371</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882987976074</v>
+        <v>48.0882949829102</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.8695220947266</v>
+        <v>47.8695106506348</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1674,7 +1674,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132652282715</v>
       </c>
       <c r="H45" t="n">
         <v>55518</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944923400879</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -2080,7 +2080,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577461242676</v>
+        <v>52.8577499389648</v>
       </c>
       <c r="H59" t="n">
         <v>33673</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579536437988</v>
+        <v>54.2579574584961</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2254,7 +2254,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955146789551</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H65" t="n">
         <v>17831</v>
@@ -2283,7 +2283,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769378662109</v>
+        <v>55.8769416809082</v>
       </c>
       <c r="H66" t="n">
         <v>30641</v>
@@ -2312,7 +2312,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336982727051</v>
+        <v>59.3336944580078</v>
       </c>
       <c r="H67" t="n">
         <v>66049</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589797973633</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2370,7 +2370,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403991699219</v>
+        <v>62.4404029846191</v>
       </c>
       <c r="H69" t="n">
         <v>51076</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965408325195</v>
+        <v>61.6965484619141</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965408325195</v>
+        <v>61.6965484619141</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2457,7 +2457,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.134105682373</v>
+        <v>62.1341094970703</v>
       </c>
       <c r="H72" t="n">
         <v>24358</v>
@@ -2486,7 +2486,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902549743652</v>
+        <v>61.3902435302734</v>
       </c>
       <c r="H73" t="n">
         <v>19520</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339981079102</v>
+        <v>61.4339942932129</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964332580566</v>
+        <v>60.9964370727539</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2573,7 +2573,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462852478027</v>
+        <v>59.9462814331055</v>
       </c>
       <c r="H76" t="n">
         <v>17560</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275047302246</v>
+        <v>59.7275085449219</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838539123535</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276084899902</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2747,7 +2747,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026306152344</v>
+        <v>60.6026344299316</v>
       </c>
       <c r="H82" t="n">
         <v>33403</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2834,7 +2834,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771415710449</v>
+        <v>57.2771377563477</v>
       </c>
       <c r="H85" t="n">
         <v>30458</v>
@@ -2892,7 +2892,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204887390137</v>
+        <v>54.5204849243164</v>
       </c>
       <c r="H87" t="n">
         <v>43778</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772453308105</v>
+        <v>57.9772415161133</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711517333984</v>
+        <v>59.0711555480957</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3095,7 +3095,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335983276367</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H94" t="n">
         <v>25066</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273933410645</v>
+        <v>59.027400970459</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335983276367</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H97" t="n">
         <v>26035</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834350585938</v>
+        <v>57.5834426879883</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276084899902</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525825500488</v>
+        <v>60.2525787353516</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335983276367</v>
+        <v>58.6335906982422</v>
       </c>
       <c r="H108" t="n">
         <v>43417</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898361206055</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897323608398</v>
+        <v>57.8897361755371</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899398803711</v>
+        <v>59.2899360656738</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962333679199</v>
+        <v>59.5962257385254</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397842407227</v>
+        <v>58.2397880554199</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4052,7 +4052,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770416259766</v>
+        <v>56.5770378112793</v>
       </c>
       <c r="H127" t="n">
         <v>42192</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.6207885742188</v>
+        <v>56.620792388916</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4284,7 +4284,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896362304688</v>
+        <v>57.189624786377</v>
       </c>
       <c r="H135" t="n">
         <v>6298</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831352233887</v>
+        <v>55.4831314086914</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582572937012</v>
+        <v>56.3582611083984</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4516,7 +4516,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955146789551</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H143" t="n">
         <v>12997</v>
@@ -4545,7 +4545,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955146789551</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H144" t="n">
         <v>26633</v>
@@ -4574,7 +4574,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892250061035</v>
+        <v>54.3892211914062</v>
       </c>
       <c r="H145" t="n">
         <v>31730</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703369140625</v>
+        <v>53.4703330993652</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394729614258</v>
+        <v>56.139476776123</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4806,7 +4806,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="n">
         <v>14177</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266822814941</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4893,7 +4893,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H156" t="n">
         <v>10320</v>
@@ -4922,7 +4922,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138877868652</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="n">
         <v>24689</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326721191406</v>
+        <v>52.3326683044434</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -4980,7 +4980,7 @@
         <v>59.5</v>
       </c>
       <c r="G159" t="n">
-        <v>52.0701293945312</v>
+        <v>52.070125579834</v>
       </c>
       <c r="H159" t="n">
         <v>10594</v>
@@ -5067,7 +5067,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196662902832</v>
+        <v>48.9196701049805</v>
       </c>
       <c r="H162" t="n">
         <v>15929</v>
@@ -5125,7 +5125,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H164" t="n">
         <v>9928</v>
@@ -5154,7 +5154,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.788402557373</v>
+        <v>48.7883987426758</v>
       </c>
       <c r="H165" t="n">
         <v>49976</v>
@@ -5212,7 +5212,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764228820801</v>
+        <v>52.3764266967773</v>
       </c>
       <c r="H167" t="n">
         <v>20718</v>
@@ -5241,7 +5241,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="n">
         <v>15941</v>
@@ -5270,7 +5270,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265747070312</v>
+        <v>53.4265785217285</v>
       </c>
       <c r="H169" t="n">
         <v>13847</v>
@@ -5328,7 +5328,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G171" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H171" t="n">
         <v>6434</v>
@@ -5357,7 +5357,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8950996398926</v>
+        <v>51.8951034545898</v>
       </c>
       <c r="H172" t="n">
         <v>4493</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889137268066</v>
+        <v>52.2889099121094</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5415,7 +5415,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>52.2013969421387</v>
+        <v>52.2014007568359</v>
       </c>
       <c r="H174" t="n">
         <v>4529</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510414123535</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5560,7 +5560,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H179" t="n">
         <v>6559</v>
@@ -5589,7 +5589,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H180" t="n">
         <v>6556</v>
@@ -5763,7 +5763,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890174865723</v>
+        <v>52.9890098571777</v>
       </c>
       <c r="H186" t="n">
         <v>12495</v>
@@ -5792,7 +5792,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H187" t="n">
         <v>10680</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.076530456543</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.95166015625</v>
+        <v>53.9516525268555</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140914916992</v>
+        <v>53.5140953063965</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -5966,7 +5966,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="n">
         <v>9212</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077903747559</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077903747559</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6111,7 +6111,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G198" t="n">
-        <v>56.4020156860352</v>
+        <v>56.4020118713379</v>
       </c>
       <c r="H198" t="n">
         <v>18097</v>
@@ -6140,7 +6140,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519638061523</v>
+        <v>56.0519676208496</v>
       </c>
       <c r="H199" t="n">
         <v>8382</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6285,7 +6285,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891098022461</v>
+        <v>53.6891136169434</v>
       </c>
       <c r="H204" t="n">
         <v>7160</v>
@@ -6314,7 +6314,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391731262207</v>
+        <v>54.0391693115234</v>
       </c>
       <c r="H205" t="n">
         <v>7569</v>
@@ -6401,7 +6401,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830238342285</v>
+        <v>54.7830276489258</v>
       </c>
       <c r="H208" t="n">
         <v>8498</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390655517578</v>
+        <v>53.3390731811523</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823089599609</v>
+        <v>49.8823127746582</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8695220947266</v>
+        <v>47.8695106506348</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6633,7 +6633,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.662296295166</v>
+        <v>44.6623001098633</v>
       </c>
       <c r="H216" t="n">
         <v>40064</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179847717285</v>
+        <v>44.6179885864258</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6720,7 +6720,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>45.8143043518066</v>
+        <v>45.8143005371094</v>
       </c>
       <c r="H219" t="n">
         <v>12637</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6836,7 +6836,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="n">
         <v>24305</v>
@@ -6894,7 +6894,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281463623047</v>
+        <v>44.928150177002</v>
       </c>
       <c r="H225" t="n">
         <v>28013</v>
@@ -6923,7 +6923,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509155273438</v>
+        <v>44.7509117126465</v>
       </c>
       <c r="H226" t="n">
         <v>9809</v>
@@ -6952,7 +6952,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982940673828</v>
+        <v>43.7982978820801</v>
       </c>
       <c r="H227" t="n">
         <v>8139</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.601978302002</v>
+        <v>42.6019859313965</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7126,7 +7126,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H233" t="n">
         <v>12552</v>
@@ -7155,7 +7155,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.9663047790527</v>
+        <v>46.96630859375</v>
       </c>
       <c r="H234" t="n">
         <v>26806</v>
@@ -7184,7 +7184,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536933898926</v>
+        <v>47.4536895751953</v>
       </c>
       <c r="H235" t="n">
         <v>27871</v>
@@ -7213,7 +7213,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272285461426</v>
+        <v>48.8272361755371</v>
       </c>
       <c r="H236" t="n">
         <v>13514</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475402832031</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7329,7 +7329,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361633300781</v>
       </c>
       <c r="H240" t="n">
         <v>97891</v>
@@ -7358,7 +7358,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.2260055541992</v>
+        <v>49.226001739502</v>
       </c>
       <c r="H241" t="n">
         <v>21035</v>
@@ -7445,7 +7445,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H244" t="n">
         <v>15929</v>
@@ -7474,7 +7474,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H245" t="n">
         <v>24572</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158477783203</v>
+        <v>48.9158515930176</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7532,7 +7532,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H247" t="n">
         <v>16775</v>
@@ -7561,7 +7561,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983177185059</v>
+        <v>50.9983215332031</v>
       </c>
       <c r="H248" t="n">
         <v>36235</v>
@@ -7619,7 +7619,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H250" t="n">
         <v>14687</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H251" t="n">
         <v>9250</v>
@@ -7677,7 +7677,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715362548828</v>
+        <v>48.8715438842773</v>
       </c>
       <c r="H252" t="n">
         <v>19047</v>
@@ -7735,7 +7735,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G254" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626167297363</v>
       </c>
       <c r="H254" t="n">
         <v>4468</v>
@@ -7764,7 +7764,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.33984375</v>
+        <v>48.3398475646973</v>
       </c>
       <c r="H255" t="n">
         <v>7923</v>
@@ -7793,7 +7793,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G256" t="n">
-        <v>48.1626129150391</v>
+        <v>48.1626167297363</v>
       </c>
       <c r="H256" t="n">
         <v>3523</v>
@@ -7851,7 +7851,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>47.8967666625977</v>
+        <v>47.8967704772949</v>
       </c>
       <c r="H258" t="n">
         <v>6947</v>
@@ -7880,7 +7880,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>47.8967666625977</v>
+        <v>47.8967704772949</v>
       </c>
       <c r="H259" t="n">
         <v>3097</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192192077637</v>
+        <v>44.2192230224609</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8054,7 +8054,7 @@
         <v>50</v>
       </c>
       <c r="G265" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H265" t="n">
         <v>13686</v>
@@ -8083,7 +8083,7 @@
         <v>50</v>
       </c>
       <c r="G266" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H266" t="n">
         <v>13575</v>
@@ -8112,7 +8112,7 @@
         <v>52.25</v>
       </c>
       <c r="G267" t="n">
-        <v>46.3016891479492</v>
+        <v>46.301685333252</v>
       </c>
       <c r="H267" t="n">
         <v>13254</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.371223449707</v>
+        <v>45.3712272644043</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8228,7 +8228,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346084594727</v>
+        <v>46.4346122741699</v>
       </c>
       <c r="H271" t="n">
         <v>6611</v>
@@ -8257,7 +8257,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232238769531</v>
+        <v>46.5232276916504</v>
       </c>
       <c r="H272" t="n">
         <v>8521</v>
@@ -8286,7 +8286,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699966430664</v>
+        <v>45.7699928283691</v>
       </c>
       <c r="H273" t="n">
         <v>5066</v>
@@ -8344,7 +8344,7 @@
         <v>50</v>
       </c>
       <c r="G275" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H275" t="n">
         <v>10055</v>
@@ -8402,7 +8402,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432113647461</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H277" t="n">
         <v>2613</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8518,7 +8518,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121398925781</v>
+        <v>42.9121360778809</v>
       </c>
       <c r="H281" t="n">
         <v>13077</v>
@@ -8576,7 +8576,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570610046387</v>
+        <v>42.7570648193359</v>
       </c>
       <c r="H283" t="n">
         <v>10993</v>
@@ -8634,7 +8634,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761459350586</v>
+        <v>43.7761421203613</v>
       </c>
       <c r="H285" t="n">
         <v>11503</v>
@@ -8750,7 +8750,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222900390625</v>
+        <v>43.2222938537598</v>
       </c>
       <c r="H289" t="n">
         <v>13085</v>
@@ -8837,7 +8837,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.200138092041</v>
+        <v>43.2001419067383</v>
       </c>
       <c r="H292" t="n">
         <v>25355</v>
@@ -8895,7 +8895,7 @@
         <v>48.3250007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>42.8235244750977</v>
+        <v>42.8235282897949</v>
       </c>
       <c r="H294" t="n">
         <v>3730</v>
@@ -8953,7 +8953,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450668334961</v>
       </c>
       <c r="H296" t="n">
         <v>6836</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444496154785</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444496154785</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9069,7 +9069,7 @@
         <v>48.8250007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>43.2666015625</v>
+        <v>43.2666053771973</v>
       </c>
       <c r="H300" t="n">
         <v>4300</v>
@@ -9156,7 +9156,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102920532227</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="n">
         <v>15525</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349014282227</v>
+        <v>42.7349052429199</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9301,7 +9301,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.8044395446777</v>
+        <v>41.804443359375</v>
       </c>
       <c r="H308" t="n">
         <v>42371</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9359,7 +9359,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170509338379</v>
+        <v>41.3170547485352</v>
       </c>
       <c r="H310" t="n">
         <v>20434</v>
@@ -9388,7 +9388,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853622436523</v>
+        <v>40.7853584289551</v>
       </c>
       <c r="H311" t="n">
         <v>17137</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9446,7 +9446,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062835693359</v>
+        <v>41.2062873840332</v>
       </c>
       <c r="H313" t="n">
         <v>4752</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638275146484</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9533,7 +9533,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H316" t="n">
         <v>7190</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465827941895</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213562011719</v>
+        <v>39.9213600158691</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9765,7 +9765,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4309005737305</v>
+        <v>40.4308967590332</v>
       </c>
       <c r="H324" t="n">
         <v>19512</v>
@@ -9823,7 +9823,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693519592285</v>
+        <v>38.7693557739258</v>
       </c>
       <c r="H326" t="n">
         <v>16647</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10142,7 +10142,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062835693359</v>
+        <v>41.2062873840332</v>
       </c>
       <c r="H337" t="n">
         <v>2833</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10200,7 +10200,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462936401367</v>
+        <v>42.6462898254395</v>
       </c>
       <c r="H339" t="n">
         <v>10608</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912147521973</v>
+        <v>42.4912109375</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10403,7 +10403,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555137634277</v>
+        <v>39.6555099487305</v>
       </c>
       <c r="H346" t="n">
         <v>10252</v>
@@ -10432,7 +10432,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573577880859</v>
+        <v>39.0573616027832</v>
       </c>
       <c r="H347" t="n">
         <v>20248</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807441711426</v>
+        <v>38.6807403564453</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10490,7 +10490,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.990894317627</v>
+        <v>38.9908981323242</v>
       </c>
       <c r="H349" t="n">
         <v>17776</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764625549316</v>
+        <v>47.2764587402344</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10693,7 +10693,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="n">
         <v>3633</v>
@@ -10722,7 +10722,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878433227539</v>
+        <v>47.1878471374512</v>
       </c>
       <c r="H357" t="n">
         <v>7547</v>
@@ -10751,7 +10751,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459930419922</v>
+        <v>46.3459968566895</v>
       </c>
       <c r="H358" t="n">
         <v>34572</v>
@@ -10780,7 +10780,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.833381652832</v>
+        <v>46.8333778381348</v>
       </c>
       <c r="H359" t="n">
         <v>4295</v>
@@ -10867,7 +10867,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432113647461</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H362" t="n">
         <v>6139</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419845581055</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10954,7 +10954,7 @@
         <v>46.375</v>
       </c>
       <c r="G365" t="n">
-        <v>41.095516204834</v>
+        <v>41.0955200195312</v>
       </c>
       <c r="H365" t="n">
         <v>6971</v>
@@ -11041,7 +11041,7 @@
         <v>45.25</v>
       </c>
       <c r="G368" t="n">
-        <v>40.0985870361328</v>
+        <v>40.0985908508301</v>
       </c>
       <c r="H368" t="n">
         <v>8869</v>
@@ -11099,7 +11099,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321311950684</v>
+        <v>40.0321350097656</v>
       </c>
       <c r="H370" t="n">
         <v>10048</v>
@@ -11128,7 +11128,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625930786133</v>
+        <v>40.962589263916</v>
       </c>
       <c r="H371" t="n">
         <v>7882</v>
@@ -11157,7 +11157,7 @@
         <v>50</v>
       </c>
       <c r="G372" t="n">
-        <v>44.3078384399414</v>
+        <v>44.3078346252441</v>
       </c>
       <c r="H372" t="n">
         <v>19533</v>
@@ -11186,7 +11186,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724540710449</v>
+        <v>44.9724502563477</v>
       </c>
       <c r="H373" t="n">
         <v>15133</v>
@@ -11215,7 +11215,7 @@
         <v>52</v>
       </c>
       <c r="G374" t="n">
-        <v>46.080150604248</v>
+        <v>46.0801467895508</v>
       </c>
       <c r="H374" t="n">
         <v>7159</v>
@@ -11244,7 +11244,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118469238281</v>
+        <v>46.6118392944336</v>
       </c>
       <c r="H375" t="n">
         <v>5727</v>
@@ -11273,7 +11273,7 @@
         <v>55.25</v>
       </c>
       <c r="G376" t="n">
-        <v>48.9601631164551</v>
+        <v>48.9601554870605</v>
       </c>
       <c r="H376" t="n">
         <v>10916</v>
@@ -11302,7 +11302,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H377" t="n">
         <v>57780</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780097961426</v>
+        <v>50.3780059814453</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11360,7 +11360,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893905639648</v>
+        <v>50.2893943786621</v>
       </c>
       <c r="H379" t="n">
         <v>16967</v>
@@ -11418,7 +11418,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.3970909118652</v>
+        <v>51.397087097168</v>
       </c>
       <c r="H381" t="n">
         <v>8438</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958602905273</v>
+        <v>51.7958564758301</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121559143066</v>
+        <v>50.1121597290039</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11563,7 +11563,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589248657227</v>
+        <v>49.3589324951172</v>
       </c>
       <c r="H386" t="n">
         <v>5737</v>
@@ -11592,7 +11592,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.7577018737793</v>
+        <v>49.757698059082</v>
       </c>
       <c r="H387" t="n">
         <v>12225</v>
@@ -11650,7 +11650,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032363891602</v>
+        <v>49.4032325744629</v>
       </c>
       <c r="H389" t="n">
         <v>4963</v>
@@ -11679,7 +11679,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H390" t="n">
         <v>14079</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11766,7 +11766,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H393" t="n">
         <v>9144</v>
@@ -11795,7 +11795,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H394" t="n">
         <v>11783</v>
@@ -11824,7 +11824,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>52.1060104370117</v>
+        <v>52.106014251709</v>
       </c>
       <c r="H395" t="n">
         <v>12740</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555534362793</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11969,7 +11969,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.390941619873</v>
+        <v>53.3909378051758</v>
       </c>
       <c r="H400" t="n">
         <v>20005</v>
@@ -12027,7 +12027,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961769104004</v>
+        <v>55.2961807250977</v>
       </c>
       <c r="H402" t="n">
         <v>18544</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555534362793</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12230,7 +12230,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="n">
         <v>12835</v>
@@ -12375,7 +12375,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.7835655212402</v>
+        <v>55.783561706543</v>
       </c>
       <c r="H414" t="n">
         <v>6786</v>
@@ -12433,7 +12433,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546508789062</v>
+        <v>57.954647064209</v>
       </c>
       <c r="H416" t="n">
         <v>19036</v>
@@ -12520,7 +12520,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038772583008</v>
+        <v>56.4038734436035</v>
       </c>
       <c r="H419" t="n">
         <v>16100</v>
@@ -12723,7 +12723,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6888008117676</v>
+        <v>57.6888046264648</v>
       </c>
       <c r="H426" t="n">
         <v>8138</v>
@@ -12752,7 +12752,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>55.2075614929199</v>
+        <v>55.2075576782227</v>
       </c>
       <c r="H427" t="n">
         <v>11503</v>
@@ -12810,7 +12810,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H429" t="n">
         <v>9582</v>
@@ -12839,7 +12839,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H430" t="n">
         <v>4618</v>
@@ -12955,7 +12955,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478607177734</v>
+        <v>52.9478645324707</v>
       </c>
       <c r="H434" t="n">
         <v>15198</v>
@@ -12984,7 +12984,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0174026489258</v>
+        <v>52.0173950195312</v>
       </c>
       <c r="H435" t="n">
         <v>15195</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.5238647460938</v>
+        <v>53.523868560791</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823387145996</v>
+        <v>56.1823348999023</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026428222656</v>
+        <v>56.8026466369629</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13187,7 +13187,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>55.2075614929199</v>
+        <v>55.2075576782227</v>
       </c>
       <c r="H442" t="n">
         <v>3795</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254196166992</v>
+        <v>56.6254081726074</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555534362793</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13651,7 +13651,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.701099395752</v>
+        <v>53.7010955810547</v>
       </c>
       <c r="H458" t="n">
         <v>31030</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149375915527</v>
+        <v>52.81494140625</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13825,7 +13825,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H464" t="n">
         <v>5606</v>
@@ -13883,7 +13883,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H466" t="n">
         <v>7562</v>
@@ -13970,7 +13970,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678520202637</v>
+        <v>50.0678558349609</v>
       </c>
       <c r="H469" t="n">
         <v>4828</v>
@@ -13999,7 +13999,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703094482422</v>
+        <v>49.2703132629395</v>
       </c>
       <c r="H470" t="n">
         <v>4310</v>
@@ -14028,7 +14028,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H471" t="n">
         <v>9753</v>
@@ -14057,7 +14057,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569038391113</v>
+        <v>50.0569114685059</v>
       </c>
       <c r="H472" t="n">
         <v>6766</v>
@@ -14144,7 +14144,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>49.0683479309082</v>
+        <v>49.0683517456055</v>
       </c>
       <c r="H475" t="n">
         <v>5767</v>
@@ -14173,7 +14173,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H476" t="n">
         <v>21249</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14231,7 +14231,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H478" t="n">
         <v>29594</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14492,7 +14492,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H487" t="n">
         <v>10895</v>
@@ -14521,7 +14521,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9555969238281</v>
+        <v>50.9556007385254</v>
       </c>
       <c r="H488" t="n">
         <v>9780</v>
@@ -14550,7 +14550,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G489" t="n">
-        <v>49.9670372009277</v>
+        <v>49.967041015625</v>
       </c>
       <c r="H489" t="n">
         <v>5862</v>
@@ -14579,7 +14579,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H490" t="n">
         <v>8141</v>
@@ -14637,7 +14637,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H492" t="n">
         <v>9874</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14869,7 +14869,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H500" t="n">
         <v>16458</v>
@@ -14898,7 +14898,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H501" t="n">
         <v>10967</v>
@@ -14927,7 +14927,7 @@
         <v>60</v>
       </c>
       <c r="G502" t="n">
-        <v>53.9212646484375</v>
+        <v>53.9212684631348</v>
       </c>
       <c r="H502" t="n">
         <v>7316</v>
@@ -15072,7 +15072,7 @@
         <v>61</v>
       </c>
       <c r="G507" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H507" t="n">
         <v>21501</v>
@@ -15130,7 +15130,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H509" t="n">
         <v>5019</v>
@@ -15217,7 +15217,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H512" t="n">
         <v>3818</v>
@@ -15246,7 +15246,7 @@
         <v>61</v>
       </c>
       <c r="G513" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H513" t="n">
         <v>4354</v>
@@ -15275,7 +15275,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604797363281</v>
+        <v>54.4604759216309</v>
       </c>
       <c r="H514" t="n">
         <v>1131</v>
@@ -15333,7 +15333,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H516" t="n">
         <v>4297</v>
@@ -15420,7 +15420,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454635620117</v>
+        <v>51.0454597473145</v>
       </c>
       <c r="H519" t="n">
         <v>2414</v>
@@ -15449,7 +15449,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H520" t="n">
         <v>4684</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644157409668</v>
+        <v>51.7644119262695</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15710,7 +15710,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H529" t="n">
         <v>9560</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16232,7 +16232,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H547" t="n">
         <v>4611</v>
@@ -16435,7 +16435,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.4507141113281</v>
+        <v>47.4507179260254</v>
       </c>
       <c r="H554" t="n">
         <v>8684</v>
@@ -16638,7 +16638,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H561" t="n">
         <v>4778</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16986,7 +16986,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>47.4507141113281</v>
+        <v>47.4507179260254</v>
       </c>
       <c r="H573" t="n">
         <v>13677</v>
@@ -17102,7 +17102,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H577" t="n">
         <v>3506</v>
@@ -17131,7 +17131,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H578" t="n">
         <v>3272</v>
@@ -17160,7 +17160,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H579" t="n">
         <v>3967</v>
@@ -17189,7 +17189,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.86572265625</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H580" t="n">
         <v>33442</v>
@@ -17218,7 +17218,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.86572265625</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H581" t="n">
         <v>21771</v>
@@ -17247,7 +17247,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="n">
         <v>5028</v>
@@ -17334,7 +17334,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454635620117</v>
+        <v>51.0454597473145</v>
       </c>
       <c r="H585" t="n">
         <v>23929</v>
@@ -17537,7 +17537,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.236644744873</v>
+        <v>50.2366485595703</v>
       </c>
       <c r="H592" t="n">
         <v>13961</v>
@@ -17595,7 +17595,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.5961227416992</v>
+        <v>50.596118927002</v>
       </c>
       <c r="H594" t="n">
         <v>10198</v>
@@ -17653,7 +17653,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595291137695</v>
       </c>
       <c r="H596" t="n">
         <v>105612</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17711,7 +17711,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H598" t="n">
         <v>23794</v>
@@ -17827,7 +17827,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H602" t="n">
         <v>37767</v>
@@ -18088,7 +18088,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H611" t="n">
         <v>7555</v>
@@ -18175,7 +18175,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203178405762</v>
+        <v>47.7203216552734</v>
       </c>
       <c r="H614" t="n">
         <v>9199</v>
@@ -18233,7 +18233,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H616" t="n">
         <v>15159</v>
@@ -18291,7 +18291,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H618" t="n">
         <v>26603</v>
@@ -18320,7 +18320,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="n">
         <v>81517</v>
@@ -18349,7 +18349,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173248291016</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="n">
         <v>114943</v>
@@ -18378,7 +18378,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.976806640625</v>
+        <v>56.9768028259277</v>
       </c>
       <c r="H621" t="n">
         <v>116812</v>
@@ -18465,7 +18465,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173248291016</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="n">
         <v>9412</v>
@@ -18494,7 +18494,7 @@
         <v>61</v>
       </c>
       <c r="G625" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H625" t="n">
         <v>14322</v>
@@ -18523,7 +18523,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.471923828125</v>
+        <v>53.4719200134277</v>
       </c>
       <c r="H626" t="n">
         <v>14829</v>
@@ -18610,7 +18610,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098243713379</v>
+        <v>54.9098205566406</v>
       </c>
       <c r="H629" t="n">
         <v>33501</v>
@@ -18639,7 +18639,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.101001739502</v>
+        <v>54.1010055541992</v>
       </c>
       <c r="H630" t="n">
         <v>9653</v>
@@ -18726,7 +18726,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H633" t="n">
         <v>35889</v>
@@ -18755,7 +18755,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313941955566</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H634" t="n">
         <v>16777</v>
@@ -18784,7 +18784,7 @@
         <v>61</v>
       </c>
       <c r="G635" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H635" t="n">
         <v>37857</v>
@@ -18871,7 +18871,7 @@
         <v>61</v>
       </c>
       <c r="G638" t="n">
-        <v>54.8199501037598</v>
+        <v>54.819953918457</v>
       </c>
       <c r="H638" t="n">
         <v>10943</v>
@@ -18900,7 +18900,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H639" t="n">
         <v>13780</v>
@@ -18929,7 +18929,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996948242188</v>
       </c>
       <c r="H640" t="n">
         <v>3403</v>
@@ -18987,7 +18987,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G642" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H642" t="n">
         <v>9990</v>
@@ -19016,7 +19016,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>53.2023162841797</v>
+        <v>53.2023124694824</v>
       </c>
       <c r="H643" t="n">
         <v>9547</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19364,7 +19364,7 @@
         <v>60</v>
       </c>
       <c r="G655" t="n">
-        <v>53.9212646484375</v>
+        <v>53.9212684631348</v>
       </c>
       <c r="H655" t="n">
         <v>139231</v>
@@ -19393,7 +19393,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173248291016</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="n">
         <v>87829</v>
@@ -19422,7 +19422,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071990966797</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H657" t="n">
         <v>41152</v>
@@ -19451,7 +19451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071990966797</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H658" t="n">
         <v>26511</v>
@@ -19567,7 +19567,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="n">
         <v>35448</v>
@@ -19654,7 +19654,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.86572265625</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H665" t="n">
         <v>44030</v>
@@ -19741,7 +19741,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H668" t="n">
         <v>31289</v>
@@ -19857,7 +19857,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="n">
         <v>35845</v>
@@ -19915,7 +19915,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.1166458129883</v>
+        <v>33.1166381835938</v>
       </c>
       <c r="H674" t="n">
         <v>38571</v>
@@ -19944,7 +19944,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>33.3413162231445</v>
+        <v>33.3413200378418</v>
       </c>
       <c r="H675" t="n">
         <v>54537</v>
@@ -19973,7 +19973,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>28.2637310028076</v>
+        <v>28.263729095459</v>
       </c>
       <c r="H676" t="n">
         <v>31730</v>
@@ -20031,7 +20031,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.163257598877</v>
+        <v>25.1632556915283</v>
       </c>
       <c r="H678" t="n">
         <v>22986</v>
@@ -20176,7 +20176,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139148712158</v>
+        <v>24.7139129638672</v>
       </c>
       <c r="H683" t="n">
         <v>30853</v>
@@ -20263,7 +20263,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>24.9835186004639</v>
+        <v>24.9835205078125</v>
       </c>
       <c r="H686" t="n">
         <v>21534</v>
@@ -20350,7 +20350,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.432861328125</v>
+        <v>25.4328632354736</v>
       </c>
       <c r="H689" t="n">
         <v>33327</v>
@@ -20495,7 +20495,7 @@
         <v>30.5</v>
       </c>
       <c r="G694" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H694" t="n">
         <v>37669</v>
@@ -20611,7 +20611,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H698" t="n">
         <v>66739</v>
@@ -20727,7 +20727,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201065063477</v>
+        <v>27.3201084136963</v>
       </c>
       <c r="H702" t="n">
         <v>11386</v>
@@ -20814,7 +20814,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="n">
         <v>71298</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130756378174</v>
+        <v>28.7130718231201</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -20930,7 +20930,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086624145508</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="n">
         <v>38489</v>
@@ -20959,7 +20959,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.050500869751</v>
+        <v>27.0505027770996</v>
       </c>
       <c r="H710" t="n">
         <v>34512</v>
@@ -21017,7 +21017,7 @@
         <v>30.5</v>
       </c>
       <c r="G712" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H712" t="n">
         <v>17158</v>
@@ -21046,7 +21046,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>27.7694530487061</v>
+        <v>27.7694511413574</v>
       </c>
       <c r="H713" t="n">
         <v>21183</v>
@@ -21075,7 +21075,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>26.6011581420898</v>
+        <v>26.6011562347412</v>
       </c>
       <c r="H714" t="n">
         <v>22864</v>
@@ -21104,7 +21104,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359619140625</v>
+        <v>26.7359600067139</v>
       </c>
       <c r="H715" t="n">
         <v>47799</v>
@@ -21249,7 +21249,7 @@
         <v>30.5</v>
       </c>
       <c r="G720" t="n">
-        <v>27.4099750518799</v>
+        <v>27.4099769592285</v>
       </c>
       <c r="H720" t="n">
         <v>38236</v>
@@ -21307,7 +21307,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998455047607</v>
+        <v>27.4998474121094</v>
       </c>
       <c r="H722" t="n">
         <v>26961</v>
@@ -21365,7 +21365,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H724" t="n">
         <v>74966</v>
@@ -21394,7 +21394,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G725" t="n">
-        <v>29.072546005249</v>
+        <v>29.0725479125977</v>
       </c>
       <c r="H725" t="n">
         <v>48547</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566963195801</v>
+        <v>29.6566982269287</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21481,7 +21481,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959056854248</v>
+        <v>30.1959075927734</v>
       </c>
       <c r="H728" t="n">
         <v>39492</v>
@@ -21539,7 +21539,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642024993896</v>
+        <v>31.3642044067383</v>
       </c>
       <c r="H730" t="n">
         <v>45462</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241539001465</v>
+        <v>34.8241500854492</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717086791992</v>
+        <v>33.0717124938965</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21713,7 +21713,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="n">
         <v>76858</v>
@@ -21800,7 +21800,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.442626953125</v>
+        <v>32.4426231384277</v>
       </c>
       <c r="H739" t="n">
         <v>87104</v>
@@ -21829,7 +21829,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501350402832</v>
+        <v>34.1501312255859</v>
       </c>
       <c r="H740" t="n">
         <v>64579</v>
@@ -21887,7 +21887,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G742" t="n">
-        <v>36.0373725891113</v>
+        <v>36.0373802185059</v>
       </c>
       <c r="H742" t="n">
         <v>82973</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.5430946350098</v>
+        <v>35.5431022644043</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -21945,7 +21945,7 @@
         <v>41</v>
       </c>
       <c r="G744" t="n">
-        <v>36.8461990356445</v>
+        <v>36.8461952209473</v>
       </c>
       <c r="H744" t="n">
         <v>59580</v>
@@ -21974,7 +21974,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>34.3298759460449</v>
+        <v>34.3298721313477</v>
       </c>
       <c r="H745" t="n">
         <v>55801</v>
@@ -22032,7 +22032,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.6444129943848</v>
+        <v>34.6444091796875</v>
       </c>
       <c r="H747" t="n">
         <v>44338</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823173522949</v>
+        <v>36.0823135375977</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22264,7 +22264,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2840957641602</v>
+        <v>38.2841033935547</v>
       </c>
       <c r="H755" t="n">
         <v>52989</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202102661133</v>
+        <v>37.5202178955078</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22409,7 +22409,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.2832565307617</v>
+        <v>42.283260345459</v>
       </c>
       <c r="H760" t="n">
         <v>39270</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22612,7 +22612,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.8339157104492</v>
+        <v>41.833911895752</v>
       </c>
       <c r="H767" t="n">
         <v>20446</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22699,7 +22699,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687232971191</v>
       </c>
       <c r="H770" t="n">
         <v>30213</v>
@@ -22757,7 +22757,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687232971191</v>
       </c>
       <c r="H772" t="n">
         <v>37447</v>
@@ -22815,7 +22815,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.5079307556152</v>
+        <v>42.5079345703125</v>
       </c>
       <c r="H774" t="n">
         <v>35151</v>
@@ -22873,7 +22873,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G776" t="n">
-        <v>41.6991157531738</v>
+        <v>41.6991119384766</v>
       </c>
       <c r="H776" t="n">
         <v>46090</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440452575684</v>
+        <v>41.7440490722656</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -22960,7 +22960,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H779" t="n">
         <v>32289</v>
@@ -23018,7 +23018,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H781" t="n">
         <v>22565</v>
@@ -23076,7 +23076,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H783" t="n">
         <v>15651</v>
@@ -23105,7 +23105,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687232971191</v>
       </c>
       <c r="H784" t="n">
         <v>26455</v>
@@ -23250,7 +23250,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>43.2718124389648</v>
+        <v>43.2718200683594</v>
       </c>
       <c r="H789" t="n">
         <v>32576</v>
@@ -23279,7 +23279,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G790" t="n">
-        <v>43.2718124389648</v>
+        <v>43.2718200683594</v>
       </c>
       <c r="H790" t="n">
         <v>17846</v>
@@ -23337,7 +23337,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H792" t="n">
         <v>8813</v>
@@ -23366,7 +23366,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>42.7326011657715</v>
+        <v>42.7326049804688</v>
       </c>
       <c r="H793" t="n">
         <v>16734</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5977973937988</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5977973937988</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5977973937988</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23569,7 +23569,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H800" t="n">
         <v>29039</v>
@@ -23627,7 +23627,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.586353302002</v>
+        <v>43.5863571166992</v>
       </c>
       <c r="H802" t="n">
         <v>53936</v>
@@ -23743,7 +23743,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G806" t="n">
-        <v>42.3731307983398</v>
+        <v>42.3731269836426</v>
       </c>
       <c r="H806" t="n">
         <v>14107</v>
@@ -23888,7 +23888,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H811" t="n">
         <v>22840</v>
@@ -23946,7 +23946,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100807189941</v>
+        <v>37.6100769042969</v>
       </c>
       <c r="H813" t="n">
         <v>22502</v>
@@ -24004,7 +24004,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594215393066</v>
+        <v>38.0594291687012</v>
       </c>
       <c r="H815" t="n">
         <v>25044</v>
@@ -24033,7 +24033,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347549438477</v>
+        <v>37.8347511291504</v>
       </c>
       <c r="H816" t="n">
         <v>19737</v>
@@ -24091,7 +24091,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898178100586</v>
+        <v>37.7898216247559</v>
       </c>
       <c r="H818" t="n">
         <v>15517</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030479431152</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986442565918</v>
+        <v>38.5986366271973</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24178,7 +24178,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H821" t="n">
         <v>16005</v>
@@ -24236,7 +24236,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.452392578125</v>
+        <v>39.4523963928223</v>
       </c>
       <c r="H823" t="n">
         <v>12453</v>
@@ -24265,7 +24265,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422592163086</v>
+        <v>39.5422630310059</v>
       </c>
       <c r="H824" t="n">
         <v>9758</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030479431152</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24468,7 +24468,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144882202148</v>
+        <v>38.0144920349121</v>
       </c>
       <c r="H831" t="n">
         <v>12021</v>
@@ -24497,7 +24497,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638328552246</v>
+        <v>38.4638366699219</v>
       </c>
       <c r="H832" t="n">
         <v>15760</v>
@@ -24526,7 +24526,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.430347442627</v>
+        <v>37.4303436279297</v>
       </c>
       <c r="H833" t="n">
         <v>8832</v>
@@ -24613,7 +24613,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G836" t="n">
-        <v>34.2400016784668</v>
+        <v>34.2400054931641</v>
       </c>
       <c r="H836" t="n">
         <v>24293</v>
@@ -24700,7 +24700,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796920776367</v>
+        <v>37.8796882629395</v>
       </c>
       <c r="H839" t="n">
         <v>16617</v>
@@ -24845,7 +24845,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105560302734</v>
+        <v>40.7105522155762</v>
       </c>
       <c r="H844" t="n">
         <v>80049</v>
@@ -24903,7 +24903,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625259399414</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H846" t="n">
         <v>19364</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24961,7 +24961,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.878849029541</v>
+        <v>41.8788452148438</v>
       </c>
       <c r="H848" t="n">
         <v>26342</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453636169434</v>
+        <v>40.8453598022461</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017372131348</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25251,7 +25251,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.530818939209</v>
+        <v>40.5308151245117</v>
       </c>
       <c r="H858" t="n">
         <v>18769</v>
@@ -25280,7 +25280,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.800422668457</v>
+        <v>40.8004264831543</v>
       </c>
       <c r="H859" t="n">
         <v>9064</v>
@@ -25396,7 +25396,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G863" t="n">
-        <v>40.3510856628418</v>
+        <v>40.3510818481445</v>
       </c>
       <c r="H863" t="n">
         <v>11672</v>
@@ -25454,7 +25454,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528602600098</v>
       </c>
       <c r="H865" t="n">
         <v>24079</v>
@@ -25483,7 +25483,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889785766602</v>
+        <v>41.7889823913574</v>
       </c>
       <c r="H866" t="n">
         <v>12381</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25570,7 +25570,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>42.3731307983398</v>
+        <v>42.3731269836426</v>
       </c>
       <c r="H869" t="n">
         <v>9988</v>
@@ -25628,7 +25628,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471458435059</v>
+        <v>43.0471420288086</v>
       </c>
       <c r="H871" t="n">
         <v>16203</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25831,7 +25831,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.361686706543</v>
+        <v>43.3616828918457</v>
       </c>
       <c r="H878" t="n">
         <v>3445</v>
@@ -25918,7 +25918,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.552864074707</v>
+        <v>42.5528602600098</v>
       </c>
       <c r="H881" t="n">
         <v>11939</v>
@@ -25947,7 +25947,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687232971191</v>
       </c>
       <c r="H882" t="n">
         <v>4266</v>
@@ -25976,7 +25976,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G883" t="n">
-        <v>42.1035232543945</v>
+        <v>42.1035194396973</v>
       </c>
       <c r="H883" t="n">
         <v>5807</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26411,7 +26411,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H898" t="n">
         <v>15858</v>
@@ -26498,7 +26498,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H901" t="n">
         <v>12391</v>
@@ -26556,7 +26556,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H903" t="n">
         <v>40528</v>
@@ -26585,7 +26585,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H904" t="n">
         <v>18296</v>
@@ -26643,7 +26643,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>49.0683479309082</v>
+        <v>49.0683517456055</v>
       </c>
       <c r="H906" t="n">
         <v>6882</v>
@@ -26701,7 +26701,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582260131836</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H908" t="n">
         <v>10471</v>
@@ -26962,7 +26962,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>47.2709770202637</v>
+        <v>47.2709732055664</v>
       </c>
       <c r="H917" t="n">
         <v>10683</v>
@@ -27049,7 +27049,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H920" t="n">
         <v>13604</v>
@@ -27136,7 +27136,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.260368347168</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H923" t="n">
         <v>10806</v>
@@ -27194,7 +27194,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G925" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H925" t="n">
         <v>24024</v>
@@ -27281,7 +27281,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H928" t="n">
         <v>14790</v>
@@ -27310,7 +27310,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H929" t="n">
         <v>14814</v>
@@ -27339,7 +27339,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H930" t="n">
         <v>11631</v>
@@ -27542,7 +27542,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>47.4507141113281</v>
+        <v>47.4507179260254</v>
       </c>
       <c r="H937" t="n">
         <v>6177</v>
@@ -27600,7 +27600,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G939" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H939" t="n">
         <v>2144</v>
@@ -27629,7 +27629,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>47.2709770202637</v>
+        <v>47.2709732055664</v>
       </c>
       <c r="H940" t="n">
         <v>9185</v>
@@ -27687,7 +27687,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G942" t="n">
-        <v>47.091236114502</v>
+        <v>47.0912399291992</v>
       </c>
       <c r="H942" t="n">
         <v>9550</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27803,7 +27803,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>47.4507141113281</v>
+        <v>47.4507179260254</v>
       </c>
       <c r="H946" t="n">
         <v>4946</v>
@@ -28006,7 +28006,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H953" t="n">
         <v>23396</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28180,7 +28180,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H959" t="n">
         <v>15470</v>
@@ -28325,7 +28325,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595291137695</v>
       </c>
       <c r="H964" t="n">
         <v>14743</v>
@@ -28354,7 +28354,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H965" t="n">
         <v>6406</v>
@@ -28412,7 +28412,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H967" t="n">
         <v>3349</v>
@@ -28441,7 +28441,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H968" t="n">
         <v>12385</v>
@@ -28470,7 +28470,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G969" t="n">
-        <v>47.4507141113281</v>
+        <v>47.4507179260254</v>
       </c>
       <c r="H969" t="n">
         <v>11609</v>
@@ -28644,7 +28644,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H975" t="n">
         <v>19832</v>
@@ -28673,7 +28673,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647834777832</v>
+        <v>44.6647796630859</v>
       </c>
       <c r="H976" t="n">
         <v>23268</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.1925506591797</v>
+        <v>46.192554473877</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28963,7 +28963,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837356567383</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H986" t="n">
         <v>9545</v>
@@ -28992,7 +28992,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H987" t="n">
         <v>17603</v>
@@ -29137,7 +29137,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432060241699</v>
+        <v>45.7432098388672</v>
       </c>
       <c r="H992" t="n">
         <v>32659</v>
@@ -29282,7 +29282,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519195556641</v>
+        <v>42.9519157409668</v>
       </c>
       <c r="H997" t="n">
         <v>575572</v>
@@ -29311,7 +29311,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765251159668</v>
+        <v>44.1765289306641</v>
       </c>
       <c r="H998" t="n">
         <v>76506</v>
@@ -29746,7 +29746,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863021850586</v>
+        <v>39.6863059997559</v>
       </c>
       <c r="H1013" t="n">
         <v>19765</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.636604309082</v>
+        <v>41.6366081237793</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797828674316</v>
+        <v>42.6797866821289</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30007,7 +30007,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1022" t="n">
-        <v>42.9972801208496</v>
+        <v>42.9972763061523</v>
       </c>
       <c r="H1022" t="n">
         <v>30204</v>
@@ -30036,7 +30036,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1023" t="n">
-        <v>41.8180236816406</v>
+        <v>41.8180274963379</v>
       </c>
       <c r="H1023" t="n">
         <v>19161</v>
@@ -30123,7 +30123,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043960571289</v>
+        <v>43.9043922424316</v>
       </c>
       <c r="H1026" t="n">
         <v>28292</v>
@@ -30152,7 +30152,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>43.8590354919434</v>
+        <v>43.8590393066406</v>
       </c>
       <c r="H1027" t="n">
         <v>19195</v>
@@ -30210,7 +30210,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1029" t="n">
         <v>17463</v>
@@ -30268,7 +30268,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1031" t="n">
-        <v>43.6322555541992</v>
+        <v>43.6322593688965</v>
       </c>
       <c r="H1031" t="n">
         <v>16965</v>
@@ -30326,7 +30326,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1033" t="n">
         <v>17232</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218818664551</v>
+        <v>44.2218856811523</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30442,7 +30442,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776123046875</v>
+        <v>43.6776161193848</v>
       </c>
       <c r="H1037" t="n">
         <v>8307</v>
@@ -30500,7 +30500,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1039" t="n">
         <v>43123</v>
@@ -30529,7 +30529,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1040" t="n">
-        <v>45.7186241149902</v>
+        <v>45.7186279296875</v>
       </c>
       <c r="H1040" t="n">
         <v>21118</v>
@@ -30645,7 +30645,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1044" t="n">
         <v>18875</v>
@@ -30790,7 +30790,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306777954102</v>
+        <v>48.5306816101074</v>
       </c>
       <c r="H1049" t="n">
         <v>8692</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328521728516</v>
+        <v>47.5328559875488</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443168640137</v>
+        <v>46.4443206787109</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -31022,7 +31022,7 @@
         <v>50</v>
       </c>
       <c r="G1057" t="n">
-        <v>45.3557777404785</v>
+        <v>45.3557739257812</v>
       </c>
       <c r="H1057" t="n">
         <v>4460</v>
@@ -31283,7 +31283,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1066" t="n">
         <v>12121</v>
@@ -31341,7 +31341,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1068" t="n">
-        <v>44.6300849914551</v>
+        <v>44.6300811767578</v>
       </c>
       <c r="H1068" t="n">
         <v>5362</v>
@@ -31428,7 +31428,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1071" t="n">
         <v>12696</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093376159668</v>
+        <v>45.8093338012695</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31573,7 +31573,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836448669434</v>
+        <v>45.0836410522461</v>
       </c>
       <c r="H1076" t="n">
         <v>6221</v>
@@ -31602,7 +31602,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>44.0404586791992</v>
+        <v>44.0404624938965</v>
       </c>
       <c r="H1077" t="n">
         <v>13929</v>
@@ -31660,7 +31660,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>44.6300849914551</v>
+        <v>44.6300811767578</v>
       </c>
       <c r="H1079" t="n">
         <v>29940</v>
@@ -31689,7 +31689,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.897876739502</v>
+        <v>46.8978729248047</v>
       </c>
       <c r="H1080" t="n">
         <v>42778</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563743591309</v>
+        <v>49.2563705444336</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31834,7 +31834,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721801757812</v>
+        <v>46.1721839904785</v>
       </c>
       <c r="H1085" t="n">
         <v>9377</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.459529876709</v>
+        <v>39.4595260620117</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31950,7 +31950,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895637512207</v>
+        <v>38.1895599365234</v>
       </c>
       <c r="H1089" t="n">
         <v>84053</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32124,7 +32124,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1095" t="n">
         <v>71980</v>
@@ -32240,7 +32240,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452941894531</v>
+        <v>37.6452980041504</v>
       </c>
       <c r="H1099" t="n">
         <v>38990</v>
@@ -32443,7 +32443,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1106" t="n">
         <v>33320</v>
@@ -32472,7 +32472,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.1485557556152</v>
+        <v>36.148551940918</v>
       </c>
       <c r="H1107" t="n">
         <v>22362</v>
@@ -32530,7 +32530,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578460693359</v>
+        <v>36.0578422546387</v>
       </c>
       <c r="H1109" t="n">
         <v>22744</v>
@@ -32559,7 +32559,7 @@
         <v>40</v>
       </c>
       <c r="G1110" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1110" t="n">
         <v>12495</v>
@@ -32588,7 +32588,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.2867965698242</v>
+        <v>35.2868003845215</v>
       </c>
       <c r="H1111" t="n">
         <v>26873</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -32849,7 +32849,7 @@
         <v>39.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>35.6042861938477</v>
+        <v>35.6042823791504</v>
       </c>
       <c r="H1120" t="n">
         <v>13419</v>
@@ -32965,7 +32965,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1124" t="n">
         <v>16911</v>
@@ -33052,7 +33052,7 @@
         <v>40.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>36.5113983154297</v>
+        <v>36.511402130127</v>
       </c>
       <c r="H1127" t="n">
         <v>35284</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463813781738</v>
+        <v>37.1463851928711</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33168,7 +33168,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884803771973</v>
+        <v>38.6884765625</v>
       </c>
       <c r="H1131" t="n">
         <v>27152</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33313,7 +33313,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698959350586</v>
+        <v>38.8698997497559</v>
       </c>
       <c r="H1136" t="n">
         <v>22436</v>
@@ -33371,7 +33371,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>37.4638710021973</v>
+        <v>37.4638748168945</v>
       </c>
       <c r="H1138" t="n">
         <v>15196</v>
@@ -33429,7 +33429,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753280639648</v>
+        <v>36.3753318786621</v>
       </c>
       <c r="H1140" t="n">
         <v>22080</v>
@@ -33516,7 +33516,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688125610352</v>
+        <v>39.3688163757324</v>
       </c>
       <c r="H1143" t="n">
         <v>170822</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764190673828</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33661,7 +33661,7 @@
         <v>39.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>35.6042861938477</v>
+        <v>35.6042823791504</v>
       </c>
       <c r="H1148" t="n">
         <v>52820</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33777,7 +33777,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146560668945</v>
+        <v>35.0146598815918</v>
       </c>
       <c r="H1152" t="n">
         <v>109200</v>
@@ -33806,7 +33806,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1153" t="n">
         <v>41376</v>
@@ -33835,7 +33835,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250373840332</v>
+        <v>34.4250335693359</v>
       </c>
       <c r="H1154" t="n">
         <v>41497</v>
@@ -33893,7 +33893,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507301330566</v>
+        <v>35.1507263183594</v>
       </c>
       <c r="H1156" t="n">
         <v>64899</v>
@@ -34009,7 +34009,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611000061035</v>
+        <v>34.5611038208008</v>
       </c>
       <c r="H1160" t="n">
         <v>37289</v>
@@ -34154,7 +34154,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1165" t="n">
         <v>37830</v>
@@ -34241,7 +34241,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556716918945</v>
+        <v>37.0556678771973</v>
       </c>
       <c r="H1168" t="n">
         <v>36948</v>
@@ -34328,7 +34328,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.103199005127</v>
+        <v>36.1031951904297</v>
       </c>
       <c r="H1171" t="n">
         <v>37325</v>
@@ -34386,7 +34386,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1173" t="n">
         <v>72195</v>
@@ -34444,7 +34444,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.8829383850098</v>
+        <v>32.882942199707</v>
       </c>
       <c r="H1175" t="n">
         <v>70764</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605033874512</v>
+        <v>30.6605052947998</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34502,7 +34502,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861961364746</v>
+        <v>31.3861980438232</v>
       </c>
       <c r="H1177" t="n">
         <v>52489</v>
@@ -34589,7 +34589,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691951751709</v>
+        <v>26.6691970825195</v>
       </c>
       <c r="H1180" t="n">
         <v>77366</v>
@@ -34618,7 +34618,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577362060547</v>
+        <v>27.7577381134033</v>
       </c>
       <c r="H1181" t="n">
         <v>42139</v>
@@ -34734,7 +34734,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233535766602</v>
+        <v>31.0233554840088</v>
       </c>
       <c r="H1185" t="n">
         <v>64152</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419303894043</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34821,7 +34821,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457885742188</v>
+        <v>33.2457847595215</v>
       </c>
       <c r="H1188" t="n">
         <v>15564</v>
@@ -34850,7 +34850,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272079467773</v>
+        <v>33.4272041320801</v>
       </c>
       <c r="H1189" t="n">
         <v>34565</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600166320801</v>
+        <v>35.0600204467773</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34937,7 +34937,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1192" t="n">
         <v>13009</v>
@@ -35111,7 +35111,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332366943359</v>
+        <v>34.8332405090332</v>
       </c>
       <c r="H1198" t="n">
         <v>31111</v>
@@ -35140,7 +35140,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1199" t="n">
         <v>16944</v>
@@ -35227,7 +35227,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1202" t="n">
         <v>27154</v>
@@ -35256,7 +35256,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403564453125</v>
+        <v>35.7403526306152</v>
       </c>
       <c r="H1203" t="n">
         <v>17730</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35401,7 +35401,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742446899414</v>
+        <v>36.8742485046387</v>
       </c>
       <c r="H1208" t="n">
         <v>18290</v>
@@ -35575,7 +35575,7 @@
         <v>40.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>36.5113983154297</v>
+        <v>36.511402130127</v>
       </c>
       <c r="H1214" t="n">
         <v>18129</v>
@@ -35633,7 +35633,7 @@
         <v>40</v>
       </c>
       <c r="G1216" t="n">
-        <v>36.2846221923828</v>
+        <v>36.2846183776855</v>
       </c>
       <c r="H1216" t="n">
         <v>38623</v>
@@ -68670,6 +68670,35 @@
         <v>1625592</v>
       </c>
       <c r="I2355" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2356" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>1.70200002193451</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>1.64800000190735</v>
+      </c>
+      <c r="G2356" t="n">
+        <v>1.64800000190735</v>
+      </c>
+      <c r="H2356" t="n">
+        <v>1171070</v>
+      </c>
+      <c r="I2356" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -543,7 +543,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H6" t="n">
         <v>100979</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318496704102</v>
+        <v>46.7318534851074</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -717,7 +717,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.9132652282715</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H12" t="n">
         <v>19418</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.8695106506348</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -833,7 +833,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632171630859</v>
+        <v>47.5632209777832</v>
       </c>
       <c r="H16" t="n">
         <v>20120</v>
@@ -920,7 +920,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>47.7382431030273</v>
+        <v>47.7382469177246</v>
       </c>
       <c r="H19" t="n">
         <v>39604</v>
@@ -949,7 +949,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0818977355957</v>
+        <v>47.081901550293</v>
       </c>
       <c r="H20" t="n">
         <v>12065</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506301879883</v>
+        <v>46.950626373291</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1007,7 +1007,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.4693069458008</v>
+        <v>46.469310760498</v>
       </c>
       <c r="H22" t="n">
         <v>15015</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131690979004</v>
+        <v>47.2131652832031</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1065,7 +1065,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880950927734</v>
+        <v>46.6880874633789</v>
       </c>
       <c r="H24" t="n">
         <v>35958</v>
@@ -1094,7 +1094,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.125659942627</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H25" t="n">
         <v>24385</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443367004395</v>
+        <v>46.6443290710449</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1210,7 +1210,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254524230957</v>
+        <v>45.7254486083984</v>
       </c>
       <c r="H29" t="n">
         <v>15825</v>
@@ -1268,7 +1268,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.5130653381348</v>
+        <v>46.513069152832</v>
       </c>
       <c r="H31" t="n">
         <v>8478</v>
@@ -1297,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="G32" t="n">
-        <v>46.3818016052246</v>
+        <v>46.3817939758301</v>
       </c>
       <c r="H32" t="n">
         <v>21384</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.681697845459</v>
+        <v>45.6816902160645</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1384,7 +1384,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.125659942627</v>
+        <v>47.1256523132324</v>
       </c>
       <c r="H35" t="n">
         <v>35180</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069793701172</v>
+        <v>47.6069755554199</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1442,7 +1442,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068756103516</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H37" t="n">
         <v>10252</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881950378418</v>
+        <v>47.3881912231445</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1529,7 +1529,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.9943809509277</v>
+        <v>46.9943885803223</v>
       </c>
       <c r="H40" t="n">
         <v>9334</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320571899414</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0882987976074</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.8695106506348</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1674,7 +1674,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.9132652282715</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H45" t="n">
         <v>55518</v>
@@ -1703,7 +1703,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068756103516</v>
+        <v>46.906867980957</v>
       </c>
       <c r="H46" t="n">
         <v>84037</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194625854492</v>
+        <v>47.5194664001465</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135765075684</v>
+        <v>50.0135841369629</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2080,7 +2080,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577499389648</v>
+        <v>52.8577461242676</v>
       </c>
       <c r="H59" t="n">
         <v>33673</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953147888184</v>
+        <v>53.2953109741211</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579574584961</v>
+        <v>54.2579498291016</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2225,7 +2225,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H64" t="n">
         <v>18989</v>
@@ -2254,7 +2254,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955184936523</v>
       </c>
       <c r="H65" t="n">
         <v>17831</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.258975982666</v>
+        <v>61.2589683532715</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2370,7 +2370,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4404029846191</v>
+        <v>62.4404067993164</v>
       </c>
       <c r="H69" t="n">
         <v>51076</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965484619141</v>
+        <v>61.6965370178223</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965484619141</v>
+        <v>61.6965370178223</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339942932129</v>
+        <v>61.4340019226074</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964370727539</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2573,7 +2573,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462814331055</v>
+        <v>59.9462852478027</v>
       </c>
       <c r="H76" t="n">
         <v>17560</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275085449219</v>
+        <v>59.7274971008301</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838500976562</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276123046875</v>
+        <v>60.4276008605957</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2747,7 +2747,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026344299316</v>
+        <v>60.6026306152344</v>
       </c>
       <c r="H82" t="n">
         <v>33403</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214073181152</v>
+        <v>60.821418762207</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898399353027</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2863,7 +2863,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H86" t="n">
         <v>30413</v>
@@ -2892,7 +2892,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>54.5204849243164</v>
+        <v>54.5204887390137</v>
       </c>
       <c r="H87" t="n">
         <v>43778</v>
@@ -2921,7 +2921,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H88" t="n">
         <v>37736</v>
@@ -2950,7 +2950,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H89" t="n">
         <v>30442</v>
@@ -2979,7 +2979,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273010253906</v>
+        <v>58.3272972106934</v>
       </c>
       <c r="H90" t="n">
         <v>24556</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772415161133</v>
+        <v>57.9772453308105</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.027400970459</v>
+        <v>59.0273895263672</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834426879883</v>
+        <v>57.583438873291</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3240,7 +3240,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583572387695</v>
+        <v>57.0583534240723</v>
       </c>
       <c r="H99" t="n">
         <v>27245</v>
@@ -3298,7 +3298,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395767211914</v>
+        <v>56.8395805358887</v>
       </c>
       <c r="H101" t="n">
         <v>37551</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708480834961</v>
+        <v>56.9708442687988</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276123046875</v>
+        <v>60.4276008605957</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525787353516</v>
+        <v>60.2525825500488</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898361206055</v>
+        <v>58.5898399353027</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3559,7 +3559,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H110" t="n">
         <v>57326</v>
@@ -3646,7 +3646,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H113" t="n">
         <v>116509</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3733,7 +3733,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.670955657959</v>
+        <v>57.6709480285645</v>
       </c>
       <c r="H116" t="n">
         <v>53938</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897361755371</v>
+        <v>57.8897323608398</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3791,7 +3791,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648620605469</v>
+        <v>58.7648544311523</v>
       </c>
       <c r="H118" t="n">
         <v>16964</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899398803711</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3849,7 +3849,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334869384766</v>
+        <v>57.9334831237793</v>
       </c>
       <c r="H120" t="n">
         <v>11962</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461776733398</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962295532227</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397880554199</v>
+        <v>58.2397842407227</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4023,7 +4023,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H126" t="n">
         <v>36944</v>
@@ -4081,7 +4081,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H128" t="n">
         <v>47008</v>
@@ -4139,7 +4139,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145027160645</v>
+        <v>56.3144989013672</v>
       </c>
       <c r="H130" t="n">
         <v>10098</v>
@@ -4168,7 +4168,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H131" t="n">
         <v>10634</v>
@@ -4197,7 +4197,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146064758301</v>
+        <v>57.0146026611328</v>
       </c>
       <c r="H132" t="n">
         <v>14544</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.620792388916</v>
+        <v>56.6207962036133</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4255,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H134" t="n">
         <v>10051</v>
@@ -4284,7 +4284,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.189624786377</v>
+        <v>57.1896286010742</v>
       </c>
       <c r="H135" t="n">
         <v>6298</v>
@@ -4342,7 +4342,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H137" t="n">
         <v>26876</v>
@@ -4400,7 +4400,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.795825958252</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H139" t="n">
         <v>15720</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831314086914</v>
+        <v>55.4831352233887</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582611083984</v>
+        <v>56.3582649230957</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4487,7 +4487,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643508911133</v>
+        <v>55.2643547058105</v>
       </c>
       <c r="H142" t="n">
         <v>21545</v>
@@ -4516,7 +4516,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955184936523</v>
       </c>
       <c r="H143" t="n">
         <v>12997</v>
@@ -4545,7 +4545,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955184936523</v>
       </c>
       <c r="H144" t="n">
         <v>26633</v>
@@ -4632,7 +4632,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H147" t="n">
         <v>49677</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.139476776123</v>
+        <v>56.1394805908203</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4719,7 +4719,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H150" t="n">
         <v>21367</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266822814941</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4864,7 +4864,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578498840332</v>
+        <v>53.5578460693359</v>
       </c>
       <c r="H155" t="n">
         <v>11308</v>
@@ -5009,7 +5009,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H160" t="n">
         <v>11068</v>
@@ -5038,7 +5038,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H161" t="n">
         <v>19271</v>
@@ -5096,7 +5096,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.357234954834</v>
+        <v>49.3572311401367</v>
       </c>
       <c r="H163" t="n">
         <v>14934</v>
@@ -5183,7 +5183,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H166" t="n">
         <v>9806</v>
@@ -5212,7 +5212,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764266967773</v>
+        <v>52.3764190673828</v>
       </c>
       <c r="H167" t="n">
         <v>20718</v>
@@ -5241,7 +5241,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201850891113</v>
+        <v>52.4201812744141</v>
       </c>
       <c r="H168" t="n">
         <v>15941</v>
@@ -5270,7 +5270,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265785217285</v>
+        <v>53.4265823364258</v>
       </c>
       <c r="H169" t="n">
         <v>13847</v>
@@ -5299,7 +5299,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H170" t="n">
         <v>15151</v>
@@ -5357,7 +5357,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8951034545898</v>
+        <v>51.8950996398926</v>
       </c>
       <c r="H172" t="n">
         <v>4493</v>
@@ -5444,7 +5444,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H175" t="n">
         <v>7119</v>
@@ -5473,7 +5473,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511413574219</v>
+        <v>50.4511489868164</v>
       </c>
       <c r="H176" t="n">
         <v>8990</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.7510452270508</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5647,7 +5647,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010932922363</v>
+        <v>50.1010971069336</v>
       </c>
       <c r="H182" t="n">
         <v>28706</v>
@@ -5676,7 +5676,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H183" t="n">
         <v>12299</v>
@@ -5705,7 +5705,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137840270996</v>
+        <v>51.4137878417969</v>
       </c>
       <c r="H184" t="n">
         <v>13554</v>
@@ -5734,7 +5734,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264785766602</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H185" t="n">
         <v>20301</v>
@@ -5850,7 +5850,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H189" t="n">
         <v>14775</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516525268555</v>
+        <v>53.9516563415527</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6169,7 +6169,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H200" t="n">
         <v>18598</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330833435059</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6256,7 +6256,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142951965332</v>
+        <v>54.9142990112305</v>
       </c>
       <c r="H203" t="n">
         <v>6842</v>
@@ -6314,7 +6314,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391693115234</v>
+        <v>54.0391654968262</v>
       </c>
       <c r="H205" t="n">
         <v>7569</v>
@@ -6372,7 +6372,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141990661621</v>
       </c>
       <c r="H207" t="n">
         <v>6821</v>
@@ -6401,7 +6401,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830276489258</v>
+        <v>54.783031463623</v>
       </c>
       <c r="H208" t="n">
         <v>8498</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390731811523</v>
+        <v>53.3390655517578</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6459,7 +6459,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.3454627990723</v>
+        <v>54.345458984375</v>
       </c>
       <c r="H210" t="n">
         <v>5210</v>
@@ -6517,7 +6517,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>55.220588684082</v>
+        <v>55.2205924987793</v>
       </c>
       <c r="H212" t="n">
         <v>2916</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823127746582</v>
+        <v>49.8823089599609</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8695106506348</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179885864258</v>
+        <v>44.617992401123</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6691,7 +6691,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041465759277</v>
+        <v>45.5041427612305</v>
       </c>
       <c r="H218" t="n">
         <v>23030</v>
@@ -6749,7 +6749,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358428955078</v>
+        <v>46.0358390808105</v>
       </c>
       <c r="H220" t="n">
         <v>30045</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6865,7 +6865,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G224" t="n">
-        <v>44.839527130127</v>
+        <v>44.8395309448242</v>
       </c>
       <c r="H224" t="n">
         <v>24015</v>
@@ -6894,7 +6894,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.928150177002</v>
+        <v>44.9281463623047</v>
       </c>
       <c r="H225" t="n">
         <v>28013</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025993347168</v>
+        <v>42.4025955200195</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7155,7 +7155,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.96630859375</v>
+        <v>46.9663009643555</v>
       </c>
       <c r="H234" t="n">
         <v>26806</v>
@@ -7242,7 +7242,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.295539855957</v>
+        <v>48.2955360412598</v>
       </c>
       <c r="H237" t="n">
         <v>20676</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475402832031</v>
+        <v>49.4475440979004</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7329,7 +7329,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361633300781</v>
+        <v>49.5361595153809</v>
       </c>
       <c r="H240" t="n">
         <v>97891</v>
@@ -7358,7 +7358,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.226001739502</v>
+        <v>49.2260055541992</v>
       </c>
       <c r="H241" t="n">
         <v>21035</v>
@@ -7416,7 +7416,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410781860352</v>
+        <v>47.9410743713379</v>
       </c>
       <c r="H243" t="n">
         <v>19274</v>
@@ -7445,7 +7445,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H244" t="n">
         <v>15929</v>
@@ -7474,7 +7474,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678596496582</v>
       </c>
       <c r="H245" t="n">
         <v>24572</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158515930176</v>
+        <v>48.9158477783203</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7532,7 +7532,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H247" t="n">
         <v>16775</v>
@@ -7561,7 +7561,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983215332031</v>
+        <v>50.9983177185059</v>
       </c>
       <c r="H248" t="n">
         <v>36235</v>
@@ -7590,7 +7590,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844757080078</v>
+        <v>51.8844718933105</v>
       </c>
       <c r="H249" t="n">
         <v>15149</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678596496582</v>
       </c>
       <c r="H251" t="n">
         <v>9250</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -7996,7 +7996,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496887207031</v>
+        <v>45.1496849060059</v>
       </c>
       <c r="H263" t="n">
         <v>17681</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.3712272644043</v>
+        <v>45.371223449707</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8257,7 +8257,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232276916504</v>
+        <v>46.5232238769531</v>
       </c>
       <c r="H272" t="n">
         <v>8521</v>
@@ -8373,7 +8373,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989074707031</v>
+        <v>43.5989112854004</v>
       </c>
       <c r="H276" t="n">
         <v>6787</v>
@@ -8402,7 +8402,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H277" t="n">
         <v>2613</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8576,7 +8576,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570648193359</v>
+        <v>42.7570571899414</v>
       </c>
       <c r="H283" t="n">
         <v>10993</v>
@@ -8605,7 +8605,7 @@
         <v>47.7249984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>42.2918281555176</v>
+        <v>42.2918243408203</v>
       </c>
       <c r="H284" t="n">
         <v>1881</v>
@@ -8663,7 +8663,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H286" t="n">
         <v>13125</v>
@@ -8837,7 +8837,7 @@
         <v>48.75</v>
       </c>
       <c r="G292" t="n">
-        <v>43.2001419067383</v>
+        <v>43.200138092041</v>
       </c>
       <c r="H292" t="n">
         <v>25355</v>
@@ -8895,7 +8895,7 @@
         <v>48.3250007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>42.8235282897949</v>
+        <v>42.8235244750977</v>
       </c>
       <c r="H294" t="n">
         <v>3730</v>
@@ -8924,7 +8924,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H295" t="n">
         <v>8398</v>
@@ -8953,7 +8953,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450668334961</v>
+        <v>43.0450592041016</v>
       </c>
       <c r="H296" t="n">
         <v>6836</v>
@@ -9069,7 +9069,7 @@
         <v>48.8250007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>43.2666053771973</v>
+        <v>43.2666015625</v>
       </c>
       <c r="H300" t="n">
         <v>4300</v>
@@ -9098,7 +9098,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H301" t="n">
         <v>1288</v>
@@ -9156,7 +9156,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102958679199</v>
+        <v>43.5102920532227</v>
       </c>
       <c r="H303" t="n">
         <v>15525</v>
@@ -9185,7 +9185,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H304" t="n">
         <v>13328</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9786033630371</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349052429199</v>
+        <v>42.7349090576172</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9301,7 +9301,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.804443359375</v>
+        <v>41.8044395446777</v>
       </c>
       <c r="H308" t="n">
         <v>42371</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9388,7 +9388,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853584289551</v>
+        <v>40.7853622436523</v>
       </c>
       <c r="H311" t="n">
         <v>17137</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638236999512</v>
+        <v>40.5638198852539</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.946590423584</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213600158691</v>
+        <v>39.9213562011719</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9736,7 +9736,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H323" t="n">
         <v>2457</v>
@@ -9794,7 +9794,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H325" t="n">
         <v>6799</v>
@@ -9852,7 +9852,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H327" t="n">
         <v>5952</v>
@@ -9939,7 +9939,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099754333496</v>
+        <v>40.0099716186523</v>
       </c>
       <c r="H330" t="n">
         <v>3763</v>
@@ -9968,7 +9968,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758255004883</v>
+        <v>40.2758178710938</v>
       </c>
       <c r="H331" t="n">
         <v>6546</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10229,7 +10229,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361396789551</v>
+        <v>42.3361358642578</v>
       </c>
       <c r="H340" t="n">
         <v>1621</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069046020508</v>
+        <v>41.0069007873535</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10374,7 +10374,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.984748840332</v>
+        <v>40.9847450256348</v>
       </c>
       <c r="H345" t="n">
         <v>10026</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807403564453</v>
+        <v>38.6807441711426</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10519,7 +10519,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684455871582</v>
+        <v>42.6684494018555</v>
       </c>
       <c r="H350" t="n">
         <v>39393</v>
@@ -10606,7 +10606,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>45.0610656738281</v>
+        <v>45.0610694885254</v>
       </c>
       <c r="H353" t="n">
         <v>7257</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764587402344</v>
+        <v>47.2764549255371</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10722,7 +10722,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878471374512</v>
+        <v>47.1878433227539</v>
       </c>
       <c r="H357" t="n">
         <v>7547</v>
@@ -10780,7 +10780,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.8333778381348</v>
+        <v>46.833381652832</v>
       </c>
       <c r="H359" t="n">
         <v>4295</v>
@@ -10867,7 +10867,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432151794434</v>
+        <v>43.6432189941406</v>
       </c>
       <c r="H362" t="n">
         <v>6139</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419845581055</v>
+        <v>44.0419883728027</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10925,7 +10925,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H364" t="n">
         <v>1387</v>
@@ -10983,7 +10983,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973602294922</v>
+        <v>40.4973564147949</v>
       </c>
       <c r="H366" t="n">
         <v>12931</v>
@@ -11070,7 +11070,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H369" t="n">
         <v>22056</v>
@@ -11099,7 +11099,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321350097656</v>
+        <v>40.0321273803711</v>
       </c>
       <c r="H370" t="n">
         <v>10048</v>
@@ -11186,7 +11186,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724502563477</v>
+        <v>44.9724540710449</v>
       </c>
       <c r="H373" t="n">
         <v>15133</v>
@@ -11273,7 +11273,7 @@
         <v>55.25</v>
       </c>
       <c r="G376" t="n">
-        <v>48.9601554870605</v>
+        <v>48.9601593017578</v>
       </c>
       <c r="H376" t="n">
         <v>10916</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780059814453</v>
+        <v>50.3780136108398</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11360,7 +11360,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893943786621</v>
+        <v>50.2893905639648</v>
       </c>
       <c r="H379" t="n">
         <v>16967</v>
@@ -11389,7 +11389,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H380" t="n">
         <v>62651</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958564758301</v>
+        <v>51.7958602905273</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11476,7 +11476,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H383" t="n">
         <v>3458</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121635437012</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11621,7 +11621,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463096618652</v>
+        <v>49.8463172912598</v>
       </c>
       <c r="H388" t="n">
         <v>9469</v>
@@ -11650,7 +11650,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032325744629</v>
+        <v>49.4032363891602</v>
       </c>
       <c r="H389" t="n">
         <v>4963</v>
@@ -11679,7 +11679,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678596496582</v>
       </c>
       <c r="H390" t="n">
         <v>14079</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11766,7 +11766,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263221740723</v>
+        <v>52.726318359375</v>
       </c>
       <c r="H393" t="n">
         <v>9144</v>
@@ -11795,7 +11795,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263221740723</v>
+        <v>52.726318359375</v>
       </c>
       <c r="H394" t="n">
         <v>11783</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -12027,7 +12027,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961807250977</v>
+        <v>55.2961769104004</v>
       </c>
       <c r="H402" t="n">
         <v>18544</v>
@@ -12056,7 +12056,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H403" t="n">
         <v>55252</v>
@@ -12085,7 +12085,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H404" t="n">
         <v>12420</v>
@@ -12114,7 +12114,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998649597168</v>
+        <v>54.0998687744141</v>
       </c>
       <c r="H405" t="n">
         <v>6186</v>
@@ -12172,7 +12172,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H407" t="n">
         <v>16902</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12230,7 +12230,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380233764648</v>
+        <v>56.1380271911621</v>
       </c>
       <c r="H409" t="n">
         <v>12835</v>
@@ -12259,7 +12259,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.7774124145508</v>
+        <v>57.7774085998535</v>
       </c>
       <c r="H410" t="n">
         <v>15892</v>
@@ -12288,7 +12288,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001815795898</v>
+        <v>57.6001853942871</v>
       </c>
       <c r="H411" t="n">
         <v>34918</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.157112121582</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12462,7 +12462,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863433837891</v>
+        <v>58.4863395690918</v>
       </c>
       <c r="H417" t="n">
         <v>56533</v>
@@ -12491,7 +12491,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H418" t="n">
         <v>12366</v>
@@ -12549,7 +12549,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>56.359561920166</v>
+        <v>56.3595657348633</v>
       </c>
       <c r="H420" t="n">
         <v>35472</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12607,7 +12607,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>57.4672622680664</v>
+        <v>57.4672584533691</v>
       </c>
       <c r="H422" t="n">
         <v>5806</v>
@@ -12665,7 +12665,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H424" t="n">
         <v>12768</v>
@@ -12694,7 +12694,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229583740234</v>
+        <v>57.4229545593262</v>
       </c>
       <c r="H425" t="n">
         <v>11750</v>
@@ -12723,7 +12723,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6888046264648</v>
+        <v>57.6887969970703</v>
       </c>
       <c r="H426" t="n">
         <v>8138</v>
@@ -12752,7 +12752,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>55.2075576782227</v>
+        <v>55.2075614929199</v>
       </c>
       <c r="H427" t="n">
         <v>11503</v>
@@ -12810,7 +12810,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H429" t="n">
         <v>9582</v>
@@ -12839,7 +12839,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278732299805</v>
+        <v>55.8278770446777</v>
       </c>
       <c r="H430" t="n">
         <v>4618</v>
@@ -12868,7 +12868,7 @@
         <v>62</v>
       </c>
       <c r="G431" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H431" t="n">
         <v>6032</v>
@@ -12955,7 +12955,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478645324707</v>
+        <v>52.9478607177734</v>
       </c>
       <c r="H434" t="n">
         <v>15198</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.523868560791</v>
+        <v>53.5238647460938</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13042,7 +13042,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.2457237243652</v>
+        <v>57.245719909668</v>
       </c>
       <c r="H437" t="n">
         <v>25131</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823348999023</v>
+        <v>56.1823387145996</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13187,7 +13187,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>55.2075576782227</v>
+        <v>55.2075614929199</v>
       </c>
       <c r="H442" t="n">
         <v>3795</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254081726074</v>
+        <v>56.625415802002</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13448,7 +13448,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164848327637</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H451" t="n">
         <v>1739</v>
@@ -13506,7 +13506,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734077453613</v>
+        <v>55.4734115600586</v>
       </c>
       <c r="H453" t="n">
         <v>9803</v>
@@ -13564,7 +13564,7 @@
         <v>62</v>
       </c>
       <c r="G455" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H455" t="n">
         <v>4038</v>
@@ -13593,7 +13593,7 @@
         <v>62</v>
       </c>
       <c r="G456" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H456" t="n">
         <v>4488</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.81494140625</v>
+        <v>52.8149375915527</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13796,7 +13796,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515487670898</v>
+        <v>51.7515525817871</v>
       </c>
       <c r="H463" t="n">
         <v>3551</v>
@@ -13825,7 +13825,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540138244629</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H464" t="n">
         <v>5606</v>
@@ -13854,7 +13854,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743179321289</v>
+        <v>51.5743217468262</v>
       </c>
       <c r="H465" t="n">
         <v>7910</v>
@@ -13883,7 +13883,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540138244629</v>
+        <v>50.9540100097656</v>
       </c>
       <c r="H466" t="n">
         <v>7562</v>
@@ -13912,7 +13912,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450866699219</v>
+        <v>50.2450828552246</v>
       </c>
       <c r="H467" t="n">
         <v>8697</v>
@@ -13941,7 +13941,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792404174805</v>
+        <v>49.9792366027832</v>
       </c>
       <c r="H468" t="n">
         <v>4011</v>
@@ -13970,7 +13970,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678558349609</v>
+        <v>50.0678596496582</v>
       </c>
       <c r="H469" t="n">
         <v>4828</v>
@@ -13999,7 +13999,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703132629395</v>
+        <v>49.2703094482422</v>
       </c>
       <c r="H470" t="n">
         <v>4310</v>
@@ -14115,7 +14115,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H474" t="n">
         <v>11773</v>
@@ -14173,7 +14173,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H476" t="n">
         <v>21249</v>
@@ -14260,7 +14260,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H479" t="n">
         <v>117335</v>
@@ -14347,7 +14347,7 @@
         <v>53.5</v>
       </c>
       <c r="G482" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H482" t="n">
         <v>3928</v>
@@ -14376,7 +14376,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H483" t="n">
         <v>12430</v>
@@ -14463,7 +14463,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441528320312</v>
+        <v>51.9441566467285</v>
       </c>
       <c r="H486" t="n">
         <v>9392</v>
@@ -14492,7 +14492,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265113830566</v>
+        <v>50.3265151977539</v>
       </c>
       <c r="H487" t="n">
         <v>10895</v>
@@ -14521,7 +14521,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9556007385254</v>
+        <v>50.9555969238281</v>
       </c>
       <c r="H488" t="n">
         <v>9780</v>
@@ -14550,7 +14550,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G489" t="n">
-        <v>49.967041015625</v>
+        <v>49.9670372009277</v>
       </c>
       <c r="H489" t="n">
         <v>5862</v>
@@ -14637,7 +14637,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H492" t="n">
         <v>9874</v>
@@ -14753,7 +14753,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H496" t="n">
         <v>19509</v>
@@ -14811,7 +14811,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441528320312</v>
+        <v>51.9441566467285</v>
       </c>
       <c r="H498" t="n">
         <v>9814</v>
@@ -14840,7 +14840,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H499" t="n">
         <v>8348</v>
@@ -14927,7 +14927,7 @@
         <v>60</v>
       </c>
       <c r="G502" t="n">
-        <v>53.9212684631348</v>
+        <v>53.9212646484375</v>
       </c>
       <c r="H502" t="n">
         <v>7316</v>
@@ -14956,7 +14956,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H503" t="n">
         <v>7536</v>
@@ -14985,7 +14985,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653625488281</v>
+        <v>57.9653663635254</v>
       </c>
       <c r="H504" t="n">
         <v>19577</v>
@@ -15188,7 +15188,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H511" t="n">
         <v>8102</v>
@@ -15333,7 +15333,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8314018249512</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H516" t="n">
         <v>4297</v>
@@ -15391,7 +15391,7 @@
         <v>57.5</v>
       </c>
       <c r="G518" t="n">
-        <v>51.6745491027832</v>
+        <v>51.6745452880859</v>
       </c>
       <c r="H518" t="n">
         <v>5582</v>
@@ -15420,7 +15420,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H519" t="n">
         <v>2414</v>
@@ -15449,7 +15449,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265113830566</v>
+        <v>50.3265151977539</v>
       </c>
       <c r="H520" t="n">
         <v>4684</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644119262695</v>
+        <v>51.7644157409668</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15623,7 +15623,7 @@
         <v>53.5</v>
       </c>
       <c r="G526" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H526" t="n">
         <v>45916</v>
@@ -15652,7 +15652,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H527" t="n">
         <v>23788</v>
@@ -15681,7 +15681,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H528" t="n">
         <v>16070</v>
@@ -15768,7 +15768,7 @@
         <v>53.5</v>
       </c>
       <c r="G531" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H531" t="n">
         <v>7140</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15855,7 +15855,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H534" t="n">
         <v>7649</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603721618652</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16000,7 +16000,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>44.5749092102051</v>
+        <v>44.5749130249023</v>
       </c>
       <c r="H539" t="n">
         <v>33506</v>
@@ -16087,7 +16087,7 @@
         <v>49.75</v>
       </c>
       <c r="G542" t="n">
-        <v>44.709716796875</v>
+        <v>44.7097206115723</v>
       </c>
       <c r="H542" t="n">
         <v>18672</v>
@@ -16174,7 +16174,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H545" t="n">
         <v>22578</v>
@@ -16261,7 +16261,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H548" t="n">
         <v>5805</v>
@@ -16319,7 +16319,7 @@
         <v>53.5</v>
       </c>
       <c r="G550" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H550" t="n">
         <v>11825</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16435,7 +16435,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.4507179260254</v>
+        <v>47.4507102966309</v>
       </c>
       <c r="H554" t="n">
         <v>8684</v>
@@ -16464,7 +16464,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H555" t="n">
         <v>15322</v>
@@ -16551,7 +16551,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H558" t="n">
         <v>8255</v>
@@ -16667,7 +16667,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H562" t="n">
         <v>2385</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16725,7 +16725,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H564" t="n">
         <v>7354</v>
@@ -16812,7 +16812,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H567" t="n">
         <v>24457</v>
@@ -16928,7 +16928,7 @@
         <v>53.5</v>
       </c>
       <c r="G571" t="n">
-        <v>48.0797920227051</v>
+        <v>48.0797958374023</v>
       </c>
       <c r="H571" t="n">
         <v>6282</v>
@@ -16957,7 +16957,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H572" t="n">
         <v>12818</v>
@@ -16986,7 +16986,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>47.4507179260254</v>
+        <v>47.4507102966309</v>
       </c>
       <c r="H573" t="n">
         <v>13677</v>
@@ -17015,7 +17015,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H574" t="n">
         <v>4749</v>
@@ -17102,7 +17102,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H577" t="n">
         <v>3506</v>
@@ -17189,7 +17189,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H580" t="n">
         <v>33442</v>
@@ -17218,7 +17218,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H581" t="n">
         <v>21771</v>
@@ -17247,7 +17247,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H582" t="n">
         <v>5028</v>
@@ -17334,7 +17334,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>51.0454597473145</v>
+        <v>51.0454635620117</v>
       </c>
       <c r="H585" t="n">
         <v>23929</v>
@@ -17392,7 +17392,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H587" t="n">
         <v>6942</v>
@@ -17450,7 +17450,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H589" t="n">
         <v>11027</v>
@@ -17537,7 +17537,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.2366485595703</v>
+        <v>50.236644744873</v>
       </c>
       <c r="H592" t="n">
         <v>13961</v>
@@ -17566,7 +17566,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H593" t="n">
         <v>40288</v>
@@ -17653,7 +17653,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595291137695</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H596" t="n">
         <v>105612</v>
@@ -17740,7 +17740,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H599" t="n">
         <v>28739</v>
@@ -18001,7 +18001,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H608" t="n">
         <v>7231</v>
@@ -18088,7 +18088,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H611" t="n">
         <v>7555</v>
@@ -18146,7 +18146,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H613" t="n">
         <v>8437</v>
@@ -18204,7 +18204,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H615" t="n">
         <v>16713</v>
@@ -18233,7 +18233,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H616" t="n">
         <v>15159</v>
@@ -18291,7 +18291,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H618" t="n">
         <v>26603</v>
@@ -18320,7 +18320,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H619" t="n">
         <v>81517</v>
@@ -18378,7 +18378,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.9768028259277</v>
+        <v>56.9768104553223</v>
       </c>
       <c r="H621" t="n">
         <v>116812</v>
@@ -18436,7 +18436,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H623" t="n">
         <v>17457</v>
@@ -18523,7 +18523,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.4719200134277</v>
+        <v>53.4719161987305</v>
       </c>
       <c r="H626" t="n">
         <v>14829</v>
@@ -18726,7 +18726,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>53.2023124694824</v>
+        <v>53.2023162841797</v>
       </c>
       <c r="H633" t="n">
         <v>35889</v>
@@ -18755,7 +18755,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8314018249512</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H634" t="n">
         <v>16777</v>
@@ -18813,7 +18813,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H636" t="n">
         <v>5975</v>
@@ -18842,7 +18842,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H637" t="n">
         <v>10609</v>
@@ -18900,7 +18900,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H639" t="n">
         <v>13780</v>
@@ -18929,7 +18929,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996948242188</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H640" t="n">
         <v>3403</v>
@@ -18987,7 +18987,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G642" t="n">
-        <v>53.2023124694824</v>
+        <v>53.2023162841797</v>
       </c>
       <c r="H642" t="n">
         <v>9990</v>
@@ -19016,7 +19016,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>53.2023124694824</v>
+        <v>53.2023162841797</v>
       </c>
       <c r="H643" t="n">
         <v>9547</v>
@@ -19045,7 +19045,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H644" t="n">
         <v>11613</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19277,7 +19277,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>52.7529716491699</v>
+        <v>52.7529678344727</v>
       </c>
       <c r="H652" t="n">
         <v>28581</v>
@@ -19306,7 +19306,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124458312988</v>
+        <v>53.1124420166016</v>
       </c>
       <c r="H653" t="n">
         <v>33977</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19364,7 +19364,7 @@
         <v>60</v>
       </c>
       <c r="G655" t="n">
-        <v>53.9212684631348</v>
+        <v>53.9212646484375</v>
       </c>
       <c r="H655" t="n">
         <v>139231</v>
@@ -19422,7 +19422,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H657" t="n">
         <v>41152</v>
@@ -19451,7 +19451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H658" t="n">
         <v>26511</v>
@@ -19480,7 +19480,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578506469727</v>
+        <v>56.2578582763672</v>
       </c>
       <c r="H659" t="n">
         <v>14809</v>
@@ -19538,7 +19538,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441528320312</v>
+        <v>51.9441566467285</v>
       </c>
       <c r="H661" t="n">
         <v>53551</v>
@@ -19567,7 +19567,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.315071105957</v>
+        <v>51.3150672912598</v>
       </c>
       <c r="H662" t="n">
         <v>35448</v>
@@ -19625,7 +19625,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441528320312</v>
+        <v>51.9441566467285</v>
       </c>
       <c r="H664" t="n">
         <v>42179</v>
@@ -19654,7 +19654,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H665" t="n">
         <v>44030</v>
@@ -19712,7 +19712,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948043823242</v>
+        <v>51.4948120117188</v>
       </c>
       <c r="H667" t="n">
         <v>35732</v>
@@ -19770,7 +19770,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H669" t="n">
         <v>36876</v>
@@ -19799,7 +19799,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H670" t="n">
         <v>17071</v>
@@ -19828,7 +19828,7 @@
         <v>48</v>
       </c>
       <c r="G671" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H671" t="n">
         <v>34722</v>
@@ -19857,7 +19857,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916038513184</v>
+        <v>39.9916000366211</v>
       </c>
       <c r="H672" t="n">
         <v>35845</v>
@@ -19915,7 +19915,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.1166381835938</v>
+        <v>33.116641998291</v>
       </c>
       <c r="H674" t="n">
         <v>38571</v>
@@ -19944,7 +19944,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>33.3413200378418</v>
+        <v>33.3413162231445</v>
       </c>
       <c r="H675" t="n">
         <v>54537</v>
@@ -19973,7 +19973,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>28.263729095459</v>
+        <v>28.2637310028076</v>
       </c>
       <c r="H676" t="n">
         <v>31730</v>
@@ -20031,7 +20031,7 @@
         <v>28</v>
       </c>
       <c r="G678" t="n">
-        <v>25.1632556915283</v>
+        <v>25.163257598877</v>
       </c>
       <c r="H678" t="n">
         <v>22986</v>
@@ -20060,7 +20060,7 @@
         <v>26.75</v>
       </c>
       <c r="G679" t="n">
-        <v>24.0398960113525</v>
+        <v>24.0398979187012</v>
       </c>
       <c r="H679" t="n">
         <v>36114</v>
@@ -20089,7 +20089,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>22.7368011474609</v>
+        <v>22.7367992401123</v>
       </c>
       <c r="H680" t="n">
         <v>105256</v>
@@ -20147,7 +20147,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861438751221</v>
+        <v>23.1861419677734</v>
       </c>
       <c r="H682" t="n">
         <v>57668</v>
@@ -20176,7 +20176,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139129638672</v>
+        <v>24.7139148712158</v>
       </c>
       <c r="H683" t="n">
         <v>30853</v>
@@ -20263,7 +20263,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>24.9835205078125</v>
+        <v>24.9835186004639</v>
       </c>
       <c r="H686" t="n">
         <v>21534</v>
@@ -20350,7 +20350,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328632354736</v>
+        <v>25.4328651428223</v>
       </c>
       <c r="H689" t="n">
         <v>33327</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.4557514190674</v>
+        <v>23.4557495117188</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20466,7 +20466,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H693" t="n">
         <v>49337</v>
@@ -20553,7 +20553,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993721008301</v>
+        <v>24.3993740081787</v>
       </c>
       <c r="H696" t="n">
         <v>24674</v>
@@ -20611,7 +20611,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928146362305</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H698" t="n">
         <v>66739</v>
@@ -20698,7 +20698,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967487335205</v>
+        <v>26.1967449188232</v>
       </c>
       <c r="H701" t="n">
         <v>24223</v>
@@ -20814,7 +20814,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H705" t="n">
         <v>71298</v>
@@ -20843,7 +20843,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>31.7236747741699</v>
+        <v>31.7236785888672</v>
       </c>
       <c r="H706" t="n">
         <v>93719</v>
@@ -20872,7 +20872,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857780456543</v>
+        <v>30.2857799530029</v>
       </c>
       <c r="H707" t="n">
         <v>60261</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130718231201</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -20988,7 +20988,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.5562229156494</v>
+        <v>26.5562210083008</v>
       </c>
       <c r="H711" t="n">
         <v>10694</v>
@@ -21075,7 +21075,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>26.6011562347412</v>
+        <v>26.6011581420898</v>
       </c>
       <c r="H714" t="n">
         <v>22864</v>
@@ -21104,7 +21104,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359600067139</v>
+        <v>26.7359580993652</v>
       </c>
       <c r="H715" t="n">
         <v>47799</v>
@@ -21162,7 +21162,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663562774658</v>
+        <v>26.4663543701172</v>
       </c>
       <c r="H717" t="n">
         <v>21538</v>
@@ -21220,7 +21220,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H719" t="n">
         <v>31154</v>
@@ -21278,7 +21278,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5562229156494</v>
+        <v>26.5562210083008</v>
       </c>
       <c r="H721" t="n">
         <v>24481</v>
@@ -21307,7 +21307,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998474121094</v>
+        <v>27.4998455047607</v>
       </c>
       <c r="H722" t="n">
         <v>26961</v>
@@ -21365,7 +21365,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928146362305</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H724" t="n">
         <v>74966</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566982269287</v>
+        <v>29.6566944122314</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21452,7 +21452,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H727" t="n">
         <v>113929</v>
@@ -21539,7 +21539,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642044067383</v>
+        <v>31.3642063140869</v>
       </c>
       <c r="H730" t="n">
         <v>45462</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990062713623</v>
+        <v>31.4990081787109</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21626,7 +21626,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620468139648</v>
       </c>
       <c r="H733" t="n">
         <v>163828</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241500854492</v>
+        <v>34.824146270752</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717124938965</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21713,7 +21713,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161743164062</v>
+        <v>30.0161724090576</v>
       </c>
       <c r="H736" t="n">
         <v>76858</v>
@@ -21742,7 +21742,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060409545898</v>
+        <v>30.1060390472412</v>
       </c>
       <c r="H737" t="n">
         <v>76564</v>
@@ -21771,7 +21771,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699226379395</v>
+        <v>30.8699264526367</v>
       </c>
       <c r="H738" t="n">
         <v>88189</v>
@@ -21800,7 +21800,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.4426231384277</v>
+        <v>32.442626953125</v>
       </c>
       <c r="H739" t="n">
         <v>87104</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.5431022644043</v>
+        <v>35.543098449707</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -22032,7 +22032,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.6444091796875</v>
+        <v>34.6444129943848</v>
       </c>
       <c r="H747" t="n">
         <v>44338</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823135375977</v>
+        <v>36.0823173522949</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22206,7 +22206,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G753" t="n">
-        <v>38.778377532959</v>
+        <v>38.7783813476562</v>
       </c>
       <c r="H753" t="n">
         <v>21833</v>
@@ -22235,7 +22235,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>38.104362487793</v>
+        <v>38.1043663024902</v>
       </c>
       <c r="H754" t="n">
         <v>28695</v>
@@ -22264,7 +22264,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G755" t="n">
-        <v>38.2841033935547</v>
+        <v>38.2840957641602</v>
       </c>
       <c r="H755" t="n">
         <v>52989</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202178955078</v>
+        <v>37.5202140808105</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22409,7 +22409,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.283260345459</v>
+        <v>42.2832565307617</v>
       </c>
       <c r="H760" t="n">
         <v>39270</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22496,7 +22496,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224716186523</v>
+        <v>42.8224754333496</v>
       </c>
       <c r="H763" t="n">
         <v>25169</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22612,7 +22612,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.833911895752</v>
+        <v>41.8339157104492</v>
       </c>
       <c r="H767" t="n">
         <v>20446</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22699,7 +22699,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>41.9687232971191</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H770" t="n">
         <v>30213</v>
@@ -22728,7 +22728,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0251007080078</v>
+        <v>41.0250968933105</v>
       </c>
       <c r="H771" t="n">
         <v>23411</v>
@@ -22757,7 +22757,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>41.9687232971191</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H772" t="n">
         <v>37447</v>
@@ -22815,7 +22815,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.5079345703125</v>
+        <v>42.5079307556152</v>
       </c>
       <c r="H774" t="n">
         <v>35151</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -22931,7 +22931,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H778" t="n">
         <v>34460</v>
@@ -22960,7 +22960,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H779" t="n">
         <v>32289</v>
@@ -23018,7 +23018,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>42.7326049804688</v>
+        <v>42.7326011657715</v>
       </c>
       <c r="H781" t="n">
         <v>22565</v>
@@ -23076,7 +23076,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G783" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H783" t="n">
         <v>15651</v>
@@ -23105,7 +23105,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>41.9687232971191</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H784" t="n">
         <v>26455</v>
@@ -23134,7 +23134,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H785" t="n">
         <v>14310</v>
@@ -23308,7 +23308,7 @@
         <v>48</v>
       </c>
       <c r="G791" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H791" t="n">
         <v>5834</v>
@@ -23337,7 +23337,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H792" t="n">
         <v>8813</v>
@@ -23366,7 +23366,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>42.7326049804688</v>
+        <v>42.7326011657715</v>
       </c>
       <c r="H793" t="n">
         <v>16734</v>
@@ -23395,7 +23395,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H794" t="n">
         <v>19217</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5977973937988</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23598,7 +23598,7 @@
         <v>48</v>
       </c>
       <c r="G801" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H801" t="n">
         <v>20720</v>
@@ -23685,7 +23685,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H804" t="n">
         <v>10945</v>
@@ -23714,7 +23714,7 @@
         <v>48</v>
       </c>
       <c r="G805" t="n">
-        <v>43.1370124816895</v>
+        <v>43.1370086669922</v>
       </c>
       <c r="H805" t="n">
         <v>8676</v>
@@ -23801,7 +23801,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.047981262207</v>
+        <v>39.0479888916016</v>
       </c>
       <c r="H808" t="n">
         <v>25259</v>
@@ -23859,7 +23859,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246253967285</v>
+        <v>37.9246215820312</v>
       </c>
       <c r="H810" t="n">
         <v>12601</v>
@@ -23888,7 +23888,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H811" t="n">
         <v>22840</v>
@@ -23946,7 +23946,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100769042969</v>
+        <v>37.6100807189941</v>
       </c>
       <c r="H813" t="n">
         <v>22502</v>
@@ -24004,7 +24004,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G815" t="n">
-        <v>38.0594291687012</v>
+        <v>38.0594253540039</v>
       </c>
       <c r="H815" t="n">
         <v>25044</v>
@@ -24062,7 +24062,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651512145996</v>
+        <v>37.5651473999023</v>
       </c>
       <c r="H817" t="n">
         <v>18022</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986366271973</v>
+        <v>38.5986404418945</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24207,7 +24207,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118629455566</v>
+        <v>39.8118705749512</v>
       </c>
       <c r="H822" t="n">
         <v>9284</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030517578125</v>
+        <v>39.0030479431152</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24352,7 +24352,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G827" t="n">
-        <v>38.778377532959</v>
+        <v>38.7783813476562</v>
       </c>
       <c r="H827" t="n">
         <v>9351</v>
@@ -24468,7 +24468,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144920349121</v>
+        <v>38.0144958496094</v>
       </c>
       <c r="H831" t="n">
         <v>12021</v>
@@ -24526,7 +24526,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G833" t="n">
-        <v>37.4303436279297</v>
+        <v>37.430347442627</v>
       </c>
       <c r="H833" t="n">
         <v>8832</v>
@@ -24642,7 +24642,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329689025879</v>
+        <v>35.6329727172852</v>
       </c>
       <c r="H837" t="n">
         <v>24505</v>
@@ -24671,7 +24671,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620468139648</v>
       </c>
       <c r="H838" t="n">
         <v>20097</v>
@@ -24700,7 +24700,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>37.8796882629395</v>
+        <v>37.8796920776367</v>
       </c>
       <c r="H839" t="n">
         <v>16617</v>
@@ -24729,7 +24729,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.1827850341797</v>
+        <v>39.182788848877</v>
       </c>
       <c r="H840" t="n">
         <v>10534</v>
@@ -24874,7 +24874,7 @@
         <v>44.75</v>
       </c>
       <c r="G845" t="n">
-        <v>40.2162780761719</v>
+        <v>40.2162742614746</v>
       </c>
       <c r="H845" t="n">
         <v>22532</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24961,7 +24961,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>41.8788452148438</v>
+        <v>41.878849029541</v>
       </c>
       <c r="H848" t="n">
         <v>26342</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453598022461</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.901741027832</v>
+        <v>39.9017372131348</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25135,7 +25135,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744415283203</v>
+        <v>41.4744453430176</v>
       </c>
       <c r="H854" t="n">
         <v>24859</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25396,7 +25396,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G863" t="n">
-        <v>40.3510818481445</v>
+        <v>40.3510780334473</v>
       </c>
       <c r="H863" t="n">
         <v>11672</v>
@@ -25454,7 +25454,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528602600098</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H865" t="n">
         <v>24079</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25628,7 +25628,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471420288086</v>
+        <v>43.0471458435059</v>
       </c>
       <c r="H871" t="n">
         <v>16203</v>
@@ -25657,7 +25657,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H872" t="n">
         <v>17923</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25802,7 +25802,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>43.1819458007812</v>
+        <v>43.1819496154785</v>
       </c>
       <c r="H877" t="n">
         <v>8885</v>
@@ -25860,7 +25860,7 @@
         <v>47.25</v>
       </c>
       <c r="G879" t="n">
-        <v>42.4629974365234</v>
+        <v>42.4629936218262</v>
       </c>
       <c r="H879" t="n">
         <v>14904</v>
@@ -25918,7 +25918,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528602600098</v>
+        <v>42.5528678894043</v>
       </c>
       <c r="H881" t="n">
         <v>11939</v>
@@ -25947,7 +25947,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>41.9687232971191</v>
+        <v>41.9687194824219</v>
       </c>
       <c r="H882" t="n">
         <v>4266</v>
@@ -26034,7 +26034,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>42.3281898498535</v>
+        <v>42.3281936645508</v>
       </c>
       <c r="H885" t="n">
         <v>8308</v>
@@ -26063,7 +26063,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H886" t="n">
         <v>16328</v>
@@ -26121,7 +26121,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H888" t="n">
         <v>23048</v>
@@ -26179,7 +26179,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H890" t="n">
         <v>20904</v>
@@ -26208,7 +26208,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H891" t="n">
         <v>22960</v>
@@ -26266,7 +26266,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G893" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H893" t="n">
         <v>9090</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26411,7 +26411,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H898" t="n">
         <v>15858</v>
@@ -26469,7 +26469,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G900" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H900" t="n">
         <v>1802</v>
@@ -26614,7 +26614,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H905" t="n">
         <v>8945</v>
@@ -26672,7 +26672,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H907" t="n">
         <v>2482</v>
@@ -26701,7 +26701,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582183837891</v>
+        <v>49.1582221984863</v>
       </c>
       <c r="H908" t="n">
         <v>10471</v>
@@ -26730,7 +26730,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G909" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H909" t="n">
         <v>24643</v>
@@ -26759,7 +26759,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696662902832</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H910" t="n">
         <v>7813</v>
@@ -27020,7 +27020,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H919" t="n">
         <v>12524</v>
@@ -27136,7 +27136,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603721618652</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H923" t="n">
         <v>10806</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.9115028381348</v>
+        <v>46.9114990234375</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27281,7 +27281,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H928" t="n">
         <v>14790</v>
@@ -27310,7 +27310,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H929" t="n">
         <v>14814</v>
@@ -27339,7 +27339,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H930" t="n">
         <v>11631</v>
@@ -27397,7 +27397,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H932" t="n">
         <v>10386</v>
@@ -27426,7 +27426,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H933" t="n">
         <v>15510</v>
@@ -27455,7 +27455,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608436584473</v>
+        <v>47.3608474731445</v>
       </c>
       <c r="H934" t="n">
         <v>3732</v>
@@ -27484,7 +27484,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>47.9000587463379</v>
+        <v>47.9000549316406</v>
       </c>
       <c r="H935" t="n">
         <v>7592</v>
@@ -27513,7 +27513,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608436584473</v>
+        <v>47.3608474731445</v>
       </c>
       <c r="H936" t="n">
         <v>6052</v>
@@ -27542,7 +27542,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>47.4507179260254</v>
+        <v>47.4507102966309</v>
       </c>
       <c r="H937" t="n">
         <v>6177</v>
@@ -27600,7 +27600,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G939" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H939" t="n">
         <v>2144</v>
@@ -27658,7 +27658,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H941" t="n">
         <v>17192</v>
@@ -27803,7 +27803,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>47.4507179260254</v>
+        <v>47.4507102966309</v>
       </c>
       <c r="H946" t="n">
         <v>4946</v>
@@ -27919,7 +27919,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H950" t="n">
         <v>5714</v>
@@ -27948,7 +27948,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H951" t="n">
         <v>7608</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28122,7 +28122,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H957" t="n">
         <v>11719</v>
@@ -28151,7 +28151,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H958" t="n">
         <v>6560</v>
@@ -28238,7 +28238,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H961" t="n">
         <v>12589</v>
@@ -28296,7 +28296,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H963" t="n">
         <v>15923</v>
@@ -28325,7 +28325,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595291137695</v>
+        <v>48.2595329284668</v>
       </c>
       <c r="H964" t="n">
         <v>14743</v>
@@ -28354,7 +28354,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>47.9899253845215</v>
+        <v>47.9899291992188</v>
       </c>
       <c r="H965" t="n">
         <v>6406</v>
@@ -28383,7 +28383,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H966" t="n">
         <v>2872</v>
@@ -28412,7 +28412,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H967" t="n">
         <v>3349</v>
@@ -28441,7 +28441,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H968" t="n">
         <v>12385</v>
@@ -28470,7 +28470,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G969" t="n">
-        <v>47.4507179260254</v>
+        <v>47.4507102966309</v>
       </c>
       <c r="H969" t="n">
         <v>11609</v>
@@ -28586,7 +28586,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H973" t="n">
         <v>226954</v>
@@ -28644,7 +28644,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H975" t="n">
         <v>19832</v>
@@ -28673,7 +28673,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>44.6647796630859</v>
+        <v>44.6647834777832</v>
       </c>
       <c r="H976" t="n">
         <v>23268</v>
@@ -28702,7 +28702,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H977" t="n">
         <v>17528</v>
@@ -28731,7 +28731,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H978" t="n">
         <v>18485</v>
@@ -28818,7 +28818,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229469299316</v>
       </c>
       <c r="H981" t="n">
         <v>20247</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.192554473877</v>
+        <v>46.1925506591797</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28876,7 +28876,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>45.5634689331055</v>
+        <v>45.5634727478027</v>
       </c>
       <c r="H983" t="n">
         <v>13464</v>
@@ -28934,7 +28934,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G985" t="n">
-        <v>45.4736022949219</v>
+        <v>45.4735984802246</v>
       </c>
       <c r="H985" t="n">
         <v>14166</v>
@@ -29050,7 +29050,7 @@
         <v>49.75</v>
       </c>
       <c r="G989" t="n">
-        <v>44.709716796875</v>
+        <v>44.7097206115723</v>
       </c>
       <c r="H989" t="n">
         <v>13481</v>
@@ -29079,7 +29079,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>45.0242538452148</v>
+        <v>45.0242576599121</v>
       </c>
       <c r="H990" t="n">
         <v>18331</v>
@@ -29282,7 +29282,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>42.9519157409668</v>
+        <v>42.9519195556641</v>
       </c>
       <c r="H997" t="n">
         <v>575572</v>
@@ -29427,7 +29427,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087409973145</v>
+        <v>41.9087371826172</v>
       </c>
       <c r="H1002" t="n">
         <v>14318</v>
@@ -29514,7 +29514,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551811218262</v>
+        <v>41.4551773071289</v>
       </c>
       <c r="H1005" t="n">
         <v>24773</v>
@@ -29543,7 +29543,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1006" t="n">
         <v>12674</v>
@@ -29572,7 +29572,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098281860352</v>
+        <v>41.4098243713379</v>
       </c>
       <c r="H1007" t="n">
         <v>7762</v>
@@ -29601,7 +29601,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1008" t="n">
-        <v>40.5027122497559</v>
+        <v>40.5027084350586</v>
       </c>
       <c r="H1008" t="n">
         <v>10378</v>
@@ -29862,7 +29862,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.0513229370117</v>
+        <v>39.051326751709</v>
       </c>
       <c r="H1017" t="n">
         <v>78089</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.6366081237793</v>
+        <v>41.636604309082</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797866821289</v>
+        <v>42.6797828674316</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30007,7 +30007,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1022" t="n">
-        <v>42.9972763061523</v>
+        <v>42.9972801208496</v>
       </c>
       <c r="H1022" t="n">
         <v>30204</v>
@@ -30036,7 +30036,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1023" t="n">
-        <v>41.8180274963379</v>
+        <v>41.8180236816406</v>
       </c>
       <c r="H1023" t="n">
         <v>19161</v>
@@ -30152,7 +30152,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>43.8590393066406</v>
+        <v>43.8590354919434</v>
       </c>
       <c r="H1027" t="n">
         <v>19195</v>
@@ -30268,7 +30268,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1031" t="n">
-        <v>43.6322593688965</v>
+        <v>43.6322555541992</v>
       </c>
       <c r="H1031" t="n">
         <v>16965</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218856811523</v>
+        <v>44.2218818664551</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951057434082</v>
+        <v>43.9951019287109</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30529,7 +30529,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1040" t="n">
-        <v>45.7186279296875</v>
+        <v>45.7186241149902</v>
       </c>
       <c r="H1040" t="n">
         <v>21118</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328559875488</v>
+        <v>47.5328521728516</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443206787109</v>
+        <v>46.4443130493164</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -30993,7 +30993,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>45.0382881164551</v>
+        <v>45.0382919311523</v>
       </c>
       <c r="H1056" t="n">
         <v>10716</v>
@@ -31022,7 +31022,7 @@
         <v>50</v>
       </c>
       <c r="G1057" t="n">
-        <v>45.3557739257812</v>
+        <v>45.3557777404785</v>
       </c>
       <c r="H1057" t="n">
         <v>4460</v>
@@ -31051,7 +31051,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164535522461</v>
+        <v>46.7164497375488</v>
       </c>
       <c r="H1058" t="n">
         <v>15938</v>
@@ -31080,7 +31080,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071632385254</v>
+        <v>46.8071594238281</v>
       </c>
       <c r="H1059" t="n">
         <v>10169</v>
@@ -31138,7 +31138,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>46.3536033630371</v>
+        <v>46.3536071777344</v>
       </c>
       <c r="H1061" t="n">
         <v>13933</v>
@@ -31341,7 +31341,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1068" t="n">
-        <v>44.6300811767578</v>
+        <v>44.6300849914551</v>
       </c>
       <c r="H1068" t="n">
         <v>5362</v>
@@ -31370,7 +31370,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>45.0382881164551</v>
+        <v>45.0382919311523</v>
       </c>
       <c r="H1069" t="n">
         <v>4742</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093338012695</v>
+        <v>45.8093376159668</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31573,7 +31573,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>45.0836410522461</v>
+        <v>45.0836448669434</v>
       </c>
       <c r="H1076" t="n">
         <v>6221</v>
@@ -31660,7 +31660,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>44.6300811767578</v>
+        <v>44.6300849914551</v>
       </c>
       <c r="H1079" t="n">
         <v>29940</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563705444336</v>
+        <v>49.2563743591309</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595260620117</v>
+        <v>39.459529876709</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31950,7 +31950,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>38.1895599365234</v>
+        <v>38.1895637512207</v>
       </c>
       <c r="H1089" t="n">
         <v>84053</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32240,7 +32240,7 @@
         <v>41.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>37.6452980041504</v>
+        <v>37.6452941894531</v>
       </c>
       <c r="H1099" t="n">
         <v>38990</v>
@@ -32356,7 +32356,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010284423828</v>
+        <v>37.1010246276855</v>
       </c>
       <c r="H1103" t="n">
         <v>27248</v>
@@ -32443,7 +32443,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1106" t="n">
         <v>33320</v>
@@ -32472,7 +32472,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>36.148551940918</v>
+        <v>36.1485557556152</v>
       </c>
       <c r="H1107" t="n">
         <v>22362</v>
@@ -32559,7 +32559,7 @@
         <v>40</v>
       </c>
       <c r="G1110" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1110" t="n">
         <v>12495</v>
@@ -32588,7 +32588,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.2868003845215</v>
+        <v>35.2867965698242</v>
       </c>
       <c r="H1111" t="n">
         <v>26873</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32733,7 +32733,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>34.7878799438477</v>
+        <v>34.7878761291504</v>
       </c>
       <c r="H1116" t="n">
         <v>14282</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -32907,7 +32907,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>33.8807640075684</v>
+        <v>33.8807678222656</v>
       </c>
       <c r="H1122" t="n">
         <v>16853</v>
@@ -32965,7 +32965,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1124" t="n">
         <v>16911</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463851928711</v>
+        <v>37.1463813781738</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33168,7 +33168,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884765625</v>
+        <v>38.6884841918945</v>
       </c>
       <c r="H1131" t="n">
         <v>27152</v>
@@ -33197,7 +33197,7 @@
         <v>42.25</v>
       </c>
       <c r="G1132" t="n">
-        <v>38.3256301879883</v>
+        <v>38.3256340026855</v>
       </c>
       <c r="H1132" t="n">
         <v>14021</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33371,7 +33371,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>37.4638748168945</v>
+        <v>37.4638710021973</v>
       </c>
       <c r="H1138" t="n">
         <v>15196</v>
@@ -33487,7 +33487,7 @@
         <v>40.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>36.7381820678711</v>
+        <v>36.7381782531738</v>
       </c>
       <c r="H1142" t="n">
         <v>14421</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764190673828</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33777,7 +33777,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G1152" t="n">
-        <v>35.0146598815918</v>
+        <v>35.0146560668945</v>
       </c>
       <c r="H1152" t="n">
         <v>109200</v>
@@ -33980,7 +33980,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1159" t="n">
         <v>19943</v>
@@ -34009,7 +34009,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>34.5611038208008</v>
+        <v>34.5611000061035</v>
       </c>
       <c r="H1160" t="n">
         <v>37289</v>
@@ -34067,7 +34067,7 @@
         <v>40.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>36.7381820678711</v>
+        <v>36.7381782531738</v>
       </c>
       <c r="H1162" t="n">
         <v>32830</v>
@@ -34386,7 +34386,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1173" t="n">
         <v>72195</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605052947998</v>
+        <v>30.6605033874512</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34502,7 +34502,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>31.3861980438232</v>
+        <v>31.3861961364746</v>
       </c>
       <c r="H1177" t="n">
         <v>52489</v>
@@ -34589,7 +34589,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>26.6691970825195</v>
+        <v>26.6691951751709</v>
       </c>
       <c r="H1180" t="n">
         <v>77366</v>
@@ -34618,7 +34618,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.7577381134033</v>
+        <v>27.7577362060547</v>
       </c>
       <c r="H1181" t="n">
         <v>42139</v>
@@ -34734,7 +34734,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233554840088</v>
+        <v>31.0233516693115</v>
       </c>
       <c r="H1185" t="n">
         <v>64152</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419303894043</v>
+        <v>30.8419284820557</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34821,7 +34821,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>33.2457847595215</v>
+        <v>33.2457885742188</v>
       </c>
       <c r="H1188" t="n">
         <v>15564</v>
@@ -34850,7 +34850,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.4272041320801</v>
+        <v>33.4272079467773</v>
       </c>
       <c r="H1189" t="n">
         <v>34565</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600204467773</v>
+        <v>35.0600166320801</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34937,7 +34937,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1192" t="n">
         <v>13009</v>
@@ -34966,7 +34966,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>33.8807640075684</v>
+        <v>33.8807678222656</v>
       </c>
       <c r="H1193" t="n">
         <v>15184</v>
@@ -34995,7 +34995,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425270080566</v>
+        <v>34.7425231933594</v>
       </c>
       <c r="H1194" t="n">
         <v>141817</v>
@@ -35024,7 +35024,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053733825684</v>
+        <v>35.1053695678711</v>
       </c>
       <c r="H1195" t="n">
         <v>36612</v>
@@ -35111,7 +35111,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>34.8332405090332</v>
+        <v>34.8332366943359</v>
       </c>
       <c r="H1198" t="n">
         <v>31111</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545883178711</v>
+        <v>37.5545845031738</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35633,7 +35633,7 @@
         <v>40</v>
       </c>
       <c r="G1216" t="n">
-        <v>36.2846183776855</v>
+        <v>36.2846221923828</v>
       </c>
       <c r="H1216" t="n">
         <v>38623</v>
@@ -35691,7 +35691,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1218" t="n">
         <v>55769</v>
@@ -35720,7 +35720,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475509643555</v>
+        <v>34.2475547790527</v>
       </c>
       <c r="H1219" t="n">
         <v>11676</v>
@@ -35923,7 +35923,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377777099609</v>
+        <v>33.7377815246582</v>
       </c>
       <c r="H1226" t="n">
         <v>7077</v>
@@ -35981,7 +35981,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280006408691</v>
+        <v>33.2280044555664</v>
       </c>
       <c r="H1228" t="n">
         <v>17594</v>
@@ -36271,7 +36271,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1238" t="n">
         <v>26308</v>
@@ -36329,7 +36329,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719528198242</v>
+        <v>34.5719566345215</v>
       </c>
       <c r="H1240" t="n">
         <v>30852</v>
@@ -36503,7 +36503,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792007446289</v>
+        <v>32.5792045593262</v>
       </c>
       <c r="H1246" t="n">
         <v>16319</v>
@@ -36532,7 +36532,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1247" t="n">
         <v>23766</v>
@@ -36590,7 +36590,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546642303467</v>
+        <v>28.4546661376953</v>
       </c>
       <c r="H1249" t="n">
         <v>16778</v>
@@ -36677,7 +36677,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1252" t="n">
         <v>55493</v>
@@ -36706,7 +36706,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692909240723</v>
+        <v>28.2692928314209</v>
       </c>
       <c r="H1253" t="n">
         <v>9517</v>
@@ -36735,7 +36735,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1254" t="n">
         <v>12548</v>
@@ -36880,7 +36880,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1259" t="n">
         <v>38924</v>
@@ -36938,7 +36938,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911674499512</v>
+        <v>26.0911655426025</v>
       </c>
       <c r="H1261" t="n">
         <v>31910</v>
@@ -37083,7 +37083,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131065368652</v>
+        <v>25.8131084442139</v>
       </c>
       <c r="H1266" t="n">
         <v>7598</v>
@@ -37112,7 +37112,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1267" t="n">
         <v>12771</v>
@@ -37170,7 +37170,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1269" t="n">
         <v>18414</v>
@@ -37344,7 +37344,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1275" t="n">
         <v>15913</v>
@@ -37431,7 +37431,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.73996925354</v>
+        <v>26.7399711608887</v>
       </c>
       <c r="H1278" t="n">
         <v>11119</v>
@@ -37489,7 +37489,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1280" t="n">
         <v>11239</v>
@@ -37547,7 +37547,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1282" t="n">
         <v>29030</v>
@@ -37576,7 +37576,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887729644775</v>
+        <v>27.3887710571289</v>
       </c>
       <c r="H1283" t="n">
         <v>13951</v>
@@ -37808,7 +37808,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473518371582</v>
+        <v>28.5473499298096</v>
       </c>
       <c r="H1291" t="n">
         <v>49073</v>
@@ -37837,7 +37837,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1292" t="n">
         <v>22316</v>
@@ -38040,7 +38040,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107158660889</v>
+        <v>27.1107139587402</v>
       </c>
       <c r="H1299" t="n">
         <v>2701</v>
@@ -38156,7 +38156,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545959472656</v>
+        <v>26.5545978546143</v>
       </c>
       <c r="H1303" t="n">
         <v>11541</v>
@@ -38301,7 +38301,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1308" t="n">
         <v>7747</v>
@@ -38359,7 +38359,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1310" t="n">
         <v>8183</v>
@@ -38533,7 +38533,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1316" t="n">
         <v>8506</v>
@@ -38562,7 +38562,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1317" t="n">
         <v>6463</v>
@@ -38765,7 +38765,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545314788818</v>
+        <v>24.6545295715332</v>
       </c>
       <c r="H1324" t="n">
         <v>11339</v>
@@ -38794,7 +38794,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984134674072</v>
+        <v>24.0984115600586</v>
       </c>
       <c r="H1325" t="n">
         <v>17104</v>
@@ -38852,7 +38852,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033313751221</v>
+        <v>25.3033332824707</v>
       </c>
       <c r="H1327" t="n">
         <v>29720</v>
@@ -38910,7 +38910,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.7204208374023</v>
+        <v>25.720422744751</v>
       </c>
       <c r="H1329" t="n">
         <v>7898</v>
@@ -39229,7 +39229,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350475311279</v>
+        <v>25.5350494384766</v>
       </c>
       <c r="H1340" t="n">
         <v>7940</v>
@@ -39316,7 +39316,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155673980713</v>
+        <v>26.4155693054199</v>
       </c>
       <c r="H1343" t="n">
         <v>17193</v>
@@ -39345,7 +39345,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.878999710083</v>
+        <v>26.8789978027344</v>
       </c>
       <c r="H1344" t="n">
         <v>16994</v>
@@ -39374,7 +39374,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301940917969</v>
+        <v>26.2301959991455</v>
       </c>
       <c r="H1345" t="n">
         <v>26909</v>
@@ -39432,7 +39432,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1347" t="n">
         <v>13917</v>
@@ -39461,7 +39461,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180282592773</v>
+        <v>27.0180263519287</v>
       </c>
       <c r="H1348" t="n">
         <v>8737</v>
@@ -39548,7 +39548,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1351" t="n">
         <v>20501</v>
@@ -39577,7 +39577,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.574146270752</v>
+        <v>27.5741443634033</v>
       </c>
       <c r="H1352" t="n">
         <v>16729</v>
@@ -39693,7 +39693,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1356" t="n">
         <v>75277</v>
@@ -39722,7 +39722,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1357" t="n">
         <v>36177</v>
@@ -39751,7 +39751,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1358" t="n">
         <v>16319</v>
@@ -39809,7 +39809,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352504730225</v>
+        <v>31.2352523803711</v>
       </c>
       <c r="H1360" t="n">
         <v>14299</v>
@@ -39867,7 +39867,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.1889095306396</v>
+        <v>31.188907623291</v>
       </c>
       <c r="H1362" t="n">
         <v>13411</v>
@@ -39896,7 +39896,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1363" t="n">
         <v>7826</v>
@@ -39954,7 +39954,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377075195312</v>
+        <v>31.8377113342285</v>
       </c>
       <c r="H1365" t="n">
         <v>22255</v>
@@ -39983,7 +39983,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962200164795</v>
+        <v>31.0962219238281</v>
       </c>
       <c r="H1366" t="n">
         <v>49622</v>
@@ -40041,7 +40041,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571933746338</v>
+        <v>30.9571914672852</v>
       </c>
       <c r="H1368" t="n">
         <v>11052</v>
@@ -40070,7 +40070,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1369" t="n">
         <v>31735</v>
@@ -40099,7 +40099,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.93039894104</v>
+        <v>31.9303970336914</v>
       </c>
       <c r="H1370" t="n">
         <v>19225</v>
@@ -40244,7 +40244,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596523284912</v>
+        <v>31.5596504211426</v>
       </c>
       <c r="H1375" t="n">
         <v>14100</v>
@@ -40273,7 +40273,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.88405418396</v>
+        <v>31.8840560913086</v>
       </c>
       <c r="H1376" t="n">
         <v>10686</v>
@@ -40302,7 +40302,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.0498790740967</v>
+        <v>31.049877166748</v>
       </c>
       <c r="H1377" t="n">
         <v>13797</v>
@@ -40331,7 +40331,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986827850342</v>
+        <v>31.6986808776855</v>
       </c>
       <c r="H1378" t="n">
         <v>16079</v>
@@ -40476,7 +40476,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182273864746</v>
+        <v>32.7182312011719</v>
       </c>
       <c r="H1383" t="n">
         <v>16458</v>
@@ -40708,7 +40708,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914329528809</v>
+        <v>33.6914367675781</v>
       </c>
       <c r="H1391" t="n">
         <v>5315</v>
@@ -40766,7 +40766,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1393" t="n">
         <v>20537</v>
@@ -40911,7 +40911,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.359790802002</v>
+        <v>35.3597869873047</v>
       </c>
       <c r="H1398" t="n">
         <v>20503</v>
@@ -40969,7 +40969,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1400" t="n">
         <v>25006</v>
@@ -40998,7 +40998,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1401" t="n">
         <v>9472</v>
@@ -41056,7 +41056,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988174438477</v>
+        <v>35.4988136291504</v>
       </c>
       <c r="H1403" t="n">
         <v>23148</v>
@@ -41085,7 +41085,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744155883789</v>
+        <v>35.1744117736816</v>
       </c>
       <c r="H1404" t="n">
         <v>45623</v>
@@ -41114,7 +41114,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1405" t="n">
         <v>28718</v>
@@ -41201,7 +41201,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890441894531</v>
+        <v>34.9890403747559</v>
       </c>
       <c r="H1408" t="n">
         <v>18517</v>
@@ -41259,7 +41259,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012100219727</v>
+        <v>34.2012138366699</v>
       </c>
       <c r="H1410" t="n">
         <v>15419</v>
@@ -41317,7 +41317,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.618293762207</v>
+        <v>34.6182975769043</v>
       </c>
       <c r="H1412" t="n">
         <v>38690</v>
@@ -41346,7 +41346,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353851318359</v>
+        <v>35.0353813171387</v>
       </c>
       <c r="H1413" t="n">
         <v>44206</v>
@@ -41404,7 +41404,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H1415" t="n">
         <v>21797</v>
@@ -41433,7 +41433,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.518367767334</v>
+        <v>36.5183639526367</v>
       </c>
       <c r="H1416" t="n">
         <v>19385</v>
@@ -41520,7 +41520,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085906982422</v>
+        <v>36.0085868835449</v>
       </c>
       <c r="H1419" t="n">
         <v>19338</v>
@@ -41607,7 +41607,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1422" t="n">
         <v>28131</v>
@@ -41665,7 +41665,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451583862305</v>
+        <v>35.5451545715332</v>
       </c>
       <c r="H1424" t="n">
         <v>37415</v>
@@ -41926,7 +41926,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059268951416</v>
+        <v>29.7059288024902</v>
       </c>
       <c r="H1433" t="n">
         <v>169855</v>
@@ -41955,7 +41955,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1434" t="n">
         <v>83833</v>
@@ -41984,7 +41984,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230163574219</v>
+        <v>30.1230144500732</v>
       </c>
       <c r="H1435" t="n">
         <v>50233</v>
@@ -42100,7 +42100,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1439" t="n">
         <v>39783</v>
@@ -42129,7 +42129,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1440" t="n">
         <v>36958</v>
@@ -42187,7 +42187,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1442" t="n">
         <v>39311</v>
@@ -42332,7 +42332,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302642822266</v>
+        <v>28.1302623748779</v>
       </c>
       <c r="H1447" t="n">
         <v>48734</v>
@@ -42361,7 +42361,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204891204834</v>
+        <v>27.6204872131348</v>
       </c>
       <c r="H1448" t="n">
         <v>29333</v>
@@ -42419,7 +42419,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863121032715</v>
+        <v>26.7863140106201</v>
       </c>
       <c r="H1450" t="n">
         <v>74959</v>
@@ -42448,7 +42448,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2034015655518</v>
+        <v>27.2033996582031</v>
       </c>
       <c r="H1451" t="n">
         <v>28955</v>
@@ -42506,7 +42506,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156356811523</v>
+        <v>28.3156337738037</v>
       </c>
       <c r="H1453" t="n">
         <v>45425</v>
@@ -42564,7 +42564,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1455" t="n">
         <v>26258</v>
@@ -42622,7 +42622,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571269989014</v>
+        <v>29.0571250915527</v>
       </c>
       <c r="H1457" t="n">
         <v>41539</v>
@@ -42767,7 +42767,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1462" t="n">
         <v>27647</v>
@@ -42796,7 +42796,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1463" t="n">
         <v>32514</v>
@@ -42825,7 +42825,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815269470215</v>
+        <v>29.3815288543701</v>
       </c>
       <c r="H1464" t="n">
         <v>59385</v>
@@ -42912,7 +42912,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1467" t="n">
         <v>22423</v>
@@ -42970,7 +42970,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.28883934021</v>
+        <v>29.2888412475586</v>
       </c>
       <c r="H1469" t="n">
         <v>33838</v>
@@ -42999,7 +42999,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644374847412</v>
+        <v>28.9644393920898</v>
       </c>
       <c r="H1470" t="n">
         <v>20524</v>
@@ -43028,7 +43028,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1471" t="n">
         <v>38899</v>
@@ -43057,7 +43057,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961536407471</v>
+        <v>29.1961555480957</v>
       </c>
       <c r="H1472" t="n">
         <v>26587</v>
@@ -43086,7 +43086,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742107391357</v>
+        <v>29.4742126464844</v>
       </c>
       <c r="H1473" t="n">
         <v>61483</v>
@@ -43202,7 +43202,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205554962158</v>
+        <v>29.5205574035645</v>
       </c>
       <c r="H1477" t="n">
         <v>81786</v>
@@ -68699,6 +68699,35 @@
         <v>1171070</v>
       </c>
       <c r="I2356" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2357" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>1.69099998474121</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>1.72899997234344</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>1.6360000371933</v>
+      </c>
+      <c r="G2357" t="n">
+        <v>1.6360000371933</v>
+      </c>
+      <c r="H2357" t="n">
+        <v>1495505</v>
+      </c>
+      <c r="I2357" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569198608398</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318534851074</v>
+        <v>46.7318496704102</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -717,7 +717,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H12" t="n">
         <v>19418</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -949,7 +949,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.081901550293</v>
+        <v>47.0818977355957</v>
       </c>
       <c r="H20" t="n">
         <v>12065</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.950626373291</v>
+        <v>46.9506340026855</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1007,7 +1007,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.469310760498</v>
+        <v>46.4693069458008</v>
       </c>
       <c r="H22" t="n">
         <v>15015</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131652832031</v>
+        <v>47.2131690979004</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756118774414</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443290710449</v>
+        <v>46.6443367004395</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1181,7 +1181,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.1192588806152</v>
+        <v>46.119255065918</v>
       </c>
       <c r="H28" t="n">
         <v>23503</v>
@@ -1210,7 +1210,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254486083984</v>
+        <v>45.7254524230957</v>
       </c>
       <c r="H29" t="n">
         <v>15825</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069755554199</v>
+        <v>47.6069793701172</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1442,7 +1442,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.906867980957</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H37" t="n">
         <v>10252</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881912231445</v>
+        <v>47.3881950378418</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756118774414</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569274902344</v>
+        <v>47.2569198608398</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320571899414</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882987976074</v>
+        <v>48.0882949829102</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1674,7 +1674,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H45" t="n">
         <v>55518</v>
@@ -1703,7 +1703,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.906867980957</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H46" t="n">
         <v>84037</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194664001465</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1993,7 +1993,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445404052734</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="n">
         <v>39379</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135841369629</v>
+        <v>50.0135765075684</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2080,7 +2080,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577461242676</v>
+        <v>52.8577499389648</v>
       </c>
       <c r="H59" t="n">
         <v>33673</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266860961914</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579498291016</v>
+        <v>54.2579460144043</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2225,7 +2225,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H64" t="n">
         <v>18989</v>
@@ -2254,7 +2254,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H65" t="n">
         <v>17831</v>
@@ -2283,7 +2283,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769416809082</v>
+        <v>55.8769378662109</v>
       </c>
       <c r="H66" t="n">
         <v>30641</v>
@@ -2312,7 +2312,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336944580078</v>
+        <v>59.3336982727051</v>
       </c>
       <c r="H67" t="n">
         <v>66049</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589683532715</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2370,7 +2370,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4404067993164</v>
+        <v>62.4403991699219</v>
       </c>
       <c r="H69" t="n">
         <v>51076</v>
@@ -2486,7 +2486,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902435302734</v>
+        <v>61.3902473449707</v>
       </c>
       <c r="H73" t="n">
         <v>19520</v>
@@ -2602,7 +2602,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399917602539</v>
+        <v>59.6399955749512</v>
       </c>
       <c r="H77" t="n">
         <v>24608</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7274971008301</v>
+        <v>59.7275009155273</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838500976562</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276008605957</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.821418762207</v>
+        <v>60.8214073181152</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898399353027</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2834,7 +2834,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771415710449</v>
       </c>
       <c r="H85" t="n">
         <v>30458</v>
@@ -2863,7 +2863,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H86" t="n">
         <v>30413</v>
@@ -2921,7 +2921,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958297729492</v>
       </c>
       <c r="H88" t="n">
         <v>37736</v>
@@ -2950,7 +2950,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958297729492</v>
       </c>
       <c r="H89" t="n">
         <v>30442</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772453308105</v>
+        <v>57.9772491455078</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711555480957</v>
+        <v>59.0711517333984</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273895263672</v>
+        <v>59.0273971557617</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834465026855</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3240,7 +3240,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G99" t="n">
-        <v>57.0583534240723</v>
+        <v>57.0583572387695</v>
       </c>
       <c r="H99" t="n">
         <v>27245</v>
@@ -3269,7 +3269,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H100" t="n">
         <v>194669</v>
@@ -3298,7 +3298,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G101" t="n">
-        <v>56.8395805358887</v>
+        <v>56.8395767211914</v>
       </c>
       <c r="H101" t="n">
         <v>37551</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708442687988</v>
+        <v>56.9708480834961</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3356,7 +3356,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396766662598</v>
       </c>
       <c r="H103" t="n">
         <v>43096</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3414,7 +3414,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712593078613</v>
+        <v>59.7712631225586</v>
       </c>
       <c r="H105" t="n">
         <v>21082</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276008605957</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525825500488</v>
+        <v>60.2525787353516</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898399353027</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3559,7 +3559,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H110" t="n">
         <v>57326</v>
@@ -3588,7 +3588,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646583557129</v>
+        <v>57.3646621704102</v>
       </c>
       <c r="H111" t="n">
         <v>384860</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.7456703186035</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3646,7 +3646,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082054138184</v>
+        <v>56.0082092285156</v>
       </c>
       <c r="H113" t="n">
         <v>116509</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330833435059</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330833435059</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3733,7 +3733,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709480285645</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="n">
         <v>53938</v>
@@ -3791,7 +3791,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648544311523</v>
+        <v>58.7648658752441</v>
       </c>
       <c r="H118" t="n">
         <v>16964</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899398803711</v>
+        <v>59.2899360656738</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3849,7 +3849,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334831237793</v>
+        <v>57.9334869384766</v>
       </c>
       <c r="H120" t="n">
         <v>11962</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461776733398</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962295532227</v>
+        <v>59.5962371826172</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397842407227</v>
+        <v>58.2397804260254</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4023,7 +4023,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H126" t="n">
         <v>36944</v>
@@ -4052,7 +4052,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770378112793</v>
+        <v>56.5770416259766</v>
       </c>
       <c r="H127" t="n">
         <v>42192</v>
@@ -4081,7 +4081,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H128" t="n">
         <v>47008</v>
@@ -4139,7 +4139,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3144989013672</v>
+        <v>56.3145027160645</v>
       </c>
       <c r="H130" t="n">
         <v>10098</v>
@@ -4168,7 +4168,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H131" t="n">
         <v>10634</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.6207962036133</v>
+        <v>56.620792388916</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4255,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833351135254</v>
+        <v>56.8833389282227</v>
       </c>
       <c r="H134" t="n">
         <v>10051</v>
@@ -4313,7 +4313,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396766662598</v>
       </c>
       <c r="H136" t="n">
         <v>78309</v>
@@ -4342,7 +4342,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.6645545959473</v>
+        <v>56.66455078125</v>
       </c>
       <c r="H137" t="n">
         <v>26876</v>
@@ -4371,7 +4371,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520637512207</v>
+        <v>56.7520599365234</v>
       </c>
       <c r="H138" t="n">
         <v>16052</v>
@@ -4400,7 +4400,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958297729492</v>
       </c>
       <c r="H139" t="n">
         <v>15720</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831352233887</v>
+        <v>55.4831275939941</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582649230957</v>
+        <v>56.3582611083984</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4487,7 +4487,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643547058105</v>
+        <v>55.264347076416</v>
       </c>
       <c r="H142" t="n">
         <v>21545</v>
@@ -4516,7 +4516,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H143" t="n">
         <v>12997</v>
@@ -4545,7 +4545,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955184936523</v>
+        <v>54.6955108642578</v>
       </c>
       <c r="H144" t="n">
         <v>26633</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703330993652</v>
+        <v>53.4703369140625</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4632,7 +4632,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H147" t="n">
         <v>49677</v>
@@ -4719,7 +4719,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264709472656</v>
       </c>
       <c r="H150" t="n">
         <v>21367</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765266418457</v>
+        <v>53.0765342712402</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266860961914</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4893,7 +4893,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766304016113</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H156" t="n">
         <v>10320</v>
@@ -4980,7 +4980,7 @@
         <v>59.5</v>
       </c>
       <c r="G159" t="n">
-        <v>52.070125579834</v>
+        <v>52.0701332092285</v>
       </c>
       <c r="H159" t="n">
         <v>10594</v>
@@ -5009,7 +5009,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449478149414</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H160" t="n">
         <v>11068</v>
@@ -5038,7 +5038,7 @@
         <v>57.25</v>
       </c>
       <c r="G161" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H161" t="n">
         <v>19271</v>
@@ -5096,7 +5096,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.3572311401367</v>
+        <v>49.357234954834</v>
       </c>
       <c r="H163" t="n">
         <v>14934</v>
@@ -5183,7 +5183,7 @@
         <v>57.25</v>
       </c>
       <c r="G166" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H166" t="n">
         <v>9806</v>
@@ -5212,7 +5212,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764190673828</v>
+        <v>52.3764228820801</v>
       </c>
       <c r="H167" t="n">
         <v>20718</v>
@@ -5241,7 +5241,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="n">
         <v>15941</v>
@@ -5270,7 +5270,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>53.4265823364258</v>
+        <v>53.4265785217285</v>
       </c>
       <c r="H169" t="n">
         <v>13847</v>
@@ -5299,7 +5299,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H170" t="n">
         <v>15151</v>
@@ -5357,7 +5357,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>51.8950996398926</v>
+        <v>51.8951034545898</v>
       </c>
       <c r="H172" t="n">
         <v>4493</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889099121094</v>
+        <v>52.2889060974121</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5444,7 +5444,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826202392578</v>
+        <v>51.9826164245605</v>
       </c>
       <c r="H175" t="n">
         <v>7119</v>
@@ -5473,7 +5473,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511489868164</v>
+        <v>50.4511451721191</v>
       </c>
       <c r="H176" t="n">
         <v>8990</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510452270508</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5531,7 +5531,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>49.8385543823242</v>
+        <v>49.838550567627</v>
       </c>
       <c r="H178" t="n">
         <v>9563</v>
@@ -5618,7 +5618,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571273803711</v>
+        <v>48.6571311950684</v>
       </c>
       <c r="H181" t="n">
         <v>8552</v>
@@ -5647,7 +5647,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" t="n">
-        <v>50.1010971069336</v>
+        <v>50.1010932922363</v>
       </c>
       <c r="H182" t="n">
         <v>28706</v>
@@ -5676,7 +5676,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449478149414</v>
+        <v>50.8449516296387</v>
       </c>
       <c r="H183" t="n">
         <v>12299</v>
@@ -5705,7 +5705,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="n">
         <v>13554</v>
@@ -5734,7 +5734,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264747619629</v>
+        <v>52.7264709472656</v>
       </c>
       <c r="H185" t="n">
         <v>20301</v>
@@ -5763,7 +5763,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890098571777</v>
+        <v>52.989013671875</v>
       </c>
       <c r="H186" t="n">
         <v>12495</v>
@@ -5792,7 +5792,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766304016113</v>
+        <v>53.7766342163086</v>
       </c>
       <c r="H187" t="n">
         <v>10680</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765266418457</v>
+        <v>53.0765342712402</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5850,7 +5850,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H189" t="n">
         <v>14775</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516563415527</v>
+        <v>53.9516525268555</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140953063965</v>
+        <v>53.5140914916992</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -5995,7 +5995,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015007019043</v>
+        <v>52.9015045166016</v>
       </c>
       <c r="H194" t="n">
         <v>32354</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2078018188477</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077941894531</v>
+        <v>53.2078018188477</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6169,7 +6169,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.3518600463867</v>
+        <v>55.351863861084</v>
       </c>
       <c r="H200" t="n">
         <v>18598</v>
@@ -6198,7 +6198,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H201" t="n">
         <v>6238</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330833435059</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6256,7 +6256,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="n">
         <v>6842</v>
@@ -6314,7 +6314,7 @@
         <v>61.75</v>
       </c>
       <c r="G205" t="n">
-        <v>54.0391654968262</v>
+        <v>54.0391693115234</v>
       </c>
       <c r="H205" t="n">
         <v>7569</v>
@@ -6372,7 +6372,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141990661621</v>
+        <v>54.2141952514648</v>
       </c>
       <c r="H207" t="n">
         <v>6821</v>
@@ -6401,7 +6401,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.783031463623</v>
+        <v>54.7830276489258</v>
       </c>
       <c r="H208" t="n">
         <v>8498</v>
@@ -6459,7 +6459,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.345458984375</v>
+        <v>54.3454627990723</v>
       </c>
       <c r="H210" t="n">
         <v>5210</v>
@@ -6488,7 +6488,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H211" t="n">
         <v>25353</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6633,7 +6633,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623001098633</v>
+        <v>44.6623039245605</v>
       </c>
       <c r="H216" t="n">
         <v>40064</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.617992401123</v>
+        <v>44.6179885864258</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6749,7 +6749,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358390808105</v>
+        <v>46.0358428955078</v>
       </c>
       <c r="H220" t="n">
         <v>30045</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247550964355</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6836,7 +6836,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.9755249023438</v>
+        <v>43.975528717041</v>
       </c>
       <c r="H223" t="n">
         <v>24305</v>
@@ -6865,7 +6865,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G224" t="n">
-        <v>44.8395309448242</v>
+        <v>44.839527130127</v>
       </c>
       <c r="H224" t="n">
         <v>24015</v>
@@ -6952,7 +6952,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982978820801</v>
+        <v>43.7982940673828</v>
       </c>
       <c r="H227" t="n">
         <v>8139</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019859313965</v>
+        <v>42.6019897460938</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7155,7 +7155,7 @@
         <v>53</v>
       </c>
       <c r="G234" t="n">
-        <v>46.9663009643555</v>
+        <v>46.9663047790527</v>
       </c>
       <c r="H234" t="n">
         <v>26806</v>
@@ -7213,7 +7213,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272361755371</v>
+        <v>48.8272323608398</v>
       </c>
       <c r="H236" t="n">
         <v>13514</v>
@@ -7242,7 +7242,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.2955360412598</v>
+        <v>48.295539855957</v>
       </c>
       <c r="H237" t="n">
         <v>20676</v>
@@ -7271,7 +7271,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755523681641</v>
+        <v>51.1755485534668</v>
       </c>
       <c r="H238" t="n">
         <v>56868</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475440979004</v>
+        <v>49.4475364685059</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7387,7 +7387,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.181697845459</v>
+        <v>49.1816940307617</v>
       </c>
       <c r="H242" t="n">
         <v>12836</v>
@@ -7416,7 +7416,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410781860352</v>
       </c>
       <c r="H243" t="n">
         <v>19274</v>
@@ -7474,7 +7474,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678596496582</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H245" t="n">
         <v>24572</v>
@@ -7590,7 +7590,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844718933105</v>
+        <v>51.8844757080078</v>
       </c>
       <c r="H249" t="n">
         <v>15149</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678596496582</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H251" t="n">
         <v>9250</v>
@@ -7706,7 +7706,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056938171387</v>
+        <v>48.6056976318359</v>
       </c>
       <c r="H253" t="n">
         <v>16185</v>
@@ -7909,7 +7909,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004585266113</v>
+        <v>46.7004547119141</v>
       </c>
       <c r="H260" t="n">
         <v>8510</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192230224609</v>
+        <v>44.2192192077637</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.371223449707</v>
+        <v>45.3712272644043</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8286,7 +8286,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699928283691</v>
+        <v>45.7699966430664</v>
       </c>
       <c r="H273" t="n">
         <v>5066</v>
@@ -8315,7 +8315,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586082458496</v>
+        <v>45.8586120605469</v>
       </c>
       <c r="H274" t="n">
         <v>4374</v>
@@ -8373,7 +8373,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989112854004</v>
+        <v>43.5989074707031</v>
       </c>
       <c r="H276" t="n">
         <v>6787</v>
@@ -8402,7 +8402,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432228088379</v>
       </c>
       <c r="H277" t="n">
         <v>2613</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8576,7 +8576,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570571899414</v>
+        <v>42.7570648193359</v>
       </c>
       <c r="H283" t="n">
         <v>10993</v>
@@ -8634,7 +8634,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761421203613</v>
+        <v>43.7761459350586</v>
       </c>
       <c r="H285" t="n">
         <v>11503</v>
@@ -8692,7 +8692,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324478149414</v>
+        <v>43.5324440002441</v>
       </c>
       <c r="H287" t="n">
         <v>11020</v>
@@ -8779,7 +8779,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H290" t="n">
         <v>2864</v>
@@ -8866,7 +8866,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H293" t="n">
         <v>11169</v>
@@ -8924,7 +8924,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H295" t="n">
         <v>8398</v>
@@ -9011,7 +9011,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H298" t="n">
         <v>11117</v>
@@ -9098,7 +9098,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H301" t="n">
         <v>1288</v>
@@ -9156,7 +9156,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102920532227</v>
+        <v>43.5102958679199</v>
       </c>
       <c r="H303" t="n">
         <v>15525</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9785957336426</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349090576172</v>
+        <v>42.7349052429199</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9272,7 +9272,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493644714355</v>
+        <v>41.6493682861328</v>
       </c>
       <c r="H307" t="n">
         <v>14885</v>
@@ -9301,7 +9301,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>41.8044395446777</v>
+        <v>41.804443359375</v>
       </c>
       <c r="H308" t="n">
         <v>42371</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9388,7 +9388,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853622436523</v>
+        <v>40.7853660583496</v>
       </c>
       <c r="H311" t="n">
         <v>17137</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9475,7 +9475,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>40.6081314086914</v>
+        <v>40.6081275939941</v>
       </c>
       <c r="H314" t="n">
         <v>7102</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638198852539</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9533,7 +9533,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H316" t="n">
         <v>7190</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.946590423584</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9620,7 +9620,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782791137695</v>
+        <v>39.4782829284668</v>
       </c>
       <c r="H319" t="n">
         <v>3338</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213562011719</v>
+        <v>39.9213600158691</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9765,7 +9765,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4308967590332</v>
+        <v>40.4309005737305</v>
       </c>
       <c r="H324" t="n">
         <v>19512</v>
@@ -9823,7 +9823,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693557739258</v>
+        <v>38.7693519592285</v>
       </c>
       <c r="H326" t="n">
         <v>16647</v>
@@ -9910,7 +9910,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>40.6081314086914</v>
+        <v>40.6081275939941</v>
       </c>
       <c r="H329" t="n">
         <v>1168</v>
@@ -9939,7 +9939,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099716186523</v>
+        <v>40.0099754333496</v>
       </c>
       <c r="H330" t="n">
         <v>3763</v>
@@ -9968,7 +9968,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758178710938</v>
+        <v>40.2758255004883</v>
       </c>
       <c r="H331" t="n">
         <v>6546</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247550964355</v>
+        <v>42.424747467041</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690628051758</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10229,7 +10229,7 @@
         <v>47.7750015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>42.3361358642578</v>
+        <v>42.3361396789551</v>
       </c>
       <c r="H340" t="n">
         <v>1621</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912109375</v>
+        <v>42.4912147521973</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10403,7 +10403,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555099487305</v>
+        <v>39.6555137634277</v>
       </c>
       <c r="H346" t="n">
         <v>10252</v>
@@ -10432,7 +10432,7 @@
         <v>44.0750007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>39.0573616027832</v>
+        <v>39.0573577880859</v>
       </c>
       <c r="H347" t="n">
         <v>20248</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807441711426</v>
+        <v>38.6807403564453</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10490,7 +10490,7 @@
         <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>38.9908981323242</v>
+        <v>38.990894317627</v>
       </c>
       <c r="H349" t="n">
         <v>17776</v>
@@ -10519,7 +10519,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684494018555</v>
+        <v>42.6684455871582</v>
       </c>
       <c r="H350" t="n">
         <v>39393</v>
@@ -10548,7 +10548,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096786499023</v>
+        <v>43.7096824645996</v>
       </c>
       <c r="H351" t="n">
         <v>27897</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370735168457</v>
+        <v>45.6370697021484</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764549255371</v>
+        <v>47.2764587402344</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10693,7 +10693,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992317199707</v>
+        <v>47.0992279052734</v>
       </c>
       <c r="H356" t="n">
         <v>3633</v>
@@ -10722,7 +10722,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878433227539</v>
+        <v>47.1878471374512</v>
       </c>
       <c r="H357" t="n">
         <v>7547</v>
@@ -10780,7 +10780,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.833381652832</v>
+        <v>46.8333778381348</v>
       </c>
       <c r="H359" t="n">
         <v>4295</v>
@@ -10867,7 +10867,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432189941406</v>
+        <v>43.6432228088379</v>
       </c>
       <c r="H362" t="n">
         <v>6139</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419883728027</v>
+        <v>44.0419921875</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10925,7 +10925,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552169799805</v>
+        <v>43.3552131652832</v>
       </c>
       <c r="H364" t="n">
         <v>1387</v>
@@ -10983,7 +10983,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973564147949</v>
+        <v>40.4973602294922</v>
       </c>
       <c r="H366" t="n">
         <v>12931</v>
@@ -11099,7 +11099,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321273803711</v>
+        <v>40.0321311950684</v>
       </c>
       <c r="H370" t="n">
         <v>10048</v>
@@ -11128,7 +11128,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.962589263916</v>
+        <v>40.9625930786133</v>
       </c>
       <c r="H371" t="n">
         <v>7882</v>
@@ -11244,7 +11244,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118392944336</v>
+        <v>46.6118431091309</v>
       </c>
       <c r="H375" t="n">
         <v>5727</v>
@@ -11302,7 +11302,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.5109329223633</v>
+        <v>50.5109367370605</v>
       </c>
       <c r="H377" t="n">
         <v>57780</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780136108398</v>
+        <v>50.3780097961426</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121635437012</v>
+        <v>50.1121673583984</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11592,7 +11592,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="n">
         <v>12225</v>
@@ -11679,7 +11679,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678596496582</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H390" t="n">
         <v>14079</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11766,7 +11766,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.726318359375</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H393" t="n">
         <v>9144</v>
@@ -11795,7 +11795,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.726318359375</v>
+        <v>52.7263259887695</v>
       </c>
       <c r="H394" t="n">
         <v>11783</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11969,7 +11969,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.3909378051758</v>
+        <v>53.390941619873</v>
       </c>
       <c r="H400" t="n">
         <v>20005</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657073974609</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12027,7 +12027,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961769104004</v>
+        <v>55.2961845397949</v>
       </c>
       <c r="H402" t="n">
         <v>18544</v>
@@ -12114,7 +12114,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>54.0998687744141</v>
+        <v>54.0998649597168</v>
       </c>
       <c r="H405" t="n">
         <v>6186</v>
@@ -12230,7 +12230,7 @@
         <v>63.3499984741211</v>
       </c>
       <c r="G409" t="n">
-        <v>56.1380271911621</v>
+        <v>56.1380233764648</v>
       </c>
       <c r="H409" t="n">
         <v>12835</v>
@@ -12259,7 +12259,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.7774085998535</v>
+        <v>57.777416229248</v>
       </c>
       <c r="H410" t="n">
         <v>15892</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.157112121582</v>
+        <v>57.1571083068848</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12404,7 +12404,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H415" t="n">
         <v>39195</v>
@@ -12433,7 +12433,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.954647064209</v>
+        <v>57.9546546936035</v>
       </c>
       <c r="H416" t="n">
         <v>19036</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12723,7 +12723,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6887969970703</v>
+        <v>57.6888008117676</v>
       </c>
       <c r="H426" t="n">
         <v>8138</v>
@@ -12868,7 +12868,7 @@
         <v>62</v>
       </c>
       <c r="G431" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H431" t="n">
         <v>6032</v>
@@ -12984,7 +12984,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0173950195312</v>
+        <v>52.0173988342285</v>
       </c>
       <c r="H435" t="n">
         <v>15195</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.5238647460938</v>
+        <v>53.523868560791</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13042,7 +13042,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.245719909668</v>
+        <v>57.2457237243652</v>
       </c>
       <c r="H437" t="n">
         <v>25131</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823387145996</v>
+        <v>56.1823348999023</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13129,7 +13129,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H440" t="n">
         <v>5382</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026466369629</v>
+        <v>56.8026428222656</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140312194824</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13361,7 +13361,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115737915039</v>
       </c>
       <c r="H448" t="n">
         <v>5054</v>
@@ -13419,7 +13419,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709503173828</v>
+        <v>56.2709465026855</v>
       </c>
       <c r="H450" t="n">
         <v>5021</v>
@@ -13506,7 +13506,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734115600586</v>
+        <v>55.4734077453613</v>
       </c>
       <c r="H453" t="n">
         <v>9803</v>
@@ -13535,7 +13535,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>55.6506423950195</v>
+        <v>55.6506385803223</v>
       </c>
       <c r="H454" t="n">
         <v>5826</v>
@@ -13564,7 +13564,7 @@
         <v>62</v>
       </c>
       <c r="G455" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H455" t="n">
         <v>4038</v>
@@ -13593,7 +13593,7 @@
         <v>62</v>
       </c>
       <c r="G456" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H456" t="n">
         <v>4488</v>
@@ -13709,7 +13709,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1694030761719</v>
+        <v>53.1693992614746</v>
       </c>
       <c r="H460" t="n">
         <v>20381</v>
@@ -13912,7 +13912,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450828552246</v>
+        <v>50.2450866699219</v>
       </c>
       <c r="H467" t="n">
         <v>8697</v>
@@ -13941,7 +13941,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792366027832</v>
+        <v>49.9792442321777</v>
       </c>
       <c r="H468" t="n">
         <v>4011</v>
@@ -13970,7 +13970,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678596496582</v>
+        <v>50.0678482055664</v>
       </c>
       <c r="H469" t="n">
         <v>4828</v>
@@ -14028,7 +14028,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.5109329223633</v>
+        <v>50.5109367370605</v>
       </c>
       <c r="H471" t="n">
         <v>9753</v>
@@ -14144,7 +14144,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H475" t="n">
         <v>5767</v>
@@ -14173,7 +14173,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H476" t="n">
         <v>21249</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14289,7 +14289,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="n">
         <v>17941</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14376,7 +14376,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H483" t="n">
         <v>12430</v>
@@ -14434,7 +14434,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="n">
         <v>17601</v>
@@ -14463,7 +14463,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.9441566467285</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H486" t="n">
         <v>9392</v>
@@ -14637,7 +14637,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H492" t="n">
         <v>9874</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14811,7 +14811,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.9441566467285</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H498" t="n">
         <v>9814</v>
@@ -14840,7 +14840,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H499" t="n">
         <v>8348</v>
@@ -14956,7 +14956,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H503" t="n">
         <v>7536</v>
@@ -14985,7 +14985,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653663635254</v>
+        <v>57.9653587341309</v>
       </c>
       <c r="H504" t="n">
         <v>19577</v>
@@ -15130,7 +15130,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H509" t="n">
         <v>5019</v>
@@ -15188,7 +15188,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H511" t="n">
         <v>8102</v>
@@ -15217,7 +15217,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H512" t="n">
         <v>3818</v>
@@ -15362,7 +15362,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111389160156</v>
       </c>
       <c r="H517" t="n">
         <v>1572</v>
@@ -15478,7 +15478,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="n">
         <v>4391</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15536,7 +15536,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353378295898</v>
+        <v>51.1353340148926</v>
       </c>
       <c r="H523" t="n">
         <v>2020</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644157409668</v>
+        <v>51.7644119262695</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15681,7 +15681,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H528" t="n">
         <v>16070</v>
@@ -15710,7 +15710,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H529" t="n">
         <v>9560</v>
@@ -15739,7 +15739,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="n">
         <v>3420</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.9114990234375</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15855,7 +15855,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H534" t="n">
         <v>7649</v>
@@ -15884,7 +15884,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H535" t="n">
         <v>48609</v>
@@ -15913,7 +15913,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502426147461</v>
+        <v>44.3502349853516</v>
       </c>
       <c r="H536" t="n">
         <v>8119</v>
@@ -16000,7 +16000,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>44.5749130249023</v>
+        <v>44.5749092102051</v>
       </c>
       <c r="H539" t="n">
         <v>33506</v>
@@ -16087,7 +16087,7 @@
         <v>49.75</v>
       </c>
       <c r="G542" t="n">
-        <v>44.7097206115723</v>
+        <v>44.709716796875</v>
       </c>
       <c r="H542" t="n">
         <v>18672</v>
@@ -16145,7 +16145,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="n">
         <v>9498</v>
@@ -16174,7 +16174,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="n">
         <v>22578</v>
@@ -16232,7 +16232,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H547" t="n">
         <v>4611</v>
@@ -16261,7 +16261,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H548" t="n">
         <v>5805</v>
@@ -16290,7 +16290,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="n">
         <v>6353</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.9114990234375</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.9114990234375</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16435,7 +16435,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H554" t="n">
         <v>8684</v>
@@ -16493,7 +16493,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H556" t="n">
         <v>14230</v>
@@ -16522,7 +16522,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H557" t="n">
         <v>5027</v>
@@ -16580,7 +16580,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H559" t="n">
         <v>15220</v>
@@ -16609,7 +16609,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H560" t="n">
         <v>18625</v>
@@ -16638,7 +16638,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G561" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H561" t="n">
         <v>4778</v>
@@ -16667,7 +16667,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H562" t="n">
         <v>2385</v>
@@ -16725,7 +16725,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H564" t="n">
         <v>7354</v>
@@ -16783,7 +16783,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H566" t="n">
         <v>2271</v>
@@ -16870,7 +16870,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H569" t="n">
         <v>7932</v>
@@ -16899,7 +16899,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H570" t="n">
         <v>7808</v>
@@ -16957,7 +16957,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H572" t="n">
         <v>12818</v>
@@ -16986,7 +16986,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H573" t="n">
         <v>13677</v>
@@ -17015,7 +17015,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190032958984</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H574" t="n">
         <v>4749</v>
@@ -17044,7 +17044,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H575" t="n">
         <v>4241</v>
@@ -17102,7 +17102,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H577" t="n">
         <v>3506</v>
@@ -17131,7 +17131,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="n">
         <v>3272</v>
@@ -17160,7 +17160,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="n">
         <v>3967</v>
@@ -17189,7 +17189,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H580" t="n">
         <v>33442</v>
@@ -17218,7 +17218,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H581" t="n">
         <v>21771</v>
@@ -17247,7 +17247,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H582" t="n">
         <v>5028</v>
@@ -17363,7 +17363,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732345581055</v>
+        <v>52.5732307434082</v>
       </c>
       <c r="H586" t="n">
         <v>22708</v>
@@ -17392,7 +17392,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G587" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H587" t="n">
         <v>6942</v>
@@ -17479,7 +17479,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H590" t="n">
         <v>18775</v>
@@ -17537,7 +17537,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>50.236644744873</v>
+        <v>50.2366485595703</v>
       </c>
       <c r="H592" t="n">
         <v>13961</v>
@@ -17566,7 +17566,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H593" t="n">
         <v>40288</v>
@@ -17624,7 +17624,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H595" t="n">
         <v>23195</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17711,7 +17711,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H598" t="n">
         <v>23794</v>
@@ -17740,7 +17740,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H599" t="n">
         <v>28739</v>
@@ -17798,7 +17798,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H601" t="n">
         <v>31734</v>
@@ -17827,7 +17827,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H602" t="n">
         <v>37767</v>
@@ -17885,7 +17885,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H604" t="n">
         <v>10561</v>
@@ -17914,7 +17914,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G605" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H605" t="n">
         <v>15945</v>
@@ -17943,7 +17943,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H606" t="n">
         <v>25059</v>
@@ -17972,7 +17972,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H607" t="n">
         <v>15227</v>
@@ -18001,7 +18001,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="n">
         <v>7231</v>
@@ -18059,7 +18059,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H610" t="n">
         <v>10851</v>
@@ -18117,7 +18117,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H612" t="n">
         <v>10436</v>
@@ -18204,7 +18204,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H615" t="n">
         <v>16713</v>
@@ -18262,7 +18262,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H617" t="n">
         <v>22606</v>
@@ -18320,7 +18320,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H619" t="n">
         <v>81517</v>
@@ -18378,7 +18378,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>56.9768104553223</v>
+        <v>56.9768028259277</v>
       </c>
       <c r="H621" t="n">
         <v>116812</v>
@@ -18407,7 +18407,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781173706055</v>
+        <v>56.0781211853027</v>
       </c>
       <c r="H622" t="n">
         <v>32833</v>
@@ -18436,7 +18436,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H623" t="n">
         <v>17457</v>
@@ -18523,7 +18523,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.4719161987305</v>
+        <v>53.471923828125</v>
       </c>
       <c r="H626" t="n">
         <v>14829</v>
@@ -18581,7 +18581,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617904663086</v>
+        <v>53.5617866516113</v>
       </c>
       <c r="H628" t="n">
         <v>10371</v>
@@ -18610,7 +18610,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098205566406</v>
+        <v>54.9098243713379</v>
       </c>
       <c r="H629" t="n">
         <v>33501</v>
@@ -18697,7 +18697,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111312866211</v>
+        <v>54.0111389160156</v>
       </c>
       <c r="H632" t="n">
         <v>15661</v>
@@ -18813,7 +18813,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H636" t="n">
         <v>5975</v>
@@ -18842,7 +18842,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.5503463745117</v>
+        <v>54.550350189209</v>
       </c>
       <c r="H637" t="n">
         <v>10609</v>
@@ -18900,7 +18900,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H639" t="n">
         <v>13780</v>
@@ -18929,7 +18929,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H640" t="n">
         <v>3403</v>
@@ -19045,7 +19045,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G644" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H644" t="n">
         <v>11613</v>
@@ -19132,7 +19132,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H647" t="n">
         <v>18138</v>
@@ -19190,7 +19190,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H649" t="n">
         <v>24403</v>
@@ -19277,7 +19277,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>52.7529678344727</v>
+        <v>52.7529716491699</v>
       </c>
       <c r="H652" t="n">
         <v>28581</v>
@@ -19306,7 +19306,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>53.1124420166016</v>
+        <v>53.1124458312988</v>
       </c>
       <c r="H653" t="n">
         <v>33977</v>
@@ -19480,7 +19480,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G659" t="n">
-        <v>56.2578582763672</v>
+        <v>56.2578544616699</v>
       </c>
       <c r="H659" t="n">
         <v>14809</v>
@@ -19509,7 +19509,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300872802734</v>
+        <v>54.7300834655762</v>
       </c>
       <c r="H660" t="n">
         <v>38065</v>
@@ -19538,7 +19538,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.9441566467285</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H661" t="n">
         <v>53551</v>
@@ -19567,7 +19567,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>51.3150672912598</v>
+        <v>51.315071105957</v>
       </c>
       <c r="H662" t="n">
         <v>35448</v>
@@ -19625,7 +19625,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.9441566467285</v>
+        <v>51.944149017334</v>
       </c>
       <c r="H664" t="n">
         <v>42179</v>
@@ -19654,7 +19654,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657302856445</v>
+        <v>50.8657264709473</v>
       </c>
       <c r="H665" t="n">
         <v>44030</v>
@@ -19683,7 +19683,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379592895508</v>
+        <v>49.3379554748535</v>
       </c>
       <c r="H666" t="n">
         <v>33866</v>
@@ -19712,7 +19712,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>51.4948120117188</v>
+        <v>51.4948081970215</v>
       </c>
       <c r="H667" t="n">
         <v>35732</v>
@@ -19799,7 +19799,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="n">
         <v>17071</v>
@@ -19828,7 +19828,7 @@
         <v>48</v>
       </c>
       <c r="G671" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H671" t="n">
         <v>34722</v>
@@ -19857,7 +19857,7 @@
         <v>44.5</v>
       </c>
       <c r="G672" t="n">
-        <v>39.9916000366211</v>
+        <v>39.9916038513184</v>
       </c>
       <c r="H672" t="n">
         <v>35845</v>
@@ -19886,7 +19886,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>39.2726554870605</v>
+        <v>39.2726593017578</v>
       </c>
       <c r="H673" t="n">
         <v>30746</v>
@@ -20147,7 +20147,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861419677734</v>
+        <v>23.1861438751221</v>
       </c>
       <c r="H682" t="n">
         <v>57668</v>
@@ -20292,7 +20292,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H687" t="n">
         <v>17426</v>
@@ -20350,7 +20350,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328651428223</v>
+        <v>25.4328632354736</v>
       </c>
       <c r="H689" t="n">
         <v>33327</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.4557495117188</v>
+        <v>23.4557514190674</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20437,7 +20437,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H692" t="n">
         <v>106161</v>
@@ -20466,7 +20466,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346492767334</v>
+        <v>27.6346473693848</v>
       </c>
       <c r="H693" t="n">
         <v>49337</v>
@@ -20553,7 +20553,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993740081787</v>
+        <v>24.3993721008301</v>
       </c>
       <c r="H696" t="n">
         <v>24674</v>
@@ -20698,7 +20698,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967449188232</v>
+        <v>26.1967487335205</v>
       </c>
       <c r="H701" t="n">
         <v>24223</v>
@@ -20814,7 +20814,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G705" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H705" t="n">
         <v>71298</v>
@@ -20843,7 +20843,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>31.7236785888672</v>
+        <v>31.7236747741699</v>
       </c>
       <c r="H706" t="n">
         <v>93719</v>
@@ -20988,7 +20988,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.5562210083008</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H711" t="n">
         <v>10694</v>
@@ -21104,7 +21104,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359580993652</v>
+        <v>26.7359619140625</v>
       </c>
       <c r="H715" t="n">
         <v>47799</v>
@@ -21162,7 +21162,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663543701172</v>
+        <v>26.4663562774658</v>
       </c>
       <c r="H717" t="n">
         <v>21538</v>
@@ -21220,7 +21220,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346492767334</v>
+        <v>27.6346473693848</v>
       </c>
       <c r="H719" t="n">
         <v>31154</v>
@@ -21278,7 +21278,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5562210083008</v>
+        <v>26.5562229156494</v>
       </c>
       <c r="H721" t="n">
         <v>24481</v>
@@ -21307,7 +21307,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998455047607</v>
+        <v>27.4998435974121</v>
       </c>
       <c r="H722" t="n">
         <v>26961</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566944122314</v>
+        <v>29.6566963195801</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21452,7 +21452,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G727" t="n">
-        <v>30.8699264526367</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H727" t="n">
         <v>113929</v>
@@ -21510,7 +21510,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743339538574</v>
+        <v>31.2743358612061</v>
       </c>
       <c r="H729" t="n">
         <v>35167</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990081787109</v>
+        <v>31.4990043640137</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21626,7 +21626,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620468139648</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H733" t="n">
         <v>163828</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.824146270752</v>
+        <v>34.8241500854492</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717086791992</v>
+        <v>33.0717124938965</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21713,7 +21713,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G736" t="n">
-        <v>30.0161724090576</v>
+        <v>30.0161743164062</v>
       </c>
       <c r="H736" t="n">
         <v>76858</v>
@@ -21742,7 +21742,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060390472412</v>
+        <v>30.1060371398926</v>
       </c>
       <c r="H737" t="n">
         <v>76564</v>
@@ -21771,7 +21771,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>30.8699264526367</v>
+        <v>30.8699226379395</v>
       </c>
       <c r="H738" t="n">
         <v>88189</v>
@@ -21800,7 +21800,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.442626953125</v>
+        <v>32.4426307678223</v>
       </c>
       <c r="H739" t="n">
         <v>87104</v>
@@ -21829,7 +21829,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501312255859</v>
+        <v>34.1501350402832</v>
       </c>
       <c r="H740" t="n">
         <v>64579</v>
@@ -21945,7 +21945,7 @@
         <v>41</v>
       </c>
       <c r="G744" t="n">
-        <v>36.8461952209473</v>
+        <v>36.8461990356445</v>
       </c>
       <c r="H744" t="n">
         <v>59580</v>
@@ -22032,7 +22032,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.6444129943848</v>
+        <v>34.644416809082</v>
       </c>
       <c r="H747" t="n">
         <v>44338</v>
@@ -22061,7 +22061,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G748" t="n">
-        <v>35.3633613586426</v>
+        <v>35.3633575439453</v>
       </c>
       <c r="H748" t="n">
         <v>41707</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823173522949</v>
+        <v>36.0823135375977</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22148,7 +22148,7 @@
         <v>42.5</v>
       </c>
       <c r="G751" t="n">
-        <v>38.1942291259766</v>
+        <v>38.1942329406738</v>
       </c>
       <c r="H751" t="n">
         <v>111612</v>
@@ -22177,7 +22177,7 @@
         <v>42.5</v>
       </c>
       <c r="G752" t="n">
-        <v>38.1942291259766</v>
+        <v>38.1942329406738</v>
       </c>
       <c r="H752" t="n">
         <v>37608</v>
@@ -22206,7 +22206,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G753" t="n">
-        <v>38.7783813476562</v>
+        <v>38.778377532959</v>
       </c>
       <c r="H753" t="n">
         <v>21833</v>
@@ -22235,7 +22235,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>38.1043663024902</v>
+        <v>38.104362487793</v>
       </c>
       <c r="H754" t="n">
         <v>28695</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202140808105</v>
+        <v>37.5202102661133</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22380,7 +22380,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>41.2947006225586</v>
+        <v>41.2947044372559</v>
       </c>
       <c r="H759" t="n">
         <v>29044</v>
@@ -22409,7 +22409,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>42.2832565307617</v>
+        <v>42.283260345459</v>
       </c>
       <c r="H760" t="n">
         <v>39270</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22786,7 +22786,7 @@
         <v>45</v>
       </c>
       <c r="G773" t="n">
-        <v>40.4409484863281</v>
+        <v>40.4409523010254</v>
       </c>
       <c r="H773" t="n">
         <v>36830</v>
@@ -22815,7 +22815,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.5079307556152</v>
+        <v>42.507926940918</v>
       </c>
       <c r="H774" t="n">
         <v>35151</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440452575684</v>
+        <v>41.7440490722656</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -22960,7 +22960,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H779" t="n">
         <v>32289</v>
@@ -23221,7 +23221,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H788" t="n">
         <v>35855</v>
@@ -23250,7 +23250,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>43.2718200683594</v>
+        <v>43.2718162536621</v>
       </c>
       <c r="H789" t="n">
         <v>32576</v>
@@ -23279,7 +23279,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G790" t="n">
-        <v>43.2718200683594</v>
+        <v>43.2718162536621</v>
       </c>
       <c r="H790" t="n">
         <v>17846</v>
@@ -23308,7 +23308,7 @@
         <v>48</v>
       </c>
       <c r="G791" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H791" t="n">
         <v>5834</v>
@@ -23337,7 +23337,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.226879119873</v>
+        <v>43.2268829345703</v>
       </c>
       <c r="H792" t="n">
         <v>8813</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23511,7 +23511,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.957275390625</v>
+        <v>42.9572715759277</v>
       </c>
       <c r="H798" t="n">
         <v>12261</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978012084961</v>
+        <v>42.5978050231934</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23598,7 +23598,7 @@
         <v>48</v>
       </c>
       <c r="G801" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H801" t="n">
         <v>20720</v>
@@ -23627,7 +23627,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.5863571166992</v>
+        <v>43.586353302002</v>
       </c>
       <c r="H802" t="n">
         <v>53936</v>
@@ -23685,7 +23685,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H804" t="n">
         <v>10945</v>
@@ -23714,7 +23714,7 @@
         <v>48</v>
       </c>
       <c r="G805" t="n">
-        <v>43.1370086669922</v>
+        <v>43.1370124816895</v>
       </c>
       <c r="H805" t="n">
         <v>8676</v>
@@ -23801,7 +23801,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479888916016</v>
+        <v>39.0479850769043</v>
       </c>
       <c r="H808" t="n">
         <v>25259</v>
@@ -23859,7 +23859,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246215820312</v>
+        <v>37.9246253967285</v>
       </c>
       <c r="H810" t="n">
         <v>12601</v>
@@ -23946,7 +23946,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100807189941</v>
+        <v>37.6100845336914</v>
       </c>
       <c r="H813" t="n">
         <v>22502</v>
@@ -24033,7 +24033,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347549438477</v>
       </c>
       <c r="H816" t="n">
         <v>19737</v>
@@ -24062,7 +24062,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651473999023</v>
+        <v>37.5651435852051</v>
       </c>
       <c r="H817" t="n">
         <v>18022</v>
@@ -24091,7 +24091,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898216247559</v>
+        <v>37.7898178100586</v>
       </c>
       <c r="H818" t="n">
         <v>15517</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030479431152</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986404418945</v>
+        <v>38.5986442565918</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24178,7 +24178,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H821" t="n">
         <v>16005</v>
@@ -24236,7 +24236,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G823" t="n">
-        <v>39.4523963928223</v>
+        <v>39.452392578125</v>
       </c>
       <c r="H823" t="n">
         <v>12453</v>
@@ -24294,7 +24294,7 @@
         <v>45.25</v>
       </c>
       <c r="G825" t="n">
-        <v>40.6656188964844</v>
+        <v>40.6656227111816</v>
       </c>
       <c r="H825" t="n">
         <v>18320</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030479431152</v>
+        <v>39.0030555725098</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24352,7 +24352,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G827" t="n">
-        <v>38.7783813476562</v>
+        <v>38.778377532959</v>
       </c>
       <c r="H827" t="n">
         <v>9351</v>
@@ -24381,7 +24381,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>39.7220001220703</v>
+        <v>39.721996307373</v>
       </c>
       <c r="H828" t="n">
         <v>19617</v>
@@ -24468,7 +24468,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144958496094</v>
+        <v>38.0144920349121</v>
       </c>
       <c r="H831" t="n">
         <v>12021</v>
@@ -24613,7 +24613,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G836" t="n">
-        <v>34.2400054931641</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="H836" t="n">
         <v>24293</v>
@@ -24642,7 +24642,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329727172852</v>
+        <v>35.6329689025879</v>
       </c>
       <c r="H837" t="n">
         <v>24505</v>
@@ -24671,7 +24671,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620468139648</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H838" t="n">
         <v>20097</v>
@@ -24729,7 +24729,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.182788848877</v>
+        <v>39.1827850341797</v>
       </c>
       <c r="H840" t="n">
         <v>10534</v>
@@ -24758,7 +24758,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448883056641</v>
+        <v>37.7448844909668</v>
       </c>
       <c r="H841" t="n">
         <v>59505</v>
@@ -24816,7 +24816,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612113952637</v>
+        <v>40.2612075805664</v>
       </c>
       <c r="H843" t="n">
         <v>56674</v>
@@ -24845,7 +24845,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>40.7105522155762</v>
+        <v>40.7105560302734</v>
       </c>
       <c r="H844" t="n">
         <v>80049</v>
@@ -24874,7 +24874,7 @@
         <v>44.75</v>
       </c>
       <c r="G845" t="n">
-        <v>40.2162742614746</v>
+        <v>40.2162780761719</v>
       </c>
       <c r="H845" t="n">
         <v>22532</v>
@@ -24903,7 +24903,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625221252441</v>
+        <v>39.3625183105469</v>
       </c>
       <c r="H846" t="n">
         <v>19364</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24990,7 +24990,7 @@
         <v>46</v>
       </c>
       <c r="G849" t="n">
-        <v>41.3396377563477</v>
+        <v>41.3396339416504</v>
       </c>
       <c r="H849" t="n">
         <v>27797</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453559875488</v>
+        <v>40.8453598022461</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25077,7 +25077,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G852" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H852" t="n">
         <v>17208</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.9017372131348</v>
+        <v>39.901741027832</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25135,7 +25135,7 @@
         <v>46.1500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>41.4744453430176</v>
+        <v>41.4744415283203</v>
       </c>
       <c r="H854" t="n">
         <v>24859</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149673461914</v>
+        <v>41.1149635314941</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25338,7 +25338,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>40.7554893493652</v>
+        <v>40.755485534668</v>
       </c>
       <c r="H861" t="n">
         <v>19057</v>
@@ -25367,7 +25367,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960151672363</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="n">
         <v>7355</v>
@@ -25396,7 +25396,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G863" t="n">
-        <v>40.3510780334473</v>
+        <v>40.3510818481445</v>
       </c>
       <c r="H863" t="n">
         <v>11672</v>
@@ -25454,7 +25454,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G865" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H865" t="n">
         <v>24079</v>
@@ -25628,7 +25628,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471458435059</v>
+        <v>43.0471420288086</v>
       </c>
       <c r="H871" t="n">
         <v>16203</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123420715332</v>
+        <v>42.9123382568359</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25802,7 +25802,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>43.1819496154785</v>
+        <v>43.1819458007812</v>
       </c>
       <c r="H877" t="n">
         <v>8885</v>
@@ -25831,7 +25831,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.3616828918457</v>
+        <v>43.361686706543</v>
       </c>
       <c r="H878" t="n">
         <v>3445</v>
@@ -25860,7 +25860,7 @@
         <v>47.25</v>
       </c>
       <c r="G879" t="n">
-        <v>42.4629936218262</v>
+        <v>42.4629974365234</v>
       </c>
       <c r="H879" t="n">
         <v>14904</v>
@@ -25918,7 +25918,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G881" t="n">
-        <v>42.5528678894043</v>
+        <v>42.552864074707</v>
       </c>
       <c r="H881" t="n">
         <v>11939</v>
@@ -26092,7 +26092,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299758911133</v>
+        <v>44.5299797058105</v>
       </c>
       <c r="H887" t="n">
         <v>28055</v>
@@ -26121,7 +26121,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H888" t="n">
         <v>23048</v>
@@ -26150,7 +26150,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H889" t="n">
         <v>14075</v>
@@ -26237,7 +26237,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H892" t="n">
         <v>9547</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26440,7 +26440,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H899" t="n">
         <v>14923</v>
@@ -26498,7 +26498,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H901" t="n">
         <v>12391</v>
@@ -26527,7 +26527,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H902" t="n">
         <v>15877</v>
@@ -26585,7 +26585,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H904" t="n">
         <v>18296</v>
@@ -26614,7 +26614,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H905" t="n">
         <v>8945</v>
@@ -26643,7 +26643,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G906" t="n">
-        <v>49.0683517456055</v>
+        <v>49.0683479309082</v>
       </c>
       <c r="H906" t="n">
         <v>6882</v>
@@ -26672,7 +26672,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190032958984</v>
+        <v>48.619010925293</v>
       </c>
       <c r="H907" t="n">
         <v>2482</v>
@@ -26759,7 +26759,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H910" t="n">
         <v>7813</v>
@@ -26846,7 +26846,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H913" t="n">
         <v>12859</v>
@@ -26875,7 +26875,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H914" t="n">
         <v>6338</v>
@@ -26904,7 +26904,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H915" t="n">
         <v>6803</v>
@@ -26962,7 +26962,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H917" t="n">
         <v>10683</v>
@@ -27049,7 +27049,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H920" t="n">
         <v>13604</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.9114990234375</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27223,7 +27223,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H926" t="n">
         <v>16584</v>
@@ -27252,7 +27252,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>47.5405807495117</v>
+        <v>47.540584564209</v>
       </c>
       <c r="H927" t="n">
         <v>8346</v>
@@ -27455,7 +27455,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G934" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H934" t="n">
         <v>3732</v>
@@ -27513,7 +27513,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>47.3608474731445</v>
+        <v>47.3608436584473</v>
       </c>
       <c r="H936" t="n">
         <v>6052</v>
@@ -27542,7 +27542,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H937" t="n">
         <v>6177</v>
@@ -27571,7 +27571,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291366577148</v>
+        <v>48.5291404724121</v>
       </c>
       <c r="H938" t="n">
         <v>7754</v>
@@ -27629,7 +27629,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>47.2709732055664</v>
+        <v>47.2709770202637</v>
       </c>
       <c r="H940" t="n">
         <v>9185</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27803,7 +27803,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H946" t="n">
         <v>4946</v>
@@ -27919,7 +27919,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H950" t="n">
         <v>5714</v>
@@ -27977,7 +27977,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H952" t="n">
         <v>12756</v>
@@ -28006,7 +28006,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>44.7546501159668</v>
+        <v>44.7546463012695</v>
       </c>
       <c r="H953" t="n">
         <v>23396</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28064,7 +28064,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H955" t="n">
         <v>6413</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894577026367</v>
+        <v>44.8894538879395</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28151,7 +28151,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H958" t="n">
         <v>6560</v>
@@ -28180,7 +28180,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>47.810188293457</v>
+        <v>47.8101921081543</v>
       </c>
       <c r="H959" t="n">
         <v>15470</v>
@@ -28209,7 +28209,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G960" t="n">
-        <v>46.1026802062988</v>
+        <v>46.1026840209961</v>
       </c>
       <c r="H960" t="n">
         <v>16648</v>
@@ -28238,7 +28238,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H961" t="n">
         <v>12589</v>
@@ -28267,7 +28267,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824211120605</v>
+        <v>46.2824172973633</v>
       </c>
       <c r="H962" t="n">
         <v>10727</v>
@@ -28383,7 +28383,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H966" t="n">
         <v>2872</v>
@@ -28412,7 +28412,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>48.888614654541</v>
+        <v>48.8886184692383</v>
       </c>
       <c r="H967" t="n">
         <v>3349</v>
@@ -28470,7 +28470,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G969" t="n">
-        <v>47.4507102966309</v>
+        <v>47.4507141113281</v>
       </c>
       <c r="H969" t="n">
         <v>11609</v>
@@ -28499,7 +28499,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H970" t="n">
         <v>15181</v>
@@ -28528,7 +28528,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H971" t="n">
         <v>12379</v>
@@ -28557,7 +28557,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G972" t="n">
-        <v>46.5520248413086</v>
+        <v>46.5520210266113</v>
       </c>
       <c r="H972" t="n">
         <v>10030</v>
@@ -28586,7 +28586,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H973" t="n">
         <v>226954</v>
@@ -28615,7 +28615,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H974" t="n">
         <v>16723</v>
@@ -28702,7 +28702,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.114128112793</v>
+        <v>45.1141242980957</v>
       </c>
       <c r="H977" t="n">
         <v>17528</v>
@@ -28731,7 +28731,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="n">
         <v>18485</v>
@@ -28760,7 +28760,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H979" t="n">
         <v>30230</v>
@@ -28789,7 +28789,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533393859863</v>
+        <v>45.6533355712891</v>
       </c>
       <c r="H980" t="n">
         <v>105542</v>
@@ -28818,7 +28818,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229469299316</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H981" t="n">
         <v>20247</v>
@@ -28963,7 +28963,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H986" t="n">
         <v>9545</v>
@@ -28992,7 +28992,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H987" t="n">
         <v>17603</v>
@@ -29021,7 +29021,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H988" t="n">
         <v>21589</v>
@@ -29050,7 +29050,7 @@
         <v>49.75</v>
       </c>
       <c r="G989" t="n">
-        <v>44.7097206115723</v>
+        <v>44.709716796875</v>
       </c>
       <c r="H989" t="n">
         <v>13481</v>
@@ -29108,7 +29108,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H991" t="n">
         <v>14665</v>
@@ -29137,7 +29137,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>45.7432098388672</v>
+        <v>45.7432060241699</v>
       </c>
       <c r="H992" t="n">
         <v>32659</v>
@@ -29166,7 +29166,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938652038574</v>
+        <v>45.2938690185547</v>
       </c>
       <c r="H993" t="n">
         <v>12269</v>
@@ -29224,7 +29224,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850463867188</v>
+        <v>44.4850425720215</v>
       </c>
       <c r="H995" t="n">
         <v>8728</v>
@@ -29485,7 +29485,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.0901641845703</v>
+        <v>42.090160369873</v>
       </c>
       <c r="H1004" t="n">
         <v>24860</v>
@@ -29514,7 +29514,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>41.4551773071289</v>
+        <v>41.4551811218262</v>
       </c>
       <c r="H1005" t="n">
         <v>24773</v>
@@ -29601,7 +29601,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1008" t="n">
-        <v>40.5027084350586</v>
+        <v>40.5027122497559</v>
       </c>
       <c r="H1008" t="n">
         <v>10378</v>
@@ -29717,7 +29717,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1012" t="n">
         <v>16272</v>
@@ -29775,7 +29775,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1014" t="n">
         <v>13467</v>
@@ -29804,7 +29804,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316627502441</v>
+        <v>39.7316589355469</v>
       </c>
       <c r="H1015" t="n">
         <v>12739</v>
@@ -29833,7 +29833,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1016" t="n">
         <v>130810</v>
@@ -29862,7 +29862,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>39.051326751709</v>
+        <v>39.0513229370117</v>
       </c>
       <c r="H1017" t="n">
         <v>78089</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.636604309082</v>
+        <v>41.6366081237793</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797828674316</v>
+        <v>42.6797866821289</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218818664551</v>
+        <v>44.2218856811523</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951019287109</v>
+        <v>43.9951057434082</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30703,7 +30703,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678352355957</v>
+        <v>48.1678314208984</v>
       </c>
       <c r="H1046" t="n">
         <v>11015</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328521728516</v>
+        <v>47.5328598022461</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443130493164</v>
+        <v>46.4443206787109</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -30964,7 +30964,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1055" t="n">
         <v>9979</v>
@@ -30993,7 +30993,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1056" t="n">
         <v>10716</v>
@@ -31109,7 +31109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1060" t="n">
         <v>8913</v>
@@ -31138,7 +31138,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>46.3536071777344</v>
+        <v>46.3536033630371</v>
       </c>
       <c r="H1061" t="n">
         <v>13933</v>
@@ -31370,7 +31370,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>45.0382919311523</v>
+        <v>45.0382881164551</v>
       </c>
       <c r="H1069" t="n">
         <v>4742</v>
@@ -31399,7 +31399,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464874267578</v>
+        <v>45.4464912414551</v>
       </c>
       <c r="H1070" t="n">
         <v>9883</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093376159668</v>
+        <v>45.8093338012695</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31515,7 +31515,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.4486618041992</v>
+        <v>44.448657989502</v>
       </c>
       <c r="H1074" t="n">
         <v>6081</v>
@@ -31544,7 +31544,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125953674316</v>
+        <v>44.3125915527344</v>
       </c>
       <c r="H1075" t="n">
         <v>11302</v>
@@ -31602,7 +31602,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>44.0404624938965</v>
+        <v>44.0404586791992</v>
       </c>
       <c r="H1077" t="n">
         <v>13929</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563743591309</v>
+        <v>49.2563705444336</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792999267578</v>
+        <v>47.0792961120605</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.459529876709</v>
+        <v>39.4595222473145</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31921,7 +31921,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.3666381835938</v>
+        <v>40.366641998291</v>
       </c>
       <c r="H1088" t="n">
         <v>48832</v>
@@ -32008,7 +32008,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1091" t="n">
         <v>42578</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163398742676</v>
+        <v>38.4163436889648</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32124,7 +32124,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1095" t="n">
         <v>71980</v>
@@ -32182,7 +32182,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1097" t="n">
         <v>51723</v>
@@ -32269,7 +32269,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999412536621</v>
+        <v>37.5999374389648</v>
       </c>
       <c r="H1100" t="n">
         <v>35064</v>
@@ -32327,7 +32327,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1102" t="n">
         <v>21799</v>
@@ -32385,7 +32385,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1104" t="n">
         <v>25963</v>
@@ -32530,7 +32530,7 @@
         <v>39.75</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.0578422546387</v>
+        <v>36.0578460693359</v>
       </c>
       <c r="H1109" t="n">
         <v>22744</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32704,7 +32704,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228630065918</v>
+        <v>35.4228591918945</v>
       </c>
       <c r="H1115" t="n">
         <v>18782</v>
@@ -32733,7 +32733,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>34.7878761291504</v>
+        <v>34.7878799438477</v>
       </c>
       <c r="H1116" t="n">
         <v>14282</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -32849,7 +32849,7 @@
         <v>39.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1120" t="n">
         <v>13419</v>
@@ -32907,7 +32907,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>33.8807678222656</v>
+        <v>33.8807640075684</v>
       </c>
       <c r="H1122" t="n">
         <v>16853</v>
@@ -33052,7 +33052,7 @@
         <v>40.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1127" t="n">
         <v>35284</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463813781738</v>
+        <v>37.1463851928711</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33168,7 +33168,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1131" t="n">
-        <v>38.6884841918945</v>
+        <v>38.6884803771973</v>
       </c>
       <c r="H1131" t="n">
         <v>27152</v>
@@ -33197,7 +33197,7 @@
         <v>42.25</v>
       </c>
       <c r="G1132" t="n">
-        <v>38.3256340026855</v>
+        <v>38.3256301879883</v>
       </c>
       <c r="H1132" t="n">
         <v>14021</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33313,7 +33313,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>38.8698997497559</v>
+        <v>38.8698959350586</v>
       </c>
       <c r="H1136" t="n">
         <v>22436</v>
@@ -33342,7 +33342,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1137" t="n">
         <v>52206</v>
@@ -33458,7 +33458,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299751281738</v>
+        <v>36.3299789428711</v>
       </c>
       <c r="H1141" t="n">
         <v>7118</v>
@@ -33487,7 +33487,7 @@
         <v>40.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1142" t="n">
         <v>14421</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764152526855</v>
+        <v>35.8764228820801</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33661,7 +33661,7 @@
         <v>39.25</v>
       </c>
       <c r="G1148" t="n">
-        <v>35.6042823791504</v>
+        <v>35.6042861938477</v>
       </c>
       <c r="H1148" t="n">
         <v>52820</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321495056152</v>
+        <v>35.3321533203125</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33719,7 +33719,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1150" t="n">
         <v>39042</v>
@@ -34067,7 +34067,7 @@
         <v>40.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>36.7381782531738</v>
+        <v>36.7381820678711</v>
       </c>
       <c r="H1162" t="n">
         <v>32830</v>
@@ -34125,7 +34125,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988540649414</v>
+        <v>38.0988578796387</v>
       </c>
       <c r="H1164" t="n">
         <v>26580</v>
@@ -34183,7 +34183,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.826717376709</v>
+        <v>37.8267211914062</v>
       </c>
       <c r="H1166" t="n">
         <v>18336</v>
@@ -34444,7 +34444,7 @@
         <v>36.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.882942199707</v>
+        <v>32.8829383850098</v>
       </c>
       <c r="H1175" t="n">
         <v>70764</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605033874512</v>
+        <v>30.6605072021484</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419284820557</v>
+        <v>30.8419322967529</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34792,7 +34792,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561622619629</v>
+        <v>32.6561584472656</v>
       </c>
       <c r="H1187" t="n">
         <v>23709</v>
@@ -34879,7 +34879,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900543212891</v>
+        <v>33.7900581359863</v>
       </c>
       <c r="H1190" t="n">
         <v>13571</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600166320801</v>
+        <v>35.0600204467773</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34966,7 +34966,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>33.8807678222656</v>
+        <v>33.8807640075684</v>
       </c>
       <c r="H1193" t="n">
         <v>15184</v>
@@ -35024,7 +35024,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>35.1053695678711</v>
+        <v>35.1053733825684</v>
       </c>
       <c r="H1195" t="n">
         <v>36612</v>
@@ -35140,7 +35140,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1199" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1199" t="n">
         <v>16944</v>
@@ -35227,7 +35227,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1202" t="n">
         <v>27154</v>
@@ -35256,7 +35256,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>35.7403526306152</v>
+        <v>35.7403564453125</v>
       </c>
       <c r="H1203" t="n">
         <v>17730</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545845031738</v>
+        <v>37.5545883178711</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.781364440918</v>
+        <v>37.7813606262207</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35430,7 +35430,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928253173828</v>
+        <v>36.6928215026855</v>
       </c>
       <c r="H1209" t="n">
         <v>25845</v>
@@ -35575,7 +35575,7 @@
         <v>40.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>36.511402130127</v>
+        <v>36.5113983154297</v>
       </c>
       <c r="H1214" t="n">
         <v>18129</v>
@@ -68728,6 +68728,35 @@
         <v>1495505</v>
       </c>
       <c r="I2357" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2358" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2358" t="n">
+        <v>1.65199995040894</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>1.65699994564056</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>1.60099995136261</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G2358" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="H2358" t="n">
+        <v>614727</v>
+      </c>
+      <c r="I2358" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569198608398</v>
+        <v>47.2569313049316</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318496704102</v>
+        <v>46.7318458557129</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -630,7 +630,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631172180176</v>
+        <v>46.8631210327148</v>
       </c>
       <c r="H9" t="n">
         <v>27464</v>
@@ -659,7 +659,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H10" t="n">
         <v>24546</v>
@@ -717,7 +717,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H12" t="n">
         <v>19418</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -833,7 +833,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632209777832</v>
+        <v>47.5632171630859</v>
       </c>
       <c r="H16" t="n">
         <v>20120</v>
@@ -978,7 +978,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9506340026855</v>
+        <v>46.9506301879883</v>
       </c>
       <c r="H21" t="n">
         <v>21782</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131690979004</v>
+        <v>47.2131652832031</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1094,7 +1094,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H25" t="n">
         <v>24385</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756118774414</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1181,7 +1181,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.119255065918</v>
+        <v>46.1192588806152</v>
       </c>
       <c r="H28" t="n">
         <v>23503</v>
@@ -1210,7 +1210,7 @@
         <v>52.25</v>
       </c>
       <c r="G29" t="n">
-        <v>45.7254524230957</v>
+        <v>45.7254486083984</v>
       </c>
       <c r="H29" t="n">
         <v>15825</v>
@@ -1239,7 +1239,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692070007324</v>
+        <v>45.7692031860352</v>
       </c>
       <c r="H30" t="n">
         <v>7291</v>
@@ -1297,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="G32" t="n">
-        <v>46.3817939758301</v>
+        <v>46.3817977905273</v>
       </c>
       <c r="H32" t="n">
         <v>21384</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816902160645</v>
+        <v>45.681697845459</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1384,7 +1384,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1256523132324</v>
+        <v>47.1256561279297</v>
       </c>
       <c r="H35" t="n">
         <v>35180</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069793701172</v>
+        <v>47.6069755554199</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1442,7 +1442,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H37" t="n">
         <v>10252</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881950378418</v>
+        <v>47.3881988525391</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756118774414</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1529,7 +1529,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>46.9943885803223</v>
+        <v>46.994384765625</v>
       </c>
       <c r="H40" t="n">
         <v>9334</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569198608398</v>
+        <v>47.2569313049316</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882949829102</v>
+        <v>48.0882987976074</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1674,7 +1674,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.913272857666</v>
+        <v>47.9132690429688</v>
       </c>
       <c r="H45" t="n">
         <v>55518</v>
@@ -1703,7 +1703,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068717956543</v>
+        <v>46.9068756103516</v>
       </c>
       <c r="H46" t="n">
         <v>84037</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1906,7 +1906,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H53" t="n">
         <v>13389</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.5194625854492</v>
+        <v>47.519458770752</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944847106934</v>
+        <v>47.6944885253906</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135765075684</v>
+        <v>50.0135803222656</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953147888184</v>
+        <v>53.2953109741211</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579460144043</v>
+        <v>54.2579498291016</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2312,7 +2312,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336982727051</v>
+        <v>59.3336944580078</v>
       </c>
       <c r="H67" t="n">
         <v>66049</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.258975982666</v>
+        <v>61.2589836120605</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2370,7 +2370,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4403991699219</v>
+        <v>62.4403953552246</v>
       </c>
       <c r="H69" t="n">
         <v>51076</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965370178223</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2457,7 +2457,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="n">
-        <v>62.1341094970703</v>
+        <v>62.134105682373</v>
       </c>
       <c r="H72" t="n">
         <v>24358</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4340019226074</v>
+        <v>61.4339981079102</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964332580566</v>
+        <v>60.9964370727539</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2573,7 +2573,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462852478027</v>
+        <v>59.9462814331055</v>
       </c>
       <c r="H76" t="n">
         <v>17560</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275009155273</v>
+        <v>59.7275085449219</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838500976562</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2689,7 +2689,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775566101074</v>
+        <v>60.0775604248047</v>
       </c>
       <c r="H80" t="n">
         <v>17247</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214073181152</v>
+        <v>60.8214111328125</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2834,7 +2834,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771415710449</v>
+        <v>57.2771377563477</v>
       </c>
       <c r="H85" t="n">
         <v>30458</v>
@@ -2863,7 +2863,7 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H86" t="n">
         <v>30413</v>
@@ -2921,7 +2921,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958297729492</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H88" t="n">
         <v>37736</v>
@@ -2950,7 +2950,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958297729492</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H89" t="n">
         <v>30442</v>
@@ -2979,7 +2979,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3272972106934</v>
+        <v>58.3273048400879</v>
       </c>
       <c r="H90" t="n">
         <v>24556</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.9772491455078</v>
+        <v>57.977237701416</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960296630859</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711517333984</v>
+        <v>59.071159362793</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3095,7 +3095,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H94" t="n">
         <v>25066</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H97" t="n">
         <v>26035</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834465026855</v>
+        <v>57.583438873291</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3269,7 +3269,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G100" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H100" t="n">
         <v>194669</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708480834961</v>
+        <v>56.9708518981934</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3356,7 +3356,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396766662598</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H103" t="n">
         <v>43096</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960296630859</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.427604675293</v>
+        <v>60.4276084899902</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335906982422</v>
+        <v>58.6335868835449</v>
       </c>
       <c r="H108" t="n">
         <v>43417</v>
@@ -3588,7 +3588,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G111" t="n">
-        <v>57.3646621704102</v>
+        <v>57.3646583557129</v>
       </c>
       <c r="H111" t="n">
         <v>384860</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456703186035</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3646,7 +3646,7 @@
         <v>64</v>
       </c>
       <c r="G113" t="n">
-        <v>56.0082092285156</v>
+        <v>56.0082054138184</v>
       </c>
       <c r="H113" t="n">
         <v>116509</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897323608398</v>
+        <v>57.8897361755371</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3791,7 +3791,7 @@
         <v>67.1500015258789</v>
       </c>
       <c r="G118" t="n">
-        <v>58.7648658752441</v>
+        <v>58.7648582458496</v>
       </c>
       <c r="H118" t="n">
         <v>16964</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899475097656</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962371826172</v>
+        <v>59.5962295532227</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960296630859</v>
+        <v>58.1960258483887</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397804260254</v>
+        <v>58.2397880554199</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4023,7 +4023,7 @@
         <v>65</v>
       </c>
       <c r="G126" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H126" t="n">
         <v>36944</v>
@@ -4110,7 +4110,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.2707481384277</v>
+        <v>56.270751953125</v>
       </c>
       <c r="H129" t="n">
         <v>14664</v>
@@ -4139,7 +4139,7 @@
         <v>64.3499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>56.3145027160645</v>
+        <v>56.3144989013672</v>
       </c>
       <c r="H130" t="n">
         <v>10098</v>
@@ -4168,7 +4168,7 @@
         <v>65</v>
       </c>
       <c r="G131" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H131" t="n">
         <v>10634</v>
@@ -4255,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="G134" t="n">
-        <v>56.8833389282227</v>
+        <v>56.8833351135254</v>
       </c>
       <c r="H134" t="n">
         <v>10051</v>
@@ -4284,7 +4284,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.1896286010742</v>
+        <v>57.189624786377</v>
       </c>
       <c r="H135" t="n">
         <v>6298</v>
@@ -4313,7 +4313,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396766662598</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H136" t="n">
         <v>78309</v>
@@ -4371,7 +4371,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.7520599365234</v>
+        <v>56.752067565918</v>
       </c>
       <c r="H138" t="n">
         <v>16052</v>
@@ -4400,7 +4400,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958297729492</v>
+        <v>56.7958221435547</v>
       </c>
       <c r="H139" t="n">
         <v>15720</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831275939941</v>
+        <v>55.4831352233887</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582611083984</v>
+        <v>56.3582572937012</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4487,7 +4487,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.264347076416</v>
+        <v>55.2643547058105</v>
       </c>
       <c r="H142" t="n">
         <v>21545</v>
@@ -4574,7 +4574,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892211914062</v>
+        <v>54.3892250061035</v>
       </c>
       <c r="H145" t="n">
         <v>31730</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.4703369140625</v>
+        <v>53.470329284668</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394805908203</v>
+        <v>56.1394729614258</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4719,7 +4719,7 @@
         <v>60.25</v>
       </c>
       <c r="G150" t="n">
-        <v>52.7264709472656</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H150" t="n">
         <v>21367</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765342712402</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4864,7 +4864,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578460693359</v>
+        <v>53.5578498840332</v>
       </c>
       <c r="H155" t="n">
         <v>11308</v>
@@ -4893,7 +4893,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H156" t="n">
         <v>10320</v>
@@ -4922,7 +4922,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.113883972168</v>
+        <v>52.1138877868652</v>
       </c>
       <c r="H157" t="n">
         <v>24689</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326683044434</v>
+        <v>52.3326721191406</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -5067,7 +5067,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>48.9196701049805</v>
+        <v>48.9196739196777</v>
       </c>
       <c r="H162" t="n">
         <v>15929</v>
@@ -5125,7 +5125,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H164" t="n">
         <v>9928</v>
@@ -5154,7 +5154,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883987426758</v>
+        <v>48.7883949279785</v>
       </c>
       <c r="H165" t="n">
         <v>49976</v>
@@ -5212,7 +5212,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764228820801</v>
+        <v>52.3764190673828</v>
       </c>
       <c r="H167" t="n">
         <v>20718</v>
@@ -5241,7 +5241,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201850891113</v>
+        <v>52.4201812744141</v>
       </c>
       <c r="H168" t="n">
         <v>15941</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889060974121</v>
+        <v>52.2889137268066</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.7510414123535</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5560,7 +5560,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H179" t="n">
         <v>6559</v>
@@ -5589,7 +5589,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.269718170166</v>
+        <v>49.2697219848633</v>
       </c>
       <c r="H180" t="n">
         <v>6556</v>
@@ -5618,7 +5618,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571311950684</v>
+        <v>48.6571273803711</v>
       </c>
       <c r="H181" t="n">
         <v>8552</v>
@@ -5734,7 +5734,7 @@
         <v>60.25</v>
       </c>
       <c r="G185" t="n">
-        <v>52.7264709472656</v>
+        <v>52.7264747619629</v>
       </c>
       <c r="H185" t="n">
         <v>20301</v>
@@ -5763,7 +5763,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.989013671875</v>
+        <v>52.9890098571777</v>
       </c>
       <c r="H186" t="n">
         <v>12495</v>
@@ -5792,7 +5792,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>53.7766342163086</v>
+        <v>53.7766304016113</v>
       </c>
       <c r="H187" t="n">
         <v>10680</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765342712402</v>
+        <v>53.0765266418457</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140914916992</v>
+        <v>53.5140953063965</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2078018188477</v>
+        <v>53.2077903747559</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2078018188477</v>
+        <v>53.2077903747559</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6140,7 +6140,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519676208496</v>
+        <v>56.0519714355469</v>
       </c>
       <c r="H199" t="n">
         <v>8382</v>
@@ -6198,7 +6198,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H201" t="n">
         <v>6238</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330795288086</v>
+        <v>55.1330757141113</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390655517578</v>
+        <v>53.3390693664551</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6459,7 +6459,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.3454627990723</v>
+        <v>54.345458984375</v>
       </c>
       <c r="H210" t="n">
         <v>5210</v>
@@ -6488,7 +6488,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893249511719</v>
+        <v>55.0893211364746</v>
       </c>
       <c r="H211" t="n">
         <v>25353</v>
@@ -6546,7 +6546,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>52.463939666748</v>
+        <v>52.4639434814453</v>
       </c>
       <c r="H213" t="n">
         <v>17630</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823089599609</v>
+        <v>49.8823051452637</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179885864258</v>
+        <v>44.617992401123</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6691,7 +6691,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041427612305</v>
+        <v>45.504150390625</v>
       </c>
       <c r="H218" t="n">
         <v>23030</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.424747467041</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6836,7 +6836,7 @@
         <v>49.625</v>
       </c>
       <c r="G223" t="n">
-        <v>43.975528717041</v>
+        <v>43.9755249023438</v>
       </c>
       <c r="H223" t="n">
         <v>24305</v>
@@ -6894,7 +6894,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281463623047</v>
+        <v>44.9281425476074</v>
       </c>
       <c r="H225" t="n">
         <v>28013</v>
@@ -6923,7 +6923,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509117126465</v>
+        <v>44.7509155273438</v>
       </c>
       <c r="H226" t="n">
         <v>9809</v>
@@ -6952,7 +6952,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982940673828</v>
+        <v>43.7982902526855</v>
       </c>
       <c r="H227" t="n">
         <v>8139</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019897460938</v>
+        <v>42.6019859313965</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025993347168</v>
+        <v>42.4025955200195</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7184,7 +7184,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>47.4536895751953</v>
+        <v>47.4536933898926</v>
       </c>
       <c r="H235" t="n">
         <v>27871</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475364685059</v>
+        <v>49.4475402832031</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7329,7 +7329,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>49.5361595153809</v>
+        <v>49.5361633300781</v>
       </c>
       <c r="H240" t="n">
         <v>97891</v>
@@ -7358,7 +7358,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.2260055541992</v>
+        <v>49.226001739502</v>
       </c>
       <c r="H241" t="n">
         <v>21035</v>
@@ -7387,7 +7387,7 @@
         <v>55.5</v>
       </c>
       <c r="G242" t="n">
-        <v>49.1816940307617</v>
+        <v>49.181697845459</v>
       </c>
       <c r="H242" t="n">
         <v>12836</v>
@@ -7416,7 +7416,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410781860352</v>
+        <v>47.9410743713379</v>
       </c>
       <c r="H243" t="n">
         <v>19274</v>
@@ -7445,7 +7445,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H244" t="n">
         <v>15929</v>
@@ -7474,7 +7474,7 @@
         <v>56.5</v>
       </c>
       <c r="G245" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H245" t="n">
         <v>24572</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158477783203</v>
+        <v>48.9158515930176</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7532,7 +7532,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.1373901367188</v>
+        <v>49.137393951416</v>
       </c>
       <c r="H247" t="n">
         <v>16775</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H251" t="n">
         <v>9250</v>
@@ -7706,7 +7706,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>48.6056976318359</v>
+        <v>48.6056938171387</v>
       </c>
       <c r="H253" t="n">
         <v>16185</v>
@@ -7735,7 +7735,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G254" t="n">
-        <v>48.1626167297363</v>
+        <v>48.1626129150391</v>
       </c>
       <c r="H254" t="n">
         <v>4468</v>
@@ -7793,7 +7793,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G256" t="n">
-        <v>48.1626167297363</v>
+        <v>48.1626129150391</v>
       </c>
       <c r="H256" t="n">
         <v>3523</v>
@@ -7822,7 +7822,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.8524627685547</v>
+        <v>47.852466583252</v>
       </c>
       <c r="H257" t="n">
         <v>5700</v>
@@ -7909,7 +7909,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004547119141</v>
+        <v>46.7004585266113</v>
       </c>
       <c r="H260" t="n">
         <v>8510</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192192077637</v>
+        <v>44.2192230224609</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8141,7 +8141,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927619934082</v>
+        <v>45.5927581787109</v>
       </c>
       <c r="H268" t="n">
         <v>9230</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.3712272644043</v>
+        <v>45.371223449707</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8257,7 +8257,7 @@
         <v>52.5</v>
       </c>
       <c r="G272" t="n">
-        <v>46.5232238769531</v>
+        <v>46.5232276916504</v>
       </c>
       <c r="H272" t="n">
         <v>8521</v>
@@ -8286,7 +8286,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699966430664</v>
+        <v>45.7699928283691</v>
       </c>
       <c r="H273" t="n">
         <v>5066</v>
@@ -8373,7 +8373,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989074707031</v>
+        <v>43.5989112854004</v>
       </c>
       <c r="H276" t="n">
         <v>6787</v>
@@ -8402,7 +8402,7 @@
         <v>49.25</v>
       </c>
       <c r="G277" t="n">
-        <v>43.6432228088379</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H277" t="n">
         <v>2613</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8634,7 +8634,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>43.7761459350586</v>
+        <v>43.7761421203613</v>
       </c>
       <c r="H285" t="n">
         <v>11503</v>
@@ -8663,7 +8663,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H286" t="n">
         <v>13125</v>
@@ -8721,7 +8721,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.3109092712402</v>
+        <v>43.310905456543</v>
       </c>
       <c r="H288" t="n">
         <v>4421</v>
@@ -8750,7 +8750,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.2222938537598</v>
+        <v>43.222297668457</v>
       </c>
       <c r="H289" t="n">
         <v>13085</v>
@@ -8779,7 +8779,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H290" t="n">
         <v>2864</v>
@@ -8866,7 +8866,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H293" t="n">
         <v>11169</v>
@@ -8953,7 +8953,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450592041016</v>
+        <v>43.0450630187988</v>
       </c>
       <c r="H296" t="n">
         <v>6836</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9011,7 +9011,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115226745605</v>
+        <v>43.1115264892578</v>
       </c>
       <c r="H298" t="n">
         <v>11117</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9127,7 +9127,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539863586426</v>
+        <v>43.7539825439453</v>
       </c>
       <c r="H302" t="n">
         <v>6369</v>
@@ -9185,7 +9185,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216804504395</v>
+        <v>43.4216766357422</v>
       </c>
       <c r="H304" t="n">
         <v>13328</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349052429199</v>
+        <v>42.7349090576172</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9272,7 +9272,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493682861328</v>
+        <v>41.6493644714355</v>
       </c>
       <c r="H307" t="n">
         <v>14885</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9359,7 +9359,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170547485352</v>
+        <v>41.3170509338379</v>
       </c>
       <c r="H310" t="n">
         <v>20434</v>
@@ -9388,7 +9388,7 @@
         <v>46.0250015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>40.7853660583496</v>
+        <v>40.7853622436523</v>
       </c>
       <c r="H311" t="n">
         <v>17137</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9475,7 +9475,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>40.6081275939941</v>
+        <v>40.6081314086914</v>
       </c>
       <c r="H314" t="n">
         <v>7102</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638236999512</v>
+        <v>40.5638198852539</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9591,7 +9591,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112060546875</v>
+        <v>39.6112022399902</v>
       </c>
       <c r="H318" t="n">
         <v>13054</v>
@@ -9620,7 +9620,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782829284668</v>
+        <v>39.4782791137695</v>
       </c>
       <c r="H319" t="n">
         <v>3338</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213600158691</v>
+        <v>39.9213638305664</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9765,7 +9765,7 @@
         <v>45.625</v>
       </c>
       <c r="G324" t="n">
-        <v>40.4309005737305</v>
+        <v>40.4308967590332</v>
       </c>
       <c r="H324" t="n">
         <v>19512</v>
@@ -9910,7 +9910,7 @@
         <v>45.8250007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>40.6081275939941</v>
+        <v>40.6081314086914</v>
       </c>
       <c r="H329" t="n">
         <v>1168</v>
@@ -9939,7 +9939,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099754333496</v>
+        <v>40.0099716186523</v>
       </c>
       <c r="H330" t="n">
         <v>3763</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.424747467041</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690628051758</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924415588379</v>
+        <v>42.0924453735352</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10200,7 +10200,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462898254395</v>
+        <v>42.6462936401367</v>
       </c>
       <c r="H339" t="n">
         <v>10608</v>
@@ -10258,7 +10258,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696762084961</v>
+        <v>42.2696800231934</v>
       </c>
       <c r="H341" t="n">
         <v>4403</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912147521973</v>
+        <v>42.4912109375</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069007873535</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10374,7 +10374,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.9847450256348</v>
+        <v>40.984748840332</v>
       </c>
       <c r="H345" t="n">
         <v>10026</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807403564453</v>
+        <v>38.6807479858398</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10519,7 +10519,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684455871582</v>
+        <v>42.6684494018555</v>
       </c>
       <c r="H350" t="n">
         <v>39393</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764587402344</v>
+        <v>47.2764549255371</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10693,7 +10693,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>47.0992279052734</v>
+        <v>47.0992317199707</v>
       </c>
       <c r="H356" t="n">
         <v>3633</v>
@@ -10751,7 +10751,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459968566895</v>
+        <v>46.3459930419922</v>
       </c>
       <c r="H358" t="n">
         <v>34572</v>
@@ -10867,7 +10867,7 @@
         <v>49.25</v>
       </c>
       <c r="G362" t="n">
-        <v>43.6432228088379</v>
+        <v>43.6432151794434</v>
       </c>
       <c r="H362" t="n">
         <v>6139</v>
@@ -10983,7 +10983,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973602294922</v>
+        <v>40.4973564147949</v>
       </c>
       <c r="H366" t="n">
         <v>12931</v>
@@ -11012,7 +11012,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992080688477</v>
+        <v>39.8992042541504</v>
       </c>
       <c r="H367" t="n">
         <v>21291</v>
@@ -11186,7 +11186,7 @@
         <v>50.75</v>
       </c>
       <c r="G373" t="n">
-        <v>44.9724540710449</v>
+        <v>44.9724502563477</v>
       </c>
       <c r="H373" t="n">
         <v>15133</v>
@@ -11244,7 +11244,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118431091309</v>
+        <v>46.6118392944336</v>
       </c>
       <c r="H375" t="n">
         <v>5727</v>
@@ -11302,7 +11302,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.5109367370605</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H377" t="n">
         <v>57780</v>
@@ -11389,7 +11389,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H380" t="n">
         <v>62651</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958602905273</v>
+        <v>51.7958564758301</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11476,7 +11476,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.3527793884277</v>
+        <v>51.352783203125</v>
       </c>
       <c r="H383" t="n">
         <v>3458</v>
@@ -11505,7 +11505,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.6881637573242</v>
+        <v>50.688159942627</v>
       </c>
       <c r="H384" t="n">
         <v>5575</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121673583984</v>
+        <v>50.1121597290039</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11592,7 +11592,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.7577018737793</v>
+        <v>49.757698059082</v>
       </c>
       <c r="H387" t="n">
         <v>12225</v>
@@ -11621,7 +11621,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463172912598</v>
+        <v>49.8463134765625</v>
       </c>
       <c r="H388" t="n">
         <v>9469</v>
@@ -11650,7 +11650,7 @@
         <v>55.75</v>
       </c>
       <c r="G389" t="n">
-        <v>49.4032363891602</v>
+        <v>49.4032325744629</v>
       </c>
       <c r="H389" t="n">
         <v>4963</v>
@@ -11679,7 +11679,7 @@
         <v>56.5</v>
       </c>
       <c r="G390" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H390" t="n">
         <v>14079</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364761352539</v>
+        <v>53.0364723205566</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11911,7 +11911,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466339111328</v>
+        <v>53.3466377258301</v>
       </c>
       <c r="H398" t="n">
         <v>16109</v>
@@ -11940,7 +11940,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250953674316</v>
+        <v>53.1250991821289</v>
       </c>
       <c r="H399" t="n">
         <v>11868</v>
@@ -11969,7 +11969,7 @@
         <v>60.25</v>
       </c>
       <c r="G400" t="n">
-        <v>53.390941619873</v>
+        <v>53.3909378051758</v>
       </c>
       <c r="H400" t="n">
         <v>20005</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657073974609</v>
+        <v>54.3657112121582</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12085,7 +12085,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.6124801635742</v>
+        <v>53.6124839782715</v>
       </c>
       <c r="H404" t="n">
         <v>12420</v>
@@ -12143,7 +12143,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>52.7706298828125</v>
+        <v>52.7706336975098</v>
       </c>
       <c r="H406" t="n">
         <v>16569</v>
@@ -12172,7 +12172,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.6124801635742</v>
+        <v>53.6124839782715</v>
       </c>
       <c r="H407" t="n">
         <v>16902</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12259,7 +12259,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G410" t="n">
-        <v>57.777416229248</v>
+        <v>57.7774124145508</v>
       </c>
       <c r="H410" t="n">
         <v>15892</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.157112121582</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12404,7 +12404,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115737915039</v>
+        <v>57.5115699768066</v>
       </c>
       <c r="H415" t="n">
         <v>39195</v>
@@ -12433,7 +12433,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546546936035</v>
+        <v>57.9546508789062</v>
       </c>
       <c r="H416" t="n">
         <v>19036</v>
@@ -12462,7 +12462,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863395690918</v>
+        <v>58.4863471984863</v>
       </c>
       <c r="H417" t="n">
         <v>56533</v>
@@ -12491,7 +12491,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H418" t="n">
         <v>12366</v>
@@ -12520,7 +12520,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038734436035</v>
+        <v>56.4038772583008</v>
       </c>
       <c r="H419" t="n">
         <v>16100</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12607,7 +12607,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>57.4672584533691</v>
+        <v>57.4672622680664</v>
       </c>
       <c r="H422" t="n">
         <v>5806</v>
@@ -12665,7 +12665,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H424" t="n">
         <v>12768</v>
@@ -12694,7 +12694,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G425" t="n">
-        <v>57.4229545593262</v>
+        <v>57.4229583740234</v>
       </c>
       <c r="H425" t="n">
         <v>11750</v>
@@ -12723,7 +12723,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6888008117676</v>
+        <v>57.6888046264648</v>
       </c>
       <c r="H426" t="n">
         <v>8138</v>
@@ -12810,7 +12810,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H429" t="n">
         <v>9582</v>
@@ -12839,7 +12839,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278770446777</v>
+        <v>55.8278694152832</v>
       </c>
       <c r="H430" t="n">
         <v>4618</v>
@@ -12868,7 +12868,7 @@
         <v>62</v>
       </c>
       <c r="G431" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H431" t="n">
         <v>6032</v>
@@ -12897,7 +12897,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>53.4795570373535</v>
+        <v>53.4795532226562</v>
       </c>
       <c r="H432" t="n">
         <v>11761</v>
@@ -12926,7 +12926,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>52.9921684265137</v>
+        <v>52.9921722412109</v>
       </c>
       <c r="H433" t="n">
         <v>13443</v>
@@ -12955,7 +12955,7 @@
         <v>59.75</v>
       </c>
       <c r="G434" t="n">
-        <v>52.9478607177734</v>
+        <v>52.9478645324707</v>
       </c>
       <c r="H434" t="n">
         <v>15198</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823348999023</v>
+        <v>56.1823387145996</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026428222656</v>
+        <v>56.8026466369629</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13245,7 +13245,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H444" t="n">
         <v>6381</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140312194824</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13303,7 +13303,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H446" t="n">
         <v>7435</v>
@@ -13332,7 +13332,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798812866211</v>
       </c>
       <c r="H447" t="n">
         <v>11987</v>
@@ -13361,7 +13361,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115737915039</v>
+        <v>57.5115699768066</v>
       </c>
       <c r="H448" t="n">
         <v>5054</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.625415802002</v>
+        <v>56.6254119873047</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13564,7 +13564,7 @@
         <v>62</v>
       </c>
       <c r="G455" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H455" t="n">
         <v>4038</v>
@@ -13593,7 +13593,7 @@
         <v>62</v>
       </c>
       <c r="G456" t="n">
-        <v>54.9417190551758</v>
+        <v>54.9417152404785</v>
       </c>
       <c r="H456" t="n">
         <v>4488</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555610656738</v>
+        <v>54.0555648803711</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13709,7 +13709,7 @@
         <v>60</v>
       </c>
       <c r="G460" t="n">
-        <v>53.1693992614746</v>
+        <v>53.1694030761719</v>
       </c>
       <c r="H460" t="n">
         <v>20381</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149375915527</v>
+        <v>52.81494140625</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13796,7 +13796,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515525817871</v>
+        <v>51.7515487670898</v>
       </c>
       <c r="H463" t="n">
         <v>3551</v>
@@ -13912,7 +13912,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>50.2450866699219</v>
+        <v>50.2450828552246</v>
       </c>
       <c r="H467" t="n">
         <v>8697</v>
@@ -13941,7 +13941,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G468" t="n">
-        <v>49.9792442321777</v>
+        <v>49.9792404174805</v>
       </c>
       <c r="H468" t="n">
         <v>4011</v>
@@ -13970,7 +13970,7 @@
         <v>56.5</v>
       </c>
       <c r="G469" t="n">
-        <v>50.0678482055664</v>
+        <v>50.0678520202637</v>
       </c>
       <c r="H469" t="n">
         <v>4828</v>
@@ -14028,7 +14028,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.5109367370605</v>
+        <v>50.510929107666</v>
       </c>
       <c r="H471" t="n">
         <v>9753</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14289,7 +14289,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H480" t="n">
         <v>17941</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14753,7 +14753,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H496" t="n">
         <v>19509</v>
@@ -14985,7 +14985,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653587341309</v>
+        <v>57.9653625488281</v>
       </c>
       <c r="H504" t="n">
         <v>19577</v>
@@ -15101,7 +15101,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G508" t="n">
-        <v>55.6287727355957</v>
+        <v>55.6287689208984</v>
       </c>
       <c r="H508" t="n">
         <v>3739</v>
@@ -15130,7 +15130,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H509" t="n">
         <v>5019</v>
@@ -15217,7 +15217,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490394592285</v>
+        <v>55.4490356445312</v>
       </c>
       <c r="H512" t="n">
         <v>3818</v>
@@ -15304,7 +15304,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H515" t="n">
         <v>5949</v>
@@ -15362,7 +15362,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G517" t="n">
-        <v>54.0111389160156</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H517" t="n">
         <v>1572</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137603759766</v>
+        <v>52.2137565612793</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15536,7 +15536,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353340148926</v>
+        <v>51.1353378295898</v>
       </c>
       <c r="H523" t="n">
         <v>2020</v>
@@ -15681,7 +15681,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722915649414</v>
       </c>
       <c r="H528" t="n">
         <v>16070</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.9115028381348</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15913,7 +15913,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>44.3502349853516</v>
+        <v>44.3502388000488</v>
       </c>
       <c r="H536" t="n">
         <v>8119</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603759765625</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16145,7 +16145,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H544" t="n">
         <v>9498</v>
@@ -16174,7 +16174,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H545" t="n">
         <v>22578</v>
@@ -16261,7 +16261,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H548" t="n">
         <v>5805</v>
@@ -16290,7 +16290,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H549" t="n">
         <v>6353</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.9115028381348</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.9115028381348</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16783,7 +16783,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H566" t="n">
         <v>2271</v>
@@ -16899,7 +16899,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H570" t="n">
         <v>7808</v>
@@ -17015,7 +17015,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.619010925293</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H574" t="n">
         <v>4749</v>
@@ -17131,7 +17131,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H578" t="n">
         <v>3272</v>
@@ -17160,7 +17160,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H579" t="n">
         <v>3967</v>
@@ -17363,7 +17363,7 @@
         <v>58.5</v>
       </c>
       <c r="G586" t="n">
-        <v>52.5732307434082</v>
+        <v>52.5732345581055</v>
       </c>
       <c r="H586" t="n">
         <v>22708</v>
@@ -17450,7 +17450,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H589" t="n">
         <v>11027</v>
@@ -17595,7 +17595,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.596118927002</v>
+        <v>50.5961227416992</v>
       </c>
       <c r="H594" t="n">
         <v>10198</v>
@@ -17624,7 +17624,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H595" t="n">
         <v>23195</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17711,7 +17711,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H598" t="n">
         <v>23794</v>
@@ -17827,7 +17827,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H602" t="n">
         <v>37767</v>
@@ -17856,7 +17856,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H603" t="n">
         <v>36430</v>
@@ -17885,7 +17885,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H604" t="n">
         <v>10561</v>
@@ -18001,7 +18001,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H608" t="n">
         <v>7231</v>
@@ -18059,7 +18059,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H610" t="n">
         <v>10851</v>
@@ -18117,7 +18117,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H612" t="n">
         <v>10436</v>
@@ -18175,7 +18175,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>47.7203216552734</v>
+        <v>47.7203178405762</v>
       </c>
       <c r="H614" t="n">
         <v>9199</v>
@@ -18291,7 +18291,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H618" t="n">
         <v>26603</v>
@@ -18349,7 +18349,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H620" t="n">
         <v>114943</v>
@@ -18465,7 +18465,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H624" t="n">
         <v>9412</v>
@@ -18552,7 +18552,7 @@
         <v>60.5</v>
       </c>
       <c r="G627" t="n">
-        <v>54.3706092834473</v>
+        <v>54.3706130981445</v>
       </c>
       <c r="H627" t="n">
         <v>23576</v>
@@ -18581,7 +18581,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>53.5617866516113</v>
+        <v>53.5617904663086</v>
       </c>
       <c r="H628" t="n">
         <v>10371</v>
@@ -18610,7 +18610,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>54.9098243713379</v>
+        <v>54.9098205566406</v>
       </c>
       <c r="H629" t="n">
         <v>33501</v>
@@ -18639,7 +18639,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.1010055541992</v>
+        <v>54.1010093688965</v>
       </c>
       <c r="H630" t="n">
         <v>9653</v>
@@ -18668,7 +18668,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516609191895</v>
+        <v>53.6516571044922</v>
       </c>
       <c r="H631" t="n">
         <v>10031</v>
@@ -18697,7 +18697,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>54.0111389160156</v>
+        <v>54.0111351013184</v>
       </c>
       <c r="H632" t="n">
         <v>15661</v>
@@ -18900,7 +18900,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H639" t="n">
         <v>13780</v>
@@ -18929,7 +18929,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996871948242</v>
+        <v>54.9996910095215</v>
       </c>
       <c r="H640" t="n">
         <v>3403</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19132,7 +19132,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H647" t="n">
         <v>18138</v>
@@ -19190,7 +19190,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631050109863</v>
+        <v>52.6631011962891</v>
       </c>
       <c r="H649" t="n">
         <v>24403</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.0225791931152</v>
+        <v>53.022575378418</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19393,7 +19393,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173324584961</v>
+        <v>56.6173286437988</v>
       </c>
       <c r="H656" t="n">
         <v>87829</v>
@@ -19422,7 +19422,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H657" t="n">
         <v>41152</v>
@@ -19451,7 +19451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071952819824</v>
+        <v>56.7071914672852</v>
       </c>
       <c r="H658" t="n">
         <v>26511</v>
@@ -19596,7 +19596,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H663" t="n">
         <v>43542</v>
@@ -19799,7 +19799,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H670" t="n">
         <v>17071</v>
@@ -19886,7 +19886,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>39.2726593017578</v>
+        <v>39.2726554870605</v>
       </c>
       <c r="H673" t="n">
         <v>30746</v>
@@ -20147,7 +20147,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861438751221</v>
+        <v>23.1861457824707</v>
       </c>
       <c r="H682" t="n">
         <v>57668</v>
@@ -20176,7 +20176,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139148712158</v>
+        <v>24.7139129638672</v>
       </c>
       <c r="H683" t="n">
         <v>30853</v>
@@ -20234,7 +20234,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024707794189</v>
+        <v>25.7024688720703</v>
       </c>
       <c r="H685" t="n">
         <v>34700</v>
@@ -20292,7 +20292,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H687" t="n">
         <v>17426</v>
@@ -20379,7 +20379,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.5905532836914</v>
+        <v>23.59055519104</v>
       </c>
       <c r="H690" t="n">
         <v>49158</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.4557514190674</v>
+        <v>23.455753326416</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20437,7 +20437,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879280090332</v>
+        <v>25.3879299163818</v>
       </c>
       <c r="H692" t="n">
         <v>106161</v>
@@ -20611,7 +20611,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H698" t="n">
         <v>66739</v>
@@ -20669,7 +20669,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258304595947</v>
+        <v>26.8258285522461</v>
       </c>
       <c r="H700" t="n">
         <v>41033</v>
@@ -20698,7 +20698,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967487335205</v>
+        <v>26.1967506408691</v>
       </c>
       <c r="H701" t="n">
         <v>24223</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130756378174</v>
+        <v>28.7130737304688</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -20930,7 +20930,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.308666229248</v>
+        <v>28.3086643218994</v>
       </c>
       <c r="H709" t="n">
         <v>38489</v>
@@ -20959,7 +20959,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.0505027770996</v>
+        <v>27.0505046844482</v>
       </c>
       <c r="H710" t="n">
         <v>34512</v>
@@ -21307,7 +21307,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998435974121</v>
+        <v>27.4998455047607</v>
       </c>
       <c r="H722" t="n">
         <v>26961</v>
@@ -21365,7 +21365,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928127288818</v>
+        <v>28.8928146362305</v>
       </c>
       <c r="H724" t="n">
         <v>74966</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566963195801</v>
+        <v>29.6566982269287</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21539,7 +21539,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642063140869</v>
+        <v>31.3642024993896</v>
       </c>
       <c r="H730" t="n">
         <v>45462</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990043640137</v>
+        <v>31.4990081787109</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21626,7 +21626,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620544433594</v>
       </c>
       <c r="H733" t="n">
         <v>163828</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.8241500854492</v>
+        <v>34.824146270752</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717124938965</v>
+        <v>33.0717086791992</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21800,7 +21800,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.4426307678223</v>
+        <v>32.442626953125</v>
       </c>
       <c r="H739" t="n">
         <v>87104</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.543098449707</v>
+        <v>35.5431022644043</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -21945,7 +21945,7 @@
         <v>41</v>
       </c>
       <c r="G744" t="n">
-        <v>36.8461990356445</v>
+        <v>36.8461952209473</v>
       </c>
       <c r="H744" t="n">
         <v>59580</v>
@@ -22032,7 +22032,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>34.644416809082</v>
+        <v>34.6444129943848</v>
       </c>
       <c r="H747" t="n">
         <v>44338</v>
@@ -22061,7 +22061,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G748" t="n">
-        <v>35.3633575439453</v>
+        <v>35.3633613586426</v>
       </c>
       <c r="H748" t="n">
         <v>41707</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202102661133</v>
+        <v>37.5202140808105</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22380,7 +22380,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>41.2947044372559</v>
+        <v>41.2947006225586</v>
       </c>
       <c r="H759" t="n">
         <v>29044</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22612,7 +22612,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.8339157104492</v>
+        <v>41.833911895752</v>
       </c>
       <c r="H767" t="n">
         <v>20446</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22931,7 +22931,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H778" t="n">
         <v>34460</v>
@@ -23047,7 +23047,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H782" t="n">
         <v>12518</v>
@@ -23134,7 +23134,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H785" t="n">
         <v>14310</v>
@@ -23395,7 +23395,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H794" t="n">
         <v>19217</v>
@@ -23453,7 +23453,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H796" t="n">
         <v>16749</v>
@@ -23482,7 +23482,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H797" t="n">
         <v>19864</v>
@@ -23511,7 +23511,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>42.9572715759277</v>
+        <v>42.957275390625</v>
       </c>
       <c r="H798" t="n">
         <v>12261</v>
@@ -23540,7 +23540,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>42.5978050231934</v>
+        <v>42.5978012084961</v>
       </c>
       <c r="H799" t="n">
         <v>25362</v>
@@ -23627,7 +23627,7 @@
         <v>48.5</v>
       </c>
       <c r="G802" t="n">
-        <v>43.586353302002</v>
+        <v>43.5863571166992</v>
       </c>
       <c r="H802" t="n">
         <v>53936</v>
@@ -23801,7 +23801,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.0479850769043</v>
+        <v>39.047981262207</v>
       </c>
       <c r="H808" t="n">
         <v>25259</v>
@@ -23946,7 +23946,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G813" t="n">
-        <v>37.6100845336914</v>
+        <v>37.6100807189941</v>
       </c>
       <c r="H813" t="n">
         <v>22502</v>
@@ -23975,7 +23975,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3069877624512</v>
+        <v>36.3069839477539</v>
       </c>
       <c r="H814" t="n">
         <v>20180</v>
@@ -24033,7 +24033,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347549438477</v>
+        <v>37.8347511291504</v>
       </c>
       <c r="H816" t="n">
         <v>19737</v>
@@ -24062,7 +24062,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>37.5651435852051</v>
+        <v>37.5651473999023</v>
       </c>
       <c r="H817" t="n">
         <v>18022</v>
@@ -24091,7 +24091,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898178100586</v>
+        <v>37.7898139953613</v>
       </c>
       <c r="H818" t="n">
         <v>15517</v>
@@ -24149,7 +24149,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>38.5986442565918</v>
+        <v>38.5986404418945</v>
       </c>
       <c r="H820" t="n">
         <v>13029</v>
@@ -24178,7 +24178,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>39.3625183105469</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H821" t="n">
         <v>16005</v>
@@ -24207,7 +24207,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118705749512</v>
+        <v>39.8118667602539</v>
       </c>
       <c r="H822" t="n">
         <v>9284</v>
@@ -24381,7 +24381,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>39.721996307373</v>
+        <v>39.7220001220703</v>
       </c>
       <c r="H828" t="n">
         <v>19617</v>
@@ -24497,7 +24497,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638366699219</v>
+        <v>38.4638404846191</v>
       </c>
       <c r="H832" t="n">
         <v>15760</v>
@@ -24671,7 +24671,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620506286621</v>
+        <v>36.2620544433594</v>
       </c>
       <c r="H838" t="n">
         <v>20097</v>
@@ -24758,7 +24758,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448844909668</v>
+        <v>37.7448883056641</v>
       </c>
       <c r="H841" t="n">
         <v>59505</v>
@@ -24903,7 +24903,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>39.3625183105469</v>
+        <v>39.3625221252441</v>
       </c>
       <c r="H846" t="n">
         <v>19364</v>
@@ -25164,7 +25164,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1598968505859</v>
+        <v>41.1599006652832</v>
       </c>
       <c r="H855" t="n">
         <v>12496</v>
@@ -25251,7 +25251,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.5308151245117</v>
+        <v>40.5308113098145</v>
       </c>
       <c r="H858" t="n">
         <v>18769</v>
@@ -25280,7 +25280,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.8004264831543</v>
+        <v>40.800422668457</v>
       </c>
       <c r="H859" t="n">
         <v>9064</v>
@@ -25367,7 +25367,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960189819336</v>
+        <v>40.3960151672363</v>
       </c>
       <c r="H862" t="n">
         <v>7355</v>
@@ -25512,7 +25512,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801597595215</v>
+        <v>40.9801635742188</v>
       </c>
       <c r="H867" t="n">
         <v>46233</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25599,7 +25599,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H870" t="n">
         <v>6994</v>
@@ -25657,7 +25657,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H872" t="n">
         <v>17923</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237823486328</v>
+        <v>41.9237861633301</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25715,7 +25715,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H874" t="n">
         <v>8152</v>
@@ -25889,7 +25889,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H880" t="n">
         <v>11127</v>
@@ -26005,7 +26005,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484565734863</v>
+        <v>42.1484603881836</v>
       </c>
       <c r="H884" t="n">
         <v>7700</v>
@@ -26063,7 +26063,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.6876678466797</v>
+        <v>42.687671661377</v>
       </c>
       <c r="H886" t="n">
         <v>16328</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26498,7 +26498,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H901" t="n">
         <v>12391</v>
@@ -26672,7 +26672,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.619010925293</v>
+        <v>48.6190071105957</v>
       </c>
       <c r="H907" t="n">
         <v>2482</v>
@@ -26759,7 +26759,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>48.1696586608887</v>
+        <v>48.1696624755859</v>
       </c>
       <c r="H910" t="n">
         <v>7813</v>
@@ -26788,7 +26788,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H911" t="n">
         <v>10719</v>
@@ -26875,7 +26875,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>46.5520210266113</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H914" t="n">
         <v>6338</v>
@@ -26904,7 +26904,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H915" t="n">
         <v>6803</v>
@@ -27049,7 +27049,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H920" t="n">
         <v>13604</v>
@@ -27136,7 +27136,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603759765625</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H923" t="n">
         <v>10806</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.9115028381348</v>
+        <v>46.911506652832</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27223,7 +27223,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H926" t="n">
         <v>16584</v>
@@ -27310,7 +27310,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H929" t="n">
         <v>14814</v>
@@ -27339,7 +27339,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278297424316</v>
+        <v>49.4278259277344</v>
       </c>
       <c r="H930" t="n">
         <v>11631</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216323852539</v>
+        <v>46.8216285705566</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27832,7 +27832,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H947" t="n">
         <v>9996</v>
@@ -27861,7 +27861,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H948" t="n">
         <v>6269</v>
@@ -27890,7 +27890,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811065673828</v>
+        <v>47.1811103820801</v>
       </c>
       <c r="H949" t="n">
         <v>4814</v>
@@ -27919,7 +27919,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722915649414</v>
       </c>
       <c r="H950" t="n">
         <v>5714</v>
@@ -27977,7 +27977,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>46.5520210266113</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H952" t="n">
         <v>12756</v>
@@ -28064,7 +28064,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H955" t="n">
         <v>6413</v>
@@ -28238,7 +28238,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722877502441</v>
+        <v>46.3722915649414</v>
       </c>
       <c r="H961" t="n">
         <v>12589</v>
@@ -28499,7 +28499,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>47.0013732910156</v>
+        <v>47.0013694763184</v>
       </c>
       <c r="H970" t="n">
         <v>15181</v>
@@ -28528,7 +28528,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>46.5520210266113</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H971" t="n">
         <v>12379</v>
@@ -28557,7 +28557,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G972" t="n">
-        <v>46.5520210266113</v>
+        <v>46.5520248413086</v>
       </c>
       <c r="H972" t="n">
         <v>10030</v>
@@ -28615,7 +28615,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H974" t="n">
         <v>16723</v>
@@ -28731,7 +28731,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.462158203125</v>
+        <v>46.4621543884277</v>
       </c>
       <c r="H978" t="n">
         <v>18485</v>
@@ -28760,7 +28760,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995872497559</v>
+        <v>44.7995834350586</v>
       </c>
       <c r="H979" t="n">
         <v>30230</v>
@@ -28789,7 +28789,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>45.6533355712891</v>
+        <v>45.6533393859863</v>
       </c>
       <c r="H980" t="n">
         <v>105542</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.1925506591797</v>
+        <v>46.192554473877</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28963,7 +28963,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.3837280273438</v>
+        <v>45.383731842041</v>
       </c>
       <c r="H986" t="n">
         <v>9545</v>
@@ -29253,7 +29253,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>43.7211608886719</v>
+        <v>43.7211647033691</v>
       </c>
       <c r="H996" t="n">
         <v>34066</v>
@@ -68745,7 +68745,7 @@
         <v>1.65699994564056</v>
       </c>
       <c r="E2358" t="n">
-        <v>1.60099995136261</v>
+        <v>1.60000002384186</v>
       </c>
       <c r="F2358" t="n">
         <v>1.60000002384186</v>
@@ -68757,6 +68757,35 @@
         <v>614727</v>
       </c>
       <c r="I2358" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2359" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2359" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>1.71599996089935</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2359" t="n">
+        <v>1.692999958992</v>
+      </c>
+      <c r="G2359" t="n">
+        <v>1.692999958992</v>
+      </c>
+      <c r="H2359" t="n">
+        <v>1532317</v>
+      </c>
+      <c r="I2359" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503227233887</v>
+        <v>44.8503189086914</v>
       </c>
       <c r="H2" t="n">
         <v>2040000</v>
@@ -485,7 +485,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H4" t="n">
         <v>315019</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320495605469</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318458557129</v>
+        <v>46.7318496704102</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -630,7 +630,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631210327148</v>
+        <v>46.8631172180176</v>
       </c>
       <c r="H9" t="n">
         <v>27464</v>
@@ -659,7 +659,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H10" t="n">
         <v>24546</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320495605469</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -717,7 +717,7 @@
         <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H12" t="n">
         <v>19418</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -833,7 +833,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632171630859</v>
+        <v>47.5632209777832</v>
       </c>
       <c r="H16" t="n">
         <v>20120</v>
@@ -862,7 +862,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319496154785</v>
+        <v>47.4319534301758</v>
       </c>
       <c r="H17" t="n">
         <v>9145</v>
@@ -1007,7 +1007,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.4693069458008</v>
+        <v>46.469310760498</v>
       </c>
       <c r="H22" t="n">
         <v>15015</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131652832031</v>
+        <v>47.2131729125977</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1065,7 +1065,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G24" t="n">
-        <v>46.6880874633789</v>
+        <v>46.6880912780762</v>
       </c>
       <c r="H24" t="n">
         <v>35958</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443367004395</v>
+        <v>46.6443328857422</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1239,7 +1239,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692031860352</v>
+        <v>45.7692108154297</v>
       </c>
       <c r="H30" t="n">
         <v>7291</v>
@@ -1268,7 +1268,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.513069152832</v>
+        <v>46.5130653381348</v>
       </c>
       <c r="H31" t="n">
         <v>8478</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.681697845459</v>
+        <v>45.6816940307617</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881988525391</v>
+        <v>47.3881950378418</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756080627441</v>
+        <v>46.7756042480469</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1558,7 +1558,7 @@
         <v>54</v>
       </c>
       <c r="G41" t="n">
-        <v>47.2569313049316</v>
+        <v>47.2569274902344</v>
       </c>
       <c r="H41" t="n">
         <v>7500</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320533752441</v>
+        <v>48.1320495605469</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1674,7 +1674,7 @@
         <v>54.75</v>
       </c>
       <c r="G45" t="n">
-        <v>47.9132690429688</v>
+        <v>47.913272857666</v>
       </c>
       <c r="H45" t="n">
         <v>55518</v>
@@ -1906,7 +1906,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507377624512</v>
+        <v>47.6507339477539</v>
       </c>
       <c r="H53" t="n">
         <v>13389</v>
@@ -1935,7 +1935,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G54" t="n">
-        <v>47.519458770752</v>
+        <v>47.5194625854492</v>
       </c>
       <c r="H54" t="n">
         <v>28001</v>
@@ -1993,7 +1993,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445442199707</v>
+        <v>48.0445365905762</v>
       </c>
       <c r="H56" t="n">
         <v>39379</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135803222656</v>
+        <v>50.0135765075684</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2051,7 +2051,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.1950035095215</v>
+        <v>51.1949996948242</v>
       </c>
       <c r="H58" t="n">
         <v>44749</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953109741211</v>
+        <v>53.2953147888184</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266860961914</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2196,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="G63" t="n">
-        <v>54.2579498291016</v>
+        <v>54.2579536437988</v>
       </c>
       <c r="H63" t="n">
         <v>40240</v>
@@ -2254,7 +2254,7 @@
         <v>62.5</v>
       </c>
       <c r="G65" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H65" t="n">
         <v>17831</v>
@@ -2283,7 +2283,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769378662109</v>
+        <v>55.8769340515137</v>
       </c>
       <c r="H66" t="n">
         <v>30641</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.2589836120605</v>
+        <v>61.258975982666</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965408325195</v>
+        <v>61.6965446472168</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965408325195</v>
+        <v>61.6965446472168</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339981079102</v>
+        <v>61.4339942932129</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964370727539</v>
+        <v>60.9964332580566</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2602,7 +2602,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399955749512</v>
+        <v>59.6399879455566</v>
       </c>
       <c r="H77" t="n">
         <v>24608</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275085449219</v>
+        <v>59.7275009155273</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.3838500976562</v>
+        <v>60.383846282959</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2689,7 +2689,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775604248047</v>
+        <v>60.0775566101074</v>
       </c>
       <c r="H80" t="n">
         <v>17247</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276084899902</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2747,7 +2747,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026306152344</v>
+        <v>60.6026344299316</v>
       </c>
       <c r="H82" t="n">
         <v>33403</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214111328125</v>
+        <v>60.8214149475098</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898284912109</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2979,7 +2979,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3273048400879</v>
+        <v>58.3272933959961</v>
       </c>
       <c r="H90" t="n">
         <v>24556</v>
@@ -3008,7 +3008,7 @@
         <v>66.25</v>
       </c>
       <c r="G91" t="n">
-        <v>57.977237701416</v>
+        <v>57.9772453308105</v>
       </c>
       <c r="H91" t="n">
         <v>27501</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.071159362793</v>
+        <v>59.0711555480957</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3095,7 +3095,7 @@
         <v>67</v>
       </c>
       <c r="G94" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H94" t="n">
         <v>25066</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H97" t="n">
         <v>26035</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.583438873291</v>
+        <v>57.5834350585938</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708518981934</v>
+        <v>56.9708442687988</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3356,7 +3356,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396881103516</v>
       </c>
       <c r="H103" t="n">
         <v>43096</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3414,7 +3414,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712631225586</v>
+        <v>59.7712593078613</v>
       </c>
       <c r="H105" t="n">
         <v>21082</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276084899902</v>
+        <v>60.4276123046875</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
       <c r="G108" t="n">
-        <v>58.6335868835449</v>
+        <v>58.6335945129395</v>
       </c>
       <c r="H108" t="n">
         <v>43417</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898323059082</v>
+        <v>58.5898284912109</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3559,7 +3559,7 @@
         <v>64.75</v>
       </c>
       <c r="G110" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H110" t="n">
         <v>57326</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456665039062</v>
+        <v>55.7456703186035</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3733,7 +3733,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.670955657959</v>
+        <v>57.6709518432617</v>
       </c>
       <c r="H116" t="n">
         <v>53938</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897361755371</v>
+        <v>57.8897323608398</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899475097656</v>
+        <v>59.2899360656738</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461738586426</v>
+        <v>59.2461814880371</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962295532227</v>
+        <v>59.5962257385254</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960258483887</v>
+        <v>58.1960220336914</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397880554199</v>
+        <v>58.2397918701172</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4081,7 +4081,7 @@
         <v>64.75</v>
       </c>
       <c r="G128" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H128" t="n">
         <v>47008</v>
@@ -4110,7 +4110,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.270751953125</v>
+        <v>56.2707481384277</v>
       </c>
       <c r="H129" t="n">
         <v>14664</v>
@@ -4197,7 +4197,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146026611328</v>
+        <v>57.0146102905273</v>
       </c>
       <c r="H132" t="n">
         <v>14544</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.620792388916</v>
+        <v>56.6207962036133</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4284,7 +4284,7 @@
         <v>65.3499984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>57.189624786377</v>
+        <v>57.1896286010742</v>
       </c>
       <c r="H135" t="n">
         <v>6298</v>
@@ -4313,7 +4313,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.539680480957</v>
+        <v>57.5396881103516</v>
       </c>
       <c r="H136" t="n">
         <v>78309</v>
@@ -4342,7 +4342,7 @@
         <v>64.75</v>
       </c>
       <c r="G137" t="n">
-        <v>56.66455078125</v>
+        <v>56.6645545959473</v>
       </c>
       <c r="H137" t="n">
         <v>26876</v>
@@ -4371,7 +4371,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>56.752067565918</v>
+        <v>56.7520637512207</v>
       </c>
       <c r="H138" t="n">
         <v>16052</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831352233887</v>
+        <v>55.4831275939941</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4458,7 +4458,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>56.3582572937012</v>
+        <v>56.3582611083984</v>
       </c>
       <c r="H141" t="n">
         <v>23525</v>
@@ -4487,7 +4487,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.2643547058105</v>
+        <v>55.264347076416</v>
       </c>
       <c r="H142" t="n">
         <v>21545</v>
@@ -4516,7 +4516,7 @@
         <v>62.5</v>
       </c>
       <c r="G143" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H143" t="n">
         <v>12997</v>
@@ -4545,7 +4545,7 @@
         <v>62.5</v>
       </c>
       <c r="G144" t="n">
-        <v>54.6955108642578</v>
+        <v>54.6955146789551</v>
       </c>
       <c r="H144" t="n">
         <v>26633</v>
@@ -4603,7 +4603,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G146" t="n">
-        <v>53.470329284668</v>
+        <v>53.4703330993652</v>
       </c>
       <c r="H146" t="n">
         <v>17711</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394729614258</v>
+        <v>56.1394805908203</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4690,7 +4690,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H149" t="n">
         <v>19902</v>
@@ -4777,7 +4777,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H152" t="n">
         <v>6908</v>
@@ -4806,7 +4806,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H153" t="n">
         <v>14177</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266860961914</v>
+        <v>54.1266784667969</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4864,7 +4864,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578498840332</v>
+        <v>53.5578536987305</v>
       </c>
       <c r="H155" t="n">
         <v>11308</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326721191406</v>
+        <v>52.3326644897461</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -4980,7 +4980,7 @@
         <v>59.5</v>
       </c>
       <c r="G159" t="n">
-        <v>52.0701332092285</v>
+        <v>52.0701293945312</v>
       </c>
       <c r="H159" t="n">
         <v>10594</v>
@@ -5009,7 +5009,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G160" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H160" t="n">
         <v>11068</v>
@@ -5096,7 +5096,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.357234954834</v>
+        <v>49.3572387695312</v>
       </c>
       <c r="H163" t="n">
         <v>14934</v>
@@ -5154,7 +5154,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.7883949279785</v>
+        <v>48.788402557373</v>
       </c>
       <c r="H165" t="n">
         <v>49976</v>
@@ -5212,7 +5212,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G167" t="n">
-        <v>52.3764190673828</v>
+        <v>52.3764228820801</v>
       </c>
       <c r="H167" t="n">
         <v>20718</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889137268066</v>
+        <v>52.2889099121094</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5473,7 +5473,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511451721191</v>
+        <v>50.4511413574219</v>
       </c>
       <c r="H176" t="n">
         <v>8990</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510414123535</v>
+        <v>49.7510375976562</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5618,7 +5618,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571273803711</v>
+        <v>48.6571311950684</v>
       </c>
       <c r="H181" t="n">
         <v>8552</v>
@@ -5676,7 +5676,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G183" t="n">
-        <v>50.8449516296387</v>
+        <v>50.8449478149414</v>
       </c>
       <c r="H183" t="n">
         <v>12299</v>
@@ -5705,7 +5705,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137840270996</v>
+        <v>51.4137878417969</v>
       </c>
       <c r="H184" t="n">
         <v>13554</v>
@@ -5763,7 +5763,7 @@
         <v>60.5499992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>52.9890098571777</v>
+        <v>52.989013671875</v>
       </c>
       <c r="H186" t="n">
         <v>12495</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.9516525268555</v>
+        <v>53.95166015625</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5966,7 +5966,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328758239746</v>
+        <v>53.7328720092773</v>
       </c>
       <c r="H193" t="n">
         <v>9212</v>
@@ -5995,7 +5995,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015045166016</v>
+        <v>52.9015007019043</v>
       </c>
       <c r="H194" t="n">
         <v>32354</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2077903747559</v>
+        <v>53.2078018188477</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2077903747559</v>
+        <v>53.2078018188477</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6140,7 +6140,7 @@
         <v>64.0500030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>56.0519714355469</v>
+        <v>56.0519676208496</v>
       </c>
       <c r="H199" t="n">
         <v>8382</v>
@@ -6198,7 +6198,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893287658691</v>
       </c>
       <c r="H201" t="n">
         <v>6238</v>
@@ -6256,7 +6256,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142951965332</v>
+        <v>54.9142990112305</v>
       </c>
       <c r="H203" t="n">
         <v>6842</v>
@@ -6285,7 +6285,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891136169434</v>
+        <v>53.6891174316406</v>
       </c>
       <c r="H204" t="n">
         <v>7160</v>
@@ -6343,7 +6343,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.907901763916</v>
+        <v>53.9078941345215</v>
       </c>
       <c r="H206" t="n">
         <v>2508</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390693664551</v>
+        <v>53.3390655517578</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6459,7 +6459,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.345458984375</v>
+        <v>54.3454627990723</v>
       </c>
       <c r="H210" t="n">
         <v>5210</v>
@@ -6488,7 +6488,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893211364746</v>
+        <v>55.0893287658691</v>
       </c>
       <c r="H211" t="n">
         <v>25353</v>
@@ -6546,7 +6546,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>52.4639434814453</v>
+        <v>52.463939666748</v>
       </c>
       <c r="H213" t="n">
         <v>17630</v>
@@ -6575,7 +6575,7 @@
         <v>57</v>
       </c>
       <c r="G214" t="n">
-        <v>49.8823051452637</v>
+        <v>49.8823089599609</v>
       </c>
       <c r="H214" t="n">
         <v>29362</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8695182800293</v>
+        <v>47.869514465332</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.617992401123</v>
+        <v>44.6179885864258</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6691,7 +6691,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.504150390625</v>
+        <v>45.5041427612305</v>
       </c>
       <c r="H218" t="n">
         <v>23030</v>
@@ -6749,7 +6749,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358428955078</v>
+        <v>46.0358390808105</v>
       </c>
       <c r="H220" t="n">
         <v>30045</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6865,7 +6865,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G224" t="n">
-        <v>44.839527130127</v>
+        <v>44.8395309448242</v>
       </c>
       <c r="H224" t="n">
         <v>24015</v>
@@ -6923,7 +6923,7 @@
         <v>50.5</v>
       </c>
       <c r="G226" t="n">
-        <v>44.7509155273438</v>
+        <v>44.7509117126465</v>
       </c>
       <c r="H226" t="n">
         <v>9809</v>
@@ -6952,7 +6952,7 @@
         <v>49.4249992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>43.7982902526855</v>
+        <v>43.7982940673828</v>
       </c>
       <c r="H227" t="n">
         <v>8139</v>
@@ -6981,7 +6981,7 @@
         <v>48.0750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>42.6019859313965</v>
+        <v>42.6019821166992</v>
       </c>
       <c r="H228" t="n">
         <v>16693</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7039,7 +7039,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G230" t="n">
-        <v>42.4025955200195</v>
+        <v>42.4025993347168</v>
       </c>
       <c r="H230" t="n">
         <v>9214</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7242,7 +7242,7 @@
         <v>54.5</v>
       </c>
       <c r="G237" t="n">
-        <v>48.295539855957</v>
+        <v>48.2955360412598</v>
       </c>
       <c r="H237" t="n">
         <v>20676</v>
@@ -7358,7 +7358,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>49.226001739502</v>
+        <v>49.2260055541992</v>
       </c>
       <c r="H241" t="n">
         <v>21035</v>
@@ -7416,7 +7416,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>47.9410743713379</v>
+        <v>47.9410781860352</v>
       </c>
       <c r="H243" t="n">
         <v>19274</v>
@@ -7445,7 +7445,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H244" t="n">
         <v>15929</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.9158515930176</v>
+        <v>48.915843963623</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7532,7 +7532,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>49.137393951416</v>
+        <v>49.1373901367188</v>
       </c>
       <c r="H247" t="n">
         <v>16775</v>
@@ -7561,7 +7561,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983177185059</v>
+        <v>50.9983139038086</v>
       </c>
       <c r="H248" t="n">
         <v>36235</v>
@@ -7590,7 +7590,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>51.8844757080078</v>
+        <v>51.8844718933105</v>
       </c>
       <c r="H249" t="n">
         <v>15149</v>
@@ -7619,7 +7619,7 @@
         <v>58</v>
       </c>
       <c r="G250" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H250" t="n">
         <v>14687</v>
@@ -7764,7 +7764,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.3398475646973</v>
+        <v>48.33984375</v>
       </c>
       <c r="H255" t="n">
         <v>7923</v>
@@ -7822,7 +7822,7 @@
         <v>54</v>
       </c>
       <c r="G257" t="n">
-        <v>47.852466583252</v>
+        <v>47.8524627685547</v>
       </c>
       <c r="H257" t="n">
         <v>5700</v>
@@ -7909,7 +7909,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>46.7004585266113</v>
+        <v>46.7004547119141</v>
       </c>
       <c r="H260" t="n">
         <v>8510</v>
@@ -8141,7 +8141,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927581787109</v>
+        <v>45.5927619934082</v>
       </c>
       <c r="H268" t="n">
         <v>9230</v>
@@ -8199,7 +8199,7 @@
         <v>51</v>
       </c>
       <c r="G270" t="n">
-        <v>45.1939926147461</v>
+        <v>45.1939888000488</v>
       </c>
       <c r="H270" t="n">
         <v>9794</v>
@@ -8286,7 +8286,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7699928283691</v>
+        <v>45.7700004577637</v>
       </c>
       <c r="H273" t="n">
         <v>5066</v>
@@ -8315,7 +8315,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586120605469</v>
+        <v>45.8586082458496</v>
       </c>
       <c r="H274" t="n">
         <v>4374</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8576,7 +8576,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570648193359</v>
+        <v>42.7570571899414</v>
       </c>
       <c r="H283" t="n">
         <v>10993</v>
@@ -8663,7 +8663,7 @@
         <v>49</v>
       </c>
       <c r="G286" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H286" t="n">
         <v>13125</v>
@@ -8692,7 +8692,7 @@
         <v>49.125</v>
       </c>
       <c r="G287" t="n">
-        <v>43.5324440002441</v>
+        <v>43.5324478149414</v>
       </c>
       <c r="H287" t="n">
         <v>11020</v>
@@ -8721,7 +8721,7 @@
         <v>48.875</v>
       </c>
       <c r="G288" t="n">
-        <v>43.310905456543</v>
+        <v>43.3109092712402</v>
       </c>
       <c r="H288" t="n">
         <v>4421</v>
@@ -8750,7 +8750,7 @@
         <v>48.7750015258789</v>
       </c>
       <c r="G289" t="n">
-        <v>43.222297668457</v>
+        <v>43.2222938537598</v>
       </c>
       <c r="H289" t="n">
         <v>13085</v>
@@ -8924,7 +8924,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H295" t="n">
         <v>8398</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.244441986084</v>
+        <v>43.2444458007812</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9098,7 +9098,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H301" t="n">
         <v>1288</v>
@@ -9156,7 +9156,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>43.5102958679199</v>
+        <v>43.5102920532227</v>
       </c>
       <c r="H303" t="n">
         <v>15525</v>
@@ -9185,7 +9185,7 @@
         <v>49</v>
       </c>
       <c r="G304" t="n">
-        <v>43.4216766357422</v>
+        <v>43.4216804504395</v>
       </c>
       <c r="H304" t="n">
         <v>13328</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785957336426</v>
+        <v>42.9785995483398</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9330,7 +9330,7 @@
         <v>47.5</v>
       </c>
       <c r="G309" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H309" t="n">
         <v>26061</v>
@@ -9359,7 +9359,7 @@
         <v>46.625</v>
       </c>
       <c r="G310" t="n">
-        <v>41.3170509338379</v>
+        <v>41.3170547485352</v>
       </c>
       <c r="H310" t="n">
         <v>20434</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410545349121</v>
+        <v>40.7410507202148</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638198852539</v>
+        <v>40.5638236999512</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.9465866088867</v>
+        <v>38.946590423584</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9591,7 +9591,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>39.6112022399902</v>
+        <v>39.6112060546875</v>
       </c>
       <c r="H318" t="n">
         <v>13054</v>
@@ -9620,7 +9620,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782791137695</v>
+        <v>39.4782829284668</v>
       </c>
       <c r="H319" t="n">
         <v>3338</v>
@@ -9649,7 +9649,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>39.9213638305664</v>
+        <v>39.9213562011719</v>
       </c>
       <c r="H320" t="n">
         <v>5411</v>
@@ -9736,7 +9736,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H323" t="n">
         <v>2457</v>
@@ -9794,7 +9794,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H325" t="n">
         <v>6799</v>
@@ -9852,7 +9852,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H327" t="n">
         <v>5952</v>
@@ -9939,7 +9939,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>40.0099716186523</v>
+        <v>40.0099754333496</v>
       </c>
       <c r="H330" t="n">
         <v>3763</v>
@@ -9968,7 +9968,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.2758255004883</v>
+        <v>40.275821685791</v>
       </c>
       <c r="H331" t="n">
         <v>6546</v>
@@ -10026,7 +10026,7 @@
         <v>47.5</v>
       </c>
       <c r="G333" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H333" t="n">
         <v>2702</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247512817383</v>
+        <v>42.4247550964355</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690589904785</v>
+        <v>42.4690551757812</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.0069046020508</v>
+        <v>41.006908416748</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10171,7 +10171,7 @@
         <v>47.5</v>
       </c>
       <c r="G338" t="n">
-        <v>42.0924453735352</v>
+        <v>42.0924415588379</v>
       </c>
       <c r="H338" t="n">
         <v>2331</v>
@@ -10200,7 +10200,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462936401367</v>
+        <v>42.6462860107422</v>
       </c>
       <c r="H339" t="n">
         <v>10608</v>
@@ -10287,7 +10287,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>42.4912109375</v>
+        <v>42.4912147521973</v>
       </c>
       <c r="H342" t="n">
         <v>5266</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.0069046020508</v>
+        <v>41.006908416748</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10374,7 +10374,7 @@
         <v>46.25</v>
       </c>
       <c r="G345" t="n">
-        <v>40.984748840332</v>
+        <v>40.9847450256348</v>
       </c>
       <c r="H345" t="n">
         <v>10026</v>
@@ -10403,7 +10403,7 @@
         <v>44.75</v>
       </c>
       <c r="G346" t="n">
-        <v>39.6555137634277</v>
+        <v>39.6555099487305</v>
       </c>
       <c r="H346" t="n">
         <v>10252</v>
@@ -10461,7 +10461,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G348" t="n">
-        <v>38.6807479858398</v>
+        <v>38.6807441711426</v>
       </c>
       <c r="H348" t="n">
         <v>9316</v>
@@ -10519,7 +10519,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>42.6684494018555</v>
+        <v>42.6684455871582</v>
       </c>
       <c r="H350" t="n">
         <v>39393</v>
@@ -10548,7 +10548,7 @@
         <v>49.3250007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>43.7096824645996</v>
+        <v>43.7096786499023</v>
       </c>
       <c r="H351" t="n">
         <v>27897</v>
@@ -10577,7 +10577,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H352" t="n">
         <v>69766</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764549255371</v>
+        <v>47.2764625549316</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10722,7 +10722,7 @@
         <v>53.25</v>
       </c>
       <c r="G357" t="n">
-        <v>47.1878471374512</v>
+        <v>47.1878433227539</v>
       </c>
       <c r="H357" t="n">
         <v>7547</v>
@@ -10751,7 +10751,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>46.3459930419922</v>
+        <v>46.3459968566895</v>
       </c>
       <c r="H358" t="n">
         <v>34572</v>
@@ -10780,7 +10780,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.8333778381348</v>
+        <v>46.833381652832</v>
       </c>
       <c r="H359" t="n">
         <v>4295</v>
@@ -10838,7 +10838,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964500427246</v>
+        <v>44.3964462280273</v>
       </c>
       <c r="H361" t="n">
         <v>27594</v>
@@ -10896,7 +10896,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>44.0419921875</v>
+        <v>44.0419883728027</v>
       </c>
       <c r="H363" t="n">
         <v>1254</v>
@@ -10925,7 +10925,7 @@
         <v>48.9249992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>43.3552131652832</v>
+        <v>43.3552169799805</v>
       </c>
       <c r="H364" t="n">
         <v>1387</v>
@@ -10954,7 +10954,7 @@
         <v>46.375</v>
       </c>
       <c r="G365" t="n">
-        <v>41.0955200195312</v>
+        <v>41.095516204834</v>
       </c>
       <c r="H365" t="n">
         <v>6971</v>
@@ -10983,7 +10983,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973564147949</v>
+        <v>40.4973602294922</v>
       </c>
       <c r="H366" t="n">
         <v>12931</v>
@@ -11012,7 +11012,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992042541504</v>
+        <v>39.8992118835449</v>
       </c>
       <c r="H367" t="n">
         <v>21291</v>
@@ -11070,7 +11070,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770523071289</v>
+        <v>39.8770484924316</v>
       </c>
       <c r="H369" t="n">
         <v>22056</v>
@@ -11099,7 +11099,7 @@
         <v>45.1749992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>40.0321311950684</v>
+        <v>40.0321273803711</v>
       </c>
       <c r="H370" t="n">
         <v>10048</v>
@@ -11128,7 +11128,7 @@
         <v>46.2249984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>40.9625930786133</v>
+        <v>40.962589263916</v>
       </c>
       <c r="H371" t="n">
         <v>7882</v>
@@ -11360,7 +11360,7 @@
         <v>56.75</v>
       </c>
       <c r="G379" t="n">
-        <v>50.2893905639648</v>
+        <v>50.2893943786621</v>
       </c>
       <c r="H379" t="n">
         <v>16967</v>
@@ -11389,7 +11389,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H380" t="n">
         <v>62651</v>
@@ -11418,7 +11418,7 @@
         <v>58</v>
       </c>
       <c r="G381" t="n">
-        <v>51.397087097168</v>
+        <v>51.3970909118652</v>
       </c>
       <c r="H381" t="n">
         <v>8438</v>
@@ -11447,7 +11447,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>51.7958564758301</v>
+        <v>51.7958602905273</v>
       </c>
       <c r="H382" t="n">
         <v>4697</v>
@@ -11476,7 +11476,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>51.352783203125</v>
+        <v>51.3527793884277</v>
       </c>
       <c r="H383" t="n">
         <v>3458</v>
@@ -11505,7 +11505,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>50.688159942627</v>
+        <v>50.6881637573242</v>
       </c>
       <c r="H384" t="n">
         <v>5575</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121597290039</v>
+        <v>50.1121635437012</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11563,7 +11563,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>49.3589324951172</v>
+        <v>49.3589286804199</v>
       </c>
       <c r="H386" t="n">
         <v>5737</v>
@@ -11592,7 +11592,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>49.757698059082</v>
+        <v>49.7577018737793</v>
       </c>
       <c r="H387" t="n">
         <v>12225</v>
@@ -11708,7 +11708,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G391" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H391" t="n">
         <v>35580</v>
@@ -11766,7 +11766,7 @@
         <v>59.5</v>
       </c>
       <c r="G393" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H393" t="n">
         <v>9144</v>
@@ -11795,7 +11795,7 @@
         <v>59.5</v>
       </c>
       <c r="G394" t="n">
-        <v>52.7263259887695</v>
+        <v>52.7263221740723</v>
       </c>
       <c r="H394" t="n">
         <v>11783</v>
@@ -11853,7 +11853,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G396" t="n">
-        <v>53.0364723205566</v>
+        <v>53.0364761352539</v>
       </c>
       <c r="H396" t="n">
         <v>15537</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555648803711</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11911,7 +11911,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466377258301</v>
+        <v>53.3466300964355</v>
       </c>
       <c r="H398" t="n">
         <v>16109</v>
@@ -11940,7 +11940,7 @@
         <v>59.9500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>53.1250991821289</v>
+        <v>53.1250953674316</v>
       </c>
       <c r="H399" t="n">
         <v>11868</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657112121582</v>
+        <v>54.3657150268555</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12027,7 +12027,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G402" t="n">
-        <v>55.2961845397949</v>
+        <v>55.2961807250977</v>
       </c>
       <c r="H402" t="n">
         <v>18544</v>
@@ -12056,7 +12056,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164924621582</v>
       </c>
       <c r="H403" t="n">
         <v>55252</v>
@@ -12085,7 +12085,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.6124839782715</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H404" t="n">
         <v>12420</v>
@@ -12143,7 +12143,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>52.7706336975098</v>
+        <v>52.7706298828125</v>
       </c>
       <c r="H406" t="n">
         <v>16569</v>
@@ -12172,7 +12172,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.6124839782715</v>
+        <v>53.612476348877</v>
       </c>
       <c r="H407" t="n">
         <v>16902</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555648803711</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12288,7 +12288,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001853942871</v>
+        <v>57.6001892089844</v>
       </c>
       <c r="H411" t="n">
         <v>34918</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.157112121582</v>
+        <v>57.1571083068848</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12404,7 +12404,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H415" t="n">
         <v>39195</v>
@@ -12433,7 +12433,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>57.9546508789062</v>
+        <v>57.954647064209</v>
       </c>
       <c r="H416" t="n">
         <v>19036</v>
@@ -12462,7 +12462,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863471984863</v>
+        <v>58.4863433837891</v>
       </c>
       <c r="H417" t="n">
         <v>56533</v>
@@ -12520,7 +12520,7 @@
         <v>63.6500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>56.4038772583008</v>
+        <v>56.4038734436035</v>
       </c>
       <c r="H419" t="n">
         <v>16100</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12636,7 +12636,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.087574005127</v>
+        <v>58.0875778198242</v>
       </c>
       <c r="H423" t="n">
         <v>4303</v>
@@ -12723,7 +12723,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>57.6888046264648</v>
+        <v>57.6888008117676</v>
       </c>
       <c r="H426" t="n">
         <v>8138</v>
@@ -12868,7 +12868,7 @@
         <v>62</v>
       </c>
       <c r="G431" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H431" t="n">
         <v>6032</v>
@@ -12897,7 +12897,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>53.4795532226562</v>
+        <v>53.4795570373535</v>
       </c>
       <c r="H432" t="n">
         <v>11761</v>
@@ -12926,7 +12926,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>52.9921722412109</v>
+        <v>52.9921684265137</v>
       </c>
       <c r="H433" t="n">
         <v>13443</v>
@@ -12984,7 +12984,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0173988342285</v>
+        <v>52.0174026489258</v>
       </c>
       <c r="H435" t="n">
         <v>15195</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823387145996</v>
+        <v>56.1823348999023</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13129,7 +13129,7 @@
         <v>63.5</v>
       </c>
       <c r="G440" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H440" t="n">
         <v>5382</v>
@@ -13158,7 +13158,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G441" t="n">
-        <v>56.8026466369629</v>
+        <v>56.8026428222656</v>
       </c>
       <c r="H441" t="n">
         <v>16913</v>
@@ -13216,7 +13216,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G443" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392616271973</v>
       </c>
       <c r="H443" t="n">
         <v>5854</v>
@@ -13245,7 +13245,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H444" t="n">
         <v>6381</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140274047852</v>
+        <v>56.7140235900879</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13303,7 +13303,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H446" t="n">
         <v>7435</v>
@@ -13332,7 +13332,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798812866211</v>
+        <v>56.9798774719238</v>
       </c>
       <c r="H447" t="n">
         <v>11987</v>
@@ -13361,7 +13361,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>57.5115699768066</v>
+        <v>57.5115661621094</v>
       </c>
       <c r="H448" t="n">
         <v>5054</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.6254119873047</v>
+        <v>56.625415802002</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13419,7 +13419,7 @@
         <v>63.5</v>
       </c>
       <c r="G450" t="n">
-        <v>56.2709465026855</v>
+        <v>56.2709503173828</v>
       </c>
       <c r="H450" t="n">
         <v>5021</v>
@@ -13448,7 +13448,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164886474609</v>
+        <v>55.9164924621582</v>
       </c>
       <c r="H451" t="n">
         <v>1739</v>
@@ -13477,7 +13477,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>55.7392578125</v>
+        <v>55.7392616271973</v>
       </c>
       <c r="H452" t="n">
         <v>2949</v>
@@ -13564,7 +13564,7 @@
         <v>62</v>
       </c>
       <c r="G455" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H455" t="n">
         <v>4038</v>
@@ -13593,7 +13593,7 @@
         <v>62</v>
       </c>
       <c r="G456" t="n">
-        <v>54.9417152404785</v>
+        <v>54.9417190551758</v>
       </c>
       <c r="H456" t="n">
         <v>4488</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555648803711</v>
+        <v>54.0555572509766</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13651,7 +13651,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G458" t="n">
-        <v>53.7010955810547</v>
+        <v>53.701099395752</v>
       </c>
       <c r="H458" t="n">
         <v>31030</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.81494140625</v>
+        <v>52.8149337768555</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13796,7 +13796,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515487670898</v>
+        <v>51.7515525817871</v>
       </c>
       <c r="H463" t="n">
         <v>3551</v>
@@ -13854,7 +13854,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743217468262</v>
+        <v>51.5743179321289</v>
       </c>
       <c r="H465" t="n">
         <v>7910</v>
@@ -13999,7 +13999,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703094482422</v>
+        <v>49.2703132629395</v>
       </c>
       <c r="H470" t="n">
         <v>4310</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14376,7 +14376,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H483" t="n">
         <v>12430</v>
@@ -14434,7 +14434,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H485" t="n">
         <v>17601</v>
@@ -14463,7 +14463,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H486" t="n">
         <v>9392</v>
@@ -14550,7 +14550,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G489" t="n">
-        <v>49.9670372009277</v>
+        <v>49.967041015625</v>
       </c>
       <c r="H489" t="n">
         <v>5862</v>
@@ -14579,7 +14579,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H490" t="n">
         <v>8141</v>
@@ -14608,7 +14608,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075630187988</v>
+        <v>49.6075668334961</v>
       </c>
       <c r="H491" t="n">
         <v>27545</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14724,7 +14724,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.6974334716797</v>
+        <v>49.6974296569824</v>
       </c>
       <c r="H495" t="n">
         <v>6839</v>
@@ -14753,7 +14753,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H496" t="n">
         <v>19509</v>
@@ -14811,7 +14811,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H498" t="n">
         <v>9814</v>
@@ -14840,7 +14840,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H499" t="n">
         <v>8348</v>
@@ -14869,7 +14869,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H500" t="n">
         <v>16458</v>
@@ -14898,7 +14898,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H501" t="n">
         <v>10967</v>
@@ -14956,7 +14956,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G503" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H503" t="n">
         <v>7536</v>
@@ -15014,7 +15014,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477249145508</v>
+        <v>56.3477210998535</v>
       </c>
       <c r="H505" t="n">
         <v>11751</v>
@@ -15043,7 +15043,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666732788086</v>
+        <v>57.0666770935059</v>
       </c>
       <c r="H506" t="n">
         <v>15695</v>
@@ -15101,7 +15101,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G508" t="n">
-        <v>55.6287689208984</v>
+        <v>55.6287727355957</v>
       </c>
       <c r="H508" t="n">
         <v>3739</v>
@@ -15159,7 +15159,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186431884766</v>
+        <v>55.7186393737793</v>
       </c>
       <c r="H510" t="n">
         <v>7322</v>
@@ -15188,7 +15188,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H511" t="n">
         <v>8102</v>
@@ -15275,7 +15275,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>54.4604759216309</v>
+        <v>54.4604797363281</v>
       </c>
       <c r="H514" t="n">
         <v>1131</v>
@@ -15304,7 +15304,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.7415313720703</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H515" t="n">
         <v>5949</v>
@@ -15333,7 +15333,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H516" t="n">
         <v>4297</v>
@@ -15478,7 +15478,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163818359375</v>
+        <v>50.4163856506348</v>
       </c>
       <c r="H521" t="n">
         <v>4391</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137565612793</v>
+        <v>52.2137603759766</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15536,7 +15536,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>51.1353378295898</v>
+        <v>51.1353340148926</v>
       </c>
       <c r="H523" t="n">
         <v>2020</v>
@@ -15594,7 +15594,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.6974334716797</v>
+        <v>49.6974296569824</v>
       </c>
       <c r="H525" t="n">
         <v>128694</v>
@@ -15652,7 +15652,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H527" t="n">
         <v>23788</v>
@@ -15681,7 +15681,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722915649414</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H528" t="n">
         <v>16070</v>
@@ -15739,7 +15739,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H530" t="n">
         <v>3420</v>
@@ -15797,7 +15797,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H532" t="n">
         <v>10021</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15855,7 +15855,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H534" t="n">
         <v>7649</v>
@@ -15884,7 +15884,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H535" t="n">
         <v>48609</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603721618652</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16174,7 +16174,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H545" t="n">
         <v>22578</v>
@@ -16377,7 +16377,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H552" t="n">
         <v>18895</v>
@@ -16406,7 +16406,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H553" t="n">
         <v>2953</v>
@@ -16464,7 +16464,7 @@
         <v>52</v>
       </c>
       <c r="G555" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H555" t="n">
         <v>15322</v>
@@ -16493,7 +16493,7 @@
         <v>51</v>
       </c>
       <c r="G556" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H556" t="n">
         <v>14230</v>
@@ -16522,7 +16522,7 @@
         <v>51.5</v>
       </c>
       <c r="G557" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H557" t="n">
         <v>5027</v>
@@ -16667,7 +16667,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H562" t="n">
         <v>2385</v>
@@ -16696,7 +16696,7 @@
         <v>49</v>
       </c>
       <c r="G563" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H563" t="n">
         <v>20001</v>
@@ -16754,7 +16754,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G565" t="n">
-        <v>44.2154388427734</v>
+        <v>44.2154426574707</v>
       </c>
       <c r="H565" t="n">
         <v>3668</v>
@@ -16783,7 +16783,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H566" t="n">
         <v>2271</v>
@@ -16957,7 +16957,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H572" t="n">
         <v>12818</v>
@@ -17015,7 +17015,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H574" t="n">
         <v>4749</v>
@@ -17044,7 +17044,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>49.3379554748535</v>
+        <v>49.337963104248</v>
       </c>
       <c r="H575" t="n">
         <v>4241</v>
@@ -17131,7 +17131,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H578" t="n">
         <v>3272</v>
@@ -17160,7 +17160,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>48.3494033813477</v>
+        <v>48.3493995666504</v>
       </c>
       <c r="H579" t="n">
         <v>3967</v>
@@ -17189,7 +17189,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H580" t="n">
         <v>33442</v>
@@ -17218,7 +17218,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H581" t="n">
         <v>21771</v>
@@ -17450,7 +17450,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>52.4833641052246</v>
+        <v>52.4833679199219</v>
       </c>
       <c r="H589" t="n">
         <v>11027</v>
@@ -17479,7 +17479,7 @@
         <v>54</v>
       </c>
       <c r="G590" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H590" t="n">
         <v>18775</v>
@@ -17566,7 +17566,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>52.9327125549316</v>
+        <v>52.9327087402344</v>
       </c>
       <c r="H593" t="n">
         <v>40288</v>
@@ -17595,7 +17595,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>50.5961227416992</v>
+        <v>50.596118927002</v>
       </c>
       <c r="H594" t="n">
         <v>10198</v>
@@ -17624,7 +17624,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G595" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H595" t="n">
         <v>23195</v>
@@ -17653,7 +17653,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H596" t="n">
         <v>105612</v>
@@ -17682,7 +17682,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G597" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H597" t="n">
         <v>16627</v>
@@ -17711,7 +17711,7 @@
         <v>50.5</v>
       </c>
       <c r="G598" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H598" t="n">
         <v>23794</v>
@@ -17740,7 +17740,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H599" t="n">
         <v>28739</v>
@@ -17798,7 +17798,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G601" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H601" t="n">
         <v>31734</v>
@@ -17827,7 +17827,7 @@
         <v>50.5</v>
       </c>
       <c r="G602" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H602" t="n">
         <v>37767</v>
@@ -17856,7 +17856,7 @@
         <v>52.5</v>
       </c>
       <c r="G603" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H603" t="n">
         <v>36430</v>
@@ -17943,7 +17943,7 @@
         <v>51.5</v>
       </c>
       <c r="G606" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H606" t="n">
         <v>25059</v>
@@ -17972,7 +17972,7 @@
         <v>51</v>
       </c>
       <c r="G607" t="n">
-        <v>45.833080291748</v>
+        <v>45.8330764770508</v>
       </c>
       <c r="H607" t="n">
         <v>15227</v>
@@ -18001,7 +18001,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H608" t="n">
         <v>7231</v>
@@ -18088,7 +18088,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G611" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H611" t="n">
         <v>7555</v>
@@ -18204,7 +18204,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H615" t="n">
         <v>16713</v>
@@ -18233,7 +18233,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>49.1582221984863</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H616" t="n">
         <v>15159</v>
@@ -18262,7 +18262,7 @@
         <v>54</v>
       </c>
       <c r="G617" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H617" t="n">
         <v>22606</v>
@@ -18291,7 +18291,7 @@
         <v>55</v>
       </c>
       <c r="G618" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H618" t="n">
         <v>26603</v>
@@ -18349,7 +18349,7 @@
         <v>63</v>
       </c>
       <c r="G620" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H620" t="n">
         <v>114943</v>
@@ -18407,7 +18407,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>56.0781211853027</v>
+        <v>56.0781173706055</v>
       </c>
       <c r="H622" t="n">
         <v>32833</v>
@@ -18436,7 +18436,7 @@
         <v>61.5</v>
       </c>
       <c r="G623" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H623" t="n">
         <v>17457</v>
@@ -18465,7 +18465,7 @@
         <v>63</v>
       </c>
       <c r="G624" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H624" t="n">
         <v>9412</v>
@@ -18523,7 +18523,7 @@
         <v>59.5</v>
       </c>
       <c r="G626" t="n">
-        <v>53.471923828125</v>
+        <v>53.4719200134277</v>
       </c>
       <c r="H626" t="n">
         <v>14829</v>
@@ -18552,7 +18552,7 @@
         <v>60.5</v>
       </c>
       <c r="G627" t="n">
-        <v>54.3706130981445</v>
+        <v>54.37060546875</v>
       </c>
       <c r="H627" t="n">
         <v>23576</v>
@@ -18639,7 +18639,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>54.1010093688965</v>
+        <v>54.1010055541992</v>
       </c>
       <c r="H630" t="n">
         <v>9653</v>
@@ -18668,7 +18668,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>53.6516571044922</v>
+        <v>53.6516609191895</v>
       </c>
       <c r="H631" t="n">
         <v>10031</v>
@@ -18755,7 +18755,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G634" t="n">
-        <v>53.8313980102539</v>
+        <v>53.8314018249512</v>
       </c>
       <c r="H634" t="n">
         <v>16777</v>
@@ -18813,7 +18813,7 @@
         <v>61.5</v>
       </c>
       <c r="G636" t="n">
-        <v>55.2692947387695</v>
+        <v>55.2692985534668</v>
       </c>
       <c r="H636" t="n">
         <v>5975</v>
@@ -18842,7 +18842,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.550350189209</v>
+        <v>54.5503463745117</v>
       </c>
       <c r="H637" t="n">
         <v>10609</v>
@@ -18900,7 +18900,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H639" t="n">
         <v>13780</v>
@@ -18929,7 +18929,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>54.9996910095215</v>
+        <v>54.9996871948242</v>
       </c>
       <c r="H640" t="n">
         <v>3403</v>
@@ -19074,7 +19074,7 @@
         <v>59</v>
       </c>
       <c r="G645" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H645" t="n">
         <v>21588</v>
@@ -19103,7 +19103,7 @@
         <v>59</v>
       </c>
       <c r="G646" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H646" t="n">
         <v>10726</v>
@@ -19132,7 +19132,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G647" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H647" t="n">
         <v>18138</v>
@@ -19190,7 +19190,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>52.6631011962891</v>
+        <v>52.6631050109863</v>
       </c>
       <c r="H649" t="n">
         <v>24403</v>
@@ -19248,7 +19248,7 @@
         <v>59</v>
       </c>
       <c r="G651" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H651" t="n">
         <v>22520</v>
@@ -19335,7 +19335,7 @@
         <v>59</v>
       </c>
       <c r="G654" t="n">
-        <v>53.022575378418</v>
+        <v>53.0225791931152</v>
       </c>
       <c r="H654" t="n">
         <v>27760</v>
@@ -19393,7 +19393,7 @@
         <v>63</v>
       </c>
       <c r="G656" t="n">
-        <v>56.6173286437988</v>
+        <v>56.6173324584961</v>
       </c>
       <c r="H656" t="n">
         <v>87829</v>
@@ -19422,7 +19422,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H657" t="n">
         <v>41152</v>
@@ -19451,7 +19451,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>56.7071914672852</v>
+        <v>56.7071952819824</v>
       </c>
       <c r="H658" t="n">
         <v>26511</v>
@@ -19509,7 +19509,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>54.7300834655762</v>
+        <v>54.7300872802734</v>
       </c>
       <c r="H660" t="n">
         <v>38065</v>
@@ -19538,7 +19538,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H661" t="n">
         <v>53551</v>
@@ -19596,7 +19596,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>53.7415313720703</v>
+        <v>53.741527557373</v>
       </c>
       <c r="H663" t="n">
         <v>43542</v>
@@ -19625,7 +19625,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>51.944149017334</v>
+        <v>51.9441528320312</v>
       </c>
       <c r="H664" t="n">
         <v>42179</v>
@@ -19654,7 +19654,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>50.8657264709473</v>
+        <v>50.8657302856445</v>
       </c>
       <c r="H665" t="n">
         <v>44030</v>
@@ -19683,7 +19683,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>49.3379554748535</v>
+        <v>49.337963104248</v>
       </c>
       <c r="H666" t="n">
         <v>33866</v>
@@ -19741,7 +19741,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>49.5176963806152</v>
+        <v>49.517692565918</v>
       </c>
       <c r="H668" t="n">
         <v>31289</v>
@@ -19799,7 +19799,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H670" t="n">
         <v>17071</v>
@@ -19915,7 +19915,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G674" t="n">
-        <v>33.116641998291</v>
+        <v>33.1166381835938</v>
       </c>
       <c r="H674" t="n">
         <v>38571</v>
@@ -20118,7 +20118,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>22.1077194213867</v>
+        <v>22.1077213287354</v>
       </c>
       <c r="H681" t="n">
         <v>123217</v>
@@ -20147,7 +20147,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>23.1861457824707</v>
+        <v>23.1861419677734</v>
       </c>
       <c r="H682" t="n">
         <v>57668</v>
@@ -20176,7 +20176,7 @@
         <v>27.5</v>
       </c>
       <c r="G683" t="n">
-        <v>24.7139129638672</v>
+        <v>24.7139148712158</v>
       </c>
       <c r="H683" t="n">
         <v>30853</v>
@@ -20234,7 +20234,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>25.7024688720703</v>
+        <v>25.7024707794189</v>
       </c>
       <c r="H685" t="n">
         <v>34700</v>
@@ -20263,7 +20263,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>24.9835186004639</v>
+        <v>24.9835205078125</v>
       </c>
       <c r="H686" t="n">
         <v>21534</v>
@@ -20292,7 +20292,7 @@
         <v>28.25</v>
       </c>
       <c r="G687" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H687" t="n">
         <v>17426</v>
@@ -20350,7 +20350,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>25.4328632354736</v>
+        <v>25.4328651428223</v>
       </c>
       <c r="H689" t="n">
         <v>33327</v>
@@ -20379,7 +20379,7 @@
         <v>26.25</v>
       </c>
       <c r="G690" t="n">
-        <v>23.59055519104</v>
+        <v>23.5905532836914</v>
       </c>
       <c r="H690" t="n">
         <v>49158</v>
@@ -20408,7 +20408,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>23.455753326416</v>
+        <v>23.4557514190674</v>
       </c>
       <c r="H691" t="n">
         <v>43298</v>
@@ -20437,7 +20437,7 @@
         <v>28.25</v>
       </c>
       <c r="G692" t="n">
-        <v>25.3879299163818</v>
+        <v>25.3879280090332</v>
       </c>
       <c r="H692" t="n">
         <v>106161</v>
@@ -20466,7 +20466,7 @@
         <v>30.75</v>
       </c>
       <c r="G693" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H693" t="n">
         <v>49337</v>
@@ -20553,7 +20553,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>24.3993721008301</v>
+        <v>24.3993740081787</v>
       </c>
       <c r="H696" t="n">
         <v>24674</v>
@@ -20582,7 +20582,7 @@
         <v>31</v>
       </c>
       <c r="G697" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H697" t="n">
         <v>84632</v>
@@ -20611,7 +20611,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>28.8928146362305</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H698" t="n">
         <v>66739</v>
@@ -20640,7 +20640,7 @@
         <v>31</v>
       </c>
       <c r="G699" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H699" t="n">
         <v>45901</v>
@@ -20669,7 +20669,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>26.8258285522461</v>
+        <v>26.8258304595947</v>
       </c>
       <c r="H700" t="n">
         <v>41033</v>
@@ -20698,7 +20698,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>26.1967506408691</v>
+        <v>26.1967449188232</v>
       </c>
       <c r="H701" t="n">
         <v>24223</v>
@@ -20727,7 +20727,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.3201084136963</v>
+        <v>27.3201103210449</v>
       </c>
       <c r="H702" t="n">
         <v>11386</v>
@@ -20872,7 +20872,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.2857799530029</v>
+        <v>30.2857780456543</v>
       </c>
       <c r="H707" t="n">
         <v>60261</v>
@@ -20901,7 +20901,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>28.7130737304688</v>
+        <v>28.7130756378174</v>
       </c>
       <c r="H708" t="n">
         <v>30718</v>
@@ -20930,7 +20930,7 @@
         <v>31.5</v>
       </c>
       <c r="G709" t="n">
-        <v>28.3086643218994</v>
+        <v>28.308666229248</v>
       </c>
       <c r="H709" t="n">
         <v>38489</v>
@@ -20959,7 +20959,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>27.0505046844482</v>
+        <v>27.0505027770996</v>
       </c>
       <c r="H710" t="n">
         <v>34512</v>
@@ -21104,7 +21104,7 @@
         <v>29.75</v>
       </c>
       <c r="G715" t="n">
-        <v>26.7359619140625</v>
+        <v>26.7359600067139</v>
       </c>
       <c r="H715" t="n">
         <v>47799</v>
@@ -21162,7 +21162,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>26.4663562774658</v>
+        <v>26.4663543701172</v>
       </c>
       <c r="H717" t="n">
         <v>21538</v>
@@ -21191,7 +21191,7 @@
         <v>31</v>
       </c>
       <c r="G718" t="n">
-        <v>27.8593215942383</v>
+        <v>27.8593196868896</v>
       </c>
       <c r="H718" t="n">
         <v>29100</v>
@@ -21220,7 +21220,7 @@
         <v>30.75</v>
       </c>
       <c r="G719" t="n">
-        <v>27.6346473693848</v>
+        <v>27.6346492767334</v>
       </c>
       <c r="H719" t="n">
         <v>31154</v>
@@ -21307,7 +21307,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>27.4998455047607</v>
+        <v>27.4998435974121</v>
       </c>
       <c r="H722" t="n">
         <v>26961</v>
@@ -21365,7 +21365,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>28.8928146362305</v>
+        <v>28.8928127288818</v>
       </c>
       <c r="H724" t="n">
         <v>74966</v>
@@ -21394,7 +21394,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G725" t="n">
-        <v>29.0725479125977</v>
+        <v>29.072546005249</v>
       </c>
       <c r="H725" t="n">
         <v>48547</v>
@@ -21423,7 +21423,7 @@
         <v>33</v>
       </c>
       <c r="G726" t="n">
-        <v>29.6566982269287</v>
+        <v>29.6566963195801</v>
       </c>
       <c r="H726" t="n">
         <v>52278</v>
@@ -21481,7 +21481,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>30.1959075927734</v>
+        <v>30.1959095001221</v>
       </c>
       <c r="H728" t="n">
         <v>39492</v>
@@ -21510,7 +21510,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>31.2743358612061</v>
+        <v>31.2743320465088</v>
       </c>
       <c r="H729" t="n">
         <v>35167</v>
@@ -21539,7 +21539,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G730" t="n">
-        <v>31.3642024993896</v>
+        <v>31.3642082214355</v>
       </c>
       <c r="H730" t="n">
         <v>45462</v>
@@ -21568,7 +21568,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>31.4990081787109</v>
+        <v>31.4990043640137</v>
       </c>
       <c r="H731" t="n">
         <v>57313</v>
@@ -21626,7 +21626,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>36.2620544433594</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H733" t="n">
         <v>163828</v>
@@ -21655,7 +21655,7 @@
         <v>38.75</v>
       </c>
       <c r="G734" t="n">
-        <v>34.824146270752</v>
+        <v>34.8241500854492</v>
       </c>
       <c r="H734" t="n">
         <v>70305</v>
@@ -21684,7 +21684,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>33.0717086791992</v>
+        <v>33.071704864502</v>
       </c>
       <c r="H735" t="n">
         <v>60680</v>
@@ -21742,7 +21742,7 @@
         <v>33.5</v>
       </c>
       <c r="G737" t="n">
-        <v>30.1060371398926</v>
+        <v>30.1060390472412</v>
       </c>
       <c r="H737" t="n">
         <v>76564</v>
@@ -21800,7 +21800,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>32.442626953125</v>
+        <v>32.4426231384277</v>
       </c>
       <c r="H739" t="n">
         <v>87104</v>
@@ -21829,7 +21829,7 @@
         <v>38</v>
       </c>
       <c r="G740" t="n">
-        <v>34.1501350402832</v>
+        <v>34.1501312255859</v>
       </c>
       <c r="H740" t="n">
         <v>64579</v>
@@ -21916,7 +21916,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>35.5431022644043</v>
+        <v>35.543098449707</v>
       </c>
       <c r="H743" t="n">
         <v>104093</v>
@@ -22090,7 +22090,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G749" t="n">
-        <v>36.0823135375977</v>
+        <v>36.0823173522949</v>
       </c>
       <c r="H749" t="n">
         <v>49003</v>
@@ -22119,7 +22119,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G750" t="n">
-        <v>36.4867210388184</v>
+        <v>36.4867248535156</v>
       </c>
       <c r="H750" t="n">
         <v>57628</v>
@@ -22148,7 +22148,7 @@
         <v>42.5</v>
       </c>
       <c r="G751" t="n">
-        <v>38.1942329406738</v>
+        <v>38.1942291259766</v>
       </c>
       <c r="H751" t="n">
         <v>111612</v>
@@ -22177,7 +22177,7 @@
         <v>42.5</v>
       </c>
       <c r="G752" t="n">
-        <v>38.1942329406738</v>
+        <v>38.1942291259766</v>
       </c>
       <c r="H752" t="n">
         <v>37608</v>
@@ -22293,7 +22293,7 @@
         <v>41.75</v>
       </c>
       <c r="G756" t="n">
-        <v>37.5202140808105</v>
+        <v>37.5202102661133</v>
       </c>
       <c r="H756" t="n">
         <v>31836</v>
@@ -22351,7 +22351,7 @@
         <v>46.25</v>
       </c>
       <c r="G758" t="n">
-        <v>41.5643081665039</v>
+        <v>41.5643119812012</v>
       </c>
       <c r="H758" t="n">
         <v>54121</v>
@@ -22438,7 +22438,7 @@
         <v>47.75</v>
       </c>
       <c r="G761" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H761" t="n">
         <v>26981</v>
@@ -22496,7 +22496,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>42.8224754333496</v>
+        <v>42.8224716186523</v>
       </c>
       <c r="H763" t="n">
         <v>25169</v>
@@ -22525,7 +22525,7 @@
         <v>47.75</v>
       </c>
       <c r="G764" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H764" t="n">
         <v>19426</v>
@@ -22583,7 +22583,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G766" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H766" t="n">
         <v>13856</v>
@@ -22612,7 +22612,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>41.833911895752</v>
+        <v>41.8339157104492</v>
       </c>
       <c r="H767" t="n">
         <v>20446</v>
@@ -22641,7 +22641,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H768" t="n">
         <v>17008</v>
@@ -22699,7 +22699,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H770" t="n">
         <v>30213</v>
@@ -22728,7 +22728,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>41.0250968933105</v>
+        <v>41.0251007080078</v>
       </c>
       <c r="H771" t="n">
         <v>23411</v>
@@ -22757,7 +22757,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H772" t="n">
         <v>37447</v>
@@ -22815,7 +22815,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>42.507926940918</v>
+        <v>42.5079307556152</v>
       </c>
       <c r="H774" t="n">
         <v>35151</v>
@@ -22902,7 +22902,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>41.7440490722656</v>
+        <v>41.7440452575684</v>
       </c>
       <c r="H777" t="n">
         <v>31489</v>
@@ -22931,7 +22931,7 @@
         <v>47.5</v>
       </c>
       <c r="G778" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H778" t="n">
         <v>34460</v>
@@ -22960,7 +22960,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G779" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H779" t="n">
         <v>32289</v>
@@ -23047,7 +23047,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H782" t="n">
         <v>12518</v>
@@ -23105,7 +23105,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H784" t="n">
         <v>26455</v>
@@ -23134,7 +23134,7 @@
         <v>47.5</v>
       </c>
       <c r="G785" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H785" t="n">
         <v>14310</v>
@@ -23221,7 +23221,7 @@
         <v>49.5</v>
       </c>
       <c r="G788" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H788" t="n">
         <v>35855</v>
@@ -23337,7 +23337,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>43.2268829345703</v>
+        <v>43.226879119873</v>
       </c>
       <c r="H792" t="n">
         <v>8813</v>
@@ -23395,7 +23395,7 @@
         <v>47.5</v>
       </c>
       <c r="G794" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H794" t="n">
         <v>19217</v>
@@ -23569,7 +23569,7 @@
         <v>46.5</v>
       </c>
       <c r="G800" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889862060547</v>
       </c>
       <c r="H800" t="n">
         <v>29039</v>
@@ -23656,7 +23656,7 @@
         <v>48.75</v>
       </c>
       <c r="G803" t="n">
-        <v>43.8110275268555</v>
+        <v>43.8110313415527</v>
       </c>
       <c r="H803" t="n">
         <v>11475</v>
@@ -23801,7 +23801,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G808" t="n">
-        <v>39.047981262207</v>
+        <v>39.0479850769043</v>
       </c>
       <c r="H808" t="n">
         <v>25259</v>
@@ -23859,7 +23859,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>37.9246253967285</v>
+        <v>37.9246215820312</v>
       </c>
       <c r="H810" t="n">
         <v>12601</v>
@@ -24033,7 +24033,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>37.8347511291504</v>
+        <v>37.8347549438477</v>
       </c>
       <c r="H816" t="n">
         <v>19737</v>
@@ -24091,7 +24091,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.7898139953613</v>
+        <v>37.7898254394531</v>
       </c>
       <c r="H818" t="n">
         <v>15517</v>
@@ -24120,7 +24120,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>39.0030555725098</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H819" t="n">
         <v>14099</v>
@@ -24207,7 +24207,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>39.8118667602539</v>
+        <v>39.8118705749512</v>
       </c>
       <c r="H822" t="n">
         <v>9284</v>
@@ -24265,7 +24265,7 @@
         <v>44</v>
       </c>
       <c r="G824" t="n">
-        <v>39.5422630310059</v>
+        <v>39.5422554016113</v>
       </c>
       <c r="H824" t="n">
         <v>9758</v>
@@ -24323,7 +24323,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G826" t="n">
-        <v>39.0030555725098</v>
+        <v>39.0030517578125</v>
       </c>
       <c r="H826" t="n">
         <v>19392</v>
@@ -24468,7 +24468,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>38.0144920349121</v>
+        <v>38.0144958496094</v>
       </c>
       <c r="H831" t="n">
         <v>12021</v>
@@ -24497,7 +24497,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>38.4638404846191</v>
+        <v>38.4638366699219</v>
       </c>
       <c r="H832" t="n">
         <v>15760</v>
@@ -24613,7 +24613,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G836" t="n">
-        <v>34.2400016784668</v>
+        <v>34.2400054931641</v>
       </c>
       <c r="H836" t="n">
         <v>24293</v>
@@ -24642,7 +24642,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>35.6329689025879</v>
+        <v>35.6329727172852</v>
       </c>
       <c r="H837" t="n">
         <v>24505</v>
@@ -24671,7 +24671,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G838" t="n">
-        <v>36.2620544433594</v>
+        <v>36.2620506286621</v>
       </c>
       <c r="H838" t="n">
         <v>20097</v>
@@ -24729,7 +24729,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>39.1827850341797</v>
+        <v>39.182788848877</v>
       </c>
       <c r="H840" t="n">
         <v>10534</v>
@@ -24758,7 +24758,7 @@
         <v>42</v>
       </c>
       <c r="G841" t="n">
-        <v>37.7448883056641</v>
+        <v>37.7448844909668</v>
       </c>
       <c r="H841" t="n">
         <v>59505</v>
@@ -24816,7 +24816,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>40.2612075805664</v>
+        <v>40.2612113952637</v>
       </c>
       <c r="H843" t="n">
         <v>56674</v>
@@ -24874,7 +24874,7 @@
         <v>44.75</v>
       </c>
       <c r="G845" t="n">
-        <v>40.2162780761719</v>
+        <v>40.2162742614746</v>
       </c>
       <c r="H845" t="n">
         <v>22532</v>
@@ -24932,7 +24932,7 @@
         <v>45.75</v>
       </c>
       <c r="G847" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H847" t="n">
         <v>23509</v>
@@ -24990,7 +24990,7 @@
         <v>46</v>
       </c>
       <c r="G849" t="n">
-        <v>41.3396339416504</v>
+        <v>41.3396377563477</v>
       </c>
       <c r="H849" t="n">
         <v>27797</v>
@@ -25019,7 +25019,7 @@
         <v>46.25</v>
       </c>
       <c r="G850" t="n">
-        <v>41.5643081665039</v>
+        <v>41.5643119812012</v>
       </c>
       <c r="H850" t="n">
         <v>22251</v>
@@ -25048,7 +25048,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G851" t="n">
-        <v>40.8453598022461</v>
+        <v>40.8453559875488</v>
       </c>
       <c r="H851" t="n">
         <v>13343</v>
@@ -25106,7 +25106,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>39.901741027832</v>
+        <v>39.9017372131348</v>
       </c>
       <c r="H853" t="n">
         <v>14943</v>
@@ -25164,7 +25164,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>41.1599006652832</v>
+        <v>41.1598968505859</v>
       </c>
       <c r="H855" t="n">
         <v>12496</v>
@@ -25193,7 +25193,7 @@
         <v>45.75</v>
       </c>
       <c r="G856" t="n">
-        <v>41.1149635314941</v>
+        <v>41.1149673461914</v>
       </c>
       <c r="H856" t="n">
         <v>12172</v>
@@ -25251,7 +25251,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>40.5308113098145</v>
+        <v>40.5308151245117</v>
       </c>
       <c r="H858" t="n">
         <v>18769</v>
@@ -25280,7 +25280,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G859" t="n">
-        <v>40.800422668457</v>
+        <v>40.8004264831543</v>
       </c>
       <c r="H859" t="n">
         <v>9064</v>
@@ -25367,7 +25367,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>40.3960151672363</v>
+        <v>40.3960189819336</v>
       </c>
       <c r="H862" t="n">
         <v>7355</v>
@@ -25483,7 +25483,7 @@
         <v>46.5</v>
       </c>
       <c r="G866" t="n">
-        <v>41.7889823913574</v>
+        <v>41.7889862060547</v>
       </c>
       <c r="H866" t="n">
         <v>12381</v>
@@ -25512,7 +25512,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>40.9801635742188</v>
+        <v>40.9801597595215</v>
       </c>
       <c r="H867" t="n">
         <v>46233</v>
@@ -25541,7 +25541,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H868" t="n">
         <v>19392</v>
@@ -25599,7 +25599,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H870" t="n">
         <v>6994</v>
@@ -25628,7 +25628,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G871" t="n">
-        <v>43.0471420288086</v>
+        <v>43.0471458435059</v>
       </c>
       <c r="H871" t="n">
         <v>16203</v>
@@ -25657,7 +25657,7 @@
         <v>47.5</v>
       </c>
       <c r="G872" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H872" t="n">
         <v>17923</v>
@@ -25686,7 +25686,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G873" t="n">
-        <v>41.9237861633301</v>
+        <v>41.9237823486328</v>
       </c>
       <c r="H873" t="n">
         <v>13670</v>
@@ -25715,7 +25715,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H874" t="n">
         <v>8152</v>
@@ -25744,7 +25744,7 @@
         <v>47.75</v>
       </c>
       <c r="G875" t="n">
-        <v>42.9123382568359</v>
+        <v>42.9123420715332</v>
       </c>
       <c r="H875" t="n">
         <v>11420</v>
@@ -25831,7 +25831,7 @@
         <v>48.25</v>
       </c>
       <c r="G878" t="n">
-        <v>43.361686706543</v>
+        <v>43.3616828918457</v>
       </c>
       <c r="H878" t="n">
         <v>3445</v>
@@ -25889,7 +25889,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G880" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H880" t="n">
         <v>11127</v>
@@ -25947,7 +25947,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>41.9687194824219</v>
+        <v>41.9687156677246</v>
       </c>
       <c r="H882" t="n">
         <v>4266</v>
@@ -26005,7 +26005,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>42.1484603881836</v>
+        <v>42.1484527587891</v>
       </c>
       <c r="H884" t="n">
         <v>7700</v>
@@ -26063,7 +26063,7 @@
         <v>47.5</v>
       </c>
       <c r="G886" t="n">
-        <v>42.687671661377</v>
+        <v>42.6876678466797</v>
       </c>
       <c r="H886" t="n">
         <v>16328</v>
@@ -26092,7 +26092,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>44.5299797058105</v>
+        <v>44.5299758911133</v>
       </c>
       <c r="H887" t="n">
         <v>28055</v>
@@ -26121,7 +26121,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H888" t="n">
         <v>23048</v>
@@ -26150,7 +26150,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G889" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H889" t="n">
         <v>14075</v>
@@ -26237,7 +26237,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H892" t="n">
         <v>9547</v>
@@ -26295,7 +26295,7 @@
         <v>49</v>
       </c>
       <c r="G894" t="n">
-        <v>44.0356979370117</v>
+        <v>44.035701751709</v>
       </c>
       <c r="H894" t="n">
         <v>9685</v>
@@ -26324,7 +26324,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H895" t="n">
         <v>4071</v>
@@ -26440,7 +26440,7 @@
         <v>49.5</v>
       </c>
       <c r="G899" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H899" t="n">
         <v>14923</v>
@@ -26498,7 +26498,7 @@
         <v>50.5</v>
       </c>
       <c r="G901" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H901" t="n">
         <v>12391</v>
@@ -26614,7 +26614,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H905" t="n">
         <v>8945</v>
@@ -26672,7 +26672,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>48.6190071105957</v>
+        <v>48.6190032958984</v>
       </c>
       <c r="H907" t="n">
         <v>2482</v>
@@ -26701,7 +26701,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>49.1582221984863</v>
+        <v>49.1582183837891</v>
       </c>
       <c r="H908" t="n">
         <v>10471</v>
@@ -26788,7 +26788,7 @@
         <v>52.5</v>
       </c>
       <c r="G911" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H911" t="n">
         <v>10719</v>
@@ -26962,7 +26962,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>47.2709770202637</v>
+        <v>47.2709732055664</v>
       </c>
       <c r="H917" t="n">
         <v>10683</v>
@@ -27020,7 +27020,7 @@
         <v>52</v>
       </c>
       <c r="G919" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H919" t="n">
         <v>12524</v>
@@ -27049,7 +27049,7 @@
         <v>50.5</v>
       </c>
       <c r="G920" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H920" t="n">
         <v>13604</v>
@@ -27136,7 +27136,7 @@
         <v>49.25</v>
       </c>
       <c r="G923" t="n">
-        <v>44.2603721618652</v>
+        <v>44.2603759765625</v>
       </c>
       <c r="H923" t="n">
         <v>10806</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>46.911506652832</v>
+        <v>46.9115028381348</v>
       </c>
       <c r="H924" t="n">
         <v>20882</v>
@@ -27281,7 +27281,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H928" t="n">
         <v>14790</v>
@@ -27310,7 +27310,7 @@
         <v>55</v>
       </c>
       <c r="G929" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H929" t="n">
         <v>14814</v>
@@ -27339,7 +27339,7 @@
         <v>55</v>
       </c>
       <c r="G930" t="n">
-        <v>49.4278259277344</v>
+        <v>49.4278297424316</v>
       </c>
       <c r="H930" t="n">
         <v>11631</v>
@@ -27426,7 +27426,7 @@
         <v>52</v>
       </c>
       <c r="G933" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H933" t="n">
         <v>15510</v>
@@ -27571,7 +27571,7 @@
         <v>54</v>
       </c>
       <c r="G938" t="n">
-        <v>48.5291404724121</v>
+        <v>48.5291366577148</v>
       </c>
       <c r="H938" t="n">
         <v>7754</v>
@@ -27600,7 +27600,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G939" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H939" t="n">
         <v>2144</v>
@@ -27629,7 +27629,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>47.2709770202637</v>
+        <v>47.2709732055664</v>
       </c>
       <c r="H940" t="n">
         <v>9185</v>
@@ -27658,7 +27658,7 @@
         <v>52</v>
       </c>
       <c r="G941" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H941" t="n">
         <v>17192</v>
@@ -27716,7 +27716,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H943" t="n">
         <v>8559</v>
@@ -27774,7 +27774,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>46.8216285705566</v>
+        <v>46.8216323852539</v>
       </c>
       <c r="H945" t="n">
         <v>6034</v>
@@ -27832,7 +27832,7 @@
         <v>52.5</v>
       </c>
       <c r="G947" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H947" t="n">
         <v>9996</v>
@@ -27861,7 +27861,7 @@
         <v>52.5</v>
       </c>
       <c r="G948" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H948" t="n">
         <v>6269</v>
@@ -27890,7 +27890,7 @@
         <v>52.5</v>
       </c>
       <c r="G949" t="n">
-        <v>47.1811103820801</v>
+        <v>47.1811065673828</v>
       </c>
       <c r="H949" t="n">
         <v>4814</v>
@@ -27919,7 +27919,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G950" t="n">
-        <v>46.3722915649414</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H950" t="n">
         <v>5714</v>
@@ -27948,7 +27948,7 @@
         <v>52</v>
       </c>
       <c r="G951" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H951" t="n">
         <v>7608</v>
@@ -28035,7 +28035,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H954" t="n">
         <v>8310</v>
@@ -28093,7 +28093,7 @@
         <v>49.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>44.8894538879395</v>
+        <v>44.8894577026367</v>
       </c>
       <c r="H956" t="n">
         <v>8007</v>
@@ -28122,7 +28122,7 @@
         <v>52</v>
       </c>
       <c r="G957" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H957" t="n">
         <v>11719</v>
@@ -28151,7 +28151,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G958" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H958" t="n">
         <v>6560</v>
@@ -28238,7 +28238,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>46.3722915649414</v>
+        <v>46.3722839355469</v>
       </c>
       <c r="H961" t="n">
         <v>12589</v>
@@ -28267,7 +28267,7 @@
         <v>51.5</v>
       </c>
       <c r="G962" t="n">
-        <v>46.2824172973633</v>
+        <v>46.2824211120605</v>
       </c>
       <c r="H962" t="n">
         <v>10727</v>
@@ -28296,7 +28296,7 @@
         <v>52</v>
       </c>
       <c r="G963" t="n">
-        <v>46.731761932373</v>
+        <v>46.7317657470703</v>
       </c>
       <c r="H963" t="n">
         <v>15923</v>
@@ -28325,7 +28325,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>48.2595329284668</v>
+        <v>48.2595367431641</v>
       </c>
       <c r="H964" t="n">
         <v>14743</v>
@@ -28354,7 +28354,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>47.9899291992188</v>
+        <v>47.9899253845215</v>
       </c>
       <c r="H965" t="n">
         <v>6406</v>
@@ -28383,7 +28383,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>48.7987442016602</v>
+        <v>48.7987480163574</v>
       </c>
       <c r="H966" t="n">
         <v>2872</v>
@@ -28441,7 +28441,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G968" t="n">
-        <v>46.6418991088867</v>
+        <v>46.6418952941895</v>
       </c>
       <c r="H968" t="n">
         <v>12385</v>
@@ -28586,7 +28586,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H973" t="n">
         <v>226954</v>
@@ -28615,7 +28615,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G974" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H974" t="n">
         <v>16723</v>
@@ -28702,7 +28702,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>45.1141242980957</v>
+        <v>45.114128112793</v>
       </c>
       <c r="H977" t="n">
         <v>17528</v>
@@ -28731,7 +28731,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G978" t="n">
-        <v>46.4621543884277</v>
+        <v>46.462158203125</v>
       </c>
       <c r="H978" t="n">
         <v>18485</v>
@@ -28760,7 +28760,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>44.7995834350586</v>
+        <v>44.7995872497559</v>
       </c>
       <c r="H979" t="n">
         <v>30230</v>
@@ -28818,7 +28818,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>45.9229431152344</v>
+        <v>45.9229393005371</v>
       </c>
       <c r="H981" t="n">
         <v>20247</v>
@@ -28847,7 +28847,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G982" t="n">
-        <v>46.192554473877</v>
+        <v>46.1925506591797</v>
       </c>
       <c r="H982" t="n">
         <v>5586</v>
@@ -28963,7 +28963,7 @@
         <v>50.5</v>
       </c>
       <c r="G986" t="n">
-        <v>45.383731842041</v>
+        <v>45.3837280273438</v>
       </c>
       <c r="H986" t="n">
         <v>9545</v>
@@ -29021,7 +29021,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H988" t="n">
         <v>21589</v>
@@ -29108,7 +29108,7 @@
         <v>49.5</v>
       </c>
       <c r="G991" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H991" t="n">
         <v>14665</v>
@@ -29166,7 +29166,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G993" t="n">
-        <v>45.2938690185547</v>
+        <v>45.2938613891602</v>
       </c>
       <c r="H993" t="n">
         <v>12269</v>
@@ -29224,7 +29224,7 @@
         <v>49.5</v>
       </c>
       <c r="G995" t="n">
-        <v>44.4850425720215</v>
+        <v>44.4850463867188</v>
       </c>
       <c r="H995" t="n">
         <v>8728</v>
@@ -29253,7 +29253,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>43.7211647033691</v>
+        <v>43.7211608886719</v>
       </c>
       <c r="H996" t="n">
         <v>34066</v>
@@ -29311,7 +29311,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>44.1765289306641</v>
+        <v>44.1765251159668</v>
       </c>
       <c r="H998" t="n">
         <v>76506</v>
@@ -29427,7 +29427,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>41.9087371826172</v>
+        <v>41.9087409973145</v>
       </c>
       <c r="H1002" t="n">
         <v>14318</v>
@@ -29485,7 +29485,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>42.090160369873</v>
+        <v>42.0901641845703</v>
       </c>
       <c r="H1004" t="n">
         <v>24860</v>
@@ -29543,7 +29543,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1006" t="n">
         <v>12674</v>
@@ -29572,7 +29572,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1007" t="n">
-        <v>41.4098243713379</v>
+        <v>41.4098281860352</v>
       </c>
       <c r="H1007" t="n">
         <v>7762</v>
@@ -29717,7 +29717,7 @@
         <v>44.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1012" t="n">
         <v>16272</v>
@@ -29746,7 +29746,7 @@
         <v>43.75</v>
       </c>
       <c r="G1013" t="n">
-        <v>39.6863059997559</v>
+        <v>39.6863021850586</v>
       </c>
       <c r="H1013" t="n">
         <v>19765</v>
@@ -29775,7 +29775,7 @@
         <v>44.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1014" t="n">
         <v>13467</v>
@@ -29804,7 +29804,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>39.7316589355469</v>
+        <v>39.7316627502441</v>
       </c>
       <c r="H1015" t="n">
         <v>12739</v>
@@ -29833,7 +29833,7 @@
         <v>44.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1016" t="n">
         <v>130810</v>
@@ -29920,7 +29920,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>41.6366081237793</v>
+        <v>41.636604309082</v>
       </c>
       <c r="H1019" t="n">
         <v>114899</v>
@@ -29949,7 +29949,7 @@
         <v>47.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>42.6797866821289</v>
+        <v>42.6797828674316</v>
       </c>
       <c r="H1020" t="n">
         <v>56881</v>
@@ -30123,7 +30123,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>43.9043922424316</v>
+        <v>43.9043960571289</v>
       </c>
       <c r="H1026" t="n">
         <v>28292</v>
@@ -30210,7 +30210,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1029" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1029" t="n">
         <v>17463</v>
@@ -30326,7 +30326,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1033" t="n">
         <v>17232</v>
@@ -30355,7 +30355,7 @@
         <v>48.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>44.2218856811523</v>
+        <v>44.2218818664551</v>
       </c>
       <c r="H1034" t="n">
         <v>9670</v>
@@ -30384,7 +30384,7 @@
         <v>48.5</v>
       </c>
       <c r="G1035" t="n">
-        <v>43.9951057434082</v>
+        <v>43.9951019287109</v>
       </c>
       <c r="H1035" t="n">
         <v>14464</v>
@@ -30442,7 +30442,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>43.6776161193848</v>
+        <v>43.6776123046875</v>
       </c>
       <c r="H1037" t="n">
         <v>8307</v>
@@ -30500,7 +30500,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1039" t="n">
         <v>43123</v>
@@ -30645,7 +30645,7 @@
         <v>53.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1044" t="n">
         <v>18875</v>
@@ -30703,7 +30703,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>48.1678314208984</v>
+        <v>48.1678352355957</v>
       </c>
       <c r="H1046" t="n">
         <v>11015</v>
@@ -30790,7 +30790,7 @@
         <v>53.5</v>
       </c>
       <c r="G1049" t="n">
-        <v>48.5306816101074</v>
+        <v>48.5306777954102</v>
       </c>
       <c r="H1049" t="n">
         <v>8692</v>
@@ -30877,7 +30877,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>47.5328598022461</v>
+        <v>47.5328521728516</v>
       </c>
       <c r="H1052" t="n">
         <v>8733</v>
@@ -30906,7 +30906,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1053" t="n">
         <v>4861</v>
@@ -30935,7 +30935,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>46.4443206787109</v>
+        <v>46.4443168640137</v>
       </c>
       <c r="H1054" t="n">
         <v>11045</v>
@@ -30964,7 +30964,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1055" t="n">
         <v>9979</v>
@@ -31051,7 +31051,7 @@
         <v>51.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>46.7164497375488</v>
+        <v>46.7164535522461</v>
       </c>
       <c r="H1058" t="n">
         <v>15938</v>
@@ -31080,7 +31080,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>46.8071594238281</v>
+        <v>46.8071632385254</v>
       </c>
       <c r="H1059" t="n">
         <v>10169</v>
@@ -31109,7 +31109,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1060" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1060" t="n">
         <v>8913</v>
@@ -31283,7 +31283,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1066" t="n">
         <v>12121</v>
@@ -31399,7 +31399,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1070" t="n">
-        <v>45.4464912414551</v>
+        <v>45.4464874267578</v>
       </c>
       <c r="H1070" t="n">
         <v>9883</v>
@@ -31428,7 +31428,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1071" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1071" t="n">
         <v>12696</v>
@@ -31486,7 +31486,7 @@
         <v>50.5</v>
       </c>
       <c r="G1073" t="n">
-        <v>45.8093338012695</v>
+        <v>45.8093376159668</v>
       </c>
       <c r="H1073" t="n">
         <v>7974</v>
@@ -31515,7 +31515,7 @@
         <v>49</v>
       </c>
       <c r="G1074" t="n">
-        <v>44.448657989502</v>
+        <v>44.4486618041992</v>
       </c>
       <c r="H1074" t="n">
         <v>6081</v>
@@ -31544,7 +31544,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>44.3125915527344</v>
+        <v>44.3125953674316</v>
       </c>
       <c r="H1075" t="n">
         <v>11302</v>
@@ -31689,7 +31689,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>46.8978729248047</v>
+        <v>46.897876739502</v>
       </c>
       <c r="H1080" t="n">
         <v>42778</v>
@@ -31747,7 +31747,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>49.2563705444336</v>
+        <v>49.2563743591309</v>
       </c>
       <c r="H1082" t="n">
         <v>46325</v>
@@ -31776,7 +31776,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1083" t="n">
-        <v>47.0792961120605</v>
+        <v>47.0792999267578</v>
       </c>
       <c r="H1083" t="n">
         <v>17625</v>
@@ -31834,7 +31834,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>46.1721839904785</v>
+        <v>46.1721801757812</v>
       </c>
       <c r="H1085" t="n">
         <v>9377</v>
@@ -31892,7 +31892,7 @@
         <v>43.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.4595222473145</v>
+        <v>39.459529876709</v>
       </c>
       <c r="H1087" t="n">
         <v>66336</v>
@@ -31921,7 +31921,7 @@
         <v>44.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>40.366641998291</v>
+        <v>40.3666381835938</v>
       </c>
       <c r="H1088" t="n">
         <v>48832</v>
@@ -32008,7 +32008,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1091" t="n">
         <v>42578</v>
@@ -32037,7 +32037,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1092" t="n">
         <v>21583</v>
@@ -32095,7 +32095,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1094" t="n">
-        <v>38.4163436889648</v>
+        <v>38.4163398742676</v>
       </c>
       <c r="H1094" t="n">
         <v>42249</v>
@@ -32182,7 +32182,7 @@
         <v>42</v>
       </c>
       <c r="G1097" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1097" t="n">
         <v>51723</v>
@@ -32269,7 +32269,7 @@
         <v>41.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>37.5999374389648</v>
+        <v>37.5999412536621</v>
       </c>
       <c r="H1100" t="n">
         <v>35064</v>
@@ -32327,7 +32327,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1102" t="n">
         <v>21799</v>
@@ -32356,7 +32356,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1103" t="n">
-        <v>37.1010246276855</v>
+        <v>37.1010284423828</v>
       </c>
       <c r="H1103" t="n">
         <v>27248</v>
@@ -32385,7 +32385,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1104" t="n">
         <v>25963</v>
@@ -32675,7 +32675,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1114" t="n">
         <v>20711</v>
@@ -32704,7 +32704,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>35.4228591918945</v>
+        <v>35.4228630065918</v>
       </c>
       <c r="H1115" t="n">
         <v>18782</v>
@@ -32820,7 +32820,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1119" t="n">
         <v>12560</v>
@@ -33081,7 +33081,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>37.1463851928711</v>
+        <v>37.1463813781738</v>
       </c>
       <c r="H1128" t="n">
         <v>24984</v>
@@ -33226,7 +33226,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1133" t="n">
         <v>16558</v>
@@ -33342,7 +33342,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1137" t="n">
         <v>52206</v>
@@ -33429,7 +33429,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>36.3753318786621</v>
+        <v>36.3753280639648</v>
       </c>
       <c r="H1140" t="n">
         <v>22080</v>
@@ -33458,7 +33458,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>36.3299789428711</v>
+        <v>36.3299751281738</v>
       </c>
       <c r="H1141" t="n">
         <v>7118</v>
@@ -33516,7 +33516,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.3688163757324</v>
+        <v>39.3688125610352</v>
       </c>
       <c r="H1143" t="n">
         <v>170822</v>
@@ -33603,7 +33603,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1146" t="n">
         <v>38296</v>
@@ -33632,7 +33632,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G1147" t="n">
-        <v>35.8764228820801</v>
+        <v>35.8764152526855</v>
       </c>
       <c r="H1147" t="n">
         <v>28893</v>
@@ -33690,7 +33690,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>35.3321533203125</v>
+        <v>35.3321495056152</v>
       </c>
       <c r="H1149" t="n">
         <v>29504</v>
@@ -33719,7 +33719,7 @@
         <v>37.25</v>
       </c>
       <c r="G1150" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1150" t="n">
         <v>39042</v>
@@ -33806,7 +33806,7 @@
         <v>38.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1153" t="n">
         <v>41376</v>
@@ -33835,7 +33835,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>34.4250335693359</v>
+        <v>34.4250373840332</v>
       </c>
       <c r="H1154" t="n">
         <v>41497</v>
@@ -33893,7 +33893,7 @@
         <v>38.75</v>
       </c>
       <c r="G1156" t="n">
-        <v>35.1507263183594</v>
+        <v>35.1507301330566</v>
       </c>
       <c r="H1156" t="n">
         <v>64899</v>
@@ -33980,7 +33980,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1159" t="n">
         <v>19943</v>
@@ -34125,7 +34125,7 @@
         <v>42</v>
       </c>
       <c r="G1164" t="n">
-        <v>38.0988578796387</v>
+        <v>38.0988540649414</v>
       </c>
       <c r="H1164" t="n">
         <v>26580</v>
@@ -34154,7 +34154,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1165" t="n">
         <v>37830</v>
@@ -34183,7 +34183,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>37.8267211914062</v>
+        <v>37.826717376709</v>
       </c>
       <c r="H1166" t="n">
         <v>18336</v>
@@ -34241,7 +34241,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>37.0556678771973</v>
+        <v>37.0556716918945</v>
       </c>
       <c r="H1168" t="n">
         <v>36948</v>
@@ -34328,7 +34328,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1171" t="n">
-        <v>36.1031951904297</v>
+        <v>36.103199005127</v>
       </c>
       <c r="H1171" t="n">
         <v>37325</v>
@@ -34473,7 +34473,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.6605072021484</v>
+        <v>30.6605033874512</v>
       </c>
       <c r="H1176" t="n">
         <v>45632</v>
@@ -34734,7 +34734,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>31.0233516693115</v>
+        <v>31.0233535766602</v>
       </c>
       <c r="H1185" t="n">
         <v>64152</v>
@@ -34763,7 +34763,7 @@
         <v>34</v>
       </c>
       <c r="G1186" t="n">
-        <v>30.8419322967529</v>
+        <v>30.8419284820557</v>
       </c>
       <c r="H1186" t="n">
         <v>23784</v>
@@ -34792,7 +34792,7 @@
         <v>36</v>
       </c>
       <c r="G1187" t="n">
-        <v>32.6561584472656</v>
+        <v>32.6561622619629</v>
       </c>
       <c r="H1187" t="n">
         <v>23709</v>
@@ -34879,7 +34879,7 @@
         <v>37.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>33.7900581359863</v>
+        <v>33.7900543212891</v>
       </c>
       <c r="H1190" t="n">
         <v>13571</v>
@@ -34908,7 +34908,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>35.0600204467773</v>
+        <v>35.0600166320801</v>
       </c>
       <c r="H1191" t="n">
         <v>25626</v>
@@ -34995,7 +34995,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>34.7425231933594</v>
+        <v>34.7425270080566</v>
       </c>
       <c r="H1194" t="n">
         <v>141817</v>
@@ -35343,7 +35343,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>37.5545883178711</v>
+        <v>37.5545845031738</v>
       </c>
       <c r="H1206" t="n">
         <v>15440</v>
@@ -35372,7 +35372,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>37.7813606262207</v>
+        <v>37.781364440918</v>
       </c>
       <c r="H1207" t="n">
         <v>12765</v>
@@ -35401,7 +35401,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>36.8742485046387</v>
+        <v>36.8742446899414</v>
       </c>
       <c r="H1208" t="n">
         <v>18290</v>
@@ -35430,7 +35430,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G1209" t="n">
-        <v>36.6928215026855</v>
+        <v>36.6928253173828</v>
       </c>
       <c r="H1209" t="n">
         <v>25845</v>
@@ -35691,7 +35691,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1218" t="n">
         <v>55769</v>
@@ -35720,7 +35720,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>34.2475547790527</v>
+        <v>34.2475509643555</v>
       </c>
       <c r="H1219" t="n">
         <v>11676</v>
@@ -35923,7 +35923,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.7377815246582</v>
+        <v>33.7377777099609</v>
       </c>
       <c r="H1226" t="n">
         <v>7077</v>
@@ -35981,7 +35981,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>33.2280044555664</v>
+        <v>33.2280006408691</v>
       </c>
       <c r="H1228" t="n">
         <v>17594</v>
@@ -36271,7 +36271,7 @@
         <v>38.75</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1238" t="n">
         <v>26308</v>
@@ -36329,7 +36329,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>34.5719566345215</v>
+        <v>34.5719528198242</v>
       </c>
       <c r="H1240" t="n">
         <v>30852</v>
@@ -36503,7 +36503,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>32.5792045593262</v>
+        <v>32.5792007446289</v>
       </c>
       <c r="H1246" t="n">
         <v>16319</v>
@@ -36532,7 +36532,7 @@
         <v>33.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1247" t="n">
         <v>23766</v>
@@ -36590,7 +36590,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>28.4546661376953</v>
+        <v>28.4546642303467</v>
       </c>
       <c r="H1249" t="n">
         <v>16778</v>
@@ -36677,7 +36677,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1252" t="n">
         <v>55493</v>
@@ -36706,7 +36706,7 @@
         <v>30.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.2692928314209</v>
+        <v>28.2692909240723</v>
       </c>
       <c r="H1253" t="n">
         <v>9517</v>
@@ -36735,7 +36735,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1254" t="n">
         <v>12548</v>
@@ -36880,7 +36880,7 @@
         <v>29</v>
       </c>
       <c r="G1259" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1259" t="n">
         <v>38924</v>
@@ -36938,7 +36938,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>26.0911655426025</v>
+        <v>26.0911674499512</v>
       </c>
       <c r="H1261" t="n">
         <v>31910</v>
@@ -37083,7 +37083,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>25.8131084442139</v>
+        <v>25.8131065368652</v>
       </c>
       <c r="H1266" t="n">
         <v>7598</v>
@@ -37112,7 +37112,7 @@
         <v>28.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1267" t="n">
         <v>12771</v>
@@ -37170,7 +37170,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1269" t="n">
         <v>18414</v>
@@ -37344,7 +37344,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1275" t="n">
         <v>15913</v>
@@ -37431,7 +37431,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.7399711608887</v>
+        <v>26.73996925354</v>
       </c>
       <c r="H1278" t="n">
         <v>11119</v>
@@ -37489,7 +37489,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1280" t="n">
         <v>11239</v>
@@ -37547,7 +37547,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1282" t="n">
         <v>29030</v>
@@ -37576,7 +37576,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>27.3887710571289</v>
+        <v>27.3887729644775</v>
       </c>
       <c r="H1283" t="n">
         <v>13951</v>
@@ -37808,7 +37808,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>28.5473499298096</v>
+        <v>28.5473518371582</v>
       </c>
       <c r="H1291" t="n">
         <v>49073</v>
@@ -37837,7 +37837,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1292" t="n">
         <v>22316</v>
@@ -38040,7 +38040,7 @@
         <v>29.25</v>
       </c>
       <c r="G1299" t="n">
-        <v>27.1107139587402</v>
+        <v>27.1107158660889</v>
       </c>
       <c r="H1299" t="n">
         <v>2701</v>
@@ -38156,7 +38156,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>26.5545978546143</v>
+        <v>26.5545959472656</v>
       </c>
       <c r="H1303" t="n">
         <v>11541</v>
@@ -38301,7 +38301,7 @@
         <v>28.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1308" t="n">
         <v>7747</v>
@@ -38359,7 +38359,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1310" t="n">
         <v>8183</v>
@@ -38533,7 +38533,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1316" t="n">
         <v>8506</v>
@@ -38562,7 +38562,7 @@
         <v>29</v>
       </c>
       <c r="G1317" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1317" t="n">
         <v>6463</v>
@@ -38765,7 +38765,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.6545295715332</v>
+        <v>24.6545314788818</v>
       </c>
       <c r="H1324" t="n">
         <v>11339</v>
@@ -38794,7 +38794,7 @@
         <v>26</v>
       </c>
       <c r="G1325" t="n">
-        <v>24.0984115600586</v>
+        <v>24.0984134674072</v>
       </c>
       <c r="H1325" t="n">
         <v>17104</v>
@@ -38852,7 +38852,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>25.3033332824707</v>
+        <v>25.3033313751221</v>
       </c>
       <c r="H1327" t="n">
         <v>29720</v>
@@ -38910,7 +38910,7 @@
         <v>27.75</v>
       </c>
       <c r="G1329" t="n">
-        <v>25.720422744751</v>
+        <v>25.7204208374023</v>
       </c>
       <c r="H1329" t="n">
         <v>7898</v>
@@ -39229,7 +39229,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>25.5350494384766</v>
+        <v>25.5350475311279</v>
       </c>
       <c r="H1340" t="n">
         <v>7940</v>
@@ -39316,7 +39316,7 @@
         <v>28.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>26.4155693054199</v>
+        <v>26.4155673980713</v>
       </c>
       <c r="H1343" t="n">
         <v>17193</v>
@@ -39345,7 +39345,7 @@
         <v>29</v>
       </c>
       <c r="G1344" t="n">
-        <v>26.8789978027344</v>
+        <v>26.878999710083</v>
       </c>
       <c r="H1344" t="n">
         <v>16994</v>
@@ -39374,7 +39374,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>26.2301959991455</v>
+        <v>26.2301940917969</v>
       </c>
       <c r="H1345" t="n">
         <v>26909</v>
@@ -39432,7 +39432,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1347" t="n">
         <v>13917</v>
@@ -39461,7 +39461,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>27.0180263519287</v>
+        <v>27.0180282592773</v>
       </c>
       <c r="H1348" t="n">
         <v>8737</v>
@@ -39548,7 +39548,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1351" t="n">
         <v>20501</v>
@@ -39577,7 +39577,7 @@
         <v>29.75</v>
       </c>
       <c r="G1352" t="n">
-        <v>27.5741443634033</v>
+        <v>27.574146270752</v>
       </c>
       <c r="H1352" t="n">
         <v>16729</v>
@@ -39693,7 +39693,7 @@
         <v>32.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1356" t="n">
         <v>75277</v>
@@ -39722,7 +39722,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1357" t="n">
         <v>36177</v>
@@ -39751,7 +39751,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1358" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1358" t="n">
         <v>16319</v>
@@ -39809,7 +39809,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1360" t="n">
-        <v>31.2352523803711</v>
+        <v>31.2352504730225</v>
       </c>
       <c r="H1360" t="n">
         <v>14299</v>
@@ -39867,7 +39867,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.188907623291</v>
+        <v>31.1889095306396</v>
       </c>
       <c r="H1362" t="n">
         <v>13411</v>
@@ -39896,7 +39896,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1363" t="n">
         <v>7826</v>
@@ -39954,7 +39954,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>31.8377113342285</v>
+        <v>31.8377075195312</v>
       </c>
       <c r="H1365" t="n">
         <v>22255</v>
@@ -39983,7 +39983,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1366" t="n">
-        <v>31.0962219238281</v>
+        <v>31.0962200164795</v>
       </c>
       <c r="H1366" t="n">
         <v>49622</v>
@@ -40041,7 +40041,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>30.9571914672852</v>
+        <v>30.9571933746338</v>
       </c>
       <c r="H1368" t="n">
         <v>11052</v>
@@ -40070,7 +40070,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1369" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1369" t="n">
         <v>31735</v>
@@ -40099,7 +40099,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>31.9303970336914</v>
+        <v>31.93039894104</v>
       </c>
       <c r="H1370" t="n">
         <v>19225</v>
@@ -40244,7 +40244,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>31.5596504211426</v>
+        <v>31.5596523284912</v>
       </c>
       <c r="H1375" t="n">
         <v>14100</v>
@@ -40273,7 +40273,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.8840560913086</v>
+        <v>31.88405418396</v>
       </c>
       <c r="H1376" t="n">
         <v>10686</v>
@@ -40302,7 +40302,7 @@
         <v>33.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.049877166748</v>
+        <v>31.0498790740967</v>
       </c>
       <c r="H1377" t="n">
         <v>13797</v>
@@ -40331,7 +40331,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.6986808776855</v>
+        <v>31.6986827850342</v>
       </c>
       <c r="H1378" t="n">
         <v>16079</v>
@@ -40476,7 +40476,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>32.7182312011719</v>
+        <v>32.7182273864746</v>
       </c>
       <c r="H1383" t="n">
         <v>16458</v>
@@ -40708,7 +40708,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>33.6914367675781</v>
+        <v>33.6914329528809</v>
       </c>
       <c r="H1391" t="n">
         <v>5315</v>
@@ -40766,7 +40766,7 @@
         <v>37.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1393" t="n">
         <v>20537</v>
@@ -40911,7 +40911,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G1398" t="n">
-        <v>35.3597869873047</v>
+        <v>35.359790802002</v>
       </c>
       <c r="H1398" t="n">
         <v>20503</v>
@@ -40969,7 +40969,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1400" t="n">
         <v>25006</v>
@@ -40998,7 +40998,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1401" t="n">
         <v>9472</v>
@@ -41056,7 +41056,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.4988136291504</v>
+        <v>35.4988174438477</v>
       </c>
       <c r="H1403" t="n">
         <v>23148</v>
@@ -41085,7 +41085,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>35.1744117736816</v>
+        <v>35.1744155883789</v>
       </c>
       <c r="H1404" t="n">
         <v>45623</v>
@@ -41114,7 +41114,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1405" t="n">
         <v>28718</v>
@@ -41201,7 +41201,7 @@
         <v>37.75</v>
       </c>
       <c r="G1408" t="n">
-        <v>34.9890403747559</v>
+        <v>34.9890441894531</v>
       </c>
       <c r="H1408" t="n">
         <v>18517</v>
@@ -41259,7 +41259,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>34.2012138366699</v>
+        <v>34.2012100219727</v>
       </c>
       <c r="H1410" t="n">
         <v>15419</v>
@@ -41317,7 +41317,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G1412" t="n">
-        <v>34.6182975769043</v>
+        <v>34.618293762207</v>
       </c>
       <c r="H1412" t="n">
         <v>38690</v>
@@ -41346,7 +41346,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>35.0353813171387</v>
+        <v>35.0353851318359</v>
       </c>
       <c r="H1413" t="n">
         <v>44206</v>
@@ -41404,7 +41404,7 @@
         <v>38.75</v>
       </c>
       <c r="G1415" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H1415" t="n">
         <v>21797</v>
@@ -41433,7 +41433,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>36.5183639526367</v>
+        <v>36.518367767334</v>
       </c>
       <c r="H1416" t="n">
         <v>19385</v>
@@ -41520,7 +41520,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1419" t="n">
-        <v>36.0085868835449</v>
+        <v>36.0085906982422</v>
       </c>
       <c r="H1419" t="n">
         <v>19338</v>
@@ -41607,7 +41607,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1422" t="n">
         <v>28131</v>
@@ -41665,7 +41665,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G1424" t="n">
-        <v>35.5451545715332</v>
+        <v>35.5451583862305</v>
       </c>
       <c r="H1424" t="n">
         <v>37415</v>
@@ -41926,7 +41926,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>29.7059288024902</v>
+        <v>29.7059268951416</v>
       </c>
       <c r="H1433" t="n">
         <v>169855</v>
@@ -41955,7 +41955,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1434" t="n">
         <v>83833</v>
@@ -41984,7 +41984,7 @@
         <v>32.5</v>
       </c>
       <c r="G1435" t="n">
-        <v>30.1230144500732</v>
+        <v>30.1230163574219</v>
       </c>
       <c r="H1435" t="n">
         <v>50233</v>
@@ -42100,7 +42100,7 @@
         <v>31.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1439" t="n">
         <v>39783</v>
@@ -42129,7 +42129,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1440" t="n">
         <v>36958</v>
@@ -42187,7 +42187,7 @@
         <v>31.25</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1442" t="n">
         <v>39311</v>
@@ -42332,7 +42332,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>28.1302623748779</v>
+        <v>28.1302642822266</v>
       </c>
       <c r="H1447" t="n">
         <v>48734</v>
@@ -42361,7 +42361,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.6204872131348</v>
+        <v>27.6204891204834</v>
       </c>
       <c r="H1448" t="n">
         <v>29333</v>
@@ -42419,7 +42419,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>26.7863140106201</v>
+        <v>26.7863121032715</v>
       </c>
       <c r="H1450" t="n">
         <v>74959</v>
@@ -42448,7 +42448,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>27.2033996582031</v>
+        <v>27.2034015655518</v>
       </c>
       <c r="H1451" t="n">
         <v>28955</v>
@@ -42506,7 +42506,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>28.3156337738037</v>
+        <v>28.3156356811523</v>
       </c>
       <c r="H1453" t="n">
         <v>45425</v>
@@ -42564,7 +42564,7 @@
         <v>31.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1455" t="n">
         <v>26258</v>
@@ -42622,7 +42622,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>29.0571250915527</v>
+        <v>29.0571269989014</v>
       </c>
       <c r="H1457" t="n">
         <v>41539</v>
@@ -42767,7 +42767,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1462" t="n">
         <v>27647</v>
@@ -42796,7 +42796,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1463" t="n">
         <v>32514</v>
@@ -42825,7 +42825,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>29.3815288543701</v>
+        <v>29.3815269470215</v>
       </c>
       <c r="H1464" t="n">
         <v>59385</v>
@@ -42912,7 +42912,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1467" t="n">
         <v>22423</v>
@@ -42970,7 +42970,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>29.2888412475586</v>
+        <v>29.28883934021</v>
       </c>
       <c r="H1469" t="n">
         <v>33838</v>
@@ -42999,7 +42999,7 @@
         <v>31.25</v>
       </c>
       <c r="G1470" t="n">
-        <v>28.9644393920898</v>
+        <v>28.9644374847412</v>
       </c>
       <c r="H1470" t="n">
         <v>20524</v>
@@ -43028,7 +43028,7 @@
         <v>31.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1471" t="n">
         <v>38899</v>
@@ -43057,7 +43057,7 @@
         <v>31.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>29.1961555480957</v>
+        <v>29.1961536407471</v>
       </c>
       <c r="H1472" t="n">
         <v>26587</v>
@@ -43086,7 +43086,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>29.4742126464844</v>
+        <v>29.4742107391357</v>
       </c>
       <c r="H1473" t="n">
         <v>61483</v>
@@ -43202,7 +43202,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>29.5205574035645</v>
+        <v>29.5205554962158</v>
       </c>
       <c r="H1477" t="n">
         <v>81786</v>
@@ -68786,6 +68786,35 @@
         <v>1532317</v>
       </c>
       <c r="I2359" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2360" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2360" t="n">
+        <v>1.67700004577637</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>1.73800003528595</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>1.6710000038147</v>
+      </c>
+      <c r="F2360" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2360" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="H2360" t="n">
+        <v>446758</v>
+      </c>
+      <c r="I2360" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOV.MI.xlsx
+++ b/data/DOV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>51.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44.8503189086914</v>
+        <v>44.8503227233887</v>
       </c>
       <c r="H2" t="n">
         <v>2040000</v>
@@ -456,7 +456,7 @@
         <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H3" t="n">
         <v>657288</v>
@@ -514,7 +514,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H5" t="n">
         <v>153513</v>
@@ -601,7 +601,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7318496704102</v>
+        <v>46.7318458557129</v>
       </c>
       <c r="H8" t="n">
         <v>57147</v>
@@ -630,7 +630,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G9" t="n">
-        <v>46.8631172180176</v>
+        <v>46.8631210327148</v>
       </c>
       <c r="H9" t="n">
         <v>27464</v>
@@ -659,7 +659,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H10" t="n">
         <v>24546</v>
@@ -688,7 +688,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H11" t="n">
         <v>29103</v>
@@ -804,7 +804,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H15" t="n">
         <v>20957</v>
@@ -833,7 +833,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G16" t="n">
-        <v>47.5632209777832</v>
+        <v>47.5632171630859</v>
       </c>
       <c r="H16" t="n">
         <v>20120</v>
@@ -862,7 +862,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G17" t="n">
-        <v>47.4319534301758</v>
+        <v>47.4319496154785</v>
       </c>
       <c r="H17" t="n">
         <v>9145</v>
@@ -949,7 +949,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0818977355957</v>
+        <v>47.081901550293</v>
       </c>
       <c r="H20" t="n">
         <v>12065</v>
@@ -1007,7 +1007,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>46.469310760498</v>
+        <v>46.4693069458008</v>
       </c>
       <c r="H22" t="n">
         <v>15015</v>
@@ -1036,7 +1036,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2131729125977</v>
+        <v>47.2131652832031</v>
       </c>
       <c r="H23" t="n">
         <v>12588</v>
@@ -1123,7 +1123,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H26" t="n">
         <v>9801</v>
@@ -1152,7 +1152,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>46.6443328857422</v>
+        <v>46.6443290710449</v>
       </c>
       <c r="H27" t="n">
         <v>26079</v>
@@ -1181,7 +1181,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>46.1192588806152</v>
+        <v>46.119255065918</v>
       </c>
       <c r="H28" t="n">
         <v>23503</v>
@@ -1239,7 +1239,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>45.7692108154297</v>
+        <v>45.7692070007324</v>
       </c>
       <c r="H30" t="n">
         <v>7291</v>
@@ -1268,7 +1268,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>46.5130653381348</v>
+        <v>46.513069152832</v>
       </c>
       <c r="H31" t="n">
         <v>8478</v>
@@ -1326,7 +1326,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>45.6816940307617</v>
+        <v>45.6816902160645</v>
       </c>
       <c r="H33" t="n">
         <v>10909</v>
@@ -1355,7 +1355,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>45.8567199707031</v>
+        <v>45.8567237854004</v>
       </c>
       <c r="H34" t="n">
         <v>9627</v>
@@ -1413,7 +1413,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G36" t="n">
-        <v>47.6069755554199</v>
+        <v>47.6069793701172</v>
       </c>
       <c r="H36" t="n">
         <v>14285</v>
@@ -1442,7 +1442,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>46.9068756103516</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H37" t="n">
         <v>10252</v>
@@ -1471,7 +1471,7 @@
         <v>54.1500015258789</v>
       </c>
       <c r="G38" t="n">
-        <v>47.3881950378418</v>
+        <v>47.3881988525391</v>
       </c>
       <c r="H38" t="n">
         <v>10869</v>
@@ -1500,7 +1500,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>46.7756042480469</v>
+        <v>46.7756080627441</v>
       </c>
       <c r="H39" t="n">
         <v>15831</v>
@@ -1587,7 +1587,7 @@
         <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>48.1320495605469</v>
+        <v>48.1320533752441</v>
       </c>
       <c r="H42" t="n">
         <v>26618</v>
@@ -1616,7 +1616,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>48.0882987976074</v>
+        <v>48.0882949829102</v>
       </c>
       <c r="H43" t="n">
         <v>49250</v>
@@ -1645,7 +1645,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H44" t="n">
         <v>43180</v>
@@ -1703,7 +1703,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>46.9068756103516</v>
+        <v>46.9068717956543</v>
       </c>
       <c r="H46" t="n">
         <v>84037</v>
@@ -1732,7 +1732,7 @@
         <v>54.5</v>
       </c>
       <c r="G47" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H47" t="n">
         <v>27840</v>
@@ -1761,7 +1761,7 @@
         <v>54.5</v>
       </c>
       <c r="G48" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H48" t="n">
         <v>4773</v>
@@ -1790,7 +1790,7 @@
         <v>54.5</v>
       </c>
       <c r="G49" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H49" t="n">
         <v>17711</v>
@@ -1819,7 +1819,7 @@
         <v>54.5</v>
       </c>
       <c r="G50" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H50" t="n">
         <v>10948</v>
@@ -1848,7 +1848,7 @@
         <v>54.5</v>
       </c>
       <c r="G51" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H51" t="n">
         <v>4417</v>
@@ -1877,7 +1877,7 @@
         <v>54.5</v>
       </c>
       <c r="G52" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H52" t="n">
         <v>17845</v>
@@ -1906,7 +1906,7 @@
         <v>54.4500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>47.6507339477539</v>
+        <v>47.6507377624512</v>
       </c>
       <c r="H53" t="n">
         <v>13389</v>
@@ -1964,7 +1964,7 @@
         <v>54.5</v>
       </c>
       <c r="G55" t="n">
-        <v>47.6944885253906</v>
+        <v>47.6944847106934</v>
       </c>
       <c r="H55" t="n">
         <v>10059</v>
@@ -1993,7 +1993,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>48.0445365905762</v>
+        <v>48.0445442199707</v>
       </c>
       <c r="H56" t="n">
         <v>39379</v>
@@ -2022,7 +2022,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G57" t="n">
-        <v>50.0135765075684</v>
+        <v>50.0135803222656</v>
       </c>
       <c r="H57" t="n">
         <v>108131</v>
@@ -2051,7 +2051,7 @@
         <v>58.5</v>
       </c>
       <c r="G58" t="n">
-        <v>51.1949996948242</v>
+        <v>51.1950035095215</v>
       </c>
       <c r="H58" t="n">
         <v>44749</v>
@@ -2080,7 +2080,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8577499389648</v>
+        <v>52.8577461242676</v>
       </c>
       <c r="H59" t="n">
         <v>33673</v>
@@ -2138,7 +2138,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G61" t="n">
-        <v>53.2953147888184</v>
+        <v>53.2953071594238</v>
       </c>
       <c r="H61" t="n">
         <v>26683</v>
@@ -2167,7 +2167,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G62" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H62" t="n">
         <v>55414</v>
@@ -2225,7 +2225,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141914367676</v>
       </c>
       <c r="H64" t="n">
         <v>18989</v>
@@ -2283,7 +2283,7 @@
         <v>63.8499984741211</v>
       </c>
       <c r="G66" t="n">
-        <v>55.8769340515137</v>
+        <v>55.8769378662109</v>
       </c>
       <c r="H66" t="n">
         <v>30641</v>
@@ -2312,7 +2312,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>59.3336944580078</v>
+        <v>59.3336868286133</v>
       </c>
       <c r="H67" t="n">
         <v>66049</v>
@@ -2341,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>61.258975982666</v>
+        <v>61.2589836120605</v>
       </c>
       <c r="H68" t="n">
         <v>67523</v>
@@ -2399,7 +2399,7 @@
         <v>70.5</v>
       </c>
       <c r="G70" t="n">
-        <v>61.6965446472168</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H70" t="n">
         <v>102718</v>
@@ -2428,7 +2428,7 @@
         <v>70.5</v>
       </c>
       <c r="G71" t="n">
-        <v>61.6965446472168</v>
+        <v>61.6965408325195</v>
       </c>
       <c r="H71" t="n">
         <v>36807</v>
@@ -2486,7 +2486,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>61.3902473449707</v>
+        <v>61.3902549743652</v>
       </c>
       <c r="H73" t="n">
         <v>19520</v>
@@ -2515,7 +2515,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G74" t="n">
-        <v>61.4339942932129</v>
+        <v>61.4339981079102</v>
       </c>
       <c r="H74" t="n">
         <v>16990</v>
@@ -2544,7 +2544,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>60.9964332580566</v>
+        <v>60.9964370727539</v>
       </c>
       <c r="H75" t="n">
         <v>21825</v>
@@ -2573,7 +2573,7 @@
         <v>68.5</v>
       </c>
       <c r="G76" t="n">
-        <v>59.9462814331055</v>
+        <v>59.9462852478027</v>
       </c>
       <c r="H76" t="n">
         <v>17560</v>
@@ -2602,7 +2602,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>59.6399879455566</v>
+        <v>59.6399955749512</v>
       </c>
       <c r="H77" t="n">
         <v>24608</v>
@@ -2631,7 +2631,7 @@
         <v>68.25</v>
       </c>
       <c r="G78" t="n">
-        <v>59.7275009155273</v>
+        <v>59.7274932861328</v>
       </c>
       <c r="H78" t="n">
         <v>23532</v>
@@ -2660,7 +2660,7 @@
         <v>69</v>
       </c>
       <c r="G79" t="n">
-        <v>60.383846282959</v>
+        <v>60.3838424682617</v>
       </c>
       <c r="H79" t="n">
         <v>10644</v>
@@ -2689,7 +2689,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>60.0775566101074</v>
+        <v>60.0775604248047</v>
       </c>
       <c r="H80" t="n">
         <v>17247</v>
@@ -2718,7 +2718,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G81" t="n">
-        <v>60.4276123046875</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H81" t="n">
         <v>22156</v>
@@ -2747,7 +2747,7 @@
         <v>69.25</v>
       </c>
       <c r="G82" t="n">
-        <v>60.6026344299316</v>
+        <v>60.6026306152344</v>
       </c>
       <c r="H82" t="n">
         <v>33403</v>
@@ -2776,7 +2776,7 @@
         <v>69.5</v>
       </c>
       <c r="G83" t="n">
-        <v>60.8214149475098</v>
+        <v>60.8214111328125</v>
       </c>
       <c r="H83" t="n">
         <v>40181</v>
@@ -2805,7 +2805,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>58.5898284912109</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H84" t="n">
         <v>42984</v>
@@ -2834,7 +2834,7 @@
         <v>65.4499969482422</v>
       </c>
       <c r="G85" t="n">
-        <v>57.2771377563477</v>
+        <v>57.2771339416504</v>
       </c>
       <c r="H85" t="n">
         <v>30458</v>
@@ -2921,7 +2921,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H88" t="n">
         <v>37736</v>
@@ -2950,7 +2950,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H89" t="n">
         <v>30442</v>
@@ -2979,7 +2979,7 @@
         <v>66.6500015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>58.3272933959961</v>
+        <v>58.3272972106934</v>
       </c>
       <c r="H90" t="n">
         <v>24556</v>
@@ -3037,7 +3037,7 @@
         <v>66.5</v>
       </c>
       <c r="G92" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H92" t="n">
         <v>27229</v>
@@ -3066,7 +3066,7 @@
         <v>67.5</v>
       </c>
       <c r="G93" t="n">
-        <v>59.0711555480957</v>
+        <v>59.0711517333984</v>
       </c>
       <c r="H93" t="n">
         <v>36066</v>
@@ -3124,7 +3124,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G95" t="n">
-        <v>59.0273971557617</v>
+        <v>59.027400970459</v>
       </c>
       <c r="H95" t="n">
         <v>15063</v>
@@ -3153,7 +3153,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H96" t="n">
         <v>12506</v>
@@ -3211,7 +3211,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>57.5834350585938</v>
+        <v>57.5834426879883</v>
       </c>
       <c r="H98" t="n">
         <v>29467</v>
@@ -3327,7 +3327,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>56.9708442687988</v>
+        <v>56.9708480834961</v>
       </c>
       <c r="H102" t="n">
         <v>41724</v>
@@ -3356,7 +3356,7 @@
         <v>65.75</v>
       </c>
       <c r="G103" t="n">
-        <v>57.5396881103516</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H103" t="n">
         <v>43096</v>
@@ -3385,7 +3385,7 @@
         <v>66.5</v>
       </c>
       <c r="G104" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H104" t="n">
         <v>14812</v>
@@ -3414,7 +3414,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>59.7712593078613</v>
+        <v>59.7712631225586</v>
       </c>
       <c r="H105" t="n">
         <v>21082</v>
@@ -3443,7 +3443,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G106" t="n">
-        <v>60.4276123046875</v>
+        <v>60.427604675293</v>
       </c>
       <c r="H106" t="n">
         <v>12395</v>
@@ -3472,7 +3472,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>60.2525787353516</v>
+        <v>60.252571105957</v>
       </c>
       <c r="H107" t="n">
         <v>19415</v>
@@ -3530,7 +3530,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>58.5898284912109</v>
+        <v>58.5898323059082</v>
       </c>
       <c r="H109" t="n">
         <v>13730</v>
@@ -3617,7 +3617,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G112" t="n">
-        <v>55.7456703186035</v>
+        <v>55.7456665039062</v>
       </c>
       <c r="H112" t="n">
         <v>100799</v>
@@ -3675,7 +3675,7 @@
         <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H114" t="n">
         <v>54000</v>
@@ -3704,7 +3704,7 @@
         <v>63</v>
       </c>
       <c r="G115" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H115" t="n">
         <v>26197</v>
@@ -3733,7 +3733,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G116" t="n">
-        <v>57.6709518432617</v>
+        <v>57.670955657959</v>
       </c>
       <c r="H116" t="n">
         <v>53938</v>
@@ -3762,7 +3762,7 @@
         <v>66.1500015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>57.8897323608398</v>
+        <v>57.8897285461426</v>
       </c>
       <c r="H117" t="n">
         <v>15058</v>
@@ -3820,7 +3820,7 @@
         <v>67.75</v>
       </c>
       <c r="G119" t="n">
-        <v>59.2899360656738</v>
+        <v>59.2899398803711</v>
       </c>
       <c r="H119" t="n">
         <v>12050</v>
@@ -3849,7 +3849,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>57.9334869384766</v>
+        <v>57.9334945678711</v>
       </c>
       <c r="H120" t="n">
         <v>11962</v>
@@ -3878,7 +3878,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G121" t="n">
-        <v>59.2461814880371</v>
+        <v>59.2461738586426</v>
       </c>
       <c r="H121" t="n">
         <v>10529</v>
@@ -3907,7 +3907,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G122" t="n">
-        <v>59.5962257385254</v>
+        <v>59.5962295532227</v>
       </c>
       <c r="H122" t="n">
         <v>11881</v>
@@ -3936,7 +3936,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G123" t="n">
-        <v>59.9900398254395</v>
+        <v>59.9900436401367</v>
       </c>
       <c r="H123" t="n">
         <v>14704</v>
@@ -3965,7 +3965,7 @@
         <v>66.5</v>
       </c>
       <c r="G124" t="n">
-        <v>58.1960220336914</v>
+        <v>58.1960296630859</v>
       </c>
       <c r="H124" t="n">
         <v>22889</v>
@@ -3994,7 +3994,7 @@
         <v>66.5500030517578</v>
       </c>
       <c r="G125" t="n">
-        <v>58.2397918701172</v>
+        <v>58.2397880554199</v>
       </c>
       <c r="H125" t="n">
         <v>21955</v>
@@ -4052,7 +4052,7 @@
         <v>64.6500015258789</v>
       </c>
       <c r="G127" t="n">
-        <v>56.5770416259766</v>
+        <v>56.5770454406738</v>
       </c>
       <c r="H127" t="n">
         <v>42192</v>
@@ -4110,7 +4110,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>56.2707481384277</v>
+        <v>56.2707443237305</v>
       </c>
       <c r="H129" t="n">
         <v>14664</v>
@@ -4197,7 +4197,7 @@
         <v>65.1500015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>57.0146102905273</v>
+        <v>57.0146064758301</v>
       </c>
       <c r="H132" t="n">
         <v>14544</v>
@@ -4226,7 +4226,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G133" t="n">
-        <v>56.6207962036133</v>
+        <v>56.620792388916</v>
       </c>
       <c r="H133" t="n">
         <v>17767</v>
@@ -4313,7 +4313,7 @@
         <v>65.75</v>
       </c>
       <c r="G136" t="n">
-        <v>57.5396881103516</v>
+        <v>57.539680480957</v>
       </c>
       <c r="H136" t="n">
         <v>78309</v>
@@ -4400,7 +4400,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>56.7958221435547</v>
+        <v>56.7958183288574</v>
       </c>
       <c r="H139" t="n">
         <v>15720</v>
@@ -4429,7 +4429,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>55.4831275939941</v>
+        <v>55.4831352233887</v>
       </c>
       <c r="H140" t="n">
         <v>20009</v>
@@ -4487,7 +4487,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>55.264347076416</v>
+        <v>55.2643508911133</v>
       </c>
       <c r="H142" t="n">
         <v>21545</v>
@@ -4574,7 +4574,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G145" t="n">
-        <v>54.3892250061035</v>
+        <v>54.3892211914062</v>
       </c>
       <c r="H145" t="n">
         <v>31730</v>
@@ -4632,7 +4632,7 @@
         <v>63.25</v>
       </c>
       <c r="G147" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H147" t="n">
         <v>49677</v>
@@ -4661,7 +4661,7 @@
         <v>64.1500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>56.1394805908203</v>
+        <v>56.139476776123</v>
       </c>
       <c r="H148" t="n">
         <v>21802</v>
@@ -4690,7 +4690,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H149" t="n">
         <v>19902</v>
@@ -4748,7 +4748,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G151" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H151" t="n">
         <v>13363</v>
@@ -4777,7 +4777,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H152" t="n">
         <v>6908</v>
@@ -4806,7 +4806,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H153" t="n">
         <v>14177</v>
@@ -4835,7 +4835,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>54.1266784667969</v>
+        <v>54.1266860961914</v>
       </c>
       <c r="H154" t="n">
         <v>9673</v>
@@ -4864,7 +4864,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>53.5578536987305</v>
+        <v>53.5578498840332</v>
       </c>
       <c r="H155" t="n">
         <v>11308</v>
@@ -4922,7 +4922,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>52.1138877868652</v>
+        <v>52.113883972168</v>
       </c>
       <c r="H157" t="n">
         <v>24689</v>
@@ -4951,7 +4951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>52.3326644897461</v>
+        <v>52.3326683044434</v>
       </c>
       <c r="H158" t="n">
         <v>18256</v>
@@ -5096,7 +5096,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>49.3572387695312</v>
+        <v>49.357234954834</v>
       </c>
       <c r="H163" t="n">
         <v>14934</v>
@@ -5125,7 +5125,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H164" t="n">
         <v>9928</v>
@@ -5154,7 +5154,7 @@
         <v>55.75</v>
       </c>
       <c r="G165" t="n">
-        <v>48.788402557373</v>
+        <v>48.7883949279785</v>
       </c>
       <c r="H165" t="n">
         <v>49976</v>
@@ -5241,7 +5241,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>52.4201812744141</v>
+        <v>52.4201850891113</v>
       </c>
       <c r="H168" t="n">
         <v>15941</v>
@@ -5299,7 +5299,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H170" t="n">
         <v>15151</v>
@@ -5328,7 +5328,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G171" t="n">
-        <v>52.2014007568359</v>
+        <v>52.2013969421387</v>
       </c>
       <c r="H171" t="n">
         <v>6434</v>
@@ -5386,7 +5386,7 @@
         <v>59.75</v>
       </c>
       <c r="G173" t="n">
-        <v>52.2889099121094</v>
+        <v>52.2889137268066</v>
       </c>
       <c r="H173" t="n">
         <v>8713</v>
@@ -5415,7 +5415,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>52.2014007568359</v>
+        <v>52.2013969421387</v>
       </c>
       <c r="H174" t="n">
         <v>4529</v>
@@ -5444,7 +5444,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>51.9826164245605</v>
+        <v>51.9826202392578</v>
       </c>
       <c r="H175" t="n">
         <v>7119</v>
@@ -5473,7 +5473,7 @@
         <v>57.6500015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>50.4511413574219</v>
+        <v>50.4511451721191</v>
       </c>
       <c r="H176" t="n">
         <v>8990</v>
@@ -5502,7 +5502,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G177" t="n">
-        <v>49.7510375976562</v>
+        <v>49.751033782959</v>
       </c>
       <c r="H177" t="n">
         <v>11502</v>
@@ -5531,7 +5531,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>49.838550567627</v>
+        <v>49.8385581970215</v>
       </c>
       <c r="H178" t="n">
         <v>9563</v>
@@ -5560,7 +5560,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H179" t="n">
         <v>6559</v>
@@ -5589,7 +5589,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>49.2697219848633</v>
+        <v>49.269718170166</v>
       </c>
       <c r="H180" t="n">
         <v>6556</v>
@@ -5618,7 +5618,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>48.6571311950684</v>
+        <v>48.6571273803711</v>
       </c>
       <c r="H181" t="n">
         <v>8552</v>
@@ -5705,7 +5705,7 @@
         <v>58.75</v>
       </c>
       <c r="G184" t="n">
-        <v>51.4137878417969</v>
+        <v>51.4137840270996</v>
       </c>
       <c r="H184" t="n">
         <v>13554</v>
@@ -5821,7 +5821,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G188" t="n">
-        <v>53.0765266418457</v>
+        <v>53.076530456543</v>
       </c>
       <c r="H188" t="n">
         <v>7403</v>
@@ -5850,7 +5850,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141914367676</v>
       </c>
       <c r="H189" t="n">
         <v>14775</v>
@@ -5879,7 +5879,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H190" t="n">
         <v>5217</v>
@@ -5908,7 +5908,7 @@
         <v>61.6500015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>53.95166015625</v>
+        <v>53.9516563415527</v>
       </c>
       <c r="H191" t="n">
         <v>10146</v>
@@ -5937,7 +5937,7 @@
         <v>61.1500015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>53.5140953063965</v>
+        <v>53.5140991210938</v>
       </c>
       <c r="H192" t="n">
         <v>8624</v>
@@ -5966,7 +5966,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>53.7328720092773</v>
+        <v>53.7328758239746</v>
       </c>
       <c r="H193" t="n">
         <v>9212</v>
@@ -5995,7 +5995,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>52.9015007019043</v>
+        <v>52.9015045166016</v>
       </c>
       <c r="H194" t="n">
         <v>32354</v>
@@ -6024,7 +6024,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>53.2078018188477</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H195" t="n">
         <v>12593</v>
@@ -6053,7 +6053,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>53.2078018188477</v>
+        <v>53.2077941894531</v>
       </c>
       <c r="H196" t="n">
         <v>9058</v>
@@ -6082,7 +6082,7 @@
         <v>62.0499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>54.3017044067383</v>
+        <v>54.3017082214355</v>
       </c>
       <c r="H197" t="n">
         <v>7723</v>
@@ -6169,7 +6169,7 @@
         <v>63.25</v>
       </c>
       <c r="G200" t="n">
-        <v>55.351863861084</v>
+        <v>55.3518600463867</v>
       </c>
       <c r="H200" t="n">
         <v>18598</v>
@@ -6198,7 +6198,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>55.0893287658691</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H201" t="n">
         <v>6238</v>
@@ -6227,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="G202" t="n">
-        <v>55.1330757141113</v>
+        <v>55.1330795288086</v>
       </c>
       <c r="H202" t="n">
         <v>6204</v>
@@ -6256,7 +6256,7 @@
         <v>62.75</v>
       </c>
       <c r="G203" t="n">
-        <v>54.9142990112305</v>
+        <v>54.9142951965332</v>
       </c>
       <c r="H203" t="n">
         <v>6842</v>
@@ -6285,7 +6285,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G204" t="n">
-        <v>53.6891174316406</v>
+        <v>53.6891098022461</v>
       </c>
       <c r="H204" t="n">
         <v>7160</v>
@@ -6343,7 +6343,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G206" t="n">
-        <v>53.9078941345215</v>
+        <v>53.907901763916</v>
       </c>
       <c r="H206" t="n">
         <v>2508</v>
@@ -6372,7 +6372,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>54.2141952514648</v>
+        <v>54.2141914367676</v>
       </c>
       <c r="H207" t="n">
         <v>6821</v>
@@ -6401,7 +6401,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>54.7830276489258</v>
+        <v>54.7830238342285</v>
       </c>
       <c r="H208" t="n">
         <v>8498</v>
@@ -6430,7 +6430,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>53.3390655517578</v>
+        <v>53.3390693664551</v>
       </c>
       <c r="H209" t="n">
         <v>5310</v>
@@ -6459,7 +6459,7 @@
         <v>62.0999984741211</v>
       </c>
       <c r="G210" t="n">
-        <v>54.3454627990723</v>
+        <v>54.345458984375</v>
       </c>
       <c r="H210" t="n">
         <v>5210</v>
@@ -6488,7 +6488,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>55.0893287658691</v>
+        <v>55.0893249511719</v>
       </c>
       <c r="H211" t="n">
         <v>25353</v>
@@ -6604,7 +6604,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>47.869514465332</v>
+        <v>47.8695182800293</v>
       </c>
       <c r="H215" t="n">
         <v>37069</v>
@@ -6633,7 +6633,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>44.6623039245605</v>
+        <v>44.6623001098633</v>
       </c>
       <c r="H216" t="n">
         <v>40064</v>
@@ -6662,7 +6662,7 @@
         <v>50.3499984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>44.6179885864258</v>
+        <v>44.6179847717285</v>
       </c>
       <c r="H217" t="n">
         <v>21183</v>
@@ -6691,7 +6691,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>45.5041427612305</v>
+        <v>45.5041465759277</v>
       </c>
       <c r="H218" t="n">
         <v>23030</v>
@@ -6749,7 +6749,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>46.0358390808105</v>
+        <v>46.0358428955078</v>
       </c>
       <c r="H220" t="n">
         <v>30045</v>
@@ -6778,7 +6778,7 @@
         <v>47.875</v>
       </c>
       <c r="G221" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H221" t="n">
         <v>57447</v>
@@ -6894,7 +6894,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G225" t="n">
-        <v>44.9281425476074</v>
+        <v>44.9281463623047</v>
       </c>
       <c r="H225" t="n">
         <v>28013</v>
@@ -7010,7 +7010,7 @@
         <v>48.5</v>
       </c>
       <c r="G229" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H229" t="n">
         <v>13302</v>
@@ -7068,7 +7068,7 @@
         <v>48.5</v>
       </c>
       <c r="G231" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H231" t="n">
         <v>13204</v>
@@ -7097,7 +7097,7 @@
         <v>48.5</v>
       </c>
       <c r="G232" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H232" t="n">
         <v>19410</v>
@@ -7126,7 +7126,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H233" t="n">
         <v>12552</v>
@@ -7213,7 +7213,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G236" t="n">
-        <v>48.8272323608398</v>
+        <v>48.8272285461426</v>
       </c>
       <c r="H236" t="n">
         <v>13514</v>
@@ -7271,7 +7271,7 @@
         <v>57.75</v>
       </c>
       <c r="G238" t="n">
-        <v>51.1755485534668</v>
+        <v>51.1755447387695</v>
       </c>
       <c r="H238" t="n">
         <v>56868</v>
@@ -7300,7 +7300,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>49.4475402832031</v>
+        <v>49.4475440979004</v>
       </c>
       <c r="H239" t="n">
         <v>23506</v>
@@ -7503,7 +7503,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>48.915843963623</v>
+        <v>48.9158515930176</v>
       </c>
       <c r="H246" t="n">
         <v>24867</v>
@@ -7561,7 +7561,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>50.9983139038086</v>
+        <v>50.9983177185059</v>
       </c>
       <c r="H248" t="n">
         <v>36235</v>
@@ -7677,7 +7677,7 @@
         <v>55.1500015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8715438842773</v>
+        <v>48.8715400695801</v>
       </c>
       <c r="H252" t="n">
         <v>19047</v>
@@ -7764,7 +7764,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>48.33984375</v>
+        <v>48.3398475646973</v>
       </c>
       <c r="H255" t="n">
         <v>7923</v>
@@ -7938,7 +7938,7 @@
         <v>51.5</v>
       </c>
       <c r="G261" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H261" t="n">
         <v>6730</v>
@@ -7967,7 +7967,7 @@
         <v>51.5</v>
       </c>
       <c r="G262" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H262" t="n">
         <v>12401</v>
@@ -7996,7 +7996,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G263" t="n">
-        <v>45.1496849060059</v>
+        <v>45.1496810913086</v>
       </c>
       <c r="H263" t="n">
         <v>17681</v>
@@ -8025,7 +8025,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G264" t="n">
-        <v>44.2192230224609</v>
+        <v>44.2192192077637</v>
       </c>
       <c r="H264" t="n">
         <v>24452</v>
@@ -8054,7 +8054,7 @@
         <v>50</v>
       </c>
       <c r="G265" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H265" t="n">
         <v>13686</v>
@@ -8083,7 +8083,7 @@
         <v>50</v>
       </c>
       <c r="G266" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H266" t="n">
         <v>13575</v>
@@ -8141,7 +8141,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G268" t="n">
-        <v>45.5927619934082</v>
+        <v>45.5927658081055</v>
       </c>
       <c r="H268" t="n">
         <v>9230</v>
@@ -8170,7 +8170,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G269" t="n">
-        <v>45.371223449707</v>
+        <v>45.3712272644043</v>
       </c>
       <c r="H269" t="n">
         <v>7135</v>
@@ -8228,7 +8228,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G271" t="n">
-        <v>46.4346122741699</v>
+        <v>46.4346160888672</v>
       </c>
       <c r="H271" t="n">
         <v>6611</v>
@@ -8286,7 +8286,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G273" t="n">
-        <v>45.7700004577637</v>
+        <v>45.7699966430664</v>
       </c>
       <c r="H273" t="n">
         <v>5066</v>
@@ -8315,7 +8315,7 @@
         <v>51.75</v>
       </c>
       <c r="G274" t="n">
-        <v>45.8586082458496</v>
+        <v>45.8586120605469</v>
       </c>
       <c r="H274" t="n">
         <v>4374</v>
@@ -8344,7 +8344,7 @@
         <v>50</v>
       </c>
       <c r="G275" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H275" t="n">
         <v>10055</v>
@@ -8373,7 +8373,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>43.5989112854004</v>
+        <v>43.5989074707031</v>
       </c>
       <c r="H276" t="n">
         <v>6787</v>
@@ -8431,7 +8431,7 @@
         <v>48.5</v>
       </c>
       <c r="G278" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H278" t="n">
         <v>24628</v>
@@ -8460,7 +8460,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H279" t="n">
         <v>13000</v>
@@ -8489,7 +8489,7 @@
         <v>48.5</v>
       </c>
       <c r="G280" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H280" t="n">
         <v>5708</v>
@@ -8518,7 +8518,7 @@
         <v>48.4249992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>42.9121360778809</v>
+        <v>42.9121398925781</v>
       </c>
       <c r="H281" t="n">
         <v>13077</v>
@@ -8576,7 +8576,7 @@
         <v>48.25</v>
       </c>
       <c r="G283" t="n">
-        <v>42.7570571899414</v>
+        <v>42.7570610046387</v>
       </c>
       <c r="H283" t="n">
         <v>10993</v>
@@ -8779,7 +8779,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H290" t="n">
         <v>2864</v>
@@ -8866,7 +8866,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H293" t="n">
         <v>11169</v>
@@ -8953,7 +8953,7 @@
         <v>48.5750007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>43.0450630187988</v>
+        <v>43.0450592041016</v>
       </c>
       <c r="H296" t="n">
         <v>6836</v>
@@ -8982,7 +8982,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H297" t="n">
         <v>6144</v>
@@ -9011,7 +9011,7 @@
         <v>48.6500015258789</v>
       </c>
       <c r="G298" t="n">
-        <v>43.1115264892578</v>
+        <v>43.1115226745605</v>
       </c>
       <c r="H298" t="n">
         <v>11117</v>
@@ -9040,7 +9040,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>43.2444458007812</v>
+        <v>43.244441986084</v>
       </c>
       <c r="H299" t="n">
         <v>1630</v>
@@ -9127,7 +9127,7 @@
         <v>49.375</v>
       </c>
       <c r="G302" t="n">
-        <v>43.7539825439453</v>
+        <v>43.7539863586426</v>
       </c>
       <c r="H302" t="n">
         <v>6369</v>
@@ -9214,7 +9214,7 @@
         <v>48.5</v>
       </c>
       <c r="G305" t="n">
-        <v>42.9785995483398</v>
+        <v>42.9786033630371</v>
       </c>
       <c r="H305" t="n">
         <v>7770</v>
@@ -9243,7 +9243,7 @@
         <v>48.2249984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>42.7349090576172</v>
+        <v>42.7349052429199</v>
       </c>
       <c r="H306" t="n">
         <v>4806</v>
@@ -9272,7 +9272,7 @@
         <v>47</v>
       </c>
       <c r="G307" t="n">
-        <v>41.6493644714355</v>
+        <v>41.6493682861328</v>
       </c>
       <c r="H307" t="n">
         <v>14885</v>
@@ -9417,7 +9417,7 @@
         <v>45.9749984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>40.7410507202148</v>
+        <v>40.7410545349121</v>
       </c>
       <c r="H312" t="n">
         <v>1751</v>
@@ -9446,7 +9446,7 @@
         <v>46.5</v>
       </c>
       <c r="G313" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H313" t="n">
         <v>4752</v>
@@ -9504,7 +9504,7 @@
         <v>45.7750015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>40.5638236999512</v>
+        <v>40.5638198852539</v>
       </c>
       <c r="H315" t="n">
         <v>9876</v>
@@ -9562,7 +9562,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>38.946590423584</v>
+        <v>38.9465866088867</v>
       </c>
       <c r="H317" t="n">
         <v>12514</v>
@@ -9620,7 +9620,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>39.4782829284668</v>
+        <v>39.4782791137695</v>
       </c>
       <c r="H319" t="n">
         <v>3338</v>
@@ -9736,7 +9736,7 @@
         <v>45</v>
       </c>
       <c r="G323" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H323" t="n">
         <v>2457</v>
@@ -9794,7 +9794,7 @@
         <v>45</v>
       </c>
       <c r="G325" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H325" t="n">
         <v>6799</v>
@@ -9823,7 +9823,7 @@
         <v>43.75</v>
       </c>
       <c r="G326" t="n">
-        <v>38.7693519592285</v>
+        <v>38.7693557739258</v>
       </c>
       <c r="H326" t="n">
         <v>16647</v>
@@ -9852,7 +9852,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H327" t="n">
         <v>5952</v>
@@ -9881,7 +9881,7 @@
         <v>45.9249992370605</v>
       </c>
       <c r="G328" t="n">
-        <v>40.6967468261719</v>
+        <v>40.6967391967773</v>
       </c>
       <c r="H328" t="n">
         <v>2339</v>
@@ -9968,7 +9968,7 @@
         <v>45.4500007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>40.275821685791</v>
+        <v>40.2758255004883</v>
       </c>
       <c r="H331" t="n">
         <v>6546</v>
@@ -10055,7 +10055,7 @@
         <v>47.875</v>
       </c>
       <c r="G334" t="n">
-        <v>42.4247550964355</v>
+        <v>42.4247512817383</v>
       </c>
       <c r="H334" t="n">
         <v>7541</v>
@@ -10084,7 +10084,7 @@
         <v>47.9249992370605</v>
       </c>
       <c r="G335" t="n">
-        <v>42.4690551757812</v>
+        <v>42.4690589904785</v>
       </c>
       <c r="H335" t="n">
         <v>4050</v>
@@ -10113,7 +10113,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>41.006908416748</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H336" t="n">
         <v>3396</v>
@@ -10142,7 +10142,7 @@
         <v>46.5</v>
       </c>
       <c r="G337" t="n">
-        <v>41.2062873840332</v>
+        <v>41.2062835693359</v>
       </c>
       <c r="H337" t="n">
         <v>2833</v>
@@ -10200,7 +10200,7 @@
         <v>48.125</v>
       </c>
       <c r="G339" t="n">
-        <v>42.6462860107422</v>
+        <v>42.6462898254395</v>
       </c>
       <c r="H339" t="n">
         <v>10608</v>
@@ -10258,7 +10258,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>42.2696800231934</v>
+        <v>42.2696762084961</v>
       </c>
       <c r="H341" t="n">
         <v>4403</v>
@@ -10345,7 +10345,7 @@
         <v>46.2750015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>41.006908416748</v>
+        <v>41.0069046020508</v>
       </c>
       <c r="H344" t="n">
         <v>8882</v>
@@ -10577,7 +10577,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G352" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H352" t="n">
         <v>69766</v>
@@ -10635,7 +10635,7 @@
         <v>51.5</v>
       </c>
       <c r="G354" t="n">
-        <v>45.6370697021484</v>
+        <v>45.6370735168457</v>
       </c>
       <c r="H354" t="n">
         <v>11332</v>
@@ -10664,7 +10664,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>47.2764625549316</v>
+        <v>47.2764587402344</v>
       </c>
       <c r="H355" t="n">
         <v>19543</v>
@@ -10780,7 +10780,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G359" t="n">
-        <v>46.833381652832</v>
+        <v>46.8333778381348</v>
       </c>
       <c r="H359" t="n">
         <v>4295</v>
@@ -10838,7 +10838,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>44.3964462280273</v>
+        <v>44.3964500427246</v>
       </c>
       <c r="H361" t="n">
         <v>27594</v>
@@ -10983,7 +10983,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>40.4973602294922</v>
+        <v>40.4973564147949</v>
       </c>
       <c r="H366" t="n">
         <v>12931</v>
@@ -11012,7 +11012,7 @@
         <v>45.0250015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>39.8992118835449</v>
+        <v>39.8992080688477</v>
       </c>
       <c r="H367" t="n">
         <v>21291</v>
@@ -11070,7 +11070,7 @@
         <v>45</v>
       </c>
       <c r="G369" t="n">
-        <v>39.8770484924316</v>
+        <v>39.8770523071289</v>
       </c>
       <c r="H369" t="n">
         <v>22056</v>
@@ -11157,7 +11157,7 @@
         <v>50</v>
       </c>
       <c r="G372" t="n">
-        <v>44.3078346252441</v>
+        <v>44.3078384399414</v>
       </c>
       <c r="H372" t="n">
         <v>19533</v>
@@ -11244,7 +11244,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6118392944336</v>
+        <v>46.6118431091309</v>
       </c>
       <c r="H375" t="n">
         <v>5727</v>
@@ -11302,7 +11302,7 @@
         <v>57</v>
       </c>
       <c r="G377" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H377" t="n">
         <v>57780</v>
@@ -11331,7 +11331,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>50.3780097961426</v>
+        <v>50.378002166748</v>
       </c>
       <c r="H378" t="n">
         <v>10777</v>
@@ -11534,7 +11534,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>50.1121635437012</v>
+        <v>50.1121597290039</v>
       </c>
       <c r="H385" t="n">
         <v>7427</v>
@@ -11621,7 +11621,7 @@
         <v>56.25</v>
       </c>
       <c r="G388" t="n">
-        <v>49.8463134765625</v>
+        <v>49.8463096618652</v>
       </c>
       <c r="H388" t="n">
         <v>9469</v>
@@ -11737,7 +11737,7 @@
         <v>59</v>
       </c>
       <c r="G392" t="n">
-        <v>52.2832450866699</v>
+        <v>52.2832412719727</v>
       </c>
       <c r="H392" t="n">
         <v>23027</v>
@@ -11882,7 +11882,7 @@
         <v>61</v>
       </c>
       <c r="G397" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H397" t="n">
         <v>35572</v>
@@ -11911,7 +11911,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>53.3466300964355</v>
+        <v>53.3466339111328</v>
       </c>
       <c r="H398" t="n">
         <v>16109</v>
@@ -11998,7 +11998,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>54.3657150268555</v>
+        <v>54.3657073974609</v>
       </c>
       <c r="H401" t="n">
         <v>25933</v>
@@ -12056,7 +12056,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>55.9164924621582</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H403" t="n">
         <v>55252</v>
@@ -12085,7 +12085,7 @@
         <v>60.5</v>
       </c>
       <c r="G404" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H404" t="n">
         <v>12420</v>
@@ -12172,7 +12172,7 @@
         <v>60.5</v>
       </c>
       <c r="G407" t="n">
-        <v>53.612476348877</v>
+        <v>53.6124801635742</v>
       </c>
       <c r="H407" t="n">
         <v>16902</v>
@@ -12201,7 +12201,7 @@
         <v>61</v>
       </c>
       <c r="G408" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H408" t="n">
         <v>15641</v>
@@ -12288,7 +12288,7 @@
         <v>65</v>
       </c>
       <c r="G411" t="n">
-        <v>57.6001892089844</v>
+        <v>57.6001853942871</v>
       </c>
       <c r="H411" t="n">
         <v>34918</v>
@@ -12317,7 +12317,7 @@
         <v>64</v>
       </c>
       <c r="G412" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H412" t="n">
         <v>30587</v>
@@ -12346,7 +12346,7 @@
         <v>64.5</v>
       </c>
       <c r="G413" t="n">
-        <v>57.1571083068848</v>
+        <v>57.157112121582</v>
       </c>
       <c r="H413" t="n">
         <v>28229</v>
@@ -12375,7 +12375,7 @@
         <v>62.9500007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>55.783561706543</v>
+        <v>55.7835655212402</v>
       </c>
       <c r="H414" t="n">
         <v>6786</v>
@@ -12462,7 +12462,7 @@
         <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>58.4863433837891</v>
+        <v>58.4863357543945</v>
       </c>
       <c r="H417" t="n">
         <v>56533</v>
@@ -12578,7 +12578,7 @@
         <v>64</v>
       </c>
       <c r="G421" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H421" t="n">
         <v>23538</v>
@@ -12607,7 +12607,7 @@
         <v>64.8499984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>57.4672622680664</v>
+        <v>57.4672584533691</v>
       </c>
       <c r="H422" t="n">
         <v>5806</v>
@@ -12636,7 +12636,7 @@
         <v>65.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>58.0875778198242</v>
+        <v>58.087574005127</v>
       </c>
       <c r="H423" t="n">
         <v>4303</v>
@@ -12810,7 +12810,7 @@
         <v>63</v>
       </c>
       <c r="G429" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H429" t="n">
         <v>9582</v>
@@ -12839,7 +12839,7 @@
         <v>63</v>
       </c>
       <c r="G430" t="n">
-        <v>55.8278694152832</v>
+        <v>55.8278732299805</v>
       </c>
       <c r="H430" t="n">
         <v>4618</v>
@@ -12984,7 +12984,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>52.0174026489258</v>
+        <v>52.0173988342285</v>
       </c>
       <c r="H435" t="n">
         <v>15195</v>
@@ -13013,7 +13013,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G436" t="n">
-        <v>53.523868560791</v>
+        <v>53.5238647460938</v>
       </c>
       <c r="H436" t="n">
         <v>33271</v>
@@ -13042,7 +13042,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G437" t="n">
-        <v>57.2457237243652</v>
+        <v>57.245719909668</v>
       </c>
       <c r="H437" t="n">
         <v>25131</v>
@@ -13071,7 +13071,7 @@
         <v>64</v>
       </c>
       <c r="G438" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H438" t="n">
         <v>9647</v>
@@ -13100,7 +13100,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>56.1823348999023</v>
+        <v>56.1823387145996</v>
       </c>
       <c r="H439" t="n">
         <v>5633</v>
@@ -13216,7 +13216,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G443" t="n">
-        <v>55.7392616271973</v>
+        <v>55.7392578125</v>
       </c>
       <c r="H443" t="n">
         <v>5854</v>
@@ -13245,7 +13245,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G444" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798736572266</v>
       </c>
       <c r="H444" t="n">
         <v>6381</v>
@@ -13274,7 +13274,7 @@
         <v>64</v>
       </c>
       <c r="G445" t="n">
-        <v>56.7140235900879</v>
+        <v>56.7140274047852</v>
       </c>
       <c r="H445" t="n">
         <v>4341</v>
@@ -13303,7 +13303,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G446" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798736572266</v>
       </c>
       <c r="H446" t="n">
         <v>7435</v>
@@ -13332,7 +13332,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G447" t="n">
-        <v>56.9798774719238</v>
+        <v>56.9798736572266</v>
       </c>
       <c r="H447" t="n">
         <v>11987</v>
@@ -13390,7 +13390,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G449" t="n">
-        <v>56.625415802002</v>
+        <v>56.6254196166992</v>
       </c>
       <c r="H449" t="n">
         <v>2810</v>
@@ -13448,7 +13448,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>55.9164924621582</v>
+        <v>55.9164886474609</v>
       </c>
       <c r="H451" t="n">
         <v>1739</v>
@@ -13477,7 +13477,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>55.7392616271973</v>
+        <v>55.7392578125</v>
       </c>
       <c r="H452" t="n">
         <v>2949</v>
@@ -13506,7 +13506,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G453" t="n">
-        <v>55.4734077453613</v>
+        <v>55.4734039306641</v>
       </c>
       <c r="H453" t="n">
         <v>9803</v>
@@ -13622,7 +13622,7 @@
         <v>61</v>
       </c>
       <c r="G457" t="n">
-        <v>54.0555572509766</v>
+        <v>54.0555610656738</v>
       </c>
       <c r="H457" t="n">
         <v>19823</v>
@@ -13738,7 +13738,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>52.8149337768555</v>
+        <v>52.8149375915527</v>
       </c>
       <c r="H461" t="n">
         <v>13931</v>
@@ -13767,7 +13767,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>50.7767791748047</v>
+        <v>50.7767753601074</v>
       </c>
       <c r="H462" t="n">
         <v>8560</v>
@@ -13796,7 +13796,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>51.7515525817871</v>
+        <v>51.7515487670898</v>
       </c>
       <c r="H463" t="n">
         <v>3551</v>
@@ -13825,7 +13825,7 @@
         <v>57.5</v>
       </c>
       <c r="G464" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H464" t="n">
         <v>5606</v>
@@ -13854,7 +13854,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>51.5743179321289</v>
+        <v>51.5743255615234</v>
       </c>
       <c r="H465" t="n">
         <v>7910</v>
@@ -13883,7 +13883,7 @@
         <v>57.5</v>
       </c>
       <c r="G466" t="n">
-        <v>50.9540100097656</v>
+        <v>50.9540138244629</v>
       </c>
       <c r="H466" t="n">
         <v>7562</v>
@@ -13999,7 +13999,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>49.2703132629395</v>
+        <v>49.2703094482422</v>
       </c>
       <c r="H470" t="n">
         <v>4310</v>
@@ -14028,7 +14028,7 @@
         <v>57</v>
       </c>
       <c r="G471" t="n">
-        <v>50.510929107666</v>
+        <v>50.5109329223633</v>
       </c>
       <c r="H471" t="n">
         <v>9753</v>
@@ -14057,7 +14057,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>50.0569114685059</v>
+        <v>50.0569076538086</v>
       </c>
       <c r="H472" t="n">
         <v>6766</v>
@@ -14173,7 +14173,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G476" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H476" t="n">
         <v>21249</v>
@@ -14202,7 +14202,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H477" t="n">
         <v>1854</v>
@@ -14260,7 +14260,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>45.0242576599121</v>
+        <v>45.0242538452148</v>
       </c>
       <c r="H479" t="n">
         <v>117335</v>
@@ -14289,7 +14289,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H480" t="n">
         <v>17941</v>
@@ -14318,7 +14318,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H481" t="n">
         <v>8345</v>
@@ -14376,7 +14376,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>48.7987480163574</v>
+        <v>48.7987442016602</v>
       </c>
       <c r="H483" t="n">
         <v>12430</v>
@@ -14434,7 +14434,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H485" t="n">
         <v>17601</v>
@@ -14492,7 +14492,7 @@
         <v>56</v>
       </c>
       <c r="G487" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H487" t="n">
         <v>10895</v>
@@ -14521,7 +14521,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>50.9555969238281</v>
+        <v>50.9555931091309</v>
       </c>
       <c r="H488" t="n">
         <v>9780</v>
@@ -14550,7 +14550,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G489" t="n">
-        <v>49.967041015625</v>
+        <v>49.9670372009277</v>
       </c>
       <c r="H489" t="n">
         <v>5862</v>
@@ -14579,7 +14579,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G490" t="n">
-        <v>49.517692565918</v>
+        <v>49.5176963806152</v>
       </c>
       <c r="H490" t="n">
         <v>8141</v>
@@ -14608,7 +14608,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>49.6075668334961</v>
+        <v>49.6075592041016</v>
       </c>
       <c r="H491" t="n">
         <v>27545</v>
@@ -14637,7 +14637,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>48.8886184692383</v>
+        <v>48.888614654541</v>
       </c>
       <c r="H492" t="n">
         <v>9874</v>
@@ -14666,7 +14666,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>48.3493995666504</v>
+        <v>48.3494033813477</v>
       </c>
       <c r="H493" t="n">
         <v>9548</v>
@@ -14724,7 +14724,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>49.6974296569824</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H495" t="n">
         <v>6839</v>
@@ -14753,7 +14753,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>52.4833679199219</v>
+        <v>52.4833641052246</v>
       </c>
       <c r="H496" t="n">
         <v>19509</v>
@@ -14840,7 +14840,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G499" t="n">
-        <v>52.9327087402344</v>
+        <v>52.9327125549316</v>
       </c>
       <c r="H499" t="n">
         <v>8348</v>
@@ -14927,7 +14927,7 @@
         <v>60</v>
       </c>
       <c r="G502" t="n">
-        <v>53.9212646484375</v>
+        <v>53.9212608337402</v>
       </c>
       <c r="H502" t="n">
         <v>7316</v>
@@ -14985,7 +14985,7 @@
         <v>64.5</v>
       </c>
       <c r="G504" t="n">
-        <v>57.9653625488281</v>
+        <v>57.9653587341309</v>
       </c>
       <c r="H504" t="n">
         <v>19577</v>
@@ -15014,7 +15014,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G505" t="n">
-        <v>56.3477210998535</v>
+        <v>56.3477249145508</v>
       </c>
       <c r="H505" t="n">
         <v>11751</v>
@@ -15043,7 +15043,7 @@
         <v>63.5</v>
       </c>
       <c r="G506" t="n">
-        <v>57.0666770935059</v>
+        <v>57.0666732788086</v>
       </c>
       <c r="H506" t="n">
         <v>15695</v>
@@ -15130,7 +15130,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H509" t="n">
         <v>5019</v>
@@ -15159,7 +15159,7 @@
         <v>62</v>
       </c>
       <c r="G510" t="n">
-        <v>55.7186393737793</v>
+        <v>55.7186431884766</v>
       </c>
       <c r="H510" t="n">
         <v>7322</v>
@@ -15188,7 +15188,7 @@
         <v>61.5</v>
       </c>
       <c r="G511" t="n">
-        <v>55.2692985534668</v>
+        <v>55.2692947387695</v>
       </c>
       <c r="H511" t="n">
         <v>8102</v>
@@ -15217,7 +15217,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>55.4490356445312</v>
+        <v>55.4490394592285</v>
       </c>
       <c r="H512" t="n">
         <v>3818</v>
@@ -15304,7 +15304,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>53.741527557373</v>
+        <v>53.7415313720703</v>
       </c>
       <c r="H515" t="n">
         <v>5949</v>
@@ -15333,7 +15333,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>53.8314018249512</v>
+        <v>53.8313980102539</v>
       </c>
       <c r="H516" t="n">
         <v>4297</v>
@@ -15449,7 +15449,7 @@
         <v>56</v>
       </c>
       <c r="G520" t="n">
-        <v>50.3265151977539</v>
+        <v>50.3265113830566</v>
       </c>
       <c r="H520" t="n">
         <v>4684</v>
@@ -15478,7 +15478,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G521" t="n">
-        <v>50.4163856506348</v>
+        <v>50.4163818359375</v>
       </c>
       <c r="H521" t="n">
         <v>4391</v>
@@ -15507,7 +15507,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>52.2137603759766</v>
+        <v>52.2137565612793</v>
       </c>
       <c r="H522" t="n">
         <v>2883</v>
@@ -15565,7 +15565,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>51.7644119262695</v>
+        <v>51.7644081115723</v>
       </c>
       <c r="H524" t="n">
         <v>15157</v>
@@ -15594,7 +15594,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>49.6974296569824</v>
+        <v>49.6974334716797</v>
       </c>
       <c r="H525" t="n">
         <v>128694</v>
@@ -15652,7 +15652,7 @@
         <v>52</v>
       </c>
       <c r="G527" t="n">
-        <v>46.7317657470703</v>
+        <v>46.731761932373</v>
       </c>
       <c r="H527" t="n">
         <v>23788</v>
@@ -15681,7 +15681,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G528" t="n">
-        <v>46.3722839355469</v>
+        <v>46.3722877502441</v>
       </c>
       <c r="H528" t="n">
         <v>16070</v>
@@ -15710,7 +15710,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>44.7546463012695</v>
+        <v>44.7546501159668</v>
       </c>
       <c r="H529" t="n">
         <v>9560</v>
@@ -15739,7 +15739,7 @@
         <v>51</v>
       </c>
       <c r="G530" t="n">
-        <v>45.8330764770508</v>
+        <v>45.833080291748</v>
       </c>
       <c r="H530" t="n">
         <v>3420</v>
@@ -15826,7 +15826,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>46.6418952941895</v>
+        <v>46.6418991088867</v>
       </c>
       <c r="H533" t="n">
         <v>9744</v>
@@ -15855,7 +15855,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>45.9229393005371</v>
+        <v>45.9229431152344</v>
       </c>
       <c r="H534" t="n">
         <v>7649</v>
@@ -15942,7 +15942,7 @@
         <v>49.25</v>
       </c>
       <c r="G537" t="n">
-        <v>44.2603759765625</v>
+        <v>44.2603721618652</v>
       </c>
       <c r="H537" t="n">
         <v>29439</v>
@@ -15971,7 +15971,7 @@
         <v>49</v>
       </c>
       <c r="G538" t="n">
-        <v>44.035701751709</v>
+        <v>44.0356979370117</v>
       </c>
       <c r="H538" t="n">
         <v>25688</v>
@@ -16058,7 +16058,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>44.8445205688477</v>
+        <v>44.8445243835449</v>
       </c>
       <c r="H541" t="n">
         <v>2582</v>
@@ -16145,7 +16145,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H544" t="n">
         <v>9498</v>
@@ -16232,7 +16232,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>47.8101921081543</v>
+        <v>47.810188293457</v>
       </c>
       <c r="H547" t="n">
         <v>4611</v>
@@ -16261,7 +16261,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>48.1696624755859</v>
+        <v>48.1696586608887</v>
       </c>
       <c r="H548" t="n">
         <v>5805</v>
@@ -16290,7 +16290,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>47.0013694763184</v>
+        <v>47.0013732910156</v>
       </c>
       <c r="H549" t="n">
         <v>6353</v>
@@ -16435,7 +16435,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>47.450